--- a/inventario_operaciones.xlsx
+++ b/inventario_operaciones.xlsx
@@ -1011,19 +1011,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K010304</t>
+          <t>K020502</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TONICO CAPILAR KABA 30ML</t>
+          <t>ESPUMA LIMPIADORA FACIAL KABA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>90</v>
+        <v>339</v>
       </c>
       <c r="D22" t="n">
-        <v>23981.2213740458</v>
+        <v>1723.396946564885</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1039,19 +1039,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K010203</t>
+          <t>K021301</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ACONDICIONADOR REPARACION SOS KABA</t>
+          <t>CONTORNO DE OJOS KABA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>141</v>
+        <v>401</v>
       </c>
       <c r="D23" t="n">
-        <v>1166.908396946565</v>
+        <v>1647.137404580153</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>K020502</t>
+          <t>KITR0102</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ESPUMA LIMPIADORA FACIAL KABA</t>
+          <t>KIT CONTROL CASPA LA RECETA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>339</v>
+        <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>1723.396946564885</v>
+        <v>64.58015267175571</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1095,19 +1095,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>K021301</t>
+          <t>K010304</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CONTORNO DE OJOS KABA</t>
+          <t>TONICO CAPILAR KABA 30ML</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>401</v>
+        <v>90</v>
       </c>
       <c r="D25" t="n">
-        <v>1647.137404580153</v>
+        <v>23981.2213740458</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KITR0102</t>
+          <t>K010203</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KIT CONTROL CASPA LA RECETA</t>
+          <t>ACONDICIONADOR REPARACION SOS KABA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="D26" t="n">
-        <v>64.58015267175571</v>
+        <v>1166.908396946565</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -3451,18 +3451,20 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KITC010202</t>
+          <t>KITK0206</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KIT BRONCEO VIVIANA GRONDONA</t>
+          <t>KIT RUTINA AM KABA</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>75</v>
-      </c>
-      <c r="D110" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="D110" t="n">
+        <v>34.69465648854962</v>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -3477,20 +3479,18 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>KITK0206</t>
+          <t>KITC010202</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KIT RUTINA AM KABA</t>
+          <t>KIT BRONCEO VIVIANA GRONDONA</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>31</v>
-      </c>
-      <c r="D111" t="n">
-        <v>34.69465648854962</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -4173,19 +4173,19 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>D031006</t>
+          <t>KITD0303</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>BRONCEADOR EN GEL DLUCHI</t>
+          <t>KIT BRONCEOPERF CON BRONCEADORGEL DLUCHI</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>161</v>
+        <v>6</v>
       </c>
       <c r="D136" t="n">
-        <v>1155.229007633588</v>
+        <v>37.21374045801527</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4201,19 +4201,19 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>KITD0303</t>
+          <t>KITK0106</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>KIT BRONCEOPERF CON BRONCEADORGEL DLUCHI</t>
+          <t>KIT MAGICO KABA KIDS</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D137" t="n">
-        <v>37.21374045801527</v>
+        <v>82.32824427480917</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4229,19 +4229,19 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>KITK0106</t>
+          <t>D031006</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>KIT MAGICO KABA KIDS</t>
+          <t>BRONCEADOR EN GEL DLUCHI</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>44</v>
+        <v>161</v>
       </c>
       <c r="D138" t="n">
-        <v>82.32824427480917</v>
+        <v>1155.229007633588</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4857,16 +4857,16 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>K051505</t>
+          <t>K051501</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>COSMETIQUERA FACIAL GRANDE KABA</t>
+          <t>COSMETIQUERA GRANDE KABA</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
@@ -4883,16 +4883,16 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>K051501</t>
+          <t>D051501</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE KABA</t>
+          <t>COSMETIQUERA GRANDE DLUCHI</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
@@ -4909,16 +4909,16 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>D051501</t>
+          <t>K051505</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE DLUCHI</t>
+          <t>COSMETIQUERA FACIAL GRANDE KABA</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>161</v>
+        <v>24</v>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
@@ -4987,16 +4987,16 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>K051502</t>
+          <t>O051501</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>COSMETIQUERA PEQUEÑA KABA</t>
+          <t>COSMETIQUERA PEQUEÑA OMG</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
@@ -5013,16 +5013,16 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>O051501</t>
+          <t>K051502</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>COSMETIQUERA PEQUEÑA OMG</t>
+          <t>COSMETIQUERA PEQUEÑA KABA</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
@@ -5835,20 +5835,18 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>K010203</t>
+          <t>DISACR010201</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ACONDICIONADOR REPARACION SOS KABA</t>
+          <t>DISPLEY SACHET DE ACONDICIONADOR LA RECE</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>81</v>
-      </c>
-      <c r="D197" t="n">
-        <v>1166.908396946565</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -5863,19 +5861,19 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>K010304</t>
+          <t>K020502</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>TONICO CAPILAR KABA 30ML</t>
+          <t>ESPUMA LIMPIADORA FACIAL KABA</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1353</v>
+        <v>1</v>
       </c>
       <c r="D198" t="n">
-        <v>23981.2213740458</v>
+        <v>1723.396946564885</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -5891,18 +5889,20 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>DISACR010201</t>
+          <t>K021301</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>DISPLEY SACHET DE ACONDICIONADOR LA RECE</t>
+          <t>CONTORNO DE OJOS KABA</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>5</v>
-      </c>
-      <c r="D199" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1647.137404580153</v>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -5917,19 +5917,19 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>K020502</t>
+          <t>KITR0103</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ESPUMA LIMPIADORA FACIAL KABA</t>
+          <t>KIT DUO ANTICASPA LA RECETA</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D200" t="n">
-        <v>1723.396946564885</v>
+        <v>164.7709923664122</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -5945,19 +5945,19 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>K021301</t>
+          <t>KITKR0104</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>CONTORNO DE OJOS KABA</t>
+          <t>KIT CRTO ACELERADO CABELLO SECO</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D201" t="n">
-        <v>1647.137404580153</v>
+        <v>15.57251908396946</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -5973,19 +5973,19 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>KITR0103</t>
+          <t>K010203</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>KIT DUO ANTICASPA LA RECETA</t>
+          <t>ACONDICIONADOR REPARACION SOS KABA</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="D202" t="n">
-        <v>164.7709923664122</v>
+        <v>1166.908396946565</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6001,19 +6001,19 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>KITKR0104</t>
+          <t>K010304</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>KIT CRTO ACELERADO CABELLO SECO</t>
+          <t>TONICO CAPILAR KABA 30ML</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>10</v>
+        <v>1353</v>
       </c>
       <c r="D203" t="n">
-        <v>15.57251908396946</v>
+        <v>23981.2213740458</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -8913,16 +8913,16 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>K051505</t>
+          <t>D051501</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>COSMETIQUERA FACIAL GRANDE KABA</t>
+          <t>COSMETIQUERA GRANDE DLUCHI</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>283</v>
+        <v>108</v>
       </c>
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
@@ -8939,16 +8939,16 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>D051501</t>
+          <t>K051505</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE DLUCHI</t>
+          <t>COSMETIQUERA FACIAL GRANDE KABA</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>108</v>
+        <v>283</v>
       </c>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
@@ -10783,20 +10783,18 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>K010203</t>
+          <t>DISACR010102</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ACONDICIONADOR REPARACION SOS KABA</t>
+          <t>DISPLEY SACHET DE SHAMPOO VAR ROMERO</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>8528</v>
-      </c>
-      <c r="D378" t="n">
-        <v>1166.908396946565</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -10811,20 +10809,18 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>K010304</t>
+          <t>DISACR010201</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>TONICO CAPILAR KABA 30ML</t>
+          <t>DISPLEY SACHET DE ACONDICIONADOR LA RECE</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>50201</v>
-      </c>
-      <c r="D379" t="n">
-        <v>23981.2213740458</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -10839,16 +10835,16 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>DISACR010102</t>
+          <t>DISACK010302</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>DISPLEY SACHET DE SHAMPOO VAR ROMERO</t>
+          <t>DISPLEY SACHET DE BIO MASCARILLA CAPILAR</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
@@ -10865,18 +10861,20 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>DISACR010201</t>
+          <t>K020502</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>DISPLEY SACHET DE ACONDICIONADOR LA RECE</t>
+          <t>ESPUMA LIMPIADORA FACIAL KABA</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>256</v>
-      </c>
-      <c r="D381" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="D381" t="n">
+        <v>1723.396946564885</v>
+      </c>
       <c r="E381" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -10891,18 +10889,20 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>DISACK010302</t>
+          <t>K021301</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>DISPLEY SACHET DE BIO MASCARILLA CAPILAR</t>
+          <t>CONTORNO DE OJOS KABA</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>2</v>
-      </c>
-      <c r="D382" t="inlineStr"/>
+        <v>3234</v>
+      </c>
+      <c r="D382" t="n">
+        <v>1647.137404580153</v>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -10917,19 +10917,19 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>K020502</t>
+          <t>K010203</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>ESPUMA LIMPIADORA FACIAL KABA</t>
+          <t>ACONDICIONADOR REPARACION SOS KABA</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>182</v>
+        <v>8528</v>
       </c>
       <c r="D383" t="n">
-        <v>1723.396946564885</v>
+        <v>1166.908396946565</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -10945,19 +10945,19 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>K021301</t>
+          <t>K010304</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>CONTORNO DE OJOS KABA</t>
+          <t>TONICO CAPILAR KABA 30ML</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>3234</v>
+        <v>50201</v>
       </c>
       <c r="D384" t="n">
-        <v>1647.137404580153</v>
+        <v>23981.2213740458</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -13053,16 +13053,16 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>R030601</t>
+          <t>D031013</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>UNGUENTO GRANDE LA RECETA</t>
+          <t>MINI CREMA AUTOBRONCEADORA 30ML</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>2</v>
+        <v>2153</v>
       </c>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr">
@@ -13079,16 +13079,16 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>D031013</t>
+          <t>K030902</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>MINI CREMA AUTOBRONCEADORA 30ML</t>
+          <t>MINI GEL LIPOREDUCTOR 30ML</t>
         </is>
       </c>
       <c r="C464" t="n">
-        <v>2153</v>
+        <v>1323</v>
       </c>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr">
@@ -13105,16 +13105,16 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>K030902</t>
+          <t>K010312</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>MINI GEL LIPOREDUCTOR 30ML</t>
+          <t>MINI TRATO CAPILAR REPOLARIZADOR 30ML</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>1323</v>
+        <v>2076</v>
       </c>
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr">
@@ -13131,16 +13131,16 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>K010312</t>
+          <t>K010108</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>MINI TRATO CAPILAR REPOLARIZADOR 30ML</t>
+          <t>MINI SHAMPOO DE CEBOLLA 30ML</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>2076</v>
+        <v>2601</v>
       </c>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr">
@@ -13157,16 +13157,16 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>K010108</t>
+          <t>R030601</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>MINI SHAMPOO DE CEBOLLA 30ML</t>
+          <t>UNGUENTO GRANDE LA RECETA</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>2601</v>
+        <v>2</v>
       </c>
       <c r="D467" t="inlineStr"/>
       <c r="E467" t="inlineStr">
@@ -13421,19 +13421,19 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>K010201</t>
+          <t>SACD031007</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>ACONDICIONADOR DE CERAMIDAS KABA</t>
+          <t>SACHET DE CREMA AUTOBRONCEADORA DLUCHI</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>21873</v>
+        <v>24500</v>
       </c>
       <c r="D477" t="n">
-        <v>39274.69465648855</v>
+        <v>942.2519083969466</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
@@ -13449,19 +13449,19 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>SACD031007</t>
+          <t>K010201</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>SACHET DE CREMA AUTOBRONCEADORA DLUCHI</t>
+          <t>ACONDICIONADOR DE CERAMIDAS KABA</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>24500</v>
+        <v>21873</v>
       </c>
       <c r="D478" t="n">
-        <v>942.2519083969466</v>
+        <v>39274.69465648855</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
@@ -16907,23 +16907,19 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>D051701</t>
+          <t>VB0307-04-04-U-13</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>TERMO DLUCHI 1200ML</t>
+          <t>TOALLA DLUCHI GRANDE-U-NARANJA</t>
         </is>
       </c>
       <c r="C608" t="n">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="D608" t="inlineStr"/>
-      <c r="E608" t="inlineStr">
-        <is>
-          <t>PRODUCTO MANUFACTURADO</t>
-        </is>
-      </c>
+      <c r="E608" t="inlineStr"/>
       <c r="F608" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -16933,16 +16929,16 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>VB0307-04-04-U-13</t>
+          <t>VB0307-05-04-U-01</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>TOALLA DLUCHI GRANDE-U-NARANJA</t>
+          <t>TOALLA KABA PEQUEÑA-U-BLANCO</t>
         </is>
       </c>
       <c r="C609" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr"/>
@@ -16955,19 +16951,23 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>VB0307-05-04-U-01</t>
+          <t>ETC0146</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>TOALLA KABA PEQUEÑA-U-BLANCO</t>
+          <t>CAJA PR KABA MAKEUP</t>
         </is>
       </c>
       <c r="C610" t="n">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="D610" t="inlineStr"/>
-      <c r="E610" t="inlineStr"/>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+        </is>
+      </c>
       <c r="F610" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -16977,16 +16977,16 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>ETC0146</t>
+          <t>ETC0147</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>CAJA PR KABA MAKEUP</t>
+          <t>CAJA PR PANAL DLUCHI</t>
         </is>
       </c>
       <c r="C611" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr">
@@ -17003,16 +17003,16 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>ETC0147</t>
+          <t>ETC0148</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>CAJA PR PANAL DLUCHI</t>
+          <t>CAJA PR KABA SOS</t>
         </is>
       </c>
       <c r="C612" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr">
@@ -17029,16 +17029,16 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>ETC0148</t>
+          <t>ETC0164</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>CAJA PR KABA SOS</t>
+          <t>CAJA PR BOX MEXICO</t>
         </is>
       </c>
       <c r="C613" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr">
@@ -17055,16 +17055,16 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>ETC0164</t>
+          <t>ETC0140</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>CAJA PR BOX MEXICO</t>
+          <t>CAJAS SACHET KABA</t>
         </is>
       </c>
       <c r="C614" t="n">
-        <v>42</v>
+        <v>420</v>
       </c>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr">
@@ -17081,16 +17081,16 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>ETC0140</t>
+          <t>ETC0139</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>CAJAS SACHET KABA</t>
+          <t>CAJAS SACHET DLUCHI</t>
         </is>
       </c>
       <c r="C615" t="n">
-        <v>420</v>
+        <v>13</v>
       </c>
       <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr">
@@ -17107,16 +17107,16 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>ETC0139</t>
+          <t>ETC0141</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>CAJAS SACHET DLUCHI</t>
+          <t>CAJAS SACHET RECETA</t>
         </is>
       </c>
       <c r="C616" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr">
@@ -17133,16 +17133,16 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>ETC0141</t>
+          <t>TA0101</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>CAJAS SACHET RECETA</t>
+          <t>TARJETA IMPERIO LUISA CHIMA</t>
         </is>
       </c>
       <c r="C617" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr">
@@ -17159,16 +17159,16 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>TA0101</t>
+          <t>TA0102</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>TARJETA IMPERIO LUISA CHIMA</t>
+          <t>TARJETA DREAM BAG</t>
         </is>
       </c>
       <c r="C618" t="n">
-        <v>25</v>
+        <v>1424</v>
       </c>
       <c r="D618" t="inlineStr"/>
       <c r="E618" t="inlineStr">
@@ -17185,16 +17185,16 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>TA0102</t>
+          <t>TA0103</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>TARJETA DREAM BAG</t>
+          <t>TARJETA DESCUENTO VB</t>
         </is>
       </c>
       <c r="C619" t="n">
-        <v>1424</v>
+        <v>1000</v>
       </c>
       <c r="D619" t="inlineStr"/>
       <c r="E619" t="inlineStr">
@@ -17211,16 +17211,16 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>TA0103</t>
+          <t>TA0104</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>TARJETA DESCUENTO VB</t>
+          <t>TARJETA KABA MAKEUP</t>
         </is>
       </c>
       <c r="C620" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="D620" t="inlineStr"/>
       <c r="E620" t="inlineStr">
@@ -17237,21 +17237,21 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>TA0104</t>
+          <t>D051703</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>TARJETA KABA MAKEUP</t>
+          <t>BOLSO PLAYERO</t>
         </is>
       </c>
       <c r="C621" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D621" t="inlineStr"/>
       <c r="E621" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>PRODUCTO MANUFACTURADO</t>
         </is>
       </c>
       <c r="F621" t="inlineStr">
@@ -17263,16 +17263,16 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>D051703</t>
+          <t>IL051701</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>BOLSO PLAYERO</t>
+          <t>WALMAN</t>
         </is>
       </c>
       <c r="C622" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D622" t="inlineStr"/>
       <c r="E622" t="inlineStr">
@@ -17289,16 +17289,16 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>IL051701</t>
+          <t>K051702</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>WALMAN</t>
+          <t>PELICULA INSTANTANEA</t>
         </is>
       </c>
       <c r="C623" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D623" t="inlineStr"/>
       <c r="E623" t="inlineStr">
@@ -17315,12 +17315,12 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>K051702</t>
+          <t>K051701</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>PELICULA INSTANTANEA</t>
+          <t>CAMARA INSTANTANEA</t>
         </is>
       </c>
       <c r="C624" t="n">
@@ -17341,16 +17341,16 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>K051701</t>
+          <t>IL051702</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>CAMARA INSTANTANEA</t>
+          <t>LLAVERO CASETTE</t>
         </is>
       </c>
       <c r="C625" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D625" t="inlineStr"/>
       <c r="E625" t="inlineStr">
@@ -17367,16 +17367,16 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>IL051702</t>
+          <t>D051701</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>LLAVERO CASETTE</t>
+          <t>TERMO DLUCHI 1200ML</t>
         </is>
       </c>
       <c r="C626" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="D626" t="inlineStr"/>
       <c r="E626" t="inlineStr">
@@ -17919,16 +17919,16 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>VB0104-01-03-L-09</t>
+          <t>VB0104-01-02-M-02</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-BEIGE</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-NEGRO</t>
         </is>
       </c>
       <c r="C648" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D648" t="inlineStr"/>
       <c r="E648" t="inlineStr"/>
@@ -17941,16 +17941,16 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>VB0304-01-01-S-02</t>
+          <t>VB0104-01-03-L-02</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-S-NEGRO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-NEGRO</t>
         </is>
       </c>
       <c r="C649" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D649" t="inlineStr"/>
       <c r="E649" t="inlineStr"/>
@@ -17963,16 +17963,16 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-09</t>
+          <t>VB0104-01-01-S-02</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-BEIGE</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-NEGRO</t>
         </is>
       </c>
       <c r="C650" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D650" t="inlineStr"/>
       <c r="E650" t="inlineStr"/>
@@ -17985,16 +17985,16 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-09</t>
+          <t>VB020101-01-01-S-25</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C651" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D651" t="inlineStr"/>
       <c r="E651" t="inlineStr"/>
@@ -18007,12 +18007,12 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-09</t>
+          <t>VB020303-01-02-M-24</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-BEIGE</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C652" t="n">
@@ -18029,16 +18029,16 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-19</t>
+          <t>VB020101-01-02-M-25</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C653" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D653" t="inlineStr"/>
       <c r="E653" t="inlineStr"/>
@@ -18051,16 +18051,16 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-37</t>
+          <t>VB020101-01-03-L-25</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-AZUL BEBE-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C654" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D654" t="inlineStr"/>
       <c r="E654" t="inlineStr"/>
@@ -18073,12 +18073,12 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-36</t>
+          <t>VB020303-01-01-S-25</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C655" t="n">
@@ -18095,16 +18095,16 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>VB0304-01-02-M-02</t>
+          <t>VB020105-01-01-S-05</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C656" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D656" t="inlineStr"/>
       <c r="E656" t="inlineStr"/>
@@ -18117,12 +18117,12 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>VB0304-01-03-L-02</t>
+          <t>VB020105-01-02-M-05</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C657" t="n">
@@ -18139,16 +18139,16 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>VB0104-01-01-S-09</t>
+          <t>VB020101-01-02-M-06</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C658" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D658" t="inlineStr"/>
       <c r="E658" t="inlineStr"/>
@@ -18161,16 +18161,16 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>VB0104-01-02-M-09</t>
+          <t>VB020101-01-03-L-06</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C659" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D659" t="inlineStr"/>
       <c r="E659" t="inlineStr"/>
@@ -18183,16 +18183,16 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-34</t>
+          <t>VB020103-03-03-L-20</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-FAUNA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C660" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D660" t="inlineStr"/>
       <c r="E660" t="inlineStr"/>
@@ -18205,16 +18205,16 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-36</t>
+          <t>VB020101-01-01-S-06</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C661" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D661" t="inlineStr"/>
       <c r="E661" t="inlineStr"/>
@@ -18227,16 +18227,16 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>VB020103-05-02-M-36</t>
+          <t>VB020303-01-01-S-24</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C662" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D662" t="inlineStr"/>
       <c r="E662" t="inlineStr"/>
@@ -18249,16 +18249,16 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-37</t>
+          <t>VB020303-01-03-L-24</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-AZUL BEBE-AGUAMARINA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C663" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr"/>
@@ -18271,16 +18271,16 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-03</t>
+          <t>VB020103-01-02-M-26</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
         </is>
       </c>
       <c r="C664" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D664" t="inlineStr"/>
       <c r="E664" t="inlineStr"/>
@@ -18293,16 +18293,16 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>VB0301-01-04-U-02</t>
+          <t>VB020105-01-03-L-13</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>FALDA GAIA MACRAME-U-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
         </is>
       </c>
       <c r="C665" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D665" t="inlineStr"/>
       <c r="E665" t="inlineStr"/>
@@ -18315,19 +18315,23 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>VB0305-01-04-U-09</t>
+          <t>DISACK010101</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-BEIGE</t>
+          <t>DISPLEY SACHET DE SHAMPO DE CEBOLLA KABA</t>
         </is>
       </c>
       <c r="C666" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D666" t="inlineStr"/>
-      <c r="E666" t="inlineStr"/>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>PRODUCTO MANUFACTURADO</t>
+        </is>
+      </c>
       <c r="F666" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -18337,16 +18341,16 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>VB0305-01-04-U-02</t>
+          <t>VB020105-01-02-M-13</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
         </is>
       </c>
       <c r="C667" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D667" t="inlineStr"/>
       <c r="E667" t="inlineStr"/>
@@ -18359,12 +18363,12 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-34</t>
+          <t>VB020101-01-01-S-19</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-FAUNA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C668" t="n">
@@ -18381,16 +18385,16 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-34</t>
+          <t>VB020101-01-03-L-30</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-FAUNA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PLUMAS</t>
         </is>
       </c>
       <c r="C669" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D669" t="inlineStr"/>
       <c r="E669" t="inlineStr"/>
@@ -18403,16 +18407,16 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-02</t>
+          <t>VB020105-01-01-S-13</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-NARANJA</t>
         </is>
       </c>
       <c r="C670" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D670" t="inlineStr"/>
       <c r="E670" t="inlineStr"/>
@@ -18425,16 +18429,16 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-01</t>
+          <t>VB020303-01-02-M-25</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-BLANCO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C671" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D671" t="inlineStr"/>
       <c r="E671" t="inlineStr"/>
@@ -18447,16 +18451,16 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-03</t>
+          <t>VB020105-01-01-S-08</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
         </is>
       </c>
       <c r="C672" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D672" t="inlineStr"/>
       <c r="E672" t="inlineStr"/>
@@ -18469,16 +18473,16 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-03</t>
+          <t>VB020303-01-03-L-25</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C673" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D673" t="inlineStr"/>
       <c r="E673" t="inlineStr"/>
@@ -18491,16 +18495,16 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-02</t>
+          <t>VB020101-01-01-S-14</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C674" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D674" t="inlineStr"/>
       <c r="E674" t="inlineStr"/>
@@ -18513,16 +18517,16 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-19</t>
+          <t>VB020103-03-02-M-20</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C675" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D675" t="inlineStr"/>
       <c r="E675" t="inlineStr"/>
@@ -18535,12 +18539,12 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>VB020205-03-01-S-28</t>
+          <t>VB020303-01-03-L-30</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-PITON BEIGE</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
         </is>
       </c>
       <c r="C676" t="n">
@@ -18557,16 +18561,16 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>VB020205-03-02-M-28</t>
+          <t>VB020105-01-02-M-08</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
         </is>
       </c>
       <c r="C677" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D677" t="inlineStr"/>
       <c r="E677" t="inlineStr"/>
@@ -18579,16 +18583,16 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>VB020205-03-03-L-28</t>
+          <t>VB020105-01-03-L-15</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-PURPURA</t>
         </is>
       </c>
       <c r="C678" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D678" t="inlineStr"/>
       <c r="E678" t="inlineStr"/>
@@ -18601,16 +18605,16 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-19</t>
+          <t>VB020103-01-03-L-26</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-L-MISTICO</t>
         </is>
       </c>
       <c r="C679" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr"/>
@@ -18623,16 +18627,16 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-28</t>
+          <t>VB020101-01-01-S-30</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PLUMAS</t>
         </is>
       </c>
       <c r="C680" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D680" t="inlineStr"/>
       <c r="E680" t="inlineStr"/>
@@ -18645,16 +18649,16 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-28</t>
+          <t>VB020101-01-03-L-14</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C681" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
@@ -18667,16 +18671,16 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-19</t>
+          <t>VB020103-01-01-S-26</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-S-MISTICO</t>
         </is>
       </c>
       <c r="C682" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr"/>
@@ -18689,12 +18693,12 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-28</t>
+          <t>VB020101-01-02-M-14</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C683" t="n">
@@ -18711,16 +18715,16 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-19</t>
+          <t>VB020303-01-02-M-30</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-PLUMAS</t>
         </is>
       </c>
       <c r="C684" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D684" t="inlineStr"/>
       <c r="E684" t="inlineStr"/>
@@ -18733,16 +18737,16 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-06</t>
+          <t>VB020303-01-01-S-30</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AZUL CELESTE</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-PLUMAS</t>
         </is>
       </c>
       <c r="C685" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
@@ -18755,16 +18759,16 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>VB020104-01-02-M-06</t>
+          <t>VB020103-03-01-S-20</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-M-AZUL CELESTE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C686" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D686" t="inlineStr"/>
       <c r="E686" t="inlineStr"/>
@@ -18777,19 +18781,25 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-06</t>
+          <t>D051601</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AZUL CELESTE</t>
+          <t>CEPILLO APLICADOR AUTOBRONCEADOR DLUCHI</t>
         </is>
       </c>
       <c r="C687" t="n">
-        <v>5</v>
-      </c>
-      <c r="D687" t="inlineStr"/>
-      <c r="E687" t="inlineStr"/>
+        <v>1019</v>
+      </c>
+      <c r="D687" t="n">
+        <v>1017.137404580153</v>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>PRODUCTO MANUFACTURADO</t>
+        </is>
+      </c>
       <c r="F687" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -18799,12 +18809,12 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-17</t>
+          <t>VB020204-01-01-S-15</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-ROSADO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-PURPURA</t>
         </is>
       </c>
       <c r="C688" t="n">
@@ -18821,16 +18831,16 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-01</t>
+          <t>VB020303-01-03-L-26</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-BLANCO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-MISTICO</t>
         </is>
       </c>
       <c r="C689" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D689" t="inlineStr"/>
       <c r="E689" t="inlineStr"/>
@@ -18843,16 +18853,16 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-14</t>
+          <t>VB020303-01-02-M-26</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-MISTICO</t>
         </is>
       </c>
       <c r="C690" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D690" t="inlineStr"/>
       <c r="E690" t="inlineStr"/>
@@ -18865,16 +18875,16 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-17</t>
+          <t>VB020101-01-01-S-03</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C691" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D691" t="inlineStr"/>
       <c r="E691" t="inlineStr"/>
@@ -18887,16 +18897,16 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-03</t>
+          <t>VB020204-01-02-M-08</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
         </is>
       </c>
       <c r="C692" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D692" t="inlineStr"/>
       <c r="E692" t="inlineStr"/>
@@ -18909,16 +18919,16 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-17</t>
+          <t>VB020202-01-02-M-23</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-ROSADO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C693" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D693" t="inlineStr"/>
       <c r="E693" t="inlineStr"/>
@@ -18931,16 +18941,16 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-06</t>
+          <t>VB0105-01-03-L-23</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-AZUL CELESTE</t>
+          <t>VB ENTERO TANGA-L-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C694" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D694" t="inlineStr"/>
       <c r="E694" t="inlineStr"/>
@@ -18953,16 +18963,16 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-03</t>
+          <t>VB020203-01-03-L-01</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-BLANCO</t>
         </is>
       </c>
       <c r="C695" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D695" t="inlineStr"/>
       <c r="E695" t="inlineStr"/>
@@ -18975,16 +18985,16 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-01</t>
+          <t>VB020203-01-02-M-01</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-BLANCO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-BLANCO</t>
         </is>
       </c>
       <c r="C696" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D696" t="inlineStr"/>
       <c r="E696" t="inlineStr"/>
@@ -18997,16 +19007,16 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-03</t>
+          <t>VB0302-01-02-M-02</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-AGUAMARINA</t>
+          <t>PANTALON ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C697" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D697" t="inlineStr"/>
       <c r="E697" t="inlineStr"/>
@@ -19019,16 +19029,16 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-01</t>
+          <t>VB020204-01-02-M-05</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C698" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D698" t="inlineStr"/>
       <c r="E698" t="inlineStr"/>
@@ -19041,16 +19051,16 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-02</t>
+          <t>VB020101-01-03-L-03</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C699" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D699" t="inlineStr"/>
       <c r="E699" t="inlineStr"/>
@@ -19063,16 +19073,16 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>VB0104-01-02-M-02</t>
+          <t>VB0105-01-01-S-23</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-NEGRO</t>
+          <t>VB ENTERO TANGA-S-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C700" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D700" t="inlineStr"/>
       <c r="E700" t="inlineStr"/>
@@ -19085,16 +19095,16 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>VB0104-01-03-L-02</t>
+          <t>VB020204-01-01-S-08</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
         </is>
       </c>
       <c r="C701" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D701" t="inlineStr"/>
       <c r="E701" t="inlineStr"/>
@@ -19107,16 +19117,16 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>VB0104-01-01-S-02</t>
+          <t>VB0302-01-03-L-02</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-NEGRO</t>
+          <t>PANTALON ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C702" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D702" t="inlineStr"/>
       <c r="E702" t="inlineStr"/>
@@ -19129,16 +19139,16 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-25</t>
+          <t>VB020204-01-01-S-11</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C703" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr"/>
@@ -19151,16 +19161,16 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-24</t>
+          <t>VB020103-02-03-L-17</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-ROSADO</t>
         </is>
       </c>
       <c r="C704" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D704" t="inlineStr"/>
       <c r="E704" t="inlineStr"/>
@@ -19173,12 +19183,12 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-25</t>
+          <t>VB0302-01-03-L-01</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-HOJAS VERDES</t>
+          <t>PANTALON ALTO-L-BLANCO</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -19195,16 +19205,16 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-25</t>
+          <t>VB020103-02-02-M-03</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C706" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D706" t="inlineStr"/>
       <c r="E706" t="inlineStr"/>
@@ -19217,12 +19227,12 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-25</t>
+          <t>VB020103-02-01-S-03</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C707" t="n">
@@ -19239,12 +19249,12 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-05</t>
+          <t>VB020204-01-01-S-05</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C708" t="n">
@@ -19261,16 +19271,16 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-05</t>
+          <t>VB020303-01-01-S-26</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
         </is>
       </c>
       <c r="C709" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D709" t="inlineStr"/>
       <c r="E709" t="inlineStr"/>
@@ -19283,16 +19293,16 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-06</t>
+          <t>VB0302-01-01-S-01</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AZUL CELESTE</t>
+          <t>PANTALON ALTO-S-BLANCO</t>
         </is>
       </c>
       <c r="C710" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D710" t="inlineStr"/>
       <c r="E710" t="inlineStr"/>
@@ -19305,16 +19315,16 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-06</t>
+          <t>VB0105-01-02-M-23</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AZUL CELESTE</t>
+          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C711" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D711" t="inlineStr"/>
       <c r="E711" t="inlineStr"/>
@@ -19327,16 +19337,16 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>VB020103-03-03-L-20</t>
+          <t>VB020204-01-03-L-11</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C712" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D712" t="inlineStr"/>
       <c r="E712" t="inlineStr"/>
@@ -19349,16 +19359,16 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-06</t>
+          <t>VB020103-02-03-L-03</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AZUL CELESTE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C713" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D713" t="inlineStr"/>
       <c r="E713" t="inlineStr"/>
@@ -19371,16 +19381,16 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-24</t>
+          <t>VB020105-01-01-S-16</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
         </is>
       </c>
       <c r="C714" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D714" t="inlineStr"/>
       <c r="E714" t="inlineStr"/>
@@ -19393,16 +19403,16 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-24</t>
+          <t>VB020204-01-03-L-15</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
         </is>
       </c>
       <c r="C715" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D715" t="inlineStr"/>
       <c r="E715" t="inlineStr"/>
@@ -19415,16 +19425,16 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>VB020103-01-02-M-26</t>
+          <t>VB0103-01-03-L-32</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C716" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr"/>
@@ -19437,16 +19447,16 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-13</t>
+          <t>VB020202-01-03-L-23</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C717" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D717" t="inlineStr"/>
       <c r="E717" t="inlineStr"/>
@@ -19459,23 +19469,19 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>DISACK010101</t>
+          <t>VB020202-01-01-S-23</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>DISPLEY SACHET DE SHAMPO DE CEBOLLA KABA</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C718" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D718" t="inlineStr"/>
-      <c r="E718" t="inlineStr">
-        <is>
-          <t>PRODUCTO MANUFACTURADO</t>
-        </is>
-      </c>
+      <c r="E718" t="inlineStr"/>
       <c r="F718" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -19485,16 +19491,16 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-13</t>
+          <t>VB0103-01-02-M-32</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C719" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D719" t="inlineStr"/>
       <c r="E719" t="inlineStr"/>
@@ -19507,12 +19513,12 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-19</t>
+          <t>VB0302-01-02-M-01</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-ANIMAL PRINT CAFÉ</t>
+          <t>PANTALON ALTO-M-BLANCO</t>
         </is>
       </c>
       <c r="C720" t="n">
@@ -19529,12 +19535,12 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-30</t>
+          <t>VB0302-01-01-S-02</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PLUMAS</t>
+          <t>PANTALON ALTO-S-NEGRO</t>
         </is>
       </c>
       <c r="C721" t="n">
@@ -19551,16 +19557,16 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-13</t>
+          <t>VB020204-01-03-L-08</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-NARANJA</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
         </is>
       </c>
       <c r="C722" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D722" t="inlineStr"/>
       <c r="E722" t="inlineStr"/>
@@ -19573,16 +19579,16 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-25</t>
+          <t>VB0103-01-01-S-32</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS VERDES</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C723" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="inlineStr"/>
@@ -19595,12 +19601,12 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-08</t>
+          <t>VB020204-01-03-L-07</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C724" t="n">
@@ -19617,16 +19623,16 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-25</t>
+          <t>VB020101-01-02-M-15</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PURPURA</t>
         </is>
       </c>
       <c r="C725" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D725" t="inlineStr"/>
       <c r="E725" t="inlineStr"/>
@@ -19639,16 +19645,16 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-14</t>
+          <t>VB020204-01-01-S-13</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
         </is>
       </c>
       <c r="C726" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr"/>
@@ -19661,16 +19667,16 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>VB020103-03-02-M-20</t>
+          <t>VB020203-01-03-L-02</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-NEGRO</t>
         </is>
       </c>
       <c r="C727" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr"/>
@@ -19683,16 +19689,16 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-30</t>
+          <t>VB020202-01-03-L-02</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C728" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr"/>
@@ -19705,16 +19711,16 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-08</t>
+          <t>VB020203-01-02-M-17</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-ROSADO</t>
         </is>
       </c>
       <c r="C729" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D729" t="inlineStr"/>
       <c r="E729" t="inlineStr"/>
@@ -19727,12 +19733,12 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-15</t>
+          <t>VB020202-01-01-S-02</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-PURPURA</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
         </is>
       </c>
       <c r="C730" t="n">
@@ -19749,16 +19755,16 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>VB020103-01-03-L-26</t>
+          <t>VB020202-01-02-M-02</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-L-MISTICO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C731" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D731" t="inlineStr"/>
       <c r="E731" t="inlineStr"/>
@@ -19771,16 +19777,16 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-30</t>
+          <t>VB020203-01-01-S-17</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PLUMAS</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-ROSADO</t>
         </is>
       </c>
       <c r="C732" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D732" t="inlineStr"/>
       <c r="E732" t="inlineStr"/>
@@ -19793,12 +19799,12 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-14</t>
+          <t>VB020105-01-03-L-01</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
         </is>
       </c>
       <c r="C733" t="n">
@@ -19815,12 +19821,12 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>VB020103-01-01-S-26</t>
+          <t>VB020203-01-01-S-01</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-S-MISTICO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
         </is>
       </c>
       <c r="C734" t="n">
@@ -19837,16 +19843,16 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-14</t>
+          <t>VB020105-01-01-S-01</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
         </is>
       </c>
       <c r="C735" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D735" t="inlineStr"/>
       <c r="E735" t="inlineStr"/>
@@ -19859,16 +19865,16 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-30</t>
+          <t>VB020204-01-02-M-11</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-PLUMAS</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C736" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D736" t="inlineStr"/>
       <c r="E736" t="inlineStr"/>
@@ -19881,16 +19887,16 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-30</t>
+          <t>VB020101-01-03-L-15</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PURPURA</t>
         </is>
       </c>
       <c r="C737" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D737" t="inlineStr"/>
       <c r="E737" t="inlineStr"/>
@@ -19903,16 +19909,16 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>VB020103-03-01-S-20</t>
+          <t>VB020204-01-01-S-07</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL CIAN</t>
         </is>
       </c>
       <c r="C738" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D738" t="inlineStr"/>
       <c r="E738" t="inlineStr"/>
@@ -19925,25 +19931,19 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>D051601</t>
+          <t>VB020204-01-02-M-13</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>CEPILLO APLICADOR AUTOBRONCEADOR DLUCHI</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
         </is>
       </c>
       <c r="C739" t="n">
-        <v>1019</v>
-      </c>
-      <c r="D739" t="n">
-        <v>1017.137404580153</v>
-      </c>
-      <c r="E739" t="inlineStr">
-        <is>
-          <t>PRODUCTO MANUFACTURADO</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D739" t="inlineStr"/>
+      <c r="E739" t="inlineStr"/>
       <c r="F739" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -19953,16 +19953,16 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-15</t>
+          <t>VB020101-03-03-L-01</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-L-BLANCO</t>
         </is>
       </c>
       <c r="C740" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D740" t="inlineStr"/>
       <c r="E740" t="inlineStr"/>
@@ -19975,12 +19975,12 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-26</t>
+          <t>VB020101-03-01-S-01</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-S-BLANCO</t>
         </is>
       </c>
       <c r="C741" t="n">
@@ -19997,16 +19997,16 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-26</t>
+          <t>VB020204-01-02-M-15</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-MISTICO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-PURPURA</t>
         </is>
       </c>
       <c r="C742" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D742" t="inlineStr"/>
       <c r="E742" t="inlineStr"/>
@@ -20019,16 +20019,16 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-03</t>
+          <t>VB0105-02-01-S-33</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AGUAMARINA</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-TIE DYE</t>
         </is>
       </c>
       <c r="C743" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D743" t="inlineStr"/>
       <c r="E743" t="inlineStr"/>
@@ -20041,16 +20041,16 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-08</t>
+          <t>VB0105-02-02-M-02</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-NEGRO</t>
         </is>
       </c>
       <c r="C744" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D744" t="inlineStr"/>
       <c r="E744" t="inlineStr"/>
@@ -20063,12 +20063,12 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-23</t>
+          <t>VB0105-02-01-S-02</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-NEGRO</t>
         </is>
       </c>
       <c r="C745" t="n">
@@ -20085,16 +20085,16 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>VB0105-01-03-L-23</t>
+          <t>VB0105-02-03-L-17</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-L-HOJAS AZUL</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-ROSADO</t>
         </is>
       </c>
       <c r="C746" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D746" t="inlineStr"/>
       <c r="E746" t="inlineStr"/>
@@ -20107,12 +20107,12 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>VB020203-01-03-L-01</t>
+          <t>VB0105-02-02-M-17</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-BLANCO</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-ROSADO</t>
         </is>
       </c>
       <c r="C747" t="n">
@@ -20129,16 +20129,16 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>VB020203-01-02-M-01</t>
+          <t>VB0105-02-01-S-17</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-BLANCO</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-ROSADO</t>
         </is>
       </c>
       <c r="C748" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D748" t="inlineStr"/>
       <c r="E748" t="inlineStr"/>
@@ -20151,12 +20151,12 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-02</t>
+          <t>VB0105-02-03-L-18</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-NEGRO</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-VERDE MENTA</t>
         </is>
       </c>
       <c r="C749" t="n">
@@ -20173,12 +20173,12 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-05</t>
+          <t>VB0105-02-01-S-18</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AMARILLO NEON</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-VERDE MENTA</t>
         </is>
       </c>
       <c r="C750" t="n">
@@ -20195,16 +20195,16 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-03</t>
+          <t>VB0105-02-02-M-18</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AGUAMARINA</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-VERDE MENTA</t>
         </is>
       </c>
       <c r="C751" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D751" t="inlineStr"/>
       <c r="E751" t="inlineStr"/>
@@ -20217,16 +20217,16 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>VB0105-01-01-S-23</t>
+          <t>VB0302-01-02-M-09</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-S-HOJAS AZUL</t>
+          <t>PANTALON ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C752" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D752" t="inlineStr"/>
       <c r="E752" t="inlineStr"/>
@@ -20239,16 +20239,16 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-08</t>
+          <t>VB0302-01-01-S-09</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
+          <t>PANTALON ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C753" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D753" t="inlineStr"/>
       <c r="E753" t="inlineStr"/>
@@ -20261,12 +20261,12 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-02</t>
+          <t>VB0303-01-02-M-01</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-NEGRO</t>
+          <t>SHORT ALTO-M-BLANCO</t>
         </is>
       </c>
       <c r="C754" t="n">
@@ -20283,16 +20283,16 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-11</t>
+          <t>VB0303-01-01-S-02</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
+          <t>SHORT ALTO-S-NEGRO</t>
         </is>
       </c>
       <c r="C755" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D755" t="inlineStr"/>
       <c r="E755" t="inlineStr"/>
@@ -20305,16 +20305,16 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-17</t>
+          <t>VB0303-01-03-L-09</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-ROSADO</t>
+          <t>SHORT ALTO-L-BEIGE</t>
         </is>
       </c>
       <c r="C756" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D756" t="inlineStr"/>
       <c r="E756" t="inlineStr"/>
@@ -20327,16 +20327,16 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-01</t>
+          <t>VB0303-01-02-M-09</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-BLANCO</t>
+          <t>SHORT ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C757" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D757" t="inlineStr"/>
       <c r="E757" t="inlineStr"/>
@@ -20349,12 +20349,12 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>VB020103-02-02-M-03</t>
+          <t>VB0303-01-01-S-09</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
+          <t>SHORT ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C758" t="n">
@@ -20371,12 +20371,12 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-03</t>
+          <t>VB0302-01-03-L-09</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
+          <t>PANTALON ALTO-L-BEIGE</t>
         </is>
       </c>
       <c r="C759" t="n">
@@ -20393,16 +20393,16 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-05</t>
+          <t>VB020203-01-01-S-02</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-NEGRO</t>
         </is>
       </c>
       <c r="C760" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D760" t="inlineStr"/>
       <c r="E760" t="inlineStr"/>
@@ -20415,12 +20415,12 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-26</t>
+          <t>VB020101-02-03-L-01</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-BLANCO</t>
         </is>
       </c>
       <c r="C761" t="n">
@@ -20437,16 +20437,16 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-01</t>
+          <t>VB020101-02-01-S-01</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-S-BLANCO</t>
         </is>
       </c>
       <c r="C762" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D762" t="inlineStr"/>
       <c r="E762" t="inlineStr"/>
@@ -20459,16 +20459,16 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>VB0105-01-02-M-23</t>
+          <t>VB020101-02-03-L-17</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-ROSADO</t>
         </is>
       </c>
       <c r="C763" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D763" t="inlineStr"/>
       <c r="E763" t="inlineStr"/>
@@ -20481,16 +20481,16 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-11</t>
+          <t>VB020101-02-02-M-17</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-M-ROSADO</t>
         </is>
       </c>
       <c r="C764" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D764" t="inlineStr"/>
       <c r="E764" t="inlineStr"/>
@@ -20503,16 +20503,16 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-03</t>
+          <t>VB0301-01-04-U-09</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
+          <t>FALDA GAIA MACRAME-U-BEIGE</t>
         </is>
       </c>
       <c r="C765" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D765" t="inlineStr"/>
       <c r="E765" t="inlineStr"/>
@@ -20525,12 +20525,12 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-16</t>
+          <t>VB020101-02-03-L-18</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-VERDE MENTA</t>
         </is>
       </c>
       <c r="C766" t="n">
@@ -20547,12 +20547,12 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-15</t>
+          <t>VB020101-02-01-S-18</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-S-VERDE MENTA</t>
         </is>
       </c>
       <c r="C767" t="n">
@@ -20569,16 +20569,16 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-32</t>
+          <t>VB020104-01-03-L-06</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C768" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D768" t="inlineStr"/>
       <c r="E768" t="inlineStr"/>
@@ -20591,16 +20591,16 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-23</t>
+          <t>VB0104-01-03-L-09</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-BEIGE</t>
         </is>
       </c>
       <c r="C769" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D769" t="inlineStr"/>
       <c r="E769" t="inlineStr"/>
@@ -20613,16 +20613,16 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-23</t>
+          <t>VB0304-01-01-S-02</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-S-NEGRO</t>
         </is>
       </c>
       <c r="C770" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D770" t="inlineStr"/>
       <c r="E770" t="inlineStr"/>
@@ -20635,12 +20635,12 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>VB0103-01-02-M-32</t>
+          <t>VB020103-04-01-S-09</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-BEIGE</t>
         </is>
       </c>
       <c r="C771" t="n">
@@ -20657,12 +20657,12 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-01</t>
+          <t>VB020103-04-02-M-09</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-BEIGE</t>
         </is>
       </c>
       <c r="C772" t="n">
@@ -20679,16 +20679,16 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-02</t>
+          <t>VB020103-04-03-L-09</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-BEIGE</t>
         </is>
       </c>
       <c r="C773" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D773" t="inlineStr"/>
       <c r="E773" t="inlineStr"/>
@@ -20701,12 +20701,12 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-08</t>
+          <t>VB020103-04-01-S-19</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C774" t="n">
@@ -20723,16 +20723,16 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-32</t>
+          <t>VB020103-05-03-L-37</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C775" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D775" t="inlineStr"/>
       <c r="E775" t="inlineStr"/>
@@ -20745,12 +20745,12 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-07</t>
+          <t>VB020103-05-03-L-36</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C776" t="n">
@@ -20767,16 +20767,16 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-15</t>
+          <t>VB0304-01-02-M-02</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PURPURA</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-M-NEGRO</t>
         </is>
       </c>
       <c r="C777" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D777" t="inlineStr"/>
       <c r="E777" t="inlineStr"/>
@@ -20789,16 +20789,16 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-13</t>
+          <t>VB0304-01-03-L-02</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-L-NEGRO</t>
         </is>
       </c>
       <c r="C778" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D778" t="inlineStr"/>
       <c r="E778" t="inlineStr"/>
@@ -20811,16 +20811,16 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>VB020203-01-03-L-02</t>
+          <t>VB0104-01-01-S-09</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-NEGRO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-BEIGE</t>
         </is>
       </c>
       <c r="C779" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D779" t="inlineStr"/>
       <c r="E779" t="inlineStr"/>
@@ -20833,16 +20833,16 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-02</t>
+          <t>VB0104-01-02-M-09</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-BEIGE</t>
         </is>
       </c>
       <c r="C780" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D780" t="inlineStr"/>
       <c r="E780" t="inlineStr"/>
@@ -20855,16 +20855,16 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>VB020203-01-02-M-17</t>
+          <t>VB020303-01-03-L-34</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-ROSADO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-FAUNA</t>
         </is>
       </c>
       <c r="C781" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D781" t="inlineStr"/>
       <c r="E781" t="inlineStr"/>
@@ -20877,16 +20877,16 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-02</t>
+          <t>VB020103-05-01-S-36</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C782" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D782" t="inlineStr"/>
       <c r="E782" t="inlineStr"/>
@@ -20899,16 +20899,16 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-02</t>
+          <t>VB020103-05-02-M-36</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C783" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D783" t="inlineStr"/>
       <c r="E783" t="inlineStr"/>
@@ -20921,16 +20921,16 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-17</t>
+          <t>VB020103-05-01-S-37</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C784" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D784" t="inlineStr"/>
       <c r="E784" t="inlineStr"/>
@@ -20943,16 +20943,16 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-01</t>
+          <t>VB020101-01-04-U-03</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-AGUAMARINA</t>
         </is>
       </c>
       <c r="C785" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D785" t="inlineStr"/>
       <c r="E785" t="inlineStr"/>
@@ -20965,16 +20965,16 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-01</t>
+          <t>VB0301-01-04-U-02</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
+          <t>FALDA GAIA MACRAME-U-NEGRO</t>
         </is>
       </c>
       <c r="C786" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D786" t="inlineStr"/>
       <c r="E786" t="inlineStr"/>
@@ -20987,16 +20987,16 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-01</t>
+          <t>VB0305-01-04-U-09</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
+          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-BEIGE</t>
         </is>
       </c>
       <c r="C787" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D787" t="inlineStr"/>
       <c r="E787" t="inlineStr"/>
@@ -21009,12 +21009,12 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-11</t>
+          <t>VB0305-01-04-U-02</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-FUCSIA NEON</t>
+          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-NEGRO</t>
         </is>
       </c>
       <c r="C788" t="n">
@@ -21031,12 +21031,12 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-15</t>
+          <t>VB020303-01-01-S-34</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PURPURA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-FAUNA</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -21053,16 +21053,16 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-07</t>
+          <t>VB020303-01-02-M-34</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL CIAN</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-FAUNA</t>
         </is>
       </c>
       <c r="C790" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D790" t="inlineStr"/>
       <c r="E790" t="inlineStr"/>
@@ -21075,16 +21075,16 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-13</t>
+          <t>VB0306-01-01-S-02</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
+          <t>TOP BÁSICO LUISA-S-NEGRO</t>
         </is>
       </c>
       <c r="C791" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D791" t="inlineStr"/>
       <c r="E791" t="inlineStr"/>
@@ -21097,16 +21097,16 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>VB020101-03-03-L-01</t>
+          <t>VB0306-01-03-L-01</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-L-BLANCO</t>
+          <t>TOP BÁSICO LUISA-L-BLANCO</t>
         </is>
       </c>
       <c r="C792" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D792" t="inlineStr"/>
       <c r="E792" t="inlineStr"/>
@@ -21119,16 +21119,16 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>VB020101-03-01-S-01</t>
+          <t>VB0306-01-02-M-03</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-S-BLANCO</t>
+          <t>TOP BÁSICO LUISA-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C793" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D793" t="inlineStr"/>
       <c r="E793" t="inlineStr"/>
@@ -21141,16 +21141,16 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-15</t>
+          <t>VB0306-01-01-S-03</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-PURPURA</t>
+          <t>TOP BÁSICO LUISA-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C794" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D794" t="inlineStr"/>
       <c r="E794" t="inlineStr"/>
@@ -21163,16 +21163,16 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-33</t>
+          <t>VB0306-01-02-M-02</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-TIE DYE</t>
+          <t>TOP BÁSICO LUISA-M-NEGRO</t>
         </is>
       </c>
       <c r="C795" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D795" t="inlineStr"/>
       <c r="E795" t="inlineStr"/>
@@ -21185,16 +21185,16 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-02</t>
+          <t>VB020303-01-03-L-19</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-NEGRO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C796" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D796" t="inlineStr"/>
       <c r="E796" t="inlineStr"/>
@@ -21207,12 +21207,12 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-02</t>
+          <t>VB020205-03-01-S-28</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-PITON BEIGE</t>
         </is>
       </c>
       <c r="C797" t="n">
@@ -21229,16 +21229,16 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>VB0105-02-03-L-17</t>
+          <t>VB020205-03-02-M-28</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-ROSADO</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-PITON BEIGE</t>
         </is>
       </c>
       <c r="C798" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D798" t="inlineStr"/>
       <c r="E798" t="inlineStr"/>
@@ -21251,16 +21251,16 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-17</t>
+          <t>VB020205-03-03-L-28</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-ROSADO</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-PITON BEIGE</t>
         </is>
       </c>
       <c r="C799" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D799" t="inlineStr"/>
       <c r="E799" t="inlineStr"/>
@@ -21273,16 +21273,16 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-17</t>
+          <t>VB020103-04-02-M-19</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C800" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D800" t="inlineStr"/>
       <c r="E800" t="inlineStr"/>
@@ -21295,12 +21295,12 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>VB0105-02-03-L-18</t>
+          <t>VB020103-04-01-S-28</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-VERDE MENTA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-PITON BEIGE</t>
         </is>
       </c>
       <c r="C801" t="n">
@@ -21317,16 +21317,16 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-18</t>
+          <t>VB020103-04-02-M-28</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-VERDE MENTA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-PITON BEIGE</t>
         </is>
       </c>
       <c r="C802" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D802" t="inlineStr"/>
       <c r="E802" t="inlineStr"/>
@@ -21339,16 +21339,16 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-18</t>
+          <t>VB020303-01-01-S-19</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-VERDE MENTA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C803" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D803" t="inlineStr"/>
       <c r="E803" t="inlineStr"/>
@@ -21361,16 +21361,16 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-09</t>
+          <t>VB020103-04-03-L-28</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-PITON BEIGE</t>
         </is>
       </c>
       <c r="C804" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D804" t="inlineStr"/>
       <c r="E804" t="inlineStr"/>
@@ -21383,12 +21383,12 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-09</t>
+          <t>VB020303-01-02-M-19</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-BEIGE</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C805" t="n">
@@ -21405,16 +21405,16 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>VB0303-01-02-M-01</t>
+          <t>VB020104-01-02-M-06</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>SHORT ALTO-M-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-M-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C806" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D806" t="inlineStr"/>
       <c r="E806" t="inlineStr"/>
@@ -21427,16 +21427,16 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>VB0303-01-01-S-02</t>
+          <t>VB020104-01-01-S-06</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>SHORT ALTO-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C807" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D807" t="inlineStr"/>
       <c r="E807" t="inlineStr"/>
@@ -21449,16 +21449,16 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>VB0303-01-03-L-09</t>
+          <t>VB020104-01-03-L-17</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>SHORT ALTO-L-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-ROSADO</t>
         </is>
       </c>
       <c r="C808" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D808" t="inlineStr"/>
       <c r="E808" t="inlineStr"/>
@@ -21471,16 +21471,16 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>VB0303-01-02-M-09</t>
+          <t>VB020101-01-04-U-01</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>SHORT ALTO-M-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-BLANCO</t>
         </is>
       </c>
       <c r="C809" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D809" t="inlineStr"/>
       <c r="E809" t="inlineStr"/>
@@ -21493,16 +21493,16 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>VB0303-01-01-S-09</t>
+          <t>VB020101-01-04-U-14</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>SHORT ALTO-S-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C810" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D810" t="inlineStr"/>
       <c r="E810" t="inlineStr"/>
@@ -21515,12 +21515,12 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-09</t>
+          <t>VB020104-01-01-S-17</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-ROSADO</t>
         </is>
       </c>
       <c r="C811" t="n">
@@ -21537,16 +21537,16 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-02</t>
+          <t>VB020104-01-03-L-03</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C812" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D812" t="inlineStr"/>
       <c r="E812" t="inlineStr"/>
@@ -21559,16 +21559,16 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>VB020101-02-03-L-01</t>
+          <t>VB020101-01-04-U-17</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-ROSADO</t>
         </is>
       </c>
       <c r="C813" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D813" t="inlineStr"/>
       <c r="E813" t="inlineStr"/>
@@ -21581,12 +21581,12 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>VB020101-02-01-S-01</t>
+          <t>VB020101-01-04-U-06</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C814" t="n">
@@ -21603,16 +21603,16 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>VB020101-02-03-L-17</t>
+          <t>VB020104-01-01-S-03</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C815" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D815" t="inlineStr"/>
       <c r="E815" t="inlineStr"/>
@@ -21625,16 +21625,16 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>VB020101-02-02-M-17</t>
+          <t>VB0306-01-02-M-01</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-M-ROSADO</t>
+          <t>TOP BÁSICO LUISA-M-BLANCO</t>
         </is>
       </c>
       <c r="C816" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D816" t="inlineStr"/>
       <c r="E816" t="inlineStr"/>
@@ -21647,16 +21647,16 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>VB0301-01-04-U-09</t>
+          <t>VB0306-01-03-L-03</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>FALDA GAIA MACRAME-U-BEIGE</t>
+          <t>TOP BÁSICO LUISA-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C817" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D817" t="inlineStr"/>
       <c r="E817" t="inlineStr"/>
@@ -21669,16 +21669,16 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>VB020101-02-03-L-18</t>
+          <t>VB0306-01-01-S-01</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-VERDE MENTA</t>
+          <t>TOP BÁSICO LUISA-S-BLANCO</t>
         </is>
       </c>
       <c r="C818" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D818" t="inlineStr"/>
       <c r="E818" t="inlineStr"/>
@@ -21691,16 +21691,16 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>VB020101-02-01-S-18</t>
+          <t>VB0306-01-03-L-02</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-S-VERDE MENTA</t>
+          <t>TOP BÁSICO LUISA-L-NEGRO</t>
         </is>
       </c>
       <c r="C819" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D819" t="inlineStr"/>
       <c r="E819" t="inlineStr"/>
@@ -22887,16 +22887,16 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>K051505</t>
+          <t>K051501</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>COSMETIQUERA FACIAL GRANDE KABA</t>
+          <t>COSMETIQUERA GRANDE KABA</t>
         </is>
       </c>
       <c r="C873" t="n">
-        <v>20600</v>
+        <v>3900</v>
       </c>
       <c r="D873" t="inlineStr"/>
       <c r="E873" t="inlineStr">
@@ -22913,16 +22913,16 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>K051501</t>
+          <t>D051501</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE KABA</t>
+          <t>COSMETIQUERA GRANDE DLUCHI</t>
         </is>
       </c>
       <c r="C874" t="n">
-        <v>3900</v>
+        <v>22000</v>
       </c>
       <c r="D874" t="inlineStr"/>
       <c r="E874" t="inlineStr">
@@ -22939,16 +22939,16 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>D051501</t>
+          <t>K051505</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE DLUCHI</t>
+          <t>COSMETIQUERA FACIAL GRANDE KABA</t>
         </is>
       </c>
       <c r="C875" t="n">
-        <v>22000</v>
+        <v>20600</v>
       </c>
       <c r="D875" t="inlineStr"/>
       <c r="E875" t="inlineStr">
@@ -23017,16 +23017,16 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>K051502</t>
+          <t>O051501</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>COSMETIQUERA PEQUEÑA KABA</t>
+          <t>COSMETIQUERA PEQUEÑA OMG</t>
         </is>
       </c>
       <c r="C878" t="n">
-        <v>10600</v>
+        <v>16000</v>
       </c>
       <c r="D878" t="inlineStr"/>
       <c r="E878" t="inlineStr">
@@ -23043,16 +23043,16 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>O051501</t>
+          <t>K051502</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>COSMETIQUERA PEQUEÑA OMG</t>
+          <t>COSMETIQUERA PEQUEÑA KABA</t>
         </is>
       </c>
       <c r="C879" t="n">
-        <v>16000</v>
+        <v>10600</v>
       </c>
       <c r="D879" t="inlineStr"/>
       <c r="E879" t="inlineStr">
@@ -24005,16 +24005,16 @@
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-19</t>
+          <t>VB020303-01-02-M-25</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C915" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D915" t="inlineStr"/>
       <c r="E915" t="inlineStr"/>
@@ -24027,16 +24027,16 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-19</t>
+          <t>VB020105-01-01-S-13</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-NARANJA</t>
         </is>
       </c>
       <c r="C916" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D916" t="inlineStr"/>
       <c r="E916" t="inlineStr"/>
@@ -24049,16 +24049,16 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-28</t>
+          <t>VB020103-03-02-M-20</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C917" t="n">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="D917" t="inlineStr"/>
       <c r="E917" t="inlineStr"/>
@@ -24071,16 +24071,16 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-28</t>
+          <t>VB020303-01-03-L-25</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-PITON BEIGE</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C918" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D918" t="inlineStr"/>
       <c r="E918" t="inlineStr"/>
@@ -24093,16 +24093,16 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-19</t>
+          <t>VB020105-01-01-S-08</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
         </is>
       </c>
       <c r="C919" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D919" t="inlineStr"/>
       <c r="E919" t="inlineStr"/>
@@ -24115,16 +24115,16 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-28</t>
+          <t>VB020103-03-01-S-32</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C920" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D920" t="inlineStr"/>
       <c r="E920" t="inlineStr"/>
@@ -24137,16 +24137,16 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-19</t>
+          <t>VB020105-01-02-M-13</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
         </is>
       </c>
       <c r="C921" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D921" t="inlineStr"/>
       <c r="E921" t="inlineStr"/>
@@ -24159,16 +24159,16 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>VB020205-03-03-L-28</t>
+          <t>VB020105-01-03-L-13</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
         </is>
       </c>
       <c r="C922" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D922" t="inlineStr"/>
       <c r="E922" t="inlineStr"/>
@@ -24181,16 +24181,16 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>VB020205-03-02-M-28</t>
+          <t>VB020103-01-02-M-26</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
         </is>
       </c>
       <c r="C923" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D923" t="inlineStr"/>
       <c r="E923" t="inlineStr"/>
@@ -24203,16 +24203,16 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>VB020205-03-01-S-28</t>
+          <t>VB020303-01-03-L-24</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-PITON BEIGE</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C924" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D924" t="inlineStr"/>
       <c r="E924" t="inlineStr"/>
@@ -24225,16 +24225,16 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-19</t>
+          <t>VB020103-03-02-M-32</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C925" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="D925" t="inlineStr"/>
       <c r="E925" t="inlineStr"/>
@@ -24247,16 +24247,16 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-02</t>
+          <t>VB020105-01-03-L-11</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C926" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D926" t="inlineStr"/>
       <c r="E926" t="inlineStr"/>
@@ -24269,16 +24269,16 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-03</t>
+          <t>VB020103-03-03-L-20</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C927" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="D927" t="inlineStr"/>
       <c r="E927" t="inlineStr"/>
@@ -24291,16 +24291,16 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-03</t>
+          <t>VB020303-01-01-S-24</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-AGUAMARINA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C928" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D928" t="inlineStr"/>
       <c r="E928" t="inlineStr"/>
@@ -24313,16 +24313,16 @@
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-01</t>
+          <t>VB020101-01-02-M-19</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C929" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D929" t="inlineStr"/>
       <c r="E929" t="inlineStr"/>
@@ -24335,16 +24335,16 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-02</t>
+          <t>VB020105-01-01-S-15</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-PURPURA</t>
         </is>
       </c>
       <c r="C930" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D930" t="inlineStr"/>
       <c r="E930" t="inlineStr"/>
@@ -24357,16 +24357,16 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>VB0104-01-03-L-09</t>
+          <t>VB020105-01-03-L-08</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AZUL REY</t>
         </is>
       </c>
       <c r="C931" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D931" t="inlineStr"/>
       <c r="E931" t="inlineStr"/>
@@ -24379,12 +24379,12 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-19</t>
+          <t>VB020105-01-02-M-05</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C932" t="n">
@@ -24401,16 +24401,16 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-09</t>
+          <t>VB020105-01-01-S-05</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C933" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D933" t="inlineStr"/>
       <c r="E933" t="inlineStr"/>
@@ -24423,16 +24423,16 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-09</t>
+          <t>VB020103-03-03-L-32</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C934" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="D934" t="inlineStr"/>
       <c r="E934" t="inlineStr"/>
@@ -24445,12 +24445,12 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-09</t>
+          <t>VB020105-01-02-M-11</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C935" t="n">
@@ -24467,16 +24467,16 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>VB0104-01-02-M-09</t>
+          <t>VB020105-01-03-L-07</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C936" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D936" t="inlineStr"/>
       <c r="E936" t="inlineStr"/>
@@ -24489,16 +24489,16 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>VB0104-01-01-S-09</t>
+          <t>VB020303-01-01-S-25</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-BEIGE</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C937" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D937" t="inlineStr"/>
       <c r="E937" t="inlineStr"/>
@@ -24511,16 +24511,16 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>VB0304-01-03-L-02</t>
+          <t>VB020303-01-02-M-24</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-L-NEGRO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C938" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D938" t="inlineStr"/>
       <c r="E938" t="inlineStr"/>
@@ -24533,16 +24533,16 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>VB0304-01-02-M-02</t>
+          <t>VB0104-01-01-S-02</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-M-NEGRO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-NEGRO</t>
         </is>
       </c>
       <c r="C939" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D939" t="inlineStr"/>
       <c r="E939" t="inlineStr"/>
@@ -24555,16 +24555,16 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-36</t>
+          <t>VB0104-01-03-L-02</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-VIOLETA-CORAL</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-NEGRO</t>
         </is>
       </c>
       <c r="C940" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D940" t="inlineStr"/>
       <c r="E940" t="inlineStr"/>
@@ -24577,16 +24577,16 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-37</t>
+          <t>VB0104-01-02-M-02</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-AZUL BEBE-AGUAMARINA</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-NEGRO</t>
         </is>
       </c>
       <c r="C941" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D941" t="inlineStr"/>
       <c r="E941" t="inlineStr"/>
@@ -24599,16 +24599,16 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>VB0307-01-04-U-13</t>
+          <t>VB020303-01-03-L-30</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>PAÑOLETA-U-NARANJA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
         </is>
       </c>
       <c r="C942" t="n">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="D942" t="inlineStr"/>
       <c r="E942" t="inlineStr"/>
@@ -24621,16 +24621,16 @@
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-34</t>
+          <t>VB020103-01-01-S-26</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-FAUNA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-S-MISTICO</t>
         </is>
       </c>
       <c r="C943" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D943" t="inlineStr"/>
       <c r="E943" t="inlineStr"/>
@@ -24643,16 +24643,16 @@
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-34</t>
+          <t>VB020105-01-03-L-05</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-FAUNA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C944" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D944" t="inlineStr"/>
       <c r="E944" t="inlineStr"/>
@@ -24665,16 +24665,16 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>VB0305-01-04-U-02</t>
+          <t>VB020204-01-03-L-05</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C945" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D945" t="inlineStr"/>
       <c r="E945" t="inlineStr"/>
@@ -24687,16 +24687,16 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>VB0304-01-01-S-09</t>
+          <t>VB020103-03-01-S-20</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-S-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C946" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D946" t="inlineStr"/>
       <c r="E946" t="inlineStr"/>
@@ -24709,16 +24709,16 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>VB0304-01-02-M-09</t>
+          <t>VB020303-01-01-S-30</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-M-BEIGE</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-PLUMAS</t>
         </is>
       </c>
       <c r="C947" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D947" t="inlineStr"/>
       <c r="E947" t="inlineStr"/>
@@ -24731,16 +24731,16 @@
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>VB0305-01-04-U-09</t>
+          <t>VB020303-01-02-M-30</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-BEIGE</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-PLUMAS</t>
         </is>
       </c>
       <c r="C948" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D948" t="inlineStr"/>
       <c r="E948" t="inlineStr"/>
@@ -24753,16 +24753,16 @@
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>VB020104-01-02-M-03</t>
+          <t>VB020105-01-01-S-11</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-M-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C949" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D949" t="inlineStr"/>
       <c r="E949" t="inlineStr"/>
@@ -24775,16 +24775,16 @@
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>VB0301-01-04-U-02</t>
+          <t>VB020103-01-03-L-26</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>FALDA GAIA MACRAME-U-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-L-MISTICO</t>
         </is>
       </c>
       <c r="C950" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D950" t="inlineStr"/>
       <c r="E950" t="inlineStr"/>
@@ -24797,16 +24797,16 @@
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-37</t>
+          <t>VB020105-01-03-L-15</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-AZUL BEBE-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-PURPURA</t>
         </is>
       </c>
       <c r="C951" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D951" t="inlineStr"/>
       <c r="E951" t="inlineStr"/>
@@ -24819,16 +24819,16 @@
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>VB020103-05-02-M-37</t>
+          <t>VB020105-01-02-M-15</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-AZUL BEBE-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-PURPURA</t>
         </is>
       </c>
       <c r="C952" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D952" t="inlineStr"/>
       <c r="E952" t="inlineStr"/>
@@ -24841,16 +24841,16 @@
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>VB020103-05-02-M-36</t>
+          <t>VB020105-01-02-M-08</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
         </is>
       </c>
       <c r="C953" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D953" t="inlineStr"/>
       <c r="E953" t="inlineStr"/>
@@ -24863,16 +24863,16 @@
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>VB0304-01-03-L-09</t>
+          <t>VB020204-01-02-M-11</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-L-BEIGE</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C954" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D954" t="inlineStr"/>
       <c r="E954" t="inlineStr"/>
@@ -24885,16 +24885,16 @@
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-36</t>
+          <t>VB020204-01-02-M-13</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
         </is>
       </c>
       <c r="C955" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D955" t="inlineStr"/>
       <c r="E955" t="inlineStr"/>
@@ -24907,16 +24907,16 @@
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-35</t>
+          <t>VB020204-01-01-S-07</t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-NEGRO-BLANCO HUESO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL CIAN</t>
         </is>
       </c>
       <c r="C956" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D956" t="inlineStr"/>
       <c r="E956" t="inlineStr"/>
@@ -24929,12 +24929,12 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>VB020103-05-02-M-35</t>
+          <t>VB0301-01-04-U-09</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-NEGRO-BLANCO HUESO</t>
+          <t>FALDA GAIA MACRAME-U-BEIGE</t>
         </is>
       </c>
       <c r="C957" t="n">
@@ -24951,16 +24951,16 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-35</t>
+          <t>VB020203-01-01-S-02</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-NEGRO-BLANCO HUESO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-NEGRO</t>
         </is>
       </c>
       <c r="C958" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D958" t="inlineStr"/>
       <c r="E958" t="inlineStr"/>
@@ -24973,16 +24973,16 @@
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-34</t>
+          <t>VB0302-01-03-L-09</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-FAUNA</t>
+          <t>PANTALON ALTO-L-BEIGE</t>
         </is>
       </c>
       <c r="C959" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D959" t="inlineStr"/>
       <c r="E959" t="inlineStr"/>
@@ -24995,12 +24995,12 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-03</t>
+          <t>VB0303-01-01-S-09</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AGUAMARINA</t>
+          <t>SHORT ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C960" t="n">
@@ -25017,12 +25017,12 @@
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-03</t>
+          <t>VB0303-01-02-M-09</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AGUAMARINA</t>
+          <t>SHORT ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C961" t="n">
@@ -25039,16 +25039,16 @@
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-17</t>
+          <t>VB0303-01-03-L-09</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-ROSADO</t>
+          <t>SHORT ALTO-L-BEIGE</t>
         </is>
       </c>
       <c r="C962" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D962" t="inlineStr"/>
       <c r="E962" t="inlineStr"/>
@@ -25061,16 +25061,16 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>VB020104-01-02-M-17</t>
+          <t>VB0303-01-01-S-01</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-M-ROSADO</t>
+          <t>SHORT ALTO-S-BLANCO</t>
         </is>
       </c>
       <c r="C963" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D963" t="inlineStr"/>
       <c r="E963" t="inlineStr"/>
@@ -25083,16 +25083,16 @@
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-17</t>
+          <t>VB0303-01-03-L-02</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-ROSADO</t>
+          <t>SHORT ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C964" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D964" t="inlineStr"/>
       <c r="E964" t="inlineStr"/>
@@ -25105,16 +25105,16 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-06</t>
+          <t>VB0303-01-02-M-02</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AZUL CELESTE</t>
+          <t>SHORT ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C965" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D965" t="inlineStr"/>
       <c r="E965" t="inlineStr"/>
@@ -25127,16 +25127,16 @@
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>VB020104-01-02-M-06</t>
+          <t>VB0303-01-02-M-01</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-M-AZUL CELESTE</t>
+          <t>SHORT ALTO-M-BLANCO</t>
         </is>
       </c>
       <c r="C966" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D966" t="inlineStr"/>
       <c r="E966" t="inlineStr"/>
@@ -25149,16 +25149,16 @@
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-02</t>
+          <t>VB0302-01-01-S-09</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-NEGRO</t>
+          <t>PANTALON ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C967" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D967" t="inlineStr"/>
       <c r="E967" t="inlineStr"/>
@@ -25171,16 +25171,16 @@
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-01</t>
+          <t>VB0303-01-03-L-01</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-BLANCO</t>
+          <t>SHORT ALTO-L-BLANCO</t>
         </is>
       </c>
       <c r="C968" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D968" t="inlineStr"/>
       <c r="E968" t="inlineStr"/>
@@ -25193,16 +25193,16 @@
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-03</t>
+          <t>VB0302-01-02-M-09</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-AGUAMARINA</t>
+          <t>PANTALON ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C969" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D969" t="inlineStr"/>
       <c r="E969" t="inlineStr"/>
@@ -25215,16 +25215,16 @@
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-01</t>
+          <t>VB0105-02-02-M-18</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-BLANCO</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-VERDE MENTA</t>
         </is>
       </c>
       <c r="C970" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D970" t="inlineStr"/>
       <c r="E970" t="inlineStr"/>
@@ -25237,16 +25237,16 @@
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-25</t>
+          <t>VB0105-02-01-S-18</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS VERDES</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-VERDE MENTA</t>
         </is>
       </c>
       <c r="C971" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D971" t="inlineStr"/>
       <c r="E971" t="inlineStr"/>
@@ -25259,16 +25259,16 @@
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-13</t>
+          <t>VB0105-02-03-L-18</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-NARANJA</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-VERDE MENTA</t>
         </is>
       </c>
       <c r="C972" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D972" t="inlineStr"/>
       <c r="E972" t="inlineStr"/>
@@ -25281,16 +25281,16 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>VB020103-03-02-M-20</t>
+          <t>VB0105-02-01-S-17</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-ANIMAL PRINT FLORES</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-ROSADO</t>
         </is>
       </c>
       <c r="C973" t="n">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="D973" t="inlineStr"/>
       <c r="E973" t="inlineStr"/>
@@ -25303,16 +25303,16 @@
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-25</t>
+          <t>VB0105-02-02-M-17</t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS VERDES</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-ROSADO</t>
         </is>
       </c>
       <c r="C974" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D974" t="inlineStr"/>
       <c r="E974" t="inlineStr"/>
@@ -25325,16 +25325,16 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-08</t>
+          <t>VB0105-02-03-L-17</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-ROSADO</t>
         </is>
       </c>
       <c r="C975" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D975" t="inlineStr"/>
       <c r="E975" t="inlineStr"/>
@@ -25347,16 +25347,16 @@
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>VB020103-03-01-S-32</t>
+          <t>VB0105-02-01-S-02</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-SELVA PAJAROS</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-NEGRO</t>
         </is>
       </c>
       <c r="C976" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D976" t="inlineStr"/>
       <c r="E976" t="inlineStr"/>
@@ -25369,16 +25369,16 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-13</t>
+          <t>VB0105-02-02-M-02</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-NEGRO</t>
         </is>
       </c>
       <c r="C977" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D977" t="inlineStr"/>
       <c r="E977" t="inlineStr"/>
@@ -25391,16 +25391,16 @@
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-13</t>
+          <t>VB0105-02-01-S-33</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-TIE DYE</t>
         </is>
       </c>
       <c r="C978" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D978" t="inlineStr"/>
       <c r="E978" t="inlineStr"/>
@@ -25413,16 +25413,16 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>VB020103-01-02-M-26</t>
+          <t>VB0105-02-03-L-02</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-NEGRO</t>
         </is>
       </c>
       <c r="C979" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D979" t="inlineStr"/>
       <c r="E979" t="inlineStr"/>
@@ -25435,16 +25435,16 @@
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-24</t>
+          <t>VB020204-01-02-M-15</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-PURPURA</t>
         </is>
       </c>
       <c r="C980" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D980" t="inlineStr"/>
       <c r="E980" t="inlineStr"/>
@@ -25457,16 +25457,16 @@
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>VB020103-03-02-M-32</t>
+          <t>VB0105-02-02-M-33</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-SELVA PAJAROS</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-TIE DYE</t>
         </is>
       </c>
       <c r="C981" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="D981" t="inlineStr"/>
       <c r="E981" t="inlineStr"/>
@@ -25479,16 +25479,16 @@
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-11</t>
+          <t>VB020105-01-03-L-16</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-ROJO</t>
         </is>
       </c>
       <c r="C982" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D982" t="inlineStr"/>
       <c r="E982" t="inlineStr"/>
@@ -25501,16 +25501,16 @@
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>VB020103-03-03-L-20</t>
+          <t>VB020105-01-02-M-16</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-ROJO</t>
         </is>
       </c>
       <c r="C983" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="D983" t="inlineStr"/>
       <c r="E983" t="inlineStr"/>
@@ -25523,16 +25523,16 @@
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-24</t>
+          <t>VB020105-01-01-S-16</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
         </is>
       </c>
       <c r="C984" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D984" t="inlineStr"/>
       <c r="E984" t="inlineStr"/>
@@ -25545,16 +25545,16 @@
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-19</t>
+          <t>VB020202-01-03-L-23</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C985" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D985" t="inlineStr"/>
       <c r="E985" t="inlineStr"/>
@@ -25567,16 +25567,16 @@
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-15</t>
+          <t>VB0103-01-03-L-32</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-PURPURA</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C986" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D986" t="inlineStr"/>
       <c r="E986" t="inlineStr"/>
@@ -25589,16 +25589,16 @@
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-08</t>
+          <t>VB020204-01-03-L-15</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
         </is>
       </c>
       <c r="C987" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D987" t="inlineStr"/>
       <c r="E987" t="inlineStr"/>
@@ -25611,16 +25611,16 @@
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-05</t>
+          <t>VB020204-01-01-S-13</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
         </is>
       </c>
       <c r="C988" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D988" t="inlineStr"/>
       <c r="E988" t="inlineStr"/>
@@ -25633,16 +25633,16 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-05</t>
+          <t>VB020204-01-03-L-07</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C989" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D989" t="inlineStr"/>
       <c r="E989" t="inlineStr"/>
@@ -25655,16 +25655,16 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>VB020103-03-03-L-32</t>
+          <t>VB020103-02-03-L-01</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-BLANCO</t>
         </is>
       </c>
       <c r="C990" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="D990" t="inlineStr"/>
       <c r="E990" t="inlineStr"/>
@@ -25677,16 +25677,16 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-11</t>
+          <t>VB0103-01-01-S-32</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-FUCSIA NEON</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C991" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D991" t="inlineStr"/>
       <c r="E991" t="inlineStr"/>
@@ -25699,16 +25699,16 @@
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-07</t>
+          <t>VB020204-01-03-L-08</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
         </is>
       </c>
       <c r="C992" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D992" t="inlineStr"/>
       <c r="E992" t="inlineStr"/>
@@ -25721,16 +25721,16 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-25</t>
+          <t>VB0302-01-02-M-01</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS VERDES</t>
+          <t>PANTALON ALTO-M-BLANCO</t>
         </is>
       </c>
       <c r="C993" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D993" t="inlineStr"/>
       <c r="E993" t="inlineStr"/>
@@ -25743,16 +25743,16 @@
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-24</t>
+          <t>VB0103-01-02-M-32</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS NEGRO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C994" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="D994" t="inlineStr"/>
       <c r="E994" t="inlineStr"/>
@@ -25765,16 +25765,16 @@
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>VB0104-01-01-S-02</t>
+          <t>VB020202-01-01-S-23</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C995" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D995" t="inlineStr"/>
       <c r="E995" t="inlineStr"/>
@@ -25787,16 +25787,16 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>VB0104-01-03-L-02</t>
+          <t>VB020105-01-01-S-01</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
         </is>
       </c>
       <c r="C996" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D996" t="inlineStr"/>
       <c r="E996" t="inlineStr"/>
@@ -25809,16 +25809,16 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>VB0104-01-02-M-02</t>
+          <t>VB020203-01-01-S-01</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-NEGRO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
         </is>
       </c>
       <c r="C997" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D997" t="inlineStr"/>
       <c r="E997" t="inlineStr"/>
@@ -25831,16 +25831,16 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-30</t>
+          <t>VB020105-01-03-L-01</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
         </is>
       </c>
       <c r="C998" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D998" t="inlineStr"/>
       <c r="E998" t="inlineStr"/>
@@ -25853,16 +25853,16 @@
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>VB020103-01-01-S-26</t>
+          <t>VB020105-01-02-M-01</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-S-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-BLANCO</t>
         </is>
       </c>
       <c r="C999" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D999" t="inlineStr"/>
       <c r="E999" t="inlineStr"/>
@@ -25875,16 +25875,16 @@
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-05</t>
+          <t>VB020202-01-01-S-09</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C1000" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D1000" t="inlineStr"/>
       <c r="E1000" t="inlineStr"/>
@@ -25897,16 +25897,16 @@
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-05</t>
+          <t>VB020202-01-02-M-02</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C1001" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D1001" t="inlineStr"/>
       <c r="E1001" t="inlineStr"/>
@@ -25919,16 +25919,16 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>VB020103-03-01-S-20</t>
+          <t>VB020202-01-01-S-02</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
         </is>
       </c>
       <c r="C1002" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D1002" t="inlineStr"/>
       <c r="E1002" t="inlineStr"/>
@@ -25941,16 +25941,16 @@
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-30</t>
+          <t>VB020202-01-03-L-09</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-PLUMAS</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-BEIGE</t>
         </is>
       </c>
       <c r="C1003" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D1003" t="inlineStr"/>
       <c r="E1003" t="inlineStr"/>
@@ -25963,16 +25963,16 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-30</t>
+          <t>VB020202-01-02-M-09</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-PLUMAS</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C1004" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D1004" t="inlineStr"/>
       <c r="E1004" t="inlineStr"/>
@@ -25985,12 +25985,12 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-11</t>
+          <t>VB020202-01-03-L-02</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C1005" t="n">
@@ -26007,16 +26007,16 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>VB020103-01-03-L-26</t>
+          <t>VB020203-01-03-L-02</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-L-MISTICO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-NEGRO</t>
         </is>
       </c>
       <c r="C1006" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D1006" t="inlineStr"/>
       <c r="E1006" t="inlineStr"/>
@@ -26029,16 +26029,16 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-15</t>
+          <t>VB020103-02-03-L-03</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1007" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1007" t="inlineStr"/>
       <c r="E1007" t="inlineStr"/>
@@ -26051,16 +26051,16 @@
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-15</t>
+          <t>VB020204-01-03-L-11</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-PURPURA</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C1008" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D1008" t="inlineStr"/>
       <c r="E1008" t="inlineStr"/>
@@ -26073,16 +26073,16 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-08</t>
+          <t>VB0105-01-02-M-23</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
+          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C1009" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D1009" t="inlineStr"/>
       <c r="E1009" t="inlineStr"/>
@@ -26095,16 +26095,16 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-11</t>
+          <t>VB0302-01-01-S-01</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-FUCSIA NEON</t>
+          <t>PANTALON ALTO-S-BLANCO</t>
         </is>
       </c>
       <c r="C1010" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D1010" t="inlineStr"/>
       <c r="E1010" t="inlineStr"/>
@@ -26117,16 +26117,16 @@
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-13</t>
+          <t>VB020103-02-01-S-17</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-ROSADO</t>
         </is>
       </c>
       <c r="C1011" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D1011" t="inlineStr"/>
       <c r="E1011" t="inlineStr"/>
@@ -26139,16 +26139,16 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-07</t>
+          <t>VB020303-01-01-S-26</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL CIAN</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
         </is>
       </c>
       <c r="C1012" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="D1012" t="inlineStr"/>
       <c r="E1012" t="inlineStr"/>
@@ -26161,16 +26161,16 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>VB0301-01-04-U-09</t>
+          <t>VB020204-01-01-S-05</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>FALDA GAIA MACRAME-U-BEIGE</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C1013" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D1013" t="inlineStr"/>
       <c r="E1013" t="inlineStr"/>
@@ -26183,16 +26183,16 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-02</t>
+          <t>VB020103-02-02-M-17</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-ROSADO</t>
         </is>
       </c>
       <c r="C1014" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D1014" t="inlineStr"/>
       <c r="E1014" t="inlineStr"/>
@@ -26205,16 +26205,16 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-09</t>
+          <t>VB020103-02-01-S-03</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1015" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D1015" t="inlineStr"/>
       <c r="E1015" t="inlineStr"/>
@@ -26227,16 +26227,16 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>VB0303-01-01-S-09</t>
+          <t>VB020103-02-01-S-02</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>SHORT ALTO-S-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-NEGRO</t>
         </is>
       </c>
       <c r="C1016" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1016" t="inlineStr"/>
       <c r="E1016" t="inlineStr"/>
@@ -26249,16 +26249,16 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>VB0303-01-02-M-09</t>
+          <t>VB020103-02-02-M-03</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>SHORT ALTO-M-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1017" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D1017" t="inlineStr"/>
       <c r="E1017" t="inlineStr"/>
@@ -26271,16 +26271,16 @@
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>VB0303-01-03-L-09</t>
+          <t>VB0302-01-03-L-01</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>SHORT ALTO-L-BEIGE</t>
+          <t>PANTALON ALTO-L-BLANCO</t>
         </is>
       </c>
       <c r="C1018" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D1018" t="inlineStr"/>
       <c r="E1018" t="inlineStr"/>
@@ -26293,16 +26293,16 @@
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>VB0303-01-01-S-01</t>
+          <t>VB020103-02-03-L-02</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>SHORT ALTO-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-NEGRO</t>
         </is>
       </c>
       <c r="C1019" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D1019" t="inlineStr"/>
       <c r="E1019" t="inlineStr"/>
@@ -26315,16 +26315,16 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>VB0303-01-03-L-02</t>
+          <t>VB020204-01-02-M-07</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>SHORT ALTO-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1020" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D1020" t="inlineStr"/>
       <c r="E1020" t="inlineStr"/>
@@ -26337,16 +26337,16 @@
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>VB0303-01-02-M-02</t>
+          <t>VB020103-02-03-L-17</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>SHORT ALTO-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-ROSADO</t>
         </is>
       </c>
       <c r="C1021" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D1021" t="inlineStr"/>
       <c r="E1021" t="inlineStr"/>
@@ -26359,16 +26359,16 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>VB0303-01-02-M-01</t>
+          <t>VB020204-01-01-S-11</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>SHORT ALTO-M-BLANCO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C1022" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D1022" t="inlineStr"/>
       <c r="E1022" t="inlineStr"/>
@@ -26381,16 +26381,16 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-09</t>
+          <t>VB0302-01-03-L-02</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-BEIGE</t>
+          <t>PANTALON ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C1023" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D1023" t="inlineStr"/>
       <c r="E1023" t="inlineStr"/>
@@ -26403,16 +26403,16 @@
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>VB0303-01-03-L-01</t>
+          <t>VB020204-01-01-S-08</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>SHORT ALTO-L-BLANCO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
         </is>
       </c>
       <c r="C1024" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D1024" t="inlineStr"/>
       <c r="E1024" t="inlineStr"/>
@@ -26425,16 +26425,16 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-09</t>
+          <t>VB0105-01-01-S-23</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-BEIGE</t>
+          <t>VB ENTERO TANGA-S-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C1025" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D1025" t="inlineStr"/>
       <c r="E1025" t="inlineStr"/>
@@ -26447,16 +26447,16 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-18</t>
+          <t>VB020204-01-03-L-13</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-VERDE MENTA</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-NARANJA</t>
         </is>
       </c>
       <c r="C1026" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D1026" t="inlineStr"/>
       <c r="E1026" t="inlineStr"/>
@@ -26469,16 +26469,16 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-18</t>
+          <t>VB020303-01-03-L-26</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-VERDE MENTA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-MISTICO</t>
         </is>
       </c>
       <c r="C1027" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D1027" t="inlineStr"/>
       <c r="E1027" t="inlineStr"/>
@@ -26491,16 +26491,16 @@
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>VB0105-02-03-L-18</t>
+          <t>VB020204-01-01-S-15</t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-VERDE MENTA</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-PURPURA</t>
         </is>
       </c>
       <c r="C1028" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D1028" t="inlineStr"/>
       <c r="E1028" t="inlineStr"/>
@@ -26513,16 +26513,16 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-17</t>
+          <t>VB020204-01-02-M-05</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-ROSADO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C1029" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D1029" t="inlineStr"/>
       <c r="E1029" t="inlineStr"/>
@@ -26535,16 +26535,16 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-17</t>
+          <t>VB020202-01-03-L-07</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-ROSADO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1030" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D1030" t="inlineStr"/>
       <c r="E1030" t="inlineStr"/>
@@ -26557,16 +26557,16 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>VB0105-02-03-L-17</t>
+          <t>VB020202-01-02-M-07</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-ROSADO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1031" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1031" t="inlineStr"/>
       <c r="E1031" t="inlineStr"/>
@@ -26579,16 +26579,16 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-02</t>
+          <t>VB020202-01-01-S-07</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1032" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D1032" t="inlineStr"/>
       <c r="E1032" t="inlineStr"/>
@@ -26601,16 +26601,16 @@
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-02</t>
+          <t>VB020101-01-01-S-15</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PURPURA</t>
         </is>
       </c>
       <c r="C1033" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1033" t="inlineStr"/>
       <c r="E1033" t="inlineStr"/>
@@ -26623,16 +26623,16 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-33</t>
+          <t>VB0302-01-02-M-02</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-TIE DYE</t>
+          <t>PANTALON ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C1034" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D1034" t="inlineStr"/>
       <c r="E1034" t="inlineStr"/>
@@ -26645,16 +26645,16 @@
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>VB0105-02-03-L-02</t>
+          <t>VB020203-01-02-M-01</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-BLANCO</t>
         </is>
       </c>
       <c r="C1035" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D1035" t="inlineStr"/>
       <c r="E1035" t="inlineStr"/>
@@ -26667,16 +26667,16 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-15</t>
+          <t>VB020203-01-03-L-01</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-PURPURA</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-BLANCO</t>
         </is>
       </c>
       <c r="C1036" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D1036" t="inlineStr"/>
       <c r="E1036" t="inlineStr"/>
@@ -26689,16 +26689,16 @@
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-33</t>
+          <t>VB0105-01-03-L-23</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-TIE DYE</t>
+          <t>VB ENTERO TANGA-L-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C1037" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D1037" t="inlineStr"/>
       <c r="E1037" t="inlineStr"/>
@@ -26711,16 +26711,16 @@
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-16</t>
+          <t>VB020202-01-02-M-23</t>
         </is>
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-ROJO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C1038" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1038" t="inlineStr"/>
       <c r="E1038" t="inlineStr"/>
@@ -26733,16 +26733,16 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-16</t>
+          <t>VB020204-01-02-M-08</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-ROJO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
         </is>
       </c>
       <c r="C1039" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D1039" t="inlineStr"/>
       <c r="E1039" t="inlineStr"/>
@@ -26755,16 +26755,16 @@
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-16</t>
+          <t>VB020303-01-02-M-26</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-MISTICO</t>
         </is>
       </c>
       <c r="C1040" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="D1040" t="inlineStr"/>
       <c r="E1040" t="inlineStr"/>
@@ -26777,16 +26777,16 @@
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-23</t>
+          <t>VB020103-04-03-L-19</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1041" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D1041" t="inlineStr"/>
       <c r="E1041" t="inlineStr"/>
@@ -26799,16 +26799,16 @@
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-32</t>
+          <t>VB020103-04-02-M-19</t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1042" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D1042" t="inlineStr"/>
       <c r="E1042" t="inlineStr"/>
@@ -26821,16 +26821,16 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-15</t>
+          <t>VB020103-04-02-M-28</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-PITON BEIGE</t>
         </is>
       </c>
       <c r="C1043" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D1043" t="inlineStr"/>
       <c r="E1043" t="inlineStr"/>
@@ -26843,16 +26843,16 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-13</t>
+          <t>VB020103-04-01-S-28</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-PITON BEIGE</t>
         </is>
       </c>
       <c r="C1044" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D1044" t="inlineStr"/>
       <c r="E1044" t="inlineStr"/>
@@ -26865,16 +26865,16 @@
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-07</t>
+          <t>VB020303-01-02-M-19</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1045" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D1045" t="inlineStr"/>
       <c r="E1045" t="inlineStr"/>
@@ -26887,16 +26887,16 @@
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-01</t>
+          <t>VB020103-04-03-L-28</t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-PITON BEIGE</t>
         </is>
       </c>
       <c r="C1046" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D1046" t="inlineStr"/>
       <c r="E1046" t="inlineStr"/>
@@ -26909,16 +26909,16 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-32</t>
+          <t>VB020303-01-01-S-19</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1047" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D1047" t="inlineStr"/>
       <c r="E1047" t="inlineStr"/>
@@ -26931,16 +26931,16 @@
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-08</t>
+          <t>VB020205-03-03-L-28</t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-PITON BEIGE</t>
         </is>
       </c>
       <c r="C1048" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D1048" t="inlineStr"/>
       <c r="E1048" t="inlineStr"/>
@@ -26953,16 +26953,16 @@
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-01</t>
+          <t>VB020205-03-02-M-28</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-PITON BEIGE</t>
         </is>
       </c>
       <c r="C1049" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D1049" t="inlineStr"/>
       <c r="E1049" t="inlineStr"/>
@@ -26975,16 +26975,16 @@
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>VB0103-01-02-M-32</t>
+          <t>VB020205-03-01-S-28</t>
         </is>
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-PITON BEIGE</t>
         </is>
       </c>
       <c r="C1050" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D1050" t="inlineStr"/>
       <c r="E1050" t="inlineStr"/>
@@ -26997,16 +26997,16 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-23</t>
+          <t>VB020303-01-03-L-19</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1051" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D1051" t="inlineStr"/>
       <c r="E1051" t="inlineStr"/>
@@ -27019,16 +27019,16 @@
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-01</t>
+          <t>VB0306-01-02-M-02</t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
+          <t>TOP BÁSICO LUISA-M-NEGRO</t>
         </is>
       </c>
       <c r="C1052" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D1052" t="inlineStr"/>
       <c r="E1052" t="inlineStr"/>
@@ -27041,16 +27041,16 @@
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-01</t>
+          <t>VB0306-01-01-S-03</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
+          <t>TOP BÁSICO LUISA-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1053" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D1053" t="inlineStr"/>
       <c r="E1053" t="inlineStr"/>
@@ -27063,16 +27063,16 @@
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-01</t>
+          <t>VB0306-01-02-M-03</t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
+          <t>TOP BÁSICO LUISA-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1054" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D1054" t="inlineStr"/>
       <c r="E1054" t="inlineStr"/>
@@ -27085,16 +27085,16 @@
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-01</t>
+          <t>VB0306-01-03-L-01</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-BLANCO</t>
+          <t>TOP BÁSICO LUISA-L-BLANCO</t>
         </is>
       </c>
       <c r="C1055" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D1055" t="inlineStr"/>
       <c r="E1055" t="inlineStr"/>
@@ -27107,16 +27107,16 @@
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-09</t>
+          <t>VB0306-01-01-S-02</t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-BEIGE</t>
+          <t>TOP BÁSICO LUISA-S-NEGRO</t>
         </is>
       </c>
       <c r="C1056" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1056" t="inlineStr"/>
       <c r="E1056" t="inlineStr"/>
@@ -27129,16 +27129,16 @@
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-02</t>
+          <t>VB0104-01-03-L-09</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-BEIGE</t>
         </is>
       </c>
       <c r="C1057" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D1057" t="inlineStr"/>
       <c r="E1057" t="inlineStr"/>
@@ -27151,16 +27151,16 @@
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-02</t>
+          <t>VB020103-04-01-S-19</t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1058" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="D1058" t="inlineStr"/>
       <c r="E1058" t="inlineStr"/>
@@ -27173,16 +27173,16 @@
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-09</t>
+          <t>VB020103-04-03-L-09</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-BEIGE</t>
         </is>
       </c>
       <c r="C1059" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D1059" t="inlineStr"/>
       <c r="E1059" t="inlineStr"/>
@@ -27195,16 +27195,16 @@
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-09</t>
+          <t>VB020103-04-02-M-09</t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-BEIGE</t>
         </is>
       </c>
       <c r="C1060" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D1060" t="inlineStr"/>
       <c r="E1060" t="inlineStr"/>
@@ -27217,16 +27217,16 @@
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-02</t>
+          <t>VB020103-04-01-S-09</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-BEIGE</t>
         </is>
       </c>
       <c r="C1061" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1061" t="inlineStr"/>
       <c r="E1061" t="inlineStr"/>
@@ -27239,16 +27239,16 @@
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>VB020203-01-03-L-02</t>
+          <t>VB0104-01-02-M-09</t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-NEGRO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-BEIGE</t>
         </is>
       </c>
       <c r="C1062" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D1062" t="inlineStr"/>
       <c r="E1062" t="inlineStr"/>
@@ -27261,16 +27261,16 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-03</t>
+          <t>VB0104-01-01-S-09</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-BEIGE</t>
         </is>
       </c>
       <c r="C1063" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D1063" t="inlineStr"/>
       <c r="E1063" t="inlineStr"/>
@@ -27283,16 +27283,16 @@
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-11</t>
+          <t>VB0304-01-03-L-02</t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-L-NEGRO</t>
         </is>
       </c>
       <c r="C1064" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D1064" t="inlineStr"/>
       <c r="E1064" t="inlineStr"/>
@@ -27305,16 +27305,16 @@
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>VB0105-01-02-M-23</t>
+          <t>VB0304-01-02-M-02</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-M-NEGRO</t>
         </is>
       </c>
       <c r="C1065" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D1065" t="inlineStr"/>
       <c r="E1065" t="inlineStr"/>
@@ -27327,16 +27327,16 @@
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-01</t>
+          <t>VB020103-05-03-L-36</t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C1066" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D1066" t="inlineStr"/>
       <c r="E1066" t="inlineStr"/>
@@ -27349,16 +27349,16 @@
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-17</t>
+          <t>VB020103-05-03-L-37</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1067" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1067" t="inlineStr"/>
       <c r="E1067" t="inlineStr"/>
@@ -27371,16 +27371,16 @@
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-26</t>
+          <t>VB0307-01-04-U-13</t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
+          <t>PAÑOLETA-U-NARANJA</t>
         </is>
       </c>
       <c r="C1068" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D1068" t="inlineStr"/>
       <c r="E1068" t="inlineStr"/>
@@ -27393,16 +27393,16 @@
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-05</t>
+          <t>VB020303-01-02-M-34</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-FAUNA</t>
         </is>
       </c>
       <c r="C1069" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D1069" t="inlineStr"/>
       <c r="E1069" t="inlineStr"/>
@@ -27415,16 +27415,16 @@
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>VB020103-02-02-M-17</t>
+          <t>VB020303-01-01-S-34</t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-ROSADO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-FAUNA</t>
         </is>
       </c>
       <c r="C1070" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D1070" t="inlineStr"/>
       <c r="E1070" t="inlineStr"/>
@@ -27437,16 +27437,16 @@
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-03</t>
+          <t>VB0305-01-04-U-02</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
+          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-NEGRO</t>
         </is>
       </c>
       <c r="C1071" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D1071" t="inlineStr"/>
       <c r="E1071" t="inlineStr"/>
@@ -27459,16 +27459,16 @@
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-02</t>
+          <t>VB0304-01-01-S-09</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-NEGRO</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-S-BEIGE</t>
         </is>
       </c>
       <c r="C1072" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D1072" t="inlineStr"/>
       <c r="E1072" t="inlineStr"/>
@@ -27481,16 +27481,16 @@
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>VB020103-02-02-M-03</t>
+          <t>VB0304-01-02-M-09</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-M-BEIGE</t>
         </is>
       </c>
       <c r="C1073" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D1073" t="inlineStr"/>
       <c r="E1073" t="inlineStr"/>
@@ -27503,16 +27503,16 @@
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-01</t>
+          <t>VB0305-01-04-U-09</t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-BLANCO</t>
+          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-BEIGE</t>
         </is>
       </c>
       <c r="C1074" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D1074" t="inlineStr"/>
       <c r="E1074" t="inlineStr"/>
@@ -27525,16 +27525,16 @@
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-02</t>
+          <t>VB020104-01-02-M-03</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1075" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D1075" t="inlineStr"/>
       <c r="E1075" t="inlineStr"/>
@@ -27547,16 +27547,16 @@
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-07</t>
+          <t>VB0301-01-04-U-02</t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AZUL CIAN</t>
+          <t>FALDA GAIA MACRAME-U-NEGRO</t>
         </is>
       </c>
       <c r="C1076" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D1076" t="inlineStr"/>
       <c r="E1076" t="inlineStr"/>
@@ -27569,12 +27569,12 @@
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-17</t>
+          <t>VB020103-05-01-S-37</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1077" t="n">
@@ -27591,16 +27591,16 @@
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-11</t>
+          <t>VB020103-05-02-M-37</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1078" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D1078" t="inlineStr"/>
       <c r="E1078" t="inlineStr"/>
@@ -27613,16 +27613,16 @@
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-02</t>
+          <t>VB020103-05-02-M-36</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C1079" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D1079" t="inlineStr"/>
       <c r="E1079" t="inlineStr"/>
@@ -27635,16 +27635,16 @@
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-08</t>
+          <t>VB0304-01-03-L-09</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-L-BEIGE</t>
         </is>
       </c>
       <c r="C1080" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D1080" t="inlineStr"/>
       <c r="E1080" t="inlineStr"/>
@@ -27657,16 +27657,16 @@
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>VB0105-01-01-S-23</t>
+          <t>VB020103-05-01-S-36</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-S-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C1081" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D1081" t="inlineStr"/>
       <c r="E1081" t="inlineStr"/>
@@ -27679,16 +27679,16 @@
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-13</t>
+          <t>VB020103-05-01-S-35</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-NEGRO-BLANCO HUESO</t>
         </is>
       </c>
       <c r="C1082" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D1082" t="inlineStr"/>
       <c r="E1082" t="inlineStr"/>
@@ -27701,16 +27701,16 @@
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-26</t>
+          <t>VB020103-05-02-M-35</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-NEGRO-BLANCO HUESO</t>
         </is>
       </c>
       <c r="C1083" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D1083" t="inlineStr"/>
       <c r="E1083" t="inlineStr"/>
@@ -27723,16 +27723,16 @@
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-15</t>
+          <t>VB020103-05-03-L-35</t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-NEGRO-BLANCO HUESO</t>
         </is>
       </c>
       <c r="C1084" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D1084" t="inlineStr"/>
       <c r="E1084" t="inlineStr"/>
@@ -27745,16 +27745,16 @@
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-05</t>
+          <t>VB020303-01-03-L-34</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-FAUNA</t>
         </is>
       </c>
       <c r="C1085" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D1085" t="inlineStr"/>
       <c r="E1085" t="inlineStr"/>
@@ -27767,16 +27767,16 @@
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-07</t>
+          <t>VB020104-01-01-S-03</t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1086" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D1086" t="inlineStr"/>
       <c r="E1086" t="inlineStr"/>
@@ -27789,16 +27789,16 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-07</t>
+          <t>VB020104-01-03-L-03</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1087" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D1087" t="inlineStr"/>
       <c r="E1087" t="inlineStr"/>
@@ -27811,16 +27811,16 @@
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-07</t>
+          <t>VB020104-01-01-S-17</t>
         </is>
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-ROSADO</t>
         </is>
       </c>
       <c r="C1088" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D1088" t="inlineStr"/>
       <c r="E1088" t="inlineStr"/>
@@ -27833,12 +27833,12 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-15</t>
+          <t>VB020104-01-02-M-17</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-M-ROSADO</t>
         </is>
       </c>
       <c r="C1089" t="n">
@@ -27855,16 +27855,16 @@
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-02</t>
+          <t>VB020104-01-03-L-17</t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-ROSADO</t>
         </is>
       </c>
       <c r="C1090" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1090" t="inlineStr"/>
       <c r="E1090" t="inlineStr"/>
@@ -27877,12 +27877,12 @@
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>VB020203-01-02-M-01</t>
+          <t>VB020104-01-01-S-06</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C1091" t="n">
@@ -27899,16 +27899,16 @@
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>VB020203-01-03-L-01</t>
+          <t>VB020104-01-02-M-06</t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-M-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C1092" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1092" t="inlineStr"/>
       <c r="E1092" t="inlineStr"/>
@@ -27921,16 +27921,16 @@
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>VB0105-01-03-L-23</t>
+          <t>VB0306-01-03-L-02</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-L-HOJAS AZUL</t>
+          <t>TOP BÁSICO LUISA-L-NEGRO</t>
         </is>
       </c>
       <c r="C1093" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D1093" t="inlineStr"/>
       <c r="E1093" t="inlineStr"/>
@@ -27943,16 +27943,16 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-23</t>
+          <t>VB0306-01-01-S-01</t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
+          <t>TOP BÁSICO LUISA-S-BLANCO</t>
         </is>
       </c>
       <c r="C1094" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D1094" t="inlineStr"/>
       <c r="E1094" t="inlineStr"/>
@@ -27965,16 +27965,16 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-08</t>
+          <t>VB0306-01-03-L-03</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
+          <t>TOP BÁSICO LUISA-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1095" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D1095" t="inlineStr"/>
       <c r="E1095" t="inlineStr"/>
@@ -27987,16 +27987,16 @@
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-26</t>
+          <t>VB0306-01-02-M-01</t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-MISTICO</t>
+          <t>TOP BÁSICO LUISA-M-BLANCO</t>
         </is>
       </c>
       <c r="C1096" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D1096" t="inlineStr"/>
       <c r="E1096" t="inlineStr"/>
@@ -44565,19 +44565,19 @@
     <row r="1742">
       <c r="A1742" t="inlineStr">
         <is>
-          <t>D030604</t>
+          <t>K020502</t>
         </is>
       </c>
       <c r="B1742" t="inlineStr">
         <is>
-          <t>REGENERADOR DE ALMENDRAS DLUCHI</t>
+          <t>ESPUMA LIMPIADORA FACIAL KABA</t>
         </is>
       </c>
       <c r="C1742" t="n">
         <v>4</v>
       </c>
       <c r="D1742" t="n">
-        <v>2585.954198473283</v>
+        <v>1723.396946564885</v>
       </c>
       <c r="E1742" t="inlineStr">
         <is>
@@ -44593,19 +44593,19 @@
     <row r="1743">
       <c r="A1743" t="inlineStr">
         <is>
-          <t>K020502</t>
+          <t>R010501</t>
         </is>
       </c>
       <c r="B1743" t="inlineStr">
         <is>
-          <t>ESPUMA LIMPIADORA FACIAL KABA</t>
+          <t>EXFOLIANTE CAPILAR LA RECETA</t>
         </is>
       </c>
       <c r="C1743" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1743" t="n">
-        <v>1723.396946564885</v>
+        <v>1616.908396946565</v>
       </c>
       <c r="E1743" t="inlineStr">
         <is>
@@ -44621,19 +44621,19 @@
     <row r="1744">
       <c r="A1744" t="inlineStr">
         <is>
-          <t>R010501</t>
+          <t>K021301</t>
         </is>
       </c>
       <c r="B1744" t="inlineStr">
         <is>
-          <t>EXFOLIANTE CAPILAR LA RECETA</t>
+          <t>CONTORNO DE OJOS KABA</t>
         </is>
       </c>
       <c r="C1744" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1744" t="n">
-        <v>1616.908396946565</v>
+        <v>1647.137404580153</v>
       </c>
       <c r="E1744" t="inlineStr">
         <is>
@@ -44649,19 +44649,19 @@
     <row r="1745">
       <c r="A1745" t="inlineStr">
         <is>
-          <t>K021301</t>
+          <t>K010101</t>
         </is>
       </c>
       <c r="B1745" t="inlineStr">
         <is>
-          <t>CONTORNO DE OJOS KABA</t>
+          <t>SHAMPO DE CEBOLLA KABA</t>
         </is>
       </c>
       <c r="C1745" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D1745" t="n">
-        <v>1647.137404580153</v>
+        <v>81409.46564885495</v>
       </c>
       <c r="E1745" t="inlineStr">
         <is>
@@ -44677,19 +44677,19 @@
     <row r="1746">
       <c r="A1746" t="inlineStr">
         <is>
-          <t>K010101</t>
+          <t>D030604</t>
         </is>
       </c>
       <c r="B1746" t="inlineStr">
         <is>
-          <t>SHAMPO DE CEBOLLA KABA</t>
+          <t>REGENERADOR DE ALMENDRAS DLUCHI</t>
         </is>
       </c>
       <c r="C1746" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1746" t="n">
-        <v>81409.46564885495</v>
+        <v>2585.954198473283</v>
       </c>
       <c r="E1746" t="inlineStr">
         <is>
@@ -45349,16 +45349,16 @@
     <row r="1770">
       <c r="A1770" t="inlineStr">
         <is>
-          <t>K051505</t>
+          <t>K051501</t>
         </is>
       </c>
       <c r="B1770" t="inlineStr">
         <is>
-          <t>COSMETIQUERA FACIAL GRANDE KABA</t>
+          <t>COSMETIQUERA GRANDE KABA</t>
         </is>
       </c>
       <c r="C1770" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D1770" t="inlineStr"/>
       <c r="E1770" t="inlineStr">
@@ -45375,16 +45375,16 @@
     <row r="1771">
       <c r="A1771" t="inlineStr">
         <is>
-          <t>K051501</t>
+          <t>K051505</t>
         </is>
       </c>
       <c r="B1771" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE KABA</t>
+          <t>COSMETIQUERA FACIAL GRANDE KABA</t>
         </is>
       </c>
       <c r="C1771" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D1771" t="inlineStr"/>
       <c r="E1771" t="inlineStr">

--- a/inventario_operaciones.xlsx
+++ b/inventario_operaciones.xlsx
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D21" t="n">
         <v>1399.809160305344</v>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D25" t="n">
         <v>23981.2213740458</v>
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="D33" t="n">
         <v>33819.04580152671</v>
@@ -1739,19 +1739,19 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KM041301</t>
+          <t>KM041302</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE GOLD</t>
+          <t>DROPS CHAMPAGNE SILVER</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>425</v>
+        <v>699</v>
       </c>
       <c r="D48" t="n">
-        <v>760.8778625954199</v>
+        <v>192.7099236641222</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1767,19 +1767,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KM041302</t>
+          <t>KM041301</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE SILVER</t>
+          <t>DROPS CHAMPAGNE GOLD</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>699</v>
+        <v>425</v>
       </c>
       <c r="D49" t="n">
-        <v>192.7099236641222</v>
+        <v>760.8778625954199</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1823,19 +1823,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KM041305</t>
+          <t>KM041307</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ILUMINADOR LIGHTS UP</t>
+          <t>ILUMINADOR LIQUIDO DAILY SHINE</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>799</v>
+        <v>665</v>
       </c>
       <c r="D51" t="n">
-        <v>162.824427480916</v>
+        <v>101.6793893129771</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1851,19 +1851,19 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KM041307</t>
+          <t>KM041305</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ILUMINADOR LIQUIDO DAILY SHINE</t>
+          <t>ILUMINADOR LIGHTS UP</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>665</v>
+        <v>799</v>
       </c>
       <c r="D52" t="n">
-        <v>101.6793893129771</v>
+        <v>162.824427480916</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="D70" t="n">
         <v>15285.91603053435</v>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D93" t="n">
         <v>2161.717557251908</v>
@@ -3117,19 +3117,19 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>KITKM0402</t>
+          <t>KITKM0404</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LIP COMBO VOLUM GOLDEN HOUR KABA MAKEUP</t>
+          <t>LIP COMBO GOLDEN HOUR KABA MAKEUP</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D98" t="n">
-        <v>8.931297709923664</v>
+        <v>4.236641221374046</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3145,19 +3145,19 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>KITKM0401</t>
+          <t>KITKM0402</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LIP COMBO VOLUM ROSE VELVET KABA MAKEUP</t>
+          <t>LIP COMBO VOLUM GOLDEN HOUR KABA MAKEUP</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D99" t="n">
-        <v>9.732824427480915</v>
+        <v>8.931297709923664</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3173,19 +3173,19 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>KITKM0404</t>
+          <t>KITKM0401</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LIP COMBO GOLDEN HOUR KABA MAKEUP</t>
+          <t>LIP COMBO VOLUM ROSE VELVET KABA MAKEUP</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D100" t="n">
-        <v>4.236641221374046</v>
+        <v>9.732824427480915</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D101" t="n">
         <v>15.11450381679389</v>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D103" t="n">
         <v>8045.038167938931</v>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D108" t="n">
         <v>230.7251908396946</v>
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D121" t="n">
         <v>11863.1679389313</v>
@@ -4285,16 +4285,16 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>C030606</t>
+          <t>KITC010201</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>GLOW GIRLS SOPHIE ECHEVERRRI</t>
+          <t>KIT VIVIANA GRONDONA</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>324</v>
+        <v>63</v>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
@@ -4311,16 +4311,16 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>KITC010201</t>
+          <t>C030606</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>KIT VIVIANA GRONDONA</t>
+          <t>GLOW GIRLS SOPHIE ECHEVERRRI</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>63</v>
+        <v>324</v>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D142" t="n">
         <v>5048.244274809161</v>
@@ -4374,7 +4374,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D143" t="n">
         <v>53.81679389312977</v>
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D151" t="n">
         <v>98.58778625954199</v>
@@ -5917,19 +5917,19 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>KITR0103</t>
+          <t>KITKR0104</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>KIT DUO ANTICASPA LA RECETA</t>
+          <t>KIT CRTO ACELERADO CABELLO SECO</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D200" t="n">
-        <v>164.7709923664122</v>
+        <v>15.57251908396946</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -5945,19 +5945,19 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>KITKR0104</t>
+          <t>KITR0103</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>KIT CRTO ACELERADO CABELLO SECO</t>
+          <t>KIT DUO ANTICASPA LA RECETA</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D201" t="n">
-        <v>15.57251908396946</v>
+        <v>164.7709923664122</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>19968</v>
+        <v>17368</v>
       </c>
       <c r="D326" t="n">
         <v>11490.45801526718</v>
@@ -9447,19 +9447,19 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>R010303</t>
+          <t>KM041202</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>SACHET BOMBA ANTIGRASA LA RECETA</t>
+          <t>LIP GLOSS GOLDEN HOUR</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>3000</v>
+        <v>943</v>
       </c>
       <c r="D328" t="n">
-        <v>180</v>
+        <v>171.412213740458</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -9475,19 +9475,19 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>KM041202</t>
+          <t>R010303</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>LIP GLOSS GOLDEN HOUR</t>
+          <t>SACHET BOMBA ANTIGRASA LA RECETA</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>943</v>
+        <v>3000</v>
       </c>
       <c r="D329" t="n">
-        <v>171.412213740458</v>
+        <v>180</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -9503,19 +9503,19 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>KM041303</t>
+          <t>KM041308</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>DROPS HONEY GOLD</t>
+          <t>ILUMINADOR PRETTY GIRL</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>5293</v>
+        <v>9802</v>
       </c>
       <c r="D330" t="n">
-        <v>531.7557251908397</v>
+        <v>148.3969465648855</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -9531,19 +9531,19 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>KM041308</t>
+          <t>KM041303</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>ILUMINADOR PRETTY GIRL</t>
+          <t>DROPS HONEY GOLD</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>9802</v>
+        <v>5293</v>
       </c>
       <c r="D331" t="n">
-        <v>148.3969465648855</v>
+        <v>531.7557251908397</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -12381,19 +12381,19 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>KM041301</t>
+          <t>KM041302</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE GOLD</t>
+          <t>DROPS CHAMPAGNE SILVER</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>4883</v>
+        <v>6380</v>
       </c>
       <c r="D438" t="n">
-        <v>760.8778625954199</v>
+        <v>192.7099236641222</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
@@ -12409,19 +12409,19 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>KM041302</t>
+          <t>KM041301</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE SILVER</t>
+          <t>DROPS CHAMPAGNE GOLD</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>6380</v>
+        <v>4883</v>
       </c>
       <c r="D439" t="n">
-        <v>192.7099236641222</v>
+        <v>760.8778625954199</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
@@ -13665,18 +13665,20 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>KM041311</t>
+          <t>KM041312</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>RUBOR LIQUIDO MARTINI</t>
+          <t>RUBOR LIQUIDO SUNRISE</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>2444</v>
-      </c>
-      <c r="D486" t="inlineStr"/>
+        <v>2154</v>
+      </c>
+      <c r="D486" t="n">
+        <v>98.587786259542</v>
+      </c>
       <c r="E486" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -13691,19 +13693,19 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>KM041313</t>
+          <t>KM041314</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>RUBOR LIQUIDO MANHATTAN</t>
+          <t>RUBOR LIQUIDO MARGARITA</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>2382</v>
+        <v>2487</v>
       </c>
       <c r="D487" t="n">
-        <v>102.0229007633588</v>
+        <v>106.8320610687023</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
@@ -13719,19 +13721,19 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>KM041314</t>
+          <t>KM041313</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>RUBOR LIQUIDO MARGARITA</t>
+          <t>RUBOR LIQUIDO MANHATTAN</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>2487</v>
+        <v>2382</v>
       </c>
       <c r="D488" t="n">
-        <v>106.8320610687023</v>
+        <v>102.0229007633588</v>
       </c>
       <c r="E488" t="inlineStr">
         <is>
@@ -13747,20 +13749,18 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>KM041312</t>
+          <t>KM041315</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>RUBOR LIQUIDO SUNRISE</t>
+          <t>RUBOR LIQUIDO COCO LOCO</t>
         </is>
       </c>
       <c r="C489" t="n">
-        <v>2154</v>
-      </c>
-      <c r="D489" t="n">
-        <v>98.587786259542</v>
-      </c>
+        <v>2612</v>
+      </c>
+      <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -13775,16 +13775,16 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>KM041315</t>
+          <t>KM041311</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>RUBOR LIQUIDO COCO LOCO</t>
+          <t>RUBOR LIQUIDO MARTINI</t>
         </is>
       </c>
       <c r="C490" t="n">
-        <v>2612</v>
+        <v>2444</v>
       </c>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
@@ -15025,19 +15025,19 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>KITKR0106</t>
+          <t>KITR0103</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>KIT CRTO Y REPARACIÓN KABA +ACEITEPUNTAS</t>
+          <t>KIT DUO ANTICASPA LA RECETA</t>
         </is>
       </c>
       <c r="C536" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="D536" t="n">
-        <v>230.7251908396946</v>
+        <v>164.7709923664122</v>
       </c>
       <c r="E536" t="inlineStr">
         <is>
@@ -15053,19 +15053,19 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>KITR0103</t>
+          <t>KITKR0106</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>KIT DUO ANTICASPA LA RECETA</t>
+          <t>KIT CRTO Y REPARACIÓN KABA +ACEITEPUNTAS</t>
         </is>
       </c>
       <c r="C537" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="D537" t="n">
-        <v>164.7709923664122</v>
+        <v>230.7251908396946</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
@@ -18249,16 +18249,16 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-24</t>
+          <t>VB020303-01-03-L-30</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
         </is>
       </c>
       <c r="C663" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr"/>
@@ -18271,12 +18271,12 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>VB020103-01-02-M-26</t>
+          <t>VB020105-01-02-M-13</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
         </is>
       </c>
       <c r="C664" t="n">
@@ -18293,16 +18293,16 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-13</t>
+          <t>VB020103-01-02-M-26</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
         </is>
       </c>
       <c r="C665" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D665" t="inlineStr"/>
       <c r="E665" t="inlineStr"/>
@@ -18315,23 +18315,19 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>DISACK010101</t>
+          <t>VB020105-01-03-L-13</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>DISPLEY SACHET DE SHAMPO DE CEBOLLA KABA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
         </is>
       </c>
       <c r="C666" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D666" t="inlineStr"/>
-      <c r="E666" t="inlineStr">
-        <is>
-          <t>PRODUCTO MANUFACTURADO</t>
-        </is>
-      </c>
+      <c r="E666" t="inlineStr"/>
       <c r="F666" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -18341,19 +18337,23 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-13</t>
+          <t>DISACK010101</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
+          <t>DISPLEY SACHET DE SHAMPO DE CEBOLLA KABA</t>
         </is>
       </c>
       <c r="C667" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D667" t="inlineStr"/>
-      <c r="E667" t="inlineStr"/>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>PRODUCTO MANUFACTURADO</t>
+        </is>
+      </c>
       <c r="F667" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -18407,16 +18407,16 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-13</t>
+          <t>VB020303-01-03-L-24</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-NARANJA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C670" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D670" t="inlineStr"/>
       <c r="E670" t="inlineStr"/>
@@ -18429,16 +18429,16 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-25</t>
+          <t>VB020303-01-03-L-25</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C671" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D671" t="inlineStr"/>
       <c r="E671" t="inlineStr"/>
@@ -18473,12 +18473,12 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-25</t>
+          <t>VB020101-01-01-S-14</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C673" t="n">
@@ -18495,12 +18495,12 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-14</t>
+          <t>VB020103-03-02-M-20</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C674" t="n">
@@ -18517,12 +18517,12 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>VB020103-03-02-M-20</t>
+          <t>VB020105-01-01-S-13</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-NARANJA</t>
         </is>
       </c>
       <c r="C675" t="n">
@@ -18539,16 +18539,16 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-30</t>
+          <t>VB020303-01-02-M-25</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C676" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D676" t="inlineStr"/>
       <c r="E676" t="inlineStr"/>
@@ -18561,16 +18561,16 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-08</t>
+          <t>VB020105-01-03-L-15</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-PURPURA</t>
         </is>
       </c>
       <c r="C677" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D677" t="inlineStr"/>
       <c r="E677" t="inlineStr"/>
@@ -18583,16 +18583,16 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-15</t>
+          <t>VB020105-01-02-M-08</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
         </is>
       </c>
       <c r="C678" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D678" t="inlineStr"/>
       <c r="E678" t="inlineStr"/>
@@ -18627,16 +18627,16 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-30</t>
+          <t>VB020103-03-01-S-20</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C680" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D680" t="inlineStr"/>
       <c r="E680" t="inlineStr"/>
@@ -18693,16 +18693,16 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-14</t>
+          <t>VB020101-01-01-S-30</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PLUMAS</t>
         </is>
       </c>
       <c r="C683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
@@ -18715,16 +18715,16 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-30</t>
+          <t>VB020101-01-02-M-14</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C684" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D684" t="inlineStr"/>
       <c r="E684" t="inlineStr"/>
@@ -18737,16 +18737,16 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-30</t>
+          <t>VB020303-01-02-M-30</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-PLUMAS</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-PLUMAS</t>
         </is>
       </c>
       <c r="C685" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
@@ -18759,16 +18759,16 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>VB020103-03-01-S-20</t>
+          <t>VB020303-01-01-S-30</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-PLUMAS</t>
         </is>
       </c>
       <c r="C686" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D686" t="inlineStr"/>
       <c r="E686" t="inlineStr"/>
@@ -19029,16 +19029,16 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-05</t>
+          <t>VB020101-01-03-L-15</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PURPURA</t>
         </is>
       </c>
       <c r="C698" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D698" t="inlineStr"/>
       <c r="E698" t="inlineStr"/>
@@ -19051,16 +19051,16 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-03</t>
+          <t>VB020204-01-01-S-07</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL CIAN</t>
         </is>
       </c>
       <c r="C699" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D699" t="inlineStr"/>
       <c r="E699" t="inlineStr"/>
@@ -19073,12 +19073,12 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>VB0105-01-01-S-23</t>
+          <t>VB020204-01-02-M-13</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-S-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
         </is>
       </c>
       <c r="C700" t="n">
@@ -19095,16 +19095,16 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-08</t>
+          <t>VB020204-01-02-M-11</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C701" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D701" t="inlineStr"/>
       <c r="E701" t="inlineStr"/>
@@ -19117,12 +19117,12 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-02</t>
+          <t>VB020204-01-02-M-15</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-PURPURA</t>
         </is>
       </c>
       <c r="C702" t="n">
@@ -19139,16 +19139,16 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-11</t>
+          <t>VB020101-03-03-L-01</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-L-BLANCO</t>
         </is>
       </c>
       <c r="C703" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr"/>
@@ -19161,16 +19161,16 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-17</t>
+          <t>VB020101-03-01-S-01</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-S-BLANCO</t>
         </is>
       </c>
       <c r="C704" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D704" t="inlineStr"/>
       <c r="E704" t="inlineStr"/>
@@ -19183,12 +19183,12 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-01</t>
+          <t>VB0105-02-01-S-33</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-BLANCO</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-TIE DYE</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -19205,12 +19205,12 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>VB020103-02-02-M-03</t>
+          <t>VB0105-02-02-M-02</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-NEGRO</t>
         </is>
       </c>
       <c r="C706" t="n">
@@ -19227,12 +19227,12 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-03</t>
+          <t>VB0105-02-01-S-02</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-NEGRO</t>
         </is>
       </c>
       <c r="C707" t="n">
@@ -19249,16 +19249,16 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-05</t>
+          <t>VB0105-02-03-L-17</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AMARILLO NEON</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-ROSADO</t>
         </is>
       </c>
       <c r="C708" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D708" t="inlineStr"/>
       <c r="E708" t="inlineStr"/>
@@ -19271,16 +19271,16 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-26</t>
+          <t>VB0105-02-02-M-17</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-ROSADO</t>
         </is>
       </c>
       <c r="C709" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D709" t="inlineStr"/>
       <c r="E709" t="inlineStr"/>
@@ -19293,16 +19293,16 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-01</t>
+          <t>VB0105-02-01-S-17</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-BLANCO</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-ROSADO</t>
         </is>
       </c>
       <c r="C710" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D710" t="inlineStr"/>
       <c r="E710" t="inlineStr"/>
@@ -19315,12 +19315,12 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>VB0105-01-02-M-23</t>
+          <t>VB0105-02-03-L-18</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-VERDE MENTA</t>
         </is>
       </c>
       <c r="C711" t="n">
@@ -19337,12 +19337,12 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-11</t>
+          <t>VB0105-02-01-S-18</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-VERDE MENTA</t>
         </is>
       </c>
       <c r="C712" t="n">
@@ -19359,12 +19359,12 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-03</t>
+          <t>VB0105-02-02-M-18</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-VERDE MENTA</t>
         </is>
       </c>
       <c r="C713" t="n">
@@ -19381,12 +19381,12 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-16</t>
+          <t>VB0302-01-02-M-09</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
+          <t>PANTALON ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C714" t="n">
@@ -19403,12 +19403,12 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-15</t>
+          <t>VB0302-01-01-S-09</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
+          <t>PANTALON ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C715" t="n">
@@ -19425,16 +19425,16 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-32</t>
+          <t>VB0303-01-02-M-01</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
+          <t>SHORT ALTO-M-BLANCO</t>
         </is>
       </c>
       <c r="C716" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr"/>
@@ -19447,16 +19447,16 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-23</t>
+          <t>VB0303-01-01-S-02</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
+          <t>SHORT ALTO-S-NEGRO</t>
         </is>
       </c>
       <c r="C717" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D717" t="inlineStr"/>
       <c r="E717" t="inlineStr"/>
@@ -19469,12 +19469,12 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-23</t>
+          <t>VB0303-01-03-L-09</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
+          <t>SHORT ALTO-L-BEIGE</t>
         </is>
       </c>
       <c r="C718" t="n">
@@ -19491,16 +19491,16 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>VB0103-01-02-M-32</t>
+          <t>VB0303-01-02-M-09</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
+          <t>SHORT ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C719" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D719" t="inlineStr"/>
       <c r="E719" t="inlineStr"/>
@@ -19513,12 +19513,12 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-01</t>
+          <t>VB0303-01-01-S-09</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-BLANCO</t>
+          <t>SHORT ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C720" t="n">
@@ -19535,16 +19535,16 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-02</t>
+          <t>VB0302-01-03-L-09</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-NEGRO</t>
+          <t>PANTALON ALTO-L-BEIGE</t>
         </is>
       </c>
       <c r="C721" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D721" t="inlineStr"/>
       <c r="E721" t="inlineStr"/>
@@ -19557,16 +19557,16 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-08</t>
+          <t>VB020203-01-01-S-02</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-NEGRO</t>
         </is>
       </c>
       <c r="C722" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D722" t="inlineStr"/>
       <c r="E722" t="inlineStr"/>
@@ -19579,16 +19579,16 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-32</t>
+          <t>VB020101-02-03-L-01</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-BLANCO</t>
         </is>
       </c>
       <c r="C723" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="inlineStr"/>
@@ -19601,16 +19601,16 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-07</t>
+          <t>VB020101-01-03-L-03</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C724" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D724" t="inlineStr"/>
       <c r="E724" t="inlineStr"/>
@@ -19623,16 +19623,16 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-15</t>
+          <t>VB0105-01-01-S-23</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PURPURA</t>
+          <t>VB ENTERO TANGA-S-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C725" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D725" t="inlineStr"/>
       <c r="E725" t="inlineStr"/>
@@ -19645,16 +19645,16 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-13</t>
+          <t>VB020204-01-01-S-08</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
         </is>
       </c>
       <c r="C726" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr"/>
@@ -19667,16 +19667,16 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>VB020203-01-03-L-02</t>
+          <t>VB0302-01-03-L-02</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-NEGRO</t>
+          <t>PANTALON ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C727" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr"/>
@@ -19689,16 +19689,16 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-02</t>
+          <t>VB020204-01-01-S-11</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C728" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr"/>
@@ -19711,16 +19711,16 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>VB020203-01-02-M-17</t>
+          <t>VB020101-01-02-M-15</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PURPURA</t>
         </is>
       </c>
       <c r="C729" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D729" t="inlineStr"/>
       <c r="E729" t="inlineStr"/>
@@ -19733,12 +19733,12 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-02</t>
+          <t>VB020204-01-01-S-13</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
         </is>
       </c>
       <c r="C730" t="n">
@@ -19755,16 +19755,16 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-02</t>
+          <t>VB0302-01-03-L-01</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
+          <t>PANTALON ALTO-L-BLANCO</t>
         </is>
       </c>
       <c r="C731" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D731" t="inlineStr"/>
       <c r="E731" t="inlineStr"/>
@@ -19777,16 +19777,16 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-17</t>
+          <t>VB020103-02-03-L-17</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-ROSADO</t>
         </is>
       </c>
       <c r="C732" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D732" t="inlineStr"/>
       <c r="E732" t="inlineStr"/>
@@ -19799,12 +19799,12 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-01</t>
+          <t>VB020204-01-01-S-05</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C733" t="n">
@@ -19821,16 +19821,16 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-01</t>
+          <t>VB020303-01-01-S-26</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
         </is>
       </c>
       <c r="C734" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D734" t="inlineStr"/>
       <c r="E734" t="inlineStr"/>
@@ -19843,12 +19843,12 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-01</t>
+          <t>VB0302-01-01-S-01</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
+          <t>PANTALON ALTO-S-BLANCO</t>
         </is>
       </c>
       <c r="C735" t="n">
@@ -19865,16 +19865,16 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-11</t>
+          <t>VB020103-02-02-M-03</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C736" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D736" t="inlineStr"/>
       <c r="E736" t="inlineStr"/>
@@ -19887,12 +19887,12 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-15</t>
+          <t>VB0105-01-02-M-23</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PURPURA</t>
+          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C737" t="n">
@@ -19909,12 +19909,12 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-07</t>
+          <t>VB020204-01-03-L-11</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C738" t="n">
@@ -19931,16 +19931,16 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-13</t>
+          <t>VB020103-02-03-L-03</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C739" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D739" t="inlineStr"/>
       <c r="E739" t="inlineStr"/>
@@ -19953,16 +19953,16 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>VB020101-03-03-L-01</t>
+          <t>VB020103-02-01-S-03</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C740" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D740" t="inlineStr"/>
       <c r="E740" t="inlineStr"/>
@@ -19975,16 +19975,16 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>VB020101-03-01-S-01</t>
+          <t>VB020105-01-03-L-01</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
         </is>
       </c>
       <c r="C741" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D741" t="inlineStr"/>
       <c r="E741" t="inlineStr"/>
@@ -19997,16 +19997,16 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-15</t>
+          <t>VB020203-01-01-S-01</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-PURPURA</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
         </is>
       </c>
       <c r="C742" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D742" t="inlineStr"/>
       <c r="E742" t="inlineStr"/>
@@ -20019,16 +20019,16 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-33</t>
+          <t>VB020105-01-01-S-16</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-TIE DYE</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
         </is>
       </c>
       <c r="C743" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D743" t="inlineStr"/>
       <c r="E743" t="inlineStr"/>
@@ -20041,12 +20041,12 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-02</t>
+          <t>VB020204-01-03-L-15</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
         </is>
       </c>
       <c r="C744" t="n">
@@ -20063,12 +20063,12 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-02</t>
+          <t>VB0103-01-03-L-32</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-NEGRO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C745" t="n">
@@ -20085,12 +20085,12 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>VB0105-02-03-L-17</t>
+          <t>VB020202-01-03-L-23</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-ROSADO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C746" t="n">
@@ -20107,16 +20107,16 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-17</t>
+          <t>VB020202-01-01-S-23</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-ROSADO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C747" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D747" t="inlineStr"/>
       <c r="E747" t="inlineStr"/>
@@ -20129,12 +20129,12 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-17</t>
+          <t>VB0103-01-02-M-32</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-ROSADO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C748" t="n">
@@ -20151,12 +20151,12 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>VB0105-02-03-L-18</t>
+          <t>VB0302-01-02-M-01</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-VERDE MENTA</t>
+          <t>PANTALON ALTO-M-BLANCO</t>
         </is>
       </c>
       <c r="C749" t="n">
@@ -20173,12 +20173,12 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-18</t>
+          <t>VB0302-01-01-S-02</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-VERDE MENTA</t>
+          <t>PANTALON ALTO-S-NEGRO</t>
         </is>
       </c>
       <c r="C750" t="n">
@@ -20195,16 +20195,16 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-18</t>
+          <t>VB020204-01-03-L-08</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-VERDE MENTA</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
         </is>
       </c>
       <c r="C751" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D751" t="inlineStr"/>
       <c r="E751" t="inlineStr"/>
@@ -20217,16 +20217,16 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-09</t>
+          <t>VB0103-01-01-S-32</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-BEIGE</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C752" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D752" t="inlineStr"/>
       <c r="E752" t="inlineStr"/>
@@ -20239,12 +20239,12 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-09</t>
+          <t>VB020204-01-03-L-07</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-BEIGE</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C753" t="n">
@@ -20261,12 +20261,12 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>VB0303-01-02-M-01</t>
+          <t>VB020204-01-02-M-05</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>SHORT ALTO-M-BLANCO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C754" t="n">
@@ -20283,12 +20283,12 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>VB0303-01-01-S-02</t>
+          <t>VB020203-01-03-L-02</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>SHORT ALTO-S-NEGRO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-NEGRO</t>
         </is>
       </c>
       <c r="C755" t="n">
@@ -20305,12 +20305,12 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>VB0303-01-03-L-09</t>
+          <t>VB020202-01-03-L-02</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>SHORT ALTO-L-BEIGE</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C756" t="n">
@@ -20327,16 +20327,16 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>VB0303-01-02-M-09</t>
+          <t>VB020203-01-02-M-17</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>SHORT ALTO-M-BEIGE</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-ROSADO</t>
         </is>
       </c>
       <c r="C757" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D757" t="inlineStr"/>
       <c r="E757" t="inlineStr"/>
@@ -20349,12 +20349,12 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>VB0303-01-01-S-09</t>
+          <t>VB020202-01-01-S-02</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>SHORT ALTO-S-BEIGE</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
         </is>
       </c>
       <c r="C758" t="n">
@@ -20371,16 +20371,16 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-09</t>
+          <t>VB020202-01-02-M-02</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-BEIGE</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C759" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D759" t="inlineStr"/>
       <c r="E759" t="inlineStr"/>
@@ -20393,16 +20393,16 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-02</t>
+          <t>VB020203-01-01-S-17</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-NEGRO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-ROSADO</t>
         </is>
       </c>
       <c r="C760" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D760" t="inlineStr"/>
       <c r="E760" t="inlineStr"/>
@@ -20415,16 +20415,16 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>VB020101-02-03-L-01</t>
+          <t>VB020105-01-01-S-01</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
         </is>
       </c>
       <c r="C761" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D761" t="inlineStr"/>
       <c r="E761" t="inlineStr"/>
@@ -20437,16 +20437,16 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>VB020101-02-01-S-01</t>
+          <t>VB0104-01-03-L-09</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-S-BLANCO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-BEIGE</t>
         </is>
       </c>
       <c r="C762" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D762" t="inlineStr"/>
       <c r="E762" t="inlineStr"/>
@@ -20459,16 +20459,16 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>VB020101-02-03-L-17</t>
+          <t>VB0304-01-01-S-02</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-ROSADO</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-S-NEGRO</t>
         </is>
       </c>
       <c r="C763" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D763" t="inlineStr"/>
       <c r="E763" t="inlineStr"/>
@@ -20481,16 +20481,16 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>VB020101-02-02-M-17</t>
+          <t>VB0304-01-03-L-02</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-M-ROSADO</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-L-NEGRO</t>
         </is>
       </c>
       <c r="C764" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D764" t="inlineStr"/>
       <c r="E764" t="inlineStr"/>
@@ -20503,16 +20503,16 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>VB0301-01-04-U-09</t>
+          <t>VB0104-01-01-S-09</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>FALDA GAIA MACRAME-U-BEIGE</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-BEIGE</t>
         </is>
       </c>
       <c r="C765" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D765" t="inlineStr"/>
       <c r="E765" t="inlineStr"/>
@@ -20525,16 +20525,16 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>VB020101-02-03-L-18</t>
+          <t>VB0104-01-02-M-09</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-VERDE MENTA</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-BEIGE</t>
         </is>
       </c>
       <c r="C766" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D766" t="inlineStr"/>
       <c r="E766" t="inlineStr"/>
@@ -20547,12 +20547,12 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>VB020101-02-01-S-18</t>
+          <t>VB020103-05-02-M-36</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-S-VERDE MENTA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C767" t="n">
@@ -20569,16 +20569,16 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-06</t>
+          <t>VB020103-05-01-S-37</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AZUL CELESTE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C768" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D768" t="inlineStr"/>
       <c r="E768" t="inlineStr"/>
@@ -20591,16 +20591,16 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>VB0104-01-03-L-09</t>
+          <t>VB020103-05-03-L-37</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C769" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D769" t="inlineStr"/>
       <c r="E769" t="inlineStr"/>
@@ -20613,12 +20613,12 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>VB0304-01-01-S-02</t>
+          <t>VB020103-05-03-L-36</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C770" t="n">
@@ -20635,12 +20635,12 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-09</t>
+          <t>VB0304-01-02-M-02</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-BEIGE</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-M-NEGRO</t>
         </is>
       </c>
       <c r="C771" t="n">
@@ -20657,16 +20657,16 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-09</t>
+          <t>VB020303-01-03-L-34</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-BEIGE</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-FAUNA</t>
         </is>
       </c>
       <c r="C772" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D772" t="inlineStr"/>
       <c r="E772" t="inlineStr"/>
@@ -20679,16 +20679,16 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-09</t>
+          <t>VB020103-05-01-S-36</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C773" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D773" t="inlineStr"/>
       <c r="E773" t="inlineStr"/>
@@ -20701,16 +20701,16 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-19</t>
+          <t>VB0305-01-04-U-02</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-ANIMAL PRINT CAFÉ</t>
+          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-NEGRO</t>
         </is>
       </c>
       <c r="C774" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D774" t="inlineStr"/>
       <c r="E774" t="inlineStr"/>
@@ -20723,16 +20723,16 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-37</t>
+          <t>VB020303-01-01-S-34</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-AZUL BEBE-AGUAMARINA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-FAUNA</t>
         </is>
       </c>
       <c r="C775" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D775" t="inlineStr"/>
       <c r="E775" t="inlineStr"/>
@@ -20745,16 +20745,16 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-36</t>
+          <t>VB020303-01-02-M-34</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-FAUNA</t>
         </is>
       </c>
       <c r="C776" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D776" t="inlineStr"/>
       <c r="E776" t="inlineStr"/>
@@ -20767,16 +20767,16 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>VB0304-01-02-M-02</t>
+          <t>VB020101-01-04-U-14</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C777" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D777" t="inlineStr"/>
       <c r="E777" t="inlineStr"/>
@@ -20789,16 +20789,16 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>VB0304-01-03-L-02</t>
+          <t>VB020104-01-01-S-17</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-ROSADO</t>
         </is>
       </c>
       <c r="C778" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D778" t="inlineStr"/>
       <c r="E778" t="inlineStr"/>
@@ -20811,16 +20811,16 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>VB0104-01-01-S-09</t>
+          <t>VB020104-01-03-L-03</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C779" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D779" t="inlineStr"/>
       <c r="E779" t="inlineStr"/>
@@ -20833,16 +20833,16 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>VB0104-01-02-M-09</t>
+          <t>VB020101-01-04-U-17</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-ROSADO</t>
         </is>
       </c>
       <c r="C780" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D780" t="inlineStr"/>
       <c r="E780" t="inlineStr"/>
@@ -20855,16 +20855,16 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-34</t>
+          <t>VB020101-01-04-U-06</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-FAUNA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C781" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D781" t="inlineStr"/>
       <c r="E781" t="inlineStr"/>
@@ -20877,16 +20877,16 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-36</t>
+          <t>VB020104-01-01-S-03</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C782" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D782" t="inlineStr"/>
       <c r="E782" t="inlineStr"/>
@@ -20899,16 +20899,16 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>VB020103-05-02-M-36</t>
+          <t>VB020101-01-04-U-03</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-AGUAMARINA</t>
         </is>
       </c>
       <c r="C783" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D783" t="inlineStr"/>
       <c r="E783" t="inlineStr"/>
@@ -20921,16 +20921,16 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-37</t>
+          <t>VB0301-01-04-U-02</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-AZUL BEBE-AGUAMARINA</t>
+          <t>FALDA GAIA MACRAME-U-NEGRO</t>
         </is>
       </c>
       <c r="C784" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D784" t="inlineStr"/>
       <c r="E784" t="inlineStr"/>
@@ -20943,12 +20943,12 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-03</t>
+          <t>VB0305-01-04-U-09</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-AGUAMARINA</t>
+          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-BEIGE</t>
         </is>
       </c>
       <c r="C785" t="n">
@@ -20965,12 +20965,12 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>VB0301-01-04-U-02</t>
+          <t>VB0306-01-01-S-02</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>FALDA GAIA MACRAME-U-NEGRO</t>
+          <t>TOP BÁSICO LUISA-S-NEGRO</t>
         </is>
       </c>
       <c r="C786" t="n">
@@ -20987,16 +20987,16 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>VB0305-01-04-U-09</t>
+          <t>VB020103-04-01-S-09</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-BEIGE</t>
         </is>
       </c>
       <c r="C787" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D787" t="inlineStr"/>
       <c r="E787" t="inlineStr"/>
@@ -21009,16 +21009,16 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>VB0305-01-04-U-02</t>
+          <t>VB020103-04-02-M-09</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-BEIGE</t>
         </is>
       </c>
       <c r="C788" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D788" t="inlineStr"/>
       <c r="E788" t="inlineStr"/>
@@ -21031,12 +21031,12 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-34</t>
+          <t>VB020103-04-03-L-09</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-FAUNA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-BEIGE</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -21053,12 +21053,12 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-34</t>
+          <t>VB020103-04-01-S-19</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-FAUNA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C790" t="n">
@@ -21075,16 +21075,16 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-02</t>
+          <t>VB020103-04-02-M-19</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C791" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D791" t="inlineStr"/>
       <c r="E791" t="inlineStr"/>
@@ -21097,16 +21097,16 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-01</t>
+          <t>VB020103-04-01-S-28</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-PITON BEIGE</t>
         </is>
       </c>
       <c r="C792" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D792" t="inlineStr"/>
       <c r="E792" t="inlineStr"/>
@@ -21119,12 +21119,12 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-03</t>
+          <t>VB020103-04-02-M-28</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-PITON BEIGE</t>
         </is>
       </c>
       <c r="C793" t="n">
@@ -21141,16 +21141,16 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-03</t>
+          <t>VB020303-01-01-S-19</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C794" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D794" t="inlineStr"/>
       <c r="E794" t="inlineStr"/>
@@ -21163,16 +21163,16 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-02</t>
+          <t>VB020103-04-03-L-28</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-PITON BEIGE</t>
         </is>
       </c>
       <c r="C795" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D795" t="inlineStr"/>
       <c r="E795" t="inlineStr"/>
@@ -21185,16 +21185,16 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-19</t>
+          <t>VB020303-01-02-M-19</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C796" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D796" t="inlineStr"/>
       <c r="E796" t="inlineStr"/>
@@ -21207,16 +21207,16 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>VB020205-03-01-S-28</t>
+          <t>VB020303-01-03-L-19</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-PITON BEIGE</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C797" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D797" t="inlineStr"/>
       <c r="E797" t="inlineStr"/>
@@ -21229,16 +21229,16 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>VB020205-03-02-M-28</t>
+          <t>VB020205-03-01-S-28</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-PITON BEIGE</t>
         </is>
       </c>
       <c r="C798" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D798" t="inlineStr"/>
       <c r="E798" t="inlineStr"/>
@@ -21251,16 +21251,16 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>VB020205-03-03-L-28</t>
+          <t>VB020205-03-02-M-28</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-PITON BEIGE</t>
         </is>
       </c>
       <c r="C799" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D799" t="inlineStr"/>
       <c r="E799" t="inlineStr"/>
@@ -21273,16 +21273,16 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-19</t>
+          <t>VB020205-03-03-L-28</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-PITON BEIGE</t>
         </is>
       </c>
       <c r="C800" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D800" t="inlineStr"/>
       <c r="E800" t="inlineStr"/>
@@ -21295,16 +21295,16 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-28</t>
+          <t>VB020101-02-01-S-01</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-S-BLANCO</t>
         </is>
       </c>
       <c r="C801" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D801" t="inlineStr"/>
       <c r="E801" t="inlineStr"/>
@@ -21317,16 +21317,16 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-28</t>
+          <t>VB020101-02-03-L-17</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-ROSADO</t>
         </is>
       </c>
       <c r="C802" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D802" t="inlineStr"/>
       <c r="E802" t="inlineStr"/>
@@ -21339,16 +21339,16 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-19</t>
+          <t>VB020101-02-02-M-17</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-M-ROSADO</t>
         </is>
       </c>
       <c r="C803" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D803" t="inlineStr"/>
       <c r="E803" t="inlineStr"/>
@@ -21361,16 +21361,16 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-28</t>
+          <t>VB0301-01-04-U-09</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-PITON BEIGE</t>
+          <t>FALDA GAIA MACRAME-U-BEIGE</t>
         </is>
       </c>
       <c r="C804" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D804" t="inlineStr"/>
       <c r="E804" t="inlineStr"/>
@@ -21383,16 +21383,16 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-19</t>
+          <t>VB020104-01-03-L-06</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C805" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D805" t="inlineStr"/>
       <c r="E805" t="inlineStr"/>
@@ -21427,16 +21427,16 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-06</t>
+          <t>VB020101-02-03-L-18</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AZUL CELESTE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-VERDE MENTA</t>
         </is>
       </c>
       <c r="C807" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D807" t="inlineStr"/>
       <c r="E807" t="inlineStr"/>
@@ -21449,12 +21449,12 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-17</t>
+          <t>VB020101-02-01-S-18</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-S-VERDE MENTA</t>
         </is>
       </c>
       <c r="C808" t="n">
@@ -21471,16 +21471,16 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-01</t>
+          <t>VB020104-01-01-S-06</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C809" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D809" t="inlineStr"/>
       <c r="E809" t="inlineStr"/>
@@ -21493,16 +21493,16 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-14</t>
+          <t>VB020104-01-03-L-17</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-ROSADO</t>
         </is>
       </c>
       <c r="C810" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D810" t="inlineStr"/>
       <c r="E810" t="inlineStr"/>
@@ -21515,16 +21515,16 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-17</t>
+          <t>VB020101-01-04-U-01</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-BLANCO</t>
         </is>
       </c>
       <c r="C811" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D811" t="inlineStr"/>
       <c r="E811" t="inlineStr"/>
@@ -21537,16 +21537,16 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-03</t>
+          <t>VB0306-01-03-L-01</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AGUAMARINA</t>
+          <t>TOP BÁSICO LUISA-L-BLANCO</t>
         </is>
       </c>
       <c r="C812" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D812" t="inlineStr"/>
       <c r="E812" t="inlineStr"/>
@@ -21559,16 +21559,16 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-17</t>
+          <t>VB0306-01-02-M-03</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-ROSADO</t>
+          <t>TOP BÁSICO LUISA-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C813" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D813" t="inlineStr"/>
       <c r="E813" t="inlineStr"/>
@@ -21581,12 +21581,12 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-06</t>
+          <t>VB0306-01-01-S-03</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-AZUL CELESTE</t>
+          <t>TOP BÁSICO LUISA-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C814" t="n">
@@ -21603,16 +21603,16 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-03</t>
+          <t>VB0306-01-02-M-02</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AGUAMARINA</t>
+          <t>TOP BÁSICO LUISA-M-NEGRO</t>
         </is>
       </c>
       <c r="C815" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D815" t="inlineStr"/>
       <c r="E815" t="inlineStr"/>
@@ -21735,12 +21735,12 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-14</t>
+          <t>VB0306-01-01-S-14</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-PALO DE ROSA</t>
+          <t>TOP BÁSICO LUISA-S-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C821" t="n">
@@ -21757,12 +21757,12 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-14</t>
+          <t>VB0306-01-02-M-14</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-PALO DE ROSA</t>
+          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C822" t="n">
@@ -21779,12 +21779,12 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-14</t>
+          <t>VB0306-01-03-L-16</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
+          <t>TOP BÁSICO LUISA-L-ROJO</t>
         </is>
       </c>
       <c r="C823" t="n">
@@ -21801,12 +21801,12 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-16</t>
+          <t>VB0306-01-03-L-14</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-ROJO</t>
+          <t>TOP BÁSICO LUISA-L-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C824" t="n">
@@ -23397,19 +23397,19 @@
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>K010304</t>
+          <t>K010203</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>TONICO CAPILAR KABA 30ML</t>
+          <t>ACONDICIONADOR REPARACION SOS KABA</t>
         </is>
       </c>
       <c r="C893" t="n">
-        <v>3528</v>
+        <v>297</v>
       </c>
       <c r="D893" t="n">
-        <v>23981.2213740458</v>
+        <v>1166.908396946565</v>
       </c>
       <c r="E893" t="inlineStr">
         <is>
@@ -23425,19 +23425,19 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>K010203</t>
+          <t>K010304</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>ACONDICIONADOR REPARACION SOS KABA</t>
+          <t>TONICO CAPILAR KABA 30ML</t>
         </is>
       </c>
       <c r="C894" t="n">
-        <v>297</v>
+        <v>3528</v>
       </c>
       <c r="D894" t="n">
-        <v>1166.908396946565</v>
+        <v>23981.2213740458</v>
       </c>
       <c r="E894" t="inlineStr">
         <is>
@@ -24071,16 +24071,16 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-25</t>
+          <t>VB020105-01-01-S-08</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
         </is>
       </c>
       <c r="C918" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D918" t="inlineStr"/>
       <c r="E918" t="inlineStr"/>
@@ -24093,16 +24093,16 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-08</t>
+          <t>VB020303-01-03-L-25</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C919" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D919" t="inlineStr"/>
       <c r="E919" t="inlineStr"/>
@@ -24115,16 +24115,16 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>VB020103-03-01-S-32</t>
+          <t>VB020303-01-03-L-24</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C920" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D920" t="inlineStr"/>
       <c r="E920" t="inlineStr"/>
@@ -24137,16 +24137,16 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-13</t>
+          <t>VB020103-03-02-M-32</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C921" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="D921" t="inlineStr"/>
       <c r="E921" t="inlineStr"/>
@@ -24159,16 +24159,16 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-13</t>
+          <t>VB020103-03-01-S-32</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C922" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D922" t="inlineStr"/>
       <c r="E922" t="inlineStr"/>
@@ -24181,16 +24181,16 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>VB020103-01-02-M-26</t>
+          <t>VB020105-01-03-L-13</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
         </is>
       </c>
       <c r="C923" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D923" t="inlineStr"/>
       <c r="E923" t="inlineStr"/>
@@ -24203,16 +24203,16 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-24</t>
+          <t>VB020103-01-02-M-26</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
         </is>
       </c>
       <c r="C924" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D924" t="inlineStr"/>
       <c r="E924" t="inlineStr"/>
@@ -24225,16 +24225,16 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>VB020103-03-02-M-32</t>
+          <t>VB020105-01-02-M-13</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
         </is>
       </c>
       <c r="C925" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D925" t="inlineStr"/>
       <c r="E925" t="inlineStr"/>
@@ -24247,16 +24247,16 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-11</t>
+          <t>VB020303-01-03-L-30</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
         </is>
       </c>
       <c r="C926" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D926" t="inlineStr"/>
       <c r="E926" t="inlineStr"/>
@@ -24269,16 +24269,16 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>VB020103-03-03-L-20</t>
+          <t>VB020105-01-03-L-11</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C927" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D927" t="inlineStr"/>
       <c r="E927" t="inlineStr"/>
@@ -24291,16 +24291,16 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-24</t>
+          <t>VB020103-03-03-L-20</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C928" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D928" t="inlineStr"/>
       <c r="E928" t="inlineStr"/>
@@ -24313,16 +24313,16 @@
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-19</t>
+          <t>VB020303-01-01-S-24</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C929" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D929" t="inlineStr"/>
       <c r="E929" t="inlineStr"/>
@@ -24335,16 +24335,16 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-15</t>
+          <t>VB020101-01-02-M-19</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C930" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D930" t="inlineStr"/>
       <c r="E930" t="inlineStr"/>
@@ -24357,16 +24357,16 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-08</t>
+          <t>VB020105-01-01-S-15</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-PURPURA</t>
         </is>
       </c>
       <c r="C931" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D931" t="inlineStr"/>
       <c r="E931" t="inlineStr"/>
@@ -24379,16 +24379,16 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-05</t>
+          <t>VB020105-01-03-L-08</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AZUL REY</t>
         </is>
       </c>
       <c r="C932" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D932" t="inlineStr"/>
       <c r="E932" t="inlineStr"/>
@@ -24401,16 +24401,16 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-05</t>
+          <t>VB020105-01-02-M-05</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C933" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D933" t="inlineStr"/>
       <c r="E933" t="inlineStr"/>
@@ -24423,16 +24423,16 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>VB020103-03-03-L-32</t>
+          <t>VB020105-01-01-S-05</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C934" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D934" t="inlineStr"/>
       <c r="E934" t="inlineStr"/>
@@ -24445,16 +24445,16 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-11</t>
+          <t>VB020103-03-03-L-32</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C935" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="D935" t="inlineStr"/>
       <c r="E935" t="inlineStr"/>
@@ -24467,16 +24467,16 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-07</t>
+          <t>VB020105-01-02-M-11</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C936" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D936" t="inlineStr"/>
       <c r="E936" t="inlineStr"/>
@@ -24489,16 +24489,16 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-25</t>
+          <t>VB020105-01-03-L-07</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C937" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D937" t="inlineStr"/>
       <c r="E937" t="inlineStr"/>
@@ -24511,16 +24511,16 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-24</t>
+          <t>VB020303-01-01-S-25</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C938" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="D938" t="inlineStr"/>
       <c r="E938" t="inlineStr"/>
@@ -24533,16 +24533,16 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>VB0104-01-01-S-02</t>
+          <t>VB020303-01-02-M-24</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-NEGRO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C939" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D939" t="inlineStr"/>
       <c r="E939" t="inlineStr"/>
@@ -24555,12 +24555,12 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>VB0104-01-03-L-02</t>
+          <t>VB0104-01-01-S-02</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-NEGRO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-NEGRO</t>
         </is>
       </c>
       <c r="C940" t="n">
@@ -24577,16 +24577,16 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>VB0104-01-02-M-02</t>
+          <t>VB0104-01-03-L-02</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-NEGRO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-NEGRO</t>
         </is>
       </c>
       <c r="C941" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D941" t="inlineStr"/>
       <c r="E941" t="inlineStr"/>
@@ -24599,16 +24599,16 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-30</t>
+          <t>VB0104-01-02-M-02</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-NEGRO</t>
         </is>
       </c>
       <c r="C942" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D942" t="inlineStr"/>
       <c r="E942" t="inlineStr"/>
@@ -24643,16 +24643,16 @@
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-05</t>
+          <t>VB020103-03-01-S-20</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C944" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D944" t="inlineStr"/>
       <c r="E944" t="inlineStr"/>
@@ -24665,16 +24665,16 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-05</t>
+          <t>VB020105-01-03-L-05</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C945" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D945" t="inlineStr"/>
       <c r="E945" t="inlineStr"/>
@@ -24687,16 +24687,16 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>VB020103-03-01-S-20</t>
+          <t>VB020204-01-03-L-05</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C946" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D946" t="inlineStr"/>
       <c r="E946" t="inlineStr"/>
@@ -24797,16 +24797,16 @@
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-15</t>
+          <t>VB020105-01-02-M-08</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
         </is>
       </c>
       <c r="C951" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D951" t="inlineStr"/>
       <c r="E951" t="inlineStr"/>
@@ -24819,16 +24819,16 @@
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-15</t>
+          <t>VB020105-01-03-L-15</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-PURPURA</t>
         </is>
       </c>
       <c r="C952" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D952" t="inlineStr"/>
       <c r="E952" t="inlineStr"/>
@@ -24841,16 +24841,16 @@
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-08</t>
+          <t>VB020105-01-02-M-15</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-PURPURA</t>
         </is>
       </c>
       <c r="C953" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D953" t="inlineStr"/>
       <c r="E953" t="inlineStr"/>
@@ -24929,16 +24929,16 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>VB0301-01-04-U-09</t>
+          <t>VB020203-01-01-S-02</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>FALDA GAIA MACRAME-U-BEIGE</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-NEGRO</t>
         </is>
       </c>
       <c r="C957" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D957" t="inlineStr"/>
       <c r="E957" t="inlineStr"/>
@@ -24951,16 +24951,16 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-02</t>
+          <t>VB0302-01-03-L-09</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-NEGRO</t>
+          <t>PANTALON ALTO-L-BEIGE</t>
         </is>
       </c>
       <c r="C958" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D958" t="inlineStr"/>
       <c r="E958" t="inlineStr"/>
@@ -24973,16 +24973,16 @@
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-09</t>
+          <t>VB0303-01-01-S-09</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-BEIGE</t>
+          <t>SHORT ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C959" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D959" t="inlineStr"/>
       <c r="E959" t="inlineStr"/>
@@ -24995,16 +24995,16 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>VB0303-01-01-S-09</t>
+          <t>VB0303-01-02-M-09</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>SHORT ALTO-S-BEIGE</t>
+          <t>SHORT ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C960" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D960" t="inlineStr"/>
       <c r="E960" t="inlineStr"/>
@@ -25017,16 +25017,16 @@
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>VB0303-01-02-M-09</t>
+          <t>VB0303-01-03-L-09</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>SHORT ALTO-M-BEIGE</t>
+          <t>SHORT ALTO-L-BEIGE</t>
         </is>
       </c>
       <c r="C961" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D961" t="inlineStr"/>
       <c r="E961" t="inlineStr"/>
@@ -25039,16 +25039,16 @@
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>VB0303-01-03-L-09</t>
+          <t>VB0303-01-01-S-01</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>SHORT ALTO-L-BEIGE</t>
+          <t>SHORT ALTO-S-BLANCO</t>
         </is>
       </c>
       <c r="C962" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D962" t="inlineStr"/>
       <c r="E962" t="inlineStr"/>
@@ -25061,16 +25061,16 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>VB0303-01-01-S-01</t>
+          <t>VB0303-01-03-L-02</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>SHORT ALTO-S-BLANCO</t>
+          <t>SHORT ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C963" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D963" t="inlineStr"/>
       <c r="E963" t="inlineStr"/>
@@ -25083,16 +25083,16 @@
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>VB0303-01-03-L-02</t>
+          <t>VB0303-01-02-M-02</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>SHORT ALTO-L-NEGRO</t>
+          <t>SHORT ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C964" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D964" t="inlineStr"/>
       <c r="E964" t="inlineStr"/>
@@ -25105,16 +25105,16 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>VB0303-01-02-M-02</t>
+          <t>VB0303-01-02-M-01</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>SHORT ALTO-M-NEGRO</t>
+          <t>SHORT ALTO-M-BLANCO</t>
         </is>
       </c>
       <c r="C965" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D965" t="inlineStr"/>
       <c r="E965" t="inlineStr"/>
@@ -25127,16 +25127,16 @@
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>VB0303-01-02-M-01</t>
+          <t>VB0302-01-01-S-09</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>SHORT ALTO-M-BLANCO</t>
+          <t>PANTALON ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C966" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D966" t="inlineStr"/>
       <c r="E966" t="inlineStr"/>
@@ -25149,16 +25149,16 @@
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-09</t>
+          <t>VB0303-01-03-L-01</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-BEIGE</t>
+          <t>SHORT ALTO-L-BLANCO</t>
         </is>
       </c>
       <c r="C967" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D967" t="inlineStr"/>
       <c r="E967" t="inlineStr"/>
@@ -25171,16 +25171,16 @@
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>VB0303-01-03-L-01</t>
+          <t>VB0302-01-02-M-09</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>SHORT ALTO-L-BLANCO</t>
+          <t>PANTALON ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C968" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D968" t="inlineStr"/>
       <c r="E968" t="inlineStr"/>
@@ -25193,16 +25193,16 @@
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-09</t>
+          <t>VB0105-02-02-M-18</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-BEIGE</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-VERDE MENTA</t>
         </is>
       </c>
       <c r="C969" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D969" t="inlineStr"/>
       <c r="E969" t="inlineStr"/>
@@ -25215,16 +25215,16 @@
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-18</t>
+          <t>VB0105-02-01-S-18</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-VERDE MENTA</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-VERDE MENTA</t>
         </is>
       </c>
       <c r="C970" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D970" t="inlineStr"/>
       <c r="E970" t="inlineStr"/>
@@ -25237,16 +25237,16 @@
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-18</t>
+          <t>VB0105-02-03-L-18</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-VERDE MENTA</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-VERDE MENTA</t>
         </is>
       </c>
       <c r="C971" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D971" t="inlineStr"/>
       <c r="E971" t="inlineStr"/>
@@ -25259,16 +25259,16 @@
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>VB0105-02-03-L-18</t>
+          <t>VB0105-02-01-S-17</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-VERDE MENTA</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-ROSADO</t>
         </is>
       </c>
       <c r="C972" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D972" t="inlineStr"/>
       <c r="E972" t="inlineStr"/>
@@ -25281,16 +25281,16 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-17</t>
+          <t>VB0105-02-02-M-17</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-ROSADO</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-ROSADO</t>
         </is>
       </c>
       <c r="C973" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D973" t="inlineStr"/>
       <c r="E973" t="inlineStr"/>
@@ -25303,16 +25303,16 @@
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-17</t>
+          <t>VB0105-02-03-L-17</t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-ROSADO</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-ROSADO</t>
         </is>
       </c>
       <c r="C974" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D974" t="inlineStr"/>
       <c r="E974" t="inlineStr"/>
@@ -25325,16 +25325,16 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>VB0105-02-03-L-17</t>
+          <t>VB0105-02-01-S-02</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-ROSADO</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-NEGRO</t>
         </is>
       </c>
       <c r="C975" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D975" t="inlineStr"/>
       <c r="E975" t="inlineStr"/>
@@ -25347,16 +25347,16 @@
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-02</t>
+          <t>VB0105-02-02-M-02</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-NEGRO</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-NEGRO</t>
         </is>
       </c>
       <c r="C976" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D976" t="inlineStr"/>
       <c r="E976" t="inlineStr"/>
@@ -25369,16 +25369,16 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-02</t>
+          <t>VB0105-02-01-S-33</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-NEGRO</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-TIE DYE</t>
         </is>
       </c>
       <c r="C977" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D977" t="inlineStr"/>
       <c r="E977" t="inlineStr"/>
@@ -25391,16 +25391,16 @@
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-33</t>
+          <t>VB0105-02-03-L-02</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-TIE DYE</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-NEGRO</t>
         </is>
       </c>
       <c r="C978" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D978" t="inlineStr"/>
       <c r="E978" t="inlineStr"/>
@@ -25413,12 +25413,12 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>VB0105-02-03-L-02</t>
+          <t>VB0105-02-02-M-33</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-NEGRO</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-TIE DYE</t>
         </is>
       </c>
       <c r="C979" t="n">
@@ -25457,16 +25457,16 @@
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-33</t>
+          <t>VB020203-01-01-S-01</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-TIE DYE</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
         </is>
       </c>
       <c r="C981" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D981" t="inlineStr"/>
       <c r="E981" t="inlineStr"/>
@@ -25479,16 +25479,16 @@
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-16</t>
+          <t>VB020105-01-03-L-01</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
         </is>
       </c>
       <c r="C982" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D982" t="inlineStr"/>
       <c r="E982" t="inlineStr"/>
@@ -25501,16 +25501,16 @@
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-16</t>
+          <t>VB020105-01-02-M-01</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-BLANCO</t>
         </is>
       </c>
       <c r="C983" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D983" t="inlineStr"/>
       <c r="E983" t="inlineStr"/>
@@ -25545,16 +25545,16 @@
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-23</t>
+          <t>VB020105-01-03-L-16</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-ROJO</t>
         </is>
       </c>
       <c r="C985" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D985" t="inlineStr"/>
       <c r="E985" t="inlineStr"/>
@@ -25567,16 +25567,16 @@
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-32</t>
+          <t>VB020105-01-02-M-16</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-ROJO</t>
         </is>
       </c>
       <c r="C986" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D986" t="inlineStr"/>
       <c r="E986" t="inlineStr"/>
@@ -25589,16 +25589,16 @@
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-15</t>
+          <t>VB020204-01-03-L-07</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C987" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D987" t="inlineStr"/>
       <c r="E987" t="inlineStr"/>
@@ -25611,16 +25611,16 @@
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-13</t>
+          <t>VB020103-02-03-L-01</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-BLANCO</t>
         </is>
       </c>
       <c r="C988" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D988" t="inlineStr"/>
       <c r="E988" t="inlineStr"/>
@@ -25633,12 +25633,12 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-07</t>
+          <t>VB0103-01-01-S-32</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C989" t="n">
@@ -25655,16 +25655,16 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-01</t>
+          <t>VB020204-01-03-L-08</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
         </is>
       </c>
       <c r="C990" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D990" t="inlineStr"/>
       <c r="E990" t="inlineStr"/>
@@ -25677,16 +25677,16 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-32</t>
+          <t>VB0302-01-02-M-01</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
+          <t>PANTALON ALTO-M-BLANCO</t>
         </is>
       </c>
       <c r="C991" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D991" t="inlineStr"/>
       <c r="E991" t="inlineStr"/>
@@ -25699,16 +25699,16 @@
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-08</t>
+          <t>VB0103-01-02-M-32</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C992" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D992" t="inlineStr"/>
       <c r="E992" t="inlineStr"/>
@@ -25721,16 +25721,16 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-01</t>
+          <t>VB020202-01-01-S-23</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C993" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D993" t="inlineStr"/>
       <c r="E993" t="inlineStr"/>
@@ -25743,16 +25743,16 @@
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>VB0103-01-02-M-32</t>
+          <t>VB020202-01-03-L-23</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C994" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D994" t="inlineStr"/>
       <c r="E994" t="inlineStr"/>
@@ -25765,16 +25765,16 @@
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-23</t>
+          <t>VB0103-01-03-L-32</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C995" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D995" t="inlineStr"/>
       <c r="E995" t="inlineStr"/>
@@ -25787,16 +25787,16 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-01</t>
+          <t>VB020204-01-03-L-15</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
         </is>
       </c>
       <c r="C996" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D996" t="inlineStr"/>
       <c r="E996" t="inlineStr"/>
@@ -25809,16 +25809,16 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-01</t>
+          <t>VB020105-01-01-S-01</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
         </is>
       </c>
       <c r="C997" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D997" t="inlineStr"/>
       <c r="E997" t="inlineStr"/>
@@ -25831,16 +25831,16 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-01</t>
+          <t>VB020202-01-01-S-09</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C998" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D998" t="inlineStr"/>
       <c r="E998" t="inlineStr"/>
@@ -25853,16 +25853,16 @@
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-01</t>
+          <t>VB020202-01-02-M-02</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C999" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D999" t="inlineStr"/>
       <c r="E999" t="inlineStr"/>
@@ -25875,16 +25875,16 @@
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-09</t>
+          <t>VB020202-01-01-S-02</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-BEIGE</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
         </is>
       </c>
       <c r="C1000" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D1000" t="inlineStr"/>
       <c r="E1000" t="inlineStr"/>
@@ -25897,16 +25897,16 @@
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-02</t>
+          <t>VB020202-01-03-L-09</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-BEIGE</t>
         </is>
       </c>
       <c r="C1001" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D1001" t="inlineStr"/>
       <c r="E1001" t="inlineStr"/>
@@ -25919,16 +25919,16 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-02</t>
+          <t>VB020202-01-02-M-09</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C1002" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D1002" t="inlineStr"/>
       <c r="E1002" t="inlineStr"/>
@@ -25941,16 +25941,16 @@
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-09</t>
+          <t>VB020202-01-03-L-02</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-BEIGE</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C1003" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D1003" t="inlineStr"/>
       <c r="E1003" t="inlineStr"/>
@@ -25963,16 +25963,16 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-09</t>
+          <t>VB020203-01-03-L-02</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-BEIGE</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-NEGRO</t>
         </is>
       </c>
       <c r="C1004" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D1004" t="inlineStr"/>
       <c r="E1004" t="inlineStr"/>
@@ -25985,16 +25985,16 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-02</t>
+          <t>VB020204-01-02-M-05</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C1005" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D1005" t="inlineStr"/>
       <c r="E1005" t="inlineStr"/>
@@ -26007,16 +26007,16 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>VB020203-01-03-L-02</t>
+          <t>VB020202-01-03-L-07</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1006" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D1006" t="inlineStr"/>
       <c r="E1006" t="inlineStr"/>
@@ -26029,16 +26029,16 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-03</t>
+          <t>VB020202-01-02-M-07</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1007" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D1007" t="inlineStr"/>
       <c r="E1007" t="inlineStr"/>
@@ -26051,16 +26051,16 @@
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-11</t>
+          <t>VB020202-01-01-S-07</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1008" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D1008" t="inlineStr"/>
       <c r="E1008" t="inlineStr"/>
@@ -26073,16 +26073,16 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>VB0105-01-02-M-23</t>
+          <t>VB020101-01-01-S-15</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PURPURA</t>
         </is>
       </c>
       <c r="C1009" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D1009" t="inlineStr"/>
       <c r="E1009" t="inlineStr"/>
@@ -26095,16 +26095,16 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-01</t>
+          <t>VB020103-02-01-S-03</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1010" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D1010" t="inlineStr"/>
       <c r="E1010" t="inlineStr"/>
@@ -26117,16 +26117,16 @@
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-17</t>
+          <t>VB020103-02-01-S-02</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-NEGRO</t>
         </is>
       </c>
       <c r="C1011" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D1011" t="inlineStr"/>
       <c r="E1011" t="inlineStr"/>
@@ -26139,16 +26139,16 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-26</t>
+          <t>VB020103-02-03-L-03</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1012" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="D1012" t="inlineStr"/>
       <c r="E1012" t="inlineStr"/>
@@ -26161,16 +26161,16 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-05</t>
+          <t>VB020204-01-03-L-11</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C1013" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D1013" t="inlineStr"/>
       <c r="E1013" t="inlineStr"/>
@@ -26183,16 +26183,16 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>VB020103-02-02-M-17</t>
+          <t>VB0105-01-02-M-23</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-ROSADO</t>
+          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C1014" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D1014" t="inlineStr"/>
       <c r="E1014" t="inlineStr"/>
@@ -26205,16 +26205,16 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-03</t>
+          <t>VB020103-02-02-M-03</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1015" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D1015" t="inlineStr"/>
       <c r="E1015" t="inlineStr"/>
@@ -26227,16 +26227,16 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-02</t>
+          <t>VB0302-01-01-S-01</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-NEGRO</t>
+          <t>PANTALON ALTO-S-BLANCO</t>
         </is>
       </c>
       <c r="C1016" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D1016" t="inlineStr"/>
       <c r="E1016" t="inlineStr"/>
@@ -26249,16 +26249,16 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>VB020103-02-02-M-03</t>
+          <t>VB020103-02-01-S-17</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-ROSADO</t>
         </is>
       </c>
       <c r="C1017" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D1017" t="inlineStr"/>
       <c r="E1017" t="inlineStr"/>
@@ -26271,16 +26271,16 @@
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-01</t>
+          <t>VB020303-01-01-S-26</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-BLANCO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
         </is>
       </c>
       <c r="C1018" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="D1018" t="inlineStr"/>
       <c r="E1018" t="inlineStr"/>
@@ -26293,16 +26293,16 @@
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-02</t>
+          <t>VB020204-01-01-S-05</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C1019" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D1019" t="inlineStr"/>
       <c r="E1019" t="inlineStr"/>
@@ -26315,16 +26315,16 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-07</t>
+          <t>VB020103-02-02-M-17</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-ROSADO</t>
         </is>
       </c>
       <c r="C1020" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D1020" t="inlineStr"/>
       <c r="E1020" t="inlineStr"/>
@@ -26359,16 +26359,16 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-11</t>
+          <t>VB0302-01-03-L-01</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
+          <t>PANTALON ALTO-L-BLANCO</t>
         </is>
       </c>
       <c r="C1022" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D1022" t="inlineStr"/>
       <c r="E1022" t="inlineStr"/>
@@ -26381,16 +26381,16 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-02</t>
+          <t>VB020204-01-01-S-13</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
         </is>
       </c>
       <c r="C1023" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D1023" t="inlineStr"/>
       <c r="E1023" t="inlineStr"/>
@@ -26403,16 +26403,16 @@
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-08</t>
+          <t>VB020204-01-01-S-11</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C1024" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D1024" t="inlineStr"/>
       <c r="E1024" t="inlineStr"/>
@@ -26425,16 +26425,16 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>VB0105-01-01-S-23</t>
+          <t>VB0302-01-03-L-02</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-S-HOJAS AZUL</t>
+          <t>PANTALON ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C1025" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D1025" t="inlineStr"/>
       <c r="E1025" t="inlineStr"/>
@@ -26447,16 +26447,16 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-13</t>
+          <t>VB020204-01-01-S-08</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-NARANJA</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
         </is>
       </c>
       <c r="C1026" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D1026" t="inlineStr"/>
       <c r="E1026" t="inlineStr"/>
@@ -26469,16 +26469,16 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-26</t>
+          <t>VB020103-02-03-L-02</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-NEGRO</t>
         </is>
       </c>
       <c r="C1027" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D1027" t="inlineStr"/>
       <c r="E1027" t="inlineStr"/>
@@ -26491,16 +26491,16 @@
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-15</t>
+          <t>VB020204-01-02-M-07</t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-PURPURA</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1028" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D1028" t="inlineStr"/>
       <c r="E1028" t="inlineStr"/>
@@ -26513,16 +26513,16 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-05</t>
+          <t>VB0105-01-01-S-23</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AMARILLO NEON</t>
+          <t>VB ENTERO TANGA-S-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C1029" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1029" t="inlineStr"/>
       <c r="E1029" t="inlineStr"/>
@@ -26535,16 +26535,16 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-07</t>
+          <t>VB020204-01-03-L-13</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-NARANJA</t>
         </is>
       </c>
       <c r="C1030" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D1030" t="inlineStr"/>
       <c r="E1030" t="inlineStr"/>
@@ -26557,16 +26557,16 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-07</t>
+          <t>VB020303-01-03-L-26</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AZUL CIAN</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-MISTICO</t>
         </is>
       </c>
       <c r="C1031" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D1031" t="inlineStr"/>
       <c r="E1031" t="inlineStr"/>
@@ -26579,16 +26579,16 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-07</t>
+          <t>VB020204-01-01-S-15</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-PURPURA</t>
         </is>
       </c>
       <c r="C1032" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D1032" t="inlineStr"/>
       <c r="E1032" t="inlineStr"/>
@@ -26601,16 +26601,16 @@
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-15</t>
+          <t>VB0302-01-02-M-02</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PURPURA</t>
+          <t>PANTALON ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C1033" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1033" t="inlineStr"/>
       <c r="E1033" t="inlineStr"/>
@@ -26623,16 +26623,16 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-02</t>
+          <t>VB020203-01-02-M-01</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-NEGRO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-BLANCO</t>
         </is>
       </c>
       <c r="C1034" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1034" t="inlineStr"/>
       <c r="E1034" t="inlineStr"/>
@@ -26645,12 +26645,12 @@
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>VB020203-01-02-M-01</t>
+          <t>VB020203-01-03-L-01</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-BLANCO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-BLANCO</t>
         </is>
       </c>
       <c r="C1035" t="n">
@@ -26667,16 +26667,16 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>VB020203-01-03-L-01</t>
+          <t>VB0105-01-03-L-23</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-BLANCO</t>
+          <t>VB ENTERO TANGA-L-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C1036" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D1036" t="inlineStr"/>
       <c r="E1036" t="inlineStr"/>
@@ -26689,16 +26689,16 @@
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>VB0105-01-03-L-23</t>
+          <t>VB020202-01-02-M-23</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-L-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C1037" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D1037" t="inlineStr"/>
       <c r="E1037" t="inlineStr"/>
@@ -26711,16 +26711,16 @@
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-23</t>
+          <t>VB020204-01-02-M-08</t>
         </is>
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
         </is>
       </c>
       <c r="C1038" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D1038" t="inlineStr"/>
       <c r="E1038" t="inlineStr"/>
@@ -26733,16 +26733,16 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-08</t>
+          <t>VB020303-01-02-M-26</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-MISTICO</t>
         </is>
       </c>
       <c r="C1039" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D1039" t="inlineStr"/>
       <c r="E1039" t="inlineStr"/>
@@ -26755,16 +26755,16 @@
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-26</t>
+          <t>VB020103-04-03-L-19</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1040" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D1040" t="inlineStr"/>
       <c r="E1040" t="inlineStr"/>
@@ -26777,16 +26777,16 @@
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-19</t>
+          <t>VB020103-04-02-M-19</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1041" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D1041" t="inlineStr"/>
       <c r="E1041" t="inlineStr"/>
@@ -26799,16 +26799,16 @@
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-19</t>
+          <t>VB020103-04-02-M-28</t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-PITON BEIGE</t>
         </is>
       </c>
       <c r="C1042" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1042" t="inlineStr"/>
       <c r="E1042" t="inlineStr"/>
@@ -26821,16 +26821,16 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-28</t>
+          <t>VB020103-04-01-S-28</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-PITON BEIGE</t>
         </is>
       </c>
       <c r="C1043" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D1043" t="inlineStr"/>
       <c r="E1043" t="inlineStr"/>
@@ -26843,16 +26843,16 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-28</t>
+          <t>VB020103-04-01-S-19</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1044" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D1044" t="inlineStr"/>
       <c r="E1044" t="inlineStr"/>
@@ -26865,16 +26865,16 @@
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-19</t>
+          <t>VB020103-04-03-L-09</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-BEIGE</t>
         </is>
       </c>
       <c r="C1045" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D1045" t="inlineStr"/>
       <c r="E1045" t="inlineStr"/>
@@ -26887,16 +26887,16 @@
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-28</t>
+          <t>VB020103-04-02-M-09</t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-BEIGE</t>
         </is>
       </c>
       <c r="C1046" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D1046" t="inlineStr"/>
       <c r="E1046" t="inlineStr"/>
@@ -26909,16 +26909,16 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-19</t>
+          <t>VB020103-04-01-S-09</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-BEIGE</t>
         </is>
       </c>
       <c r="C1047" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D1047" t="inlineStr"/>
       <c r="E1047" t="inlineStr"/>
@@ -27019,16 +27019,16 @@
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-02</t>
+          <t>VB020303-01-02-M-19</t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-NEGRO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1052" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D1052" t="inlineStr"/>
       <c r="E1052" t="inlineStr"/>
@@ -27041,16 +27041,16 @@
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-03</t>
+          <t>VB020103-04-03-L-28</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-PITON BEIGE</t>
         </is>
       </c>
       <c r="C1053" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D1053" t="inlineStr"/>
       <c r="E1053" t="inlineStr"/>
@@ -27063,16 +27063,16 @@
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-03</t>
+          <t>VB020303-01-01-S-19</t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-AGUAMARINA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1054" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D1054" t="inlineStr"/>
       <c r="E1054" t="inlineStr"/>
@@ -27085,16 +27085,16 @@
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-01</t>
+          <t>VB0306-01-01-S-02</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-BLANCO</t>
+          <t>TOP BÁSICO LUISA-S-NEGRO</t>
         </is>
       </c>
       <c r="C1055" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D1055" t="inlineStr"/>
       <c r="E1055" t="inlineStr"/>
@@ -27107,16 +27107,16 @@
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-02</t>
+          <t>VB0104-01-03-L-09</t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-NEGRO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-BEIGE</t>
         </is>
       </c>
       <c r="C1056" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D1056" t="inlineStr"/>
       <c r="E1056" t="inlineStr"/>
@@ -27129,16 +27129,16 @@
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>VB0104-01-03-L-09</t>
+          <t>VB0104-01-02-M-09</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-BEIGE</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-BEIGE</t>
         </is>
       </c>
       <c r="C1057" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D1057" t="inlineStr"/>
       <c r="E1057" t="inlineStr"/>
@@ -27151,16 +27151,16 @@
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-19</t>
+          <t>VB0104-01-01-S-09</t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-BEIGE</t>
         </is>
       </c>
       <c r="C1058" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D1058" t="inlineStr"/>
       <c r="E1058" t="inlineStr"/>
@@ -27173,16 +27173,16 @@
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-09</t>
+          <t>VB0304-01-03-L-02</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-BEIGE</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-L-NEGRO</t>
         </is>
       </c>
       <c r="C1059" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D1059" t="inlineStr"/>
       <c r="E1059" t="inlineStr"/>
@@ -27195,16 +27195,16 @@
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-09</t>
+          <t>VB0304-01-02-M-02</t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-BEIGE</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-M-NEGRO</t>
         </is>
       </c>
       <c r="C1060" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D1060" t="inlineStr"/>
       <c r="E1060" t="inlineStr"/>
@@ -27217,16 +27217,16 @@
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-09</t>
+          <t>VB020103-05-03-L-36</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C1061" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D1061" t="inlineStr"/>
       <c r="E1061" t="inlineStr"/>
@@ -27239,16 +27239,16 @@
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>VB0104-01-02-M-09</t>
+          <t>VB020103-05-03-L-37</t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1062" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D1062" t="inlineStr"/>
       <c r="E1062" t="inlineStr"/>
@@ -27261,16 +27261,16 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>VB0104-01-01-S-09</t>
+          <t>VB0307-01-04-U-13</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-BEIGE</t>
+          <t>PAÑOLETA-U-NARANJA</t>
         </is>
       </c>
       <c r="C1063" t="n">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="D1063" t="inlineStr"/>
       <c r="E1063" t="inlineStr"/>
@@ -27283,16 +27283,16 @@
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>VB0304-01-03-L-02</t>
+          <t>VB020103-05-01-S-37</t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1064" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D1064" t="inlineStr"/>
       <c r="E1064" t="inlineStr"/>
@@ -27305,16 +27305,16 @@
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>VB0304-01-02-M-02</t>
+          <t>VB020103-05-02-M-37</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1065" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D1065" t="inlineStr"/>
       <c r="E1065" t="inlineStr"/>
@@ -27327,16 +27327,16 @@
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-36</t>
+          <t>VB020103-05-02-M-36</t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C1066" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D1066" t="inlineStr"/>
       <c r="E1066" t="inlineStr"/>
@@ -27349,16 +27349,16 @@
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-37</t>
+          <t>VB0304-01-03-L-09</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-AZUL BEBE-AGUAMARINA</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-L-BEIGE</t>
         </is>
       </c>
       <c r="C1067" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D1067" t="inlineStr"/>
       <c r="E1067" t="inlineStr"/>
@@ -27371,16 +27371,16 @@
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>VB0307-01-04-U-13</t>
+          <t>VB0305-01-04-U-09</t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>PAÑOLETA-U-NARANJA</t>
+          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-BEIGE</t>
         </is>
       </c>
       <c r="C1068" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="D1068" t="inlineStr"/>
       <c r="E1068" t="inlineStr"/>
@@ -27393,16 +27393,16 @@
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-34</t>
+          <t>VB020104-01-02-M-03</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-FAUNA</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1069" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D1069" t="inlineStr"/>
       <c r="E1069" t="inlineStr"/>
@@ -27415,16 +27415,16 @@
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-34</t>
+          <t>VB0301-01-04-U-02</t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-FAUNA</t>
+          <t>FALDA GAIA MACRAME-U-NEGRO</t>
         </is>
       </c>
       <c r="C1070" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D1070" t="inlineStr"/>
       <c r="E1070" t="inlineStr"/>
@@ -27437,16 +27437,16 @@
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>VB0305-01-04-U-02</t>
+          <t>VB020104-01-01-S-03</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1071" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D1071" t="inlineStr"/>
       <c r="E1071" t="inlineStr"/>
@@ -27459,16 +27459,16 @@
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>VB0304-01-01-S-09</t>
+          <t>VB020104-01-03-L-03</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-S-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1072" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D1072" t="inlineStr"/>
       <c r="E1072" t="inlineStr"/>
@@ -27481,16 +27481,16 @@
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>VB0304-01-02-M-09</t>
+          <t>VB020104-01-01-S-17</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-M-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-ROSADO</t>
         </is>
       </c>
       <c r="C1073" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D1073" t="inlineStr"/>
       <c r="E1073" t="inlineStr"/>
@@ -27503,12 +27503,12 @@
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>VB0305-01-04-U-09</t>
+          <t>VB020303-01-02-M-34</t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-BEIGE</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-FAUNA</t>
         </is>
       </c>
       <c r="C1074" t="n">
@@ -27525,16 +27525,16 @@
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>VB020104-01-02-M-03</t>
+          <t>VB020303-01-01-S-34</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-M-AGUAMARINA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-FAUNA</t>
         </is>
       </c>
       <c r="C1075" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D1075" t="inlineStr"/>
       <c r="E1075" t="inlineStr"/>
@@ -27547,16 +27547,16 @@
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>VB0301-01-04-U-02</t>
+          <t>VB0305-01-04-U-02</t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>FALDA GAIA MACRAME-U-NEGRO</t>
+          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-NEGRO</t>
         </is>
       </c>
       <c r="C1076" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D1076" t="inlineStr"/>
       <c r="E1076" t="inlineStr"/>
@@ -27569,16 +27569,16 @@
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-37</t>
+          <t>VB0304-01-01-S-09</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-AZUL BEBE-AGUAMARINA</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-S-BEIGE</t>
         </is>
       </c>
       <c r="C1077" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D1077" t="inlineStr"/>
       <c r="E1077" t="inlineStr"/>
@@ -27591,16 +27591,16 @@
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>VB020103-05-02-M-37</t>
+          <t>VB0304-01-02-M-09</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-AZUL BEBE-AGUAMARINA</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-M-BEIGE</t>
         </is>
       </c>
       <c r="C1078" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D1078" t="inlineStr"/>
       <c r="E1078" t="inlineStr"/>
@@ -27613,16 +27613,16 @@
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>VB020103-05-02-M-36</t>
+          <t>VB020103-05-01-S-36</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C1079" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D1079" t="inlineStr"/>
       <c r="E1079" t="inlineStr"/>
@@ -27635,16 +27635,16 @@
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>VB0304-01-03-L-09</t>
+          <t>VB020103-05-01-S-35</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-L-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-NEGRO-BLANCO HUESO</t>
         </is>
       </c>
       <c r="C1080" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D1080" t="inlineStr"/>
       <c r="E1080" t="inlineStr"/>
@@ -27657,16 +27657,16 @@
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-36</t>
+          <t>VB020103-05-02-M-35</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-NEGRO-BLANCO HUESO</t>
         </is>
       </c>
       <c r="C1081" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D1081" t="inlineStr"/>
       <c r="E1081" t="inlineStr"/>
@@ -27679,16 +27679,16 @@
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-35</t>
+          <t>VB020103-05-03-L-35</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-NEGRO-BLANCO HUESO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-NEGRO-BLANCO HUESO</t>
         </is>
       </c>
       <c r="C1082" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D1082" t="inlineStr"/>
       <c r="E1082" t="inlineStr"/>
@@ -27701,16 +27701,16 @@
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>VB020103-05-02-M-35</t>
+          <t>VB020303-01-03-L-34</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-NEGRO-BLANCO HUESO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-FAUNA</t>
         </is>
       </c>
       <c r="C1083" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D1083" t="inlineStr"/>
       <c r="E1083" t="inlineStr"/>
@@ -27723,16 +27723,16 @@
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-35</t>
+          <t>VB020104-01-02-M-17</t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-NEGRO-BLANCO HUESO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-M-ROSADO</t>
         </is>
       </c>
       <c r="C1084" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D1084" t="inlineStr"/>
       <c r="E1084" t="inlineStr"/>
@@ -27745,16 +27745,16 @@
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-34</t>
+          <t>VB020104-01-03-L-17</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-FAUNA</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-ROSADO</t>
         </is>
       </c>
       <c r="C1085" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D1085" t="inlineStr"/>
       <c r="E1085" t="inlineStr"/>
@@ -27767,12 +27767,12 @@
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-03</t>
+          <t>VB020104-01-01-S-06</t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C1086" t="n">
@@ -27789,16 +27789,16 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-03</t>
+          <t>VB020104-01-02-M-06</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-M-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C1087" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D1087" t="inlineStr"/>
       <c r="E1087" t="inlineStr"/>
@@ -27811,16 +27811,16 @@
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-17</t>
+          <t>VB0301-01-04-U-09</t>
         </is>
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-ROSADO</t>
+          <t>FALDA GAIA MACRAME-U-BEIGE</t>
         </is>
       </c>
       <c r="C1088" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D1088" t="inlineStr"/>
       <c r="E1088" t="inlineStr"/>
@@ -27833,16 +27833,16 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>VB020104-01-02-M-17</t>
+          <t>VB0306-01-03-L-02</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-M-ROSADO</t>
+          <t>TOP BÁSICO LUISA-L-NEGRO</t>
         </is>
       </c>
       <c r="C1089" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D1089" t="inlineStr"/>
       <c r="E1089" t="inlineStr"/>
@@ -27855,16 +27855,16 @@
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-17</t>
+          <t>VB0306-01-01-S-01</t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-ROSADO</t>
+          <t>TOP BÁSICO LUISA-S-BLANCO</t>
         </is>
       </c>
       <c r="C1090" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D1090" t="inlineStr"/>
       <c r="E1090" t="inlineStr"/>
@@ -27877,16 +27877,16 @@
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-06</t>
+          <t>VB0306-01-03-L-03</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AZUL CELESTE</t>
+          <t>TOP BÁSICO LUISA-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1091" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D1091" t="inlineStr"/>
       <c r="E1091" t="inlineStr"/>
@@ -27899,16 +27899,16 @@
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>VB020104-01-02-M-06</t>
+          <t>VB0306-01-02-M-01</t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-M-AZUL CELESTE</t>
+          <t>TOP BÁSICO LUISA-M-BLANCO</t>
         </is>
       </c>
       <c r="C1092" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D1092" t="inlineStr"/>
       <c r="E1092" t="inlineStr"/>
@@ -27921,16 +27921,16 @@
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-02</t>
+          <t>VB0306-01-02-M-02</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-NEGRO</t>
+          <t>TOP BÁSICO LUISA-M-NEGRO</t>
         </is>
       </c>
       <c r="C1093" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D1093" t="inlineStr"/>
       <c r="E1093" t="inlineStr"/>
@@ -27943,16 +27943,16 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-01</t>
+          <t>VB0306-01-01-S-03</t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-BLANCO</t>
+          <t>TOP BÁSICO LUISA-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1094" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D1094" t="inlineStr"/>
       <c r="E1094" t="inlineStr"/>
@@ -27965,16 +27965,16 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-03</t>
+          <t>VB0306-01-02-M-03</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-AGUAMARINA</t>
+          <t>TOP BÁSICO LUISA-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1095" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D1095" t="inlineStr"/>
       <c r="E1095" t="inlineStr"/>
@@ -27987,16 +27987,16 @@
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-01</t>
+          <t>VB0306-01-03-L-01</t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-BLANCO</t>
+          <t>TOP BÁSICO LUISA-L-BLANCO</t>
         </is>
       </c>
       <c r="C1096" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D1096" t="inlineStr"/>
       <c r="E1096" t="inlineStr"/>
@@ -28009,16 +28009,16 @@
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-16</t>
+          <t>VB0306-01-03-L-14</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-ROJO</t>
+          <t>TOP BÁSICO LUISA-L-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C1097" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1097" t="inlineStr"/>
       <c r="E1097" t="inlineStr"/>
@@ -28097,16 +28097,16 @@
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-14</t>
+          <t>VB0306-01-01-S-16</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-PALO DE ROSA</t>
+          <t>TOP BÁSICO LUISA-S-ROJO</t>
         </is>
       </c>
       <c r="C1101" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D1101" t="inlineStr"/>
       <c r="E1101" t="inlineStr"/>
@@ -28119,16 +28119,16 @@
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-16</t>
+          <t>VB0306-01-02-M-16</t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-ROJO</t>
+          <t>TOP BÁSICO LUISA-M-ROJO</t>
         </is>
       </c>
       <c r="C1102" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D1102" t="inlineStr"/>
       <c r="E1102" t="inlineStr"/>
@@ -39014,7 +39014,7 @@
         </is>
       </c>
       <c r="C1529" t="n">
-        <v>28215</v>
+        <v>28035</v>
       </c>
       <c r="D1529" t="inlineStr"/>
       <c r="E1529" t="inlineStr">
@@ -40314,7 +40314,7 @@
         </is>
       </c>
       <c r="C1579" t="n">
-        <v>16988</v>
+        <v>13588</v>
       </c>
       <c r="D1579" t="inlineStr"/>
       <c r="E1579" t="inlineStr">
@@ -42676,7 +42676,7 @@
         </is>
       </c>
       <c r="C1670" t="n">
-        <v>5517</v>
+        <v>3767</v>
       </c>
       <c r="D1670" t="inlineStr"/>
       <c r="E1670" t="inlineStr">

--- a/inventario_operaciones.xlsx
+++ b/inventario_operaciones.xlsx
@@ -535,19 +535,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KM041303</t>
+          <t>KM041105</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DROPS HONEY GOLD</t>
+          <t>CORRECTOR DE OJERAS MACADAMIA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>584</v>
+        <v>726</v>
       </c>
       <c r="D5" t="n">
-        <v>531.7557251908397</v>
+        <v>347.2900763358779</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -563,19 +563,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KM041204</t>
+          <t>KM041103</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LIP GLOSS VOLUMINIZANTE GOLDEN HOUR</t>
+          <t>CORRECTOR DE OJERAS AVELLANA</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>678</v>
+        <v>616</v>
       </c>
       <c r="D6" t="n">
-        <v>166.2595419847328</v>
+        <v>423.8931297709924</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -591,19 +591,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KM041105</t>
+          <t>R010303</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS MACADAMIA</t>
+          <t>SACHET BOMBA ANTIGRASA LA RECETA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>726</v>
+        <v>587</v>
       </c>
       <c r="D7" t="n">
-        <v>347.2900763358779</v>
+        <v>180</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KM041103</t>
+          <t>KM041202</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS AVELLANA</t>
+          <t>LIP GLOSS GOLDEN HOUR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>616</v>
+        <v>655</v>
       </c>
       <c r="D8" t="n">
-        <v>423.8931297709924</v>
+        <v>171.412213740458</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -647,19 +647,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R010303</t>
+          <t>KM041303</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SACHET BOMBA ANTIGRASA LA RECETA</t>
+          <t>DROPS HONEY GOLD</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D9" t="n">
-        <v>180</v>
+        <v>531.7557251908397</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -675,19 +675,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KM041202</t>
+          <t>KM041204</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LIP GLOSS GOLDEN HOUR</t>
+          <t>LIP GLOSS VOLUMINIZANTE GOLDEN HOUR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>655</v>
+        <v>678</v>
       </c>
       <c r="D10" t="n">
-        <v>171.412213740458</v>
+        <v>166.2595419847328</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -815,19 +815,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D031009</t>
+          <t>K010402</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ESPUMA AUTOBRONCEADORA TON OSCURO DLUCHI</t>
+          <t>PERFUME PARA EL CABELLO CONFIDENTE KABA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>143</v>
+        <v>322</v>
       </c>
       <c r="D15" t="n">
-        <v>666.412213740458</v>
+        <v>1163.473282442748</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -843,19 +843,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K010402</t>
+          <t>D030601</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO CONFIDENTE KABA</t>
+          <t>FRESHING POP AFTER SUN DLUCHI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>322</v>
+        <v>144</v>
       </c>
       <c r="D16" t="n">
-        <v>1163.473282442748</v>
+        <v>267.9389312977099</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -871,19 +871,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D030601</t>
+          <t>K010403</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FRESHING POP AFTER SUN DLUCHI</t>
+          <t>PERFUME PARA EL CABELLO SOÑADORA KABA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>144</v>
+        <v>280</v>
       </c>
       <c r="D17" t="n">
-        <v>267.9389312977099</v>
+        <v>1100.954198473282</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -899,19 +899,19 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K010403</t>
+          <t>D031009</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO SOÑADORA KABA</t>
+          <t>ESPUMA AUTOBRONCEADORA TON OSCURO DLUCHI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>280</v>
+        <v>143</v>
       </c>
       <c r="D18" t="n">
-        <v>1100.954198473282</v>
+        <v>666.412213740458</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1207,19 +1207,19 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>D031008</t>
+          <t>K020602</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ESPUMA AUTOBRONCEADORA TON MEDIO DLUCHI</t>
+          <t>CREMA FACIAL TENSORA KABA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="D29" t="n">
-        <v>1374.389312977099</v>
+        <v>914.0839694656488</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1235,19 +1235,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>K020602</t>
+          <t>D031008</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CREMA FACIAL TENSORA KABA</t>
+          <t>ESPUMA AUTOBRONCEADORA TON MEDIO DLUCHI</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>134</v>
+        <v>215</v>
       </c>
       <c r="D30" t="n">
-        <v>914.0839694656488</v>
+        <v>1374.389312977099</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1347,19 +1347,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>K010404</t>
+          <t>K020503</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO ARRIESGADA KABA</t>
+          <t>MASCARILLA FACIAL DE BANANO KABA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>292</v>
+        <v>180</v>
       </c>
       <c r="D34" t="n">
-        <v>1492.557251908397</v>
+        <v>85.87786259541986</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1375,19 +1375,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>K020503</t>
+          <t>K020603</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MASCARILLA FACIAL DE BANANO KABA</t>
+          <t>TONICO DE ROSAS KABA</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>180</v>
+        <v>211</v>
       </c>
       <c r="D35" t="n">
-        <v>85.87786259541986</v>
+        <v>975.2290076335877</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1403,19 +1403,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>K020603</t>
+          <t>K010301</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TONICO DE ROSAS KABA</t>
+          <t>TRATAMIENTO CAPILAR REPOLARIZADOR KABA</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>211</v>
+        <v>425</v>
       </c>
       <c r="D36" t="n">
-        <v>975.2290076335877</v>
+        <v>8401.603053435116</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1431,19 +1431,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>K010301</t>
+          <t>K010404</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TRATAMIENTO CAPILAR REPOLARIZADOR KABA</t>
+          <t>PERFUME PARA EL CABELLO ARRIESGADA KABA</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>425</v>
+        <v>292</v>
       </c>
       <c r="D37" t="n">
-        <v>8401.603053435116</v>
+        <v>1492.557251908397</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1655,19 +1655,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KM041104</t>
+          <t>K020506</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS CARAMELO</t>
+          <t>MASCARILLA FACIAL DE CHOCOLATE KABA</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>618</v>
+        <v>192</v>
       </c>
       <c r="D45" t="n">
-        <v>217.4427480916031</v>
+        <v>138.7786259541985</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1683,19 +1683,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KM041302</t>
+          <t>KM041304</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE SILVER</t>
+          <t>DROPS PINK GOLD</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>699</v>
+        <v>742</v>
       </c>
       <c r="D46" t="n">
-        <v>192.7099236641222</v>
+        <v>178.6259541984733</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1711,19 +1711,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KM041301</t>
+          <t>KM041104</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE GOLD</t>
+          <t>CORRECTOR DE OJERAS CARAMELO</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>425</v>
+        <v>618</v>
       </c>
       <c r="D47" t="n">
-        <v>760.8778625954199</v>
+        <v>217.4427480916031</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1739,19 +1739,19 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>K020506</t>
+          <t>KM041302</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MASCARILLA FACIAL DE CHOCOLATE KABA</t>
+          <t>DROPS CHAMPAGNE SILVER</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>192</v>
+        <v>699</v>
       </c>
       <c r="D48" t="n">
-        <v>138.7786259541985</v>
+        <v>192.7099236641222</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1767,19 +1767,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KM041304</t>
+          <t>KM041301</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DROPS PINK GOLD</t>
+          <t>DROPS CHAMPAGNE GOLD</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>742</v>
+        <v>425</v>
       </c>
       <c r="D49" t="n">
-        <v>178.6259541984733</v>
+        <v>760.8778625954199</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1823,19 +1823,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KM041106</t>
+          <t>D031004</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS MIEL</t>
+          <t>MINI BRONCEADOR ZANAHORIA CANELA DLUCHI</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>665</v>
+        <v>607</v>
       </c>
       <c r="D51" t="n">
-        <v>1522.786259541985</v>
+        <v>4990.534351145038</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1851,19 +1851,19 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KM041308</t>
+          <t>KM041305</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ILUMINADOR PRETTY GIRL</t>
+          <t>ILUMINADOR LIGHTS UP</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>741</v>
+        <v>799</v>
       </c>
       <c r="D52" t="n">
-        <v>148.3969465648855</v>
+        <v>162.824427480916</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1879,19 +1879,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>O030501</t>
+          <t>KM041307</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MANTEQUILLA EXFOLIANTE OMG</t>
+          <t>ILUMINADOR LIQUIDO DAILY SHINE</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>96</v>
+        <v>665</v>
       </c>
       <c r="D53" t="n">
-        <v>4206.641221374046</v>
+        <v>101.6793893129771</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1907,19 +1907,19 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>D031004</t>
+          <t>KM041106</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MINI BRONCEADOR ZANAHORIA CANELA DLUCHI</t>
+          <t>CORRECTOR DE OJERAS MIEL</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>607</v>
+        <v>665</v>
       </c>
       <c r="D54" t="n">
-        <v>4990.534351145038</v>
+        <v>1522.786259541985</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1935,19 +1935,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>KM041305</t>
+          <t>KM041308</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ILUMINADOR LIGHTS UP</t>
+          <t>ILUMINADOR PRETTY GIRL</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>799</v>
+        <v>741</v>
       </c>
       <c r="D55" t="n">
-        <v>162.824427480916</v>
+        <v>148.3969465648855</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1963,19 +1963,19 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>KM041307</t>
+          <t>O030501</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ILUMINADOR LIQUIDO DAILY SHINE</t>
+          <t>MANTEQUILLA EXFOLIANTE OMG</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>665</v>
+        <v>96</v>
       </c>
       <c r="D56" t="n">
-        <v>101.6793893129771</v>
+        <v>4206.641221374046</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3673,19 +3673,19 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>KM041108</t>
+          <t>KITD0307</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GEL FIJADOR DE CEJAS</t>
+          <t>KIT DUO BRONCEADORES DLUCHI</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>192</v>
+        <v>24</v>
       </c>
       <c r="D118" t="n">
-        <v>4274.312977099236</v>
+        <v>36.64122137404581</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3701,19 +3701,19 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KITD0307</t>
+          <t>KM041108</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>KIT DUO BRONCEADORES DLUCHI</t>
+          <t>GEL FIJADOR DE CEJAS</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="D119" t="n">
-        <v>36.64122137404581</v>
+        <v>4274.312977099236</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3951,19 +3951,19 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>KITK0105</t>
+          <t>KITK0205</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>KIT DE PERFUMES PARA CABELLO KABA</t>
+          <t>KIT PIEL PERFECTA KABA</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="D128" t="n">
-        <v>20.72519083969465</v>
+        <v>87.25190839694656</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -3979,19 +3979,19 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>KITK0205</t>
+          <t>KITK0105</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>KIT PIEL PERFECTA KABA</t>
+          <t>KIT DE PERFUMES PARA CABELLO KABA</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="D129" t="n">
-        <v>87.25190839694656</v>
+        <v>20.72519083969465</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4505,19 +4505,19 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>KITO0301</t>
+          <t>KITD0308</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>KIT MANTEQUILLAS OMG</t>
+          <t>MINIKIT DE BRONCEO DLUCHI</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="D148" t="n">
-        <v>118.5114503816794</v>
+        <v>520.8778625954199</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4533,19 +4533,19 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>KITD0308</t>
+          <t>KITK0109</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MINIKIT DE BRONCEO DLUCHI</t>
+          <t>KIT RUTINA CAPILAR KABA</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="D149" t="n">
-        <v>520.8778625954199</v>
+        <v>383.3587786259542</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4561,19 +4561,19 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>KITK0109</t>
+          <t>KITO0301</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>KIT RUTINA CAPILAR KABA</t>
+          <t>KIT MANTEQUILLAS OMG</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D150" t="n">
-        <v>383.3587786259542</v>
+        <v>118.5114503816794</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -4939,16 +4939,16 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>D051501</t>
+          <t>K051501</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE DLUCHI</t>
+          <t>COSMETIQUERA GRANDE KABA</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
@@ -4965,16 +4965,16 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>K051501</t>
+          <t>D051501</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE KABA</t>
+          <t>COSMETIQUERA GRANDE DLUCHI</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
@@ -5497,19 +5497,19 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>KM041303</t>
+          <t>KM041105</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>DROPS HONEY GOLD</t>
+          <t>CORRECTOR DE OJERAS MACADAMIA</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1</v>
+        <v>287</v>
       </c>
       <c r="D185" t="n">
-        <v>531.7557251908397</v>
+        <v>347.2900763358779</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -5525,19 +5525,19 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>KM041204</t>
+          <t>R010303</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>LIP GLOSS VOLUMINIZANTE GOLDEN HOUR</t>
+          <t>SACHET BOMBA ANTIGRASA LA RECETA</t>
         </is>
       </c>
       <c r="C186" t="n">
         <v>1</v>
       </c>
       <c r="D186" t="n">
-        <v>166.2595419847328</v>
+        <v>180</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -5553,19 +5553,19 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>KM041105</t>
+          <t>KM041103</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS MACADAMIA</t>
+          <t>CORRECTOR DE OJERAS AVELLANA</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>287</v>
+        <v>1</v>
       </c>
       <c r="D187" t="n">
-        <v>347.2900763358779</v>
+        <v>423.8931297709924</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -5581,19 +5581,19 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>R010303</t>
+          <t>KM041202</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SACHET BOMBA ANTIGRASA LA RECETA</t>
+          <t>LIP GLOSS GOLDEN HOUR</t>
         </is>
       </c>
       <c r="C188" t="n">
         <v>1</v>
       </c>
       <c r="D188" t="n">
-        <v>180</v>
+        <v>171.412213740458</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -5609,19 +5609,19 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>KM041103</t>
+          <t>KM041303</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS AVELLANA</t>
+          <t>DROPS HONEY GOLD</t>
         </is>
       </c>
       <c r="C189" t="n">
         <v>1</v>
       </c>
       <c r="D189" t="n">
-        <v>423.8931297709924</v>
+        <v>531.7557251908397</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -5637,19 +5637,19 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>KM041202</t>
+          <t>KM041204</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>LIP GLOSS GOLDEN HOUR</t>
+          <t>LIP GLOSS VOLUMINIZANTE GOLDEN HOUR</t>
         </is>
       </c>
       <c r="C190" t="n">
         <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>171.412213740458</v>
+        <v>166.2595419847328</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -5749,19 +5749,19 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>D031009</t>
+          <t>K010402</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ESPUMA AUTOBRONCEADORA TON OSCURO DLUCHI</t>
+          <t>PERFUME PARA EL CABELLO CONFIDENTE KABA</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D194" t="n">
-        <v>666.412213740458</v>
+        <v>1163.473282442748</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -5777,19 +5777,19 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>K010402</t>
+          <t>D030601</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO CONFIDENTE KABA</t>
+          <t>FRESHING POP AFTER SUN DLUCHI</t>
         </is>
       </c>
       <c r="C195" t="n">
         <v>1</v>
       </c>
       <c r="D195" t="n">
-        <v>1163.473282442748</v>
+        <v>267.9389312977099</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -5805,19 +5805,19 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>D030601</t>
+          <t>D031009</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>FRESHING POP AFTER SUN DLUCHI</t>
+          <t>ESPUMA AUTOBRONCEADORA TON OSCURO DLUCHI</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D196" t="n">
-        <v>267.9389312977099</v>
+        <v>666.412213740458</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6251,19 +6251,19 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>K010404</t>
+          <t>K020503</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO ARRIESGADA KABA</t>
+          <t>MASCARILLA FACIAL DE BANANO KABA</t>
         </is>
       </c>
       <c r="C212" t="n">
         <v>1</v>
       </c>
       <c r="D212" t="n">
-        <v>1492.557251908397</v>
+        <v>85.87786259541986</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -6279,19 +6279,19 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>K020503</t>
+          <t>K020603</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>MASCARILLA FACIAL DE BANANO KABA</t>
+          <t>TONICO DE ROSAS KABA</t>
         </is>
       </c>
       <c r="C213" t="n">
         <v>1</v>
       </c>
       <c r="D213" t="n">
-        <v>85.87786259541986</v>
+        <v>975.2290076335877</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6307,19 +6307,19 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>K020603</t>
+          <t>K010403</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>TONICO DE ROSAS KABA</t>
+          <t>PERFUME PARA EL CABELLO SOÑADORA KABA</t>
         </is>
       </c>
       <c r="C214" t="n">
         <v>1</v>
       </c>
       <c r="D214" t="n">
-        <v>975.2290076335877</v>
+        <v>1100.954198473282</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6335,19 +6335,19 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>K010403</t>
+          <t>K010404</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO SOÑADORA KABA</t>
+          <t>PERFUME PARA EL CABELLO ARRIESGADA KABA</t>
         </is>
       </c>
       <c r="C215" t="n">
         <v>1</v>
       </c>
       <c r="D215" t="n">
-        <v>1100.954198473282</v>
+        <v>1492.557251908397</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -6643,19 +6643,19 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>KM041104</t>
+          <t>K020506</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS CARAMELO</t>
+          <t>MASCARILLA FACIAL DE CHOCOLATE KABA</t>
         </is>
       </c>
       <c r="C226" t="n">
         <v>1</v>
       </c>
       <c r="D226" t="n">
-        <v>217.4427480916031</v>
+        <v>138.7786259541985</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -6671,19 +6671,19 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>KM041302</t>
+          <t>KM041304</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE SILVER</t>
+          <t>DROPS PINK GOLD</t>
         </is>
       </c>
       <c r="C227" t="n">
         <v>1</v>
       </c>
       <c r="D227" t="n">
-        <v>192.7099236641222</v>
+        <v>178.6259541984733</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -6699,19 +6699,19 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>KM041301</t>
+          <t>KM041104</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE GOLD</t>
+          <t>CORRECTOR DE OJERAS CARAMELO</t>
         </is>
       </c>
       <c r="C228" t="n">
         <v>1</v>
       </c>
       <c r="D228" t="n">
-        <v>760.8778625954199</v>
+        <v>217.4427480916031</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -6727,19 +6727,19 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>K020506</t>
+          <t>KM041302</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>MASCARILLA FACIAL DE CHOCOLATE KABA</t>
+          <t>DROPS CHAMPAGNE SILVER</t>
         </is>
       </c>
       <c r="C229" t="n">
         <v>1</v>
       </c>
       <c r="D229" t="n">
-        <v>138.7786259541985</v>
+        <v>192.7099236641222</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -6755,19 +6755,19 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>KM041304</t>
+          <t>KM041301</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>DROPS PINK GOLD</t>
+          <t>DROPS CHAMPAGNE GOLD</t>
         </is>
       </c>
       <c r="C230" t="n">
         <v>1</v>
       </c>
       <c r="D230" t="n">
-        <v>178.6259541984733</v>
+        <v>760.8778625954199</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -6783,19 +6783,19 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>KM041106</t>
+          <t>D031004</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS MIEL</t>
+          <t>MINI BRONCEADOR ZANAHORIA CANELA DLUCHI</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>265</v>
+        <v>1</v>
       </c>
       <c r="D231" t="n">
-        <v>1522.786259541985</v>
+        <v>4990.534351145038</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -6811,19 +6811,19 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>KM041308</t>
+          <t>KM041305</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>ILUMINADOR PRETTY GIRL</t>
+          <t>ILUMINADOR LIGHTS UP</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>217</v>
+        <v>1</v>
       </c>
       <c r="D232" t="n">
-        <v>148.3969465648855</v>
+        <v>162.824427480916</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -6839,19 +6839,19 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>O030501</t>
+          <t>KM041307</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>MANTEQUILLA EXFOLIANTE OMG</t>
+          <t>ILUMINADOR LIQUIDO DAILY SHINE</t>
         </is>
       </c>
       <c r="C233" t="n">
         <v>1</v>
       </c>
       <c r="D233" t="n">
-        <v>4206.641221374046</v>
+        <v>101.6793893129771</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -6867,19 +6867,19 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>D031004</t>
+          <t>KM041106</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>MINI BRONCEADOR ZANAHORIA CANELA DLUCHI</t>
+          <t>CORRECTOR DE OJERAS MIEL</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>1</v>
+        <v>265</v>
       </c>
       <c r="D234" t="n">
-        <v>4990.534351145038</v>
+        <v>1522.786259541985</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -6895,19 +6895,19 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>KM041305</t>
+          <t>KM041308</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ILUMINADOR LIGHTS UP</t>
+          <t>ILUMINADOR PRETTY GIRL</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>1</v>
+        <v>217</v>
       </c>
       <c r="D235" t="n">
-        <v>162.824427480916</v>
+        <v>148.3969465648855</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -6923,19 +6923,19 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>KM041307</t>
+          <t>O030501</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>ILUMINADOR LIQUIDO DAILY SHINE</t>
+          <t>MANTEQUILLA EXFOLIANTE OMG</t>
         </is>
       </c>
       <c r="C236" t="n">
         <v>1</v>
       </c>
       <c r="D236" t="n">
-        <v>101.6793893129771</v>
+        <v>4206.641221374046</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -8001,18 +8001,20 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>KM041310</t>
+          <t>K010301</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>RUBOR LIQUIDO DAIQUIRI</t>
+          <t>TRATAMIENTO CAPILAR REPOLARIZADOR KABA</t>
         </is>
       </c>
       <c r="C275" t="n">
         <v>1</v>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="n">
+        <v>8401.603053435116</v>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -8027,20 +8029,18 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>K010301</t>
+          <t>KM041310</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>TRATAMIENTO CAPILAR REPOLARIZADOR KABA</t>
+          <t>RUBOR LIQUIDO DAIQUIRI</t>
         </is>
       </c>
       <c r="C276" t="n">
         <v>1</v>
       </c>
-      <c r="D276" t="n">
-        <v>8401.603053435116</v>
-      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -8693,19 +8693,19 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>KITO0301</t>
+          <t>KITD0308</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>KIT MANTEQUILLAS OMG</t>
+          <t>MINIKIT DE BRONCEO DLUCHI</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="D300" t="n">
-        <v>118.5114503816794</v>
+        <v>520.8778625954199</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -8721,19 +8721,19 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>KITD0308</t>
+          <t>KITK0109</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>MINIKIT DE BRONCEO DLUCHI</t>
+          <t>KIT RUTINA CAPILAR KABA</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D301" t="n">
-        <v>520.8778625954199</v>
+        <v>383.3587786259542</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -8749,19 +8749,19 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>KITK0109</t>
+          <t>KITO0301</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>KIT RUTINA CAPILAR KABA</t>
+          <t>KIT MANTEQUILLAS OMG</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="D302" t="n">
-        <v>383.3587786259542</v>
+        <v>118.5114503816794</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -9503,19 +9503,19 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>KM041303</t>
+          <t>R010303</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>DROPS HONEY GOLD</t>
+          <t>SACHET BOMBA ANTIGRASA LA RECETA</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>5293</v>
+        <v>3000</v>
       </c>
       <c r="D330" t="n">
-        <v>531.7557251908397</v>
+        <v>180</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -9531,19 +9531,19 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>KM041308</t>
+          <t>KM041202</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>ILUMINADOR PRETTY GIRL</t>
+          <t>LIP GLOSS GOLDEN HOUR</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>9802</v>
+        <v>943</v>
       </c>
       <c r="D331" t="n">
-        <v>148.3969465648855</v>
+        <v>171.412213740458</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -9559,19 +9559,19 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>R010303</t>
+          <t>KM041303</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>SACHET BOMBA ANTIGRASA LA RECETA</t>
+          <t>DROPS HONEY GOLD</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>3000</v>
+        <v>5293</v>
       </c>
       <c r="D332" t="n">
-        <v>180</v>
+        <v>531.7557251908397</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -9587,19 +9587,19 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>KM041202</t>
+          <t>KM041308</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>LIP GLOSS GOLDEN HOUR</t>
+          <t>ILUMINADOR PRETTY GIRL</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>943</v>
+        <v>9802</v>
       </c>
       <c r="D333" t="n">
-        <v>171.412213740458</v>
+        <v>148.3969465648855</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -10225,19 +10225,19 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>K010404</t>
+          <t>K010402</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO ARRIESGADA KABA</t>
+          <t>PERFUME PARA EL CABELLO CONFIDENTE KABA</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>2520</v>
+        <v>2016</v>
       </c>
       <c r="D357" t="n">
-        <v>1492.557251908397</v>
+        <v>1163.473282442748</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -10253,19 +10253,19 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>D031009</t>
+          <t>D030601</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>ESPUMA AUTOBRONCEADORA TON OSCURO DLUCHI</t>
+          <t>FRESHING POP AFTER SUN DLUCHI</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>1365</v>
+        <v>20434</v>
       </c>
       <c r="D358" t="n">
-        <v>666.412213740458</v>
+        <v>267.9389312977099</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -10281,19 +10281,19 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>K010402</t>
+          <t>K010403</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO CONFIDENTE KABA</t>
+          <t>PERFUME PARA EL CABELLO SOÑADORA KABA</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>2016</v>
+        <v>5573</v>
       </c>
       <c r="D359" t="n">
-        <v>1163.473282442748</v>
+        <v>1100.954198473282</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -10309,19 +10309,19 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>D030601</t>
+          <t>K010404</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>FRESHING POP AFTER SUN DLUCHI</t>
+          <t>PERFUME PARA EL CABELLO ARRIESGADA KABA</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>20434</v>
+        <v>2520</v>
       </c>
       <c r="D360" t="n">
-        <v>267.9389312977099</v>
+        <v>1492.557251908397</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -10337,19 +10337,19 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>K010403</t>
+          <t>D031009</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO SOÑADORA KABA</t>
+          <t>ESPUMA AUTOBRONCEADORA TON OSCURO DLUCHI</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>5573</v>
+        <v>1365</v>
       </c>
       <c r="D361" t="n">
-        <v>1100.954198473282</v>
+        <v>666.412213740458</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -11057,19 +11057,19 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>KM041101</t>
+          <t>K010102</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS ALMENDRA</t>
+          <t>SHAMPO KIDS KABA</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>4248</v>
+        <v>2500</v>
       </c>
       <c r="D388" t="n">
-        <v>2872.786259541985</v>
+        <v>2141.106870229008</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -11085,19 +11085,19 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>K010102</t>
+          <t>R010302</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>SHAMPO KIDS KABA</t>
+          <t>TONICO CAPILAR LA RECETA</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>2500</v>
+        <v>14006</v>
       </c>
       <c r="D389" t="n">
-        <v>2141.106870229008</v>
+        <v>3218.702290076336</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -11113,19 +11113,19 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>R010302</t>
+          <t>K010101</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>TONICO CAPILAR LA RECETA</t>
+          <t>SHAMPO DE CEBOLLA KABA</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>14006</v>
+        <v>177726</v>
       </c>
       <c r="D390" t="n">
-        <v>3218.702290076336</v>
+        <v>81409.46564885495</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -11141,19 +11141,19 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>K010101</t>
+          <t>KM041101</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>SHAMPO DE CEBOLLA KABA</t>
+          <t>CORRECTOR DE OJERAS ALMENDRA</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>177726</v>
+        <v>4248</v>
       </c>
       <c r="D391" t="n">
-        <v>81409.46564885495</v>
+        <v>2872.786259541985</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
@@ -12353,19 +12353,19 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>KM041302</t>
+          <t>K020506</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE SILVER</t>
+          <t>MASCARILLA FACIAL DE CHOCOLATE KABA</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>6380</v>
+        <v>511</v>
       </c>
       <c r="D437" t="n">
-        <v>192.7099236641222</v>
+        <v>138.7786259541985</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
@@ -12381,19 +12381,19 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>KM041301</t>
+          <t>KM041304</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE GOLD</t>
+          <t>DROPS PINK GOLD</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>4883</v>
+        <v>5472</v>
       </c>
       <c r="D438" t="n">
-        <v>760.8778625954199</v>
+        <v>178.6259541984733</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
@@ -12409,19 +12409,19 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>K020506</t>
+          <t>KM041302</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>MASCARILLA FACIAL DE CHOCOLATE KABA</t>
+          <t>DROPS CHAMPAGNE SILVER</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>511</v>
+        <v>6380</v>
       </c>
       <c r="D439" t="n">
-        <v>138.7786259541985</v>
+        <v>192.7099236641222</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
@@ -12437,19 +12437,19 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>KM041304</t>
+          <t>KM041301</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>DROPS PINK GOLD</t>
+          <t>DROPS CHAMPAGNE GOLD</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>5472</v>
+        <v>4883</v>
       </c>
       <c r="D440" t="n">
-        <v>178.6259541984733</v>
+        <v>760.8778625954199</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
@@ -12571,19 +12571,19 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>KM041106</t>
+          <t>D031004</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS MIEL</t>
+          <t>MINI BRONCEADOR ZANAHORIA CANELA DLUCHI</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>2734</v>
+        <v>200</v>
       </c>
       <c r="D445" t="n">
-        <v>1522.786259541985</v>
+        <v>4990.534351145038</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
@@ -12599,19 +12599,19 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>D031004</t>
+          <t>KM041305</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>MINI BRONCEADOR ZANAHORIA CANELA DLUCHI</t>
+          <t>ILUMINADOR LIGHTS UP</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>200</v>
+        <v>9468</v>
       </c>
       <c r="D446" t="n">
-        <v>4990.534351145038</v>
+        <v>162.824427480916</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
@@ -12627,19 +12627,19 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>KM041305</t>
+          <t>KM041307</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>ILUMINADOR LIGHTS UP</t>
+          <t>ILUMINADOR LIQUIDO DAILY SHINE</t>
         </is>
       </c>
       <c r="C447" t="n">
-        <v>9468</v>
+        <v>10397</v>
       </c>
       <c r="D447" t="n">
-        <v>162.824427480916</v>
+        <v>101.6793893129771</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
@@ -12655,19 +12655,19 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>KM041307</t>
+          <t>KM041106</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>ILUMINADOR LIQUIDO DAILY SHINE</t>
+          <t>CORRECTOR DE OJERAS MIEL</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>10397</v>
+        <v>2734</v>
       </c>
       <c r="D448" t="n">
-        <v>101.6793893129771</v>
+        <v>1522.786259541985</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
@@ -14995,19 +14995,19 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>KITK0206</t>
+          <t>KITK0301</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>KIT RUTINA AM KABA</t>
+          <t>KIT ADIOS MANCHAS KABA</t>
         </is>
       </c>
       <c r="C535" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D535" t="n">
-        <v>34.69465648854962</v>
+        <v>98.58778625954199</v>
       </c>
       <c r="E535" t="inlineStr">
         <is>
@@ -15023,19 +15023,19 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>KITD0304</t>
+          <t>KITK0206</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>KIT BRONCEOPERF VAR ZANA CANELA DLUCHI</t>
+          <t>KIT RUTINA AM KABA</t>
         </is>
       </c>
       <c r="C536" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="D536" t="n">
-        <v>116.9083969465649</v>
+        <v>34.69465648854962</v>
       </c>
       <c r="E536" t="inlineStr">
         <is>
@@ -15051,19 +15051,19 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>KITK0301</t>
+          <t>KITD0304</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>KIT ADIOS MANCHAS KABA</t>
+          <t>KIT BRONCEOPERF VAR ZANA CANELA DLUCHI</t>
         </is>
       </c>
       <c r="C537" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="D537" t="n">
-        <v>98.58778625954199</v>
+        <v>116.9083969465649</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
@@ -15825,21 +15825,21 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>155301</t>
+          <t>ME1011</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>ESTOGEL M</t>
+          <t>LOTIÓN PUMP 28/410 SILVER/WHITE</t>
         </is>
       </c>
       <c r="C566" t="n">
-        <v>100000</v>
+        <v>326790</v>
       </c>
       <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
@@ -15851,21 +15851,21 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>ME1011</t>
+          <t>155301</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>LOTIÓN PUMP 28/410 SILVER/WHITE</t>
+          <t>ESTOGEL M</t>
         </is>
       </c>
       <c r="C567" t="n">
-        <v>326790</v>
+        <v>100000</v>
       </c>
       <c r="D567" t="inlineStr"/>
       <c r="E567" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
@@ -16007,16 +16007,16 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>ME0507</t>
+          <t>ME1028</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 30ML</t>
+          <t>TAPA CON APLICADOR PUNTA PINCEL</t>
         </is>
       </c>
       <c r="C573" t="n">
-        <v>34020</v>
+        <v>14930</v>
       </c>
       <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr">
@@ -16033,16 +16033,16 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>ME1028</t>
+          <t>ME0507</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>TAPA CON APLICADOR PUNTA PINCEL</t>
+          <t>BALA TRANSPARENTE 30ML</t>
         </is>
       </c>
       <c r="C574" t="n">
-        <v>14930</v>
+        <v>34020</v>
       </c>
       <c r="D574" t="inlineStr"/>
       <c r="E574" t="inlineStr">
@@ -23149,16 +23149,16 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>D051501</t>
+          <t>K051501</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE DLUCHI</t>
+          <t>COSMETIQUERA GRANDE KABA</t>
         </is>
       </c>
       <c r="C883" t="n">
-        <v>22000</v>
+        <v>3900</v>
       </c>
       <c r="D883" t="inlineStr"/>
       <c r="E883" t="inlineStr">
@@ -23175,16 +23175,16 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>K051501</t>
+          <t>D051501</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE KABA</t>
+          <t>COSMETIQUERA GRANDE DLUCHI</t>
         </is>
       </c>
       <c r="C884" t="n">
-        <v>3900</v>
+        <v>22000</v>
       </c>
       <c r="D884" t="inlineStr"/>
       <c r="E884" t="inlineStr">
@@ -36897,21 +36897,21 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>314208</t>
+          <t>ME1049</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>GEMTONE AMBER G001</t>
+          <t>TAPA PUSH PULL DORADA ROSCA 24</t>
         </is>
       </c>
       <c r="C1448" t="n">
-        <v>73488</v>
+        <v>3386</v>
       </c>
       <c r="D1448" t="inlineStr"/>
       <c r="E1448" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1448" t="inlineStr">
@@ -36923,21 +36923,21 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>ME1049</t>
+          <t>314208</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>TAPA PUSH PULL DORADA ROSCA 24</t>
+          <t>GEMTONE AMBER G001</t>
         </is>
       </c>
       <c r="C1449" t="n">
-        <v>3386</v>
+        <v>73488</v>
       </c>
       <c r="D1449" t="inlineStr"/>
       <c r="E1449" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1449" t="inlineStr">
@@ -37287,21 +37287,21 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>ME0505</t>
+          <t>ET0202</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 120ML</t>
+          <t>ETIQUETA PERFUME CABELLO ARRIESGAD 120ML</t>
         </is>
       </c>
       <c r="C1463" t="n">
-        <v>2543</v>
+        <v>140</v>
       </c>
       <c r="D1463" t="inlineStr"/>
       <c r="E1463" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1463" t="inlineStr">
@@ -37313,21 +37313,21 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>ET0202</t>
+          <t>ME0505</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>ETIQUETA PERFUME CABELLO ARRIESGAD 120ML</t>
+          <t>BALA TRANSPARENTE 120ML</t>
         </is>
       </c>
       <c r="C1464" t="n">
-        <v>140</v>
+        <v>2543</v>
       </c>
       <c r="D1464" t="inlineStr"/>
       <c r="E1464" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1464" t="inlineStr">
@@ -38197,21 +38197,21 @@
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>173501</t>
+          <t>ME1043</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>ULTRAMAR U-200 AZUL</t>
+          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
         </is>
       </c>
       <c r="C1498" t="n">
-        <v>5979</v>
+        <v>4500</v>
       </c>
       <c r="D1498" t="inlineStr"/>
       <c r="E1498" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1498" t="inlineStr">
@@ -38223,16 +38223,16 @@
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>ME1043</t>
+          <t>ME1044</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
+          <t>TAPA FLIP TOP PLATEADA ROSCA 18</t>
         </is>
       </c>
       <c r="C1499" t="n">
-        <v>4500</v>
+        <v>39551</v>
       </c>
       <c r="D1499" t="inlineStr"/>
       <c r="E1499" t="inlineStr">
@@ -38249,21 +38249,21 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>ME1044</t>
+          <t>173501</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP PLATEADA ROSCA 18</t>
+          <t>ULTRAMAR U-200 AZUL</t>
         </is>
       </c>
       <c r="C1500" t="n">
-        <v>39551</v>
+        <v>5979</v>
       </c>
       <c r="D1500" t="inlineStr"/>
       <c r="E1500" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1500" t="inlineStr">
@@ -39185,16 +39185,16 @@
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>ME0578</t>
+          <t>ME1055</t>
         </is>
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>ENVASE ROJO RUBOR EN CREMA RUBY</t>
+          <t>TAPA SPRAY VERDE ROSCA 18</t>
         </is>
       </c>
       <c r="C1536" t="n">
-        <v>19980</v>
+        <v>11362</v>
       </c>
       <c r="D1536" t="inlineStr"/>
       <c r="E1536" t="inlineStr">
@@ -39211,16 +39211,16 @@
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>ME0579</t>
+          <t>ME0511</t>
         </is>
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>ENVASE NARANJA RUBOR EN CREMA SALLY</t>
+          <t>ENV PEAD KABA B28 500ML</t>
         </is>
       </c>
       <c r="C1537" t="n">
-        <v>19475</v>
+        <v>28261</v>
       </c>
       <c r="D1537" t="inlineStr"/>
       <c r="E1537" t="inlineStr">
@@ -39237,21 +39237,21 @@
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>ME1067</t>
+          <t>ET0253</t>
         </is>
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>TAPA NARANJA RUBOR EN BARRA SALLY</t>
+          <t>ETIQUETA BRONC DE CHOCOLATE MIEL 45ML</t>
         </is>
       </c>
       <c r="C1538" t="n">
-        <v>19440</v>
+        <v>22864</v>
       </c>
       <c r="D1538" t="inlineStr"/>
       <c r="E1538" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1538" t="inlineStr">
@@ -39263,16 +39263,16 @@
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>ME1055</t>
+          <t>ME0578</t>
         </is>
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>TAPA SPRAY VERDE ROSCA 18</t>
+          <t>ENVASE ROJO RUBOR EN CREMA RUBY</t>
         </is>
       </c>
       <c r="C1539" t="n">
-        <v>11362</v>
+        <v>19980</v>
       </c>
       <c r="D1539" t="inlineStr"/>
       <c r="E1539" t="inlineStr">
@@ -39289,16 +39289,16 @@
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>ME0511</t>
+          <t>ME0579</t>
         </is>
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>ENV PEAD KABA B28 500ML</t>
+          <t>ENVASE NARANJA RUBOR EN CREMA SALLY</t>
         </is>
       </c>
       <c r="C1540" t="n">
-        <v>28261</v>
+        <v>19475</v>
       </c>
       <c r="D1540" t="inlineStr"/>
       <c r="E1540" t="inlineStr">
@@ -39315,21 +39315,21 @@
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>ET0253</t>
+          <t>ME1067</t>
         </is>
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>ETIQUETA BRONC DE CHOCOLATE MIEL 45ML</t>
+          <t>TAPA NARANJA RUBOR EN BARRA SALLY</t>
         </is>
       </c>
       <c r="C1541" t="n">
-        <v>22864</v>
+        <v>19440</v>
       </c>
       <c r="D1541" t="inlineStr"/>
       <c r="E1541" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1541" t="inlineStr">
@@ -39627,16 +39627,16 @@
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>ME0504</t>
+          <t>ME1028</t>
         </is>
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>BALA NEGRA LARGA 120ML</t>
+          <t>TAPA CON APLICADOR PUNTA PINCEL</t>
         </is>
       </c>
       <c r="C1553" t="n">
-        <v>9239</v>
+        <v>15877</v>
       </c>
       <c r="D1553" t="inlineStr"/>
       <c r="E1553" t="inlineStr">
@@ -39653,16 +39653,16 @@
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>ME0507</t>
+          <t>ME1059</t>
         </is>
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 30ML</t>
+          <t>WIPER ( ESCURRIDOR/BARREDOR) NATURAL</t>
         </is>
       </c>
       <c r="C1554" t="n">
-        <v>24300</v>
+        <v>30387</v>
       </c>
       <c r="D1554" t="inlineStr"/>
       <c r="E1554" t="inlineStr">
@@ -39679,16 +39679,16 @@
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>ME1028</t>
+          <t>ME0504</t>
         </is>
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>TAPA CON APLICADOR PUNTA PINCEL</t>
+          <t>BALA NEGRA LARGA 120ML</t>
         </is>
       </c>
       <c r="C1555" t="n">
-        <v>15877</v>
+        <v>9239</v>
       </c>
       <c r="D1555" t="inlineStr"/>
       <c r="E1555" t="inlineStr">
@@ -39705,16 +39705,16 @@
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>ME1059</t>
+          <t>ME0507</t>
         </is>
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>WIPER ( ESCURRIDOR/BARREDOR) NATURAL</t>
+          <t>BALA TRANSPARENTE 30ML</t>
         </is>
       </c>
       <c r="C1556" t="n">
-        <v>30387</v>
+        <v>24300</v>
       </c>
       <c r="D1556" t="inlineStr"/>
       <c r="E1556" t="inlineStr">
@@ -39913,16 +39913,16 @@
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>ME0542</t>
+          <t>ME0523</t>
         </is>
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>TUBO COLAP ANTOBRONCEADORA 120ML V1</t>
+          <t>ENVASE PVC COLOR BLANCO POCIMA 6ML</t>
         </is>
       </c>
       <c r="C1564" t="n">
-        <v>3493</v>
+        <v>33606</v>
       </c>
       <c r="D1564" t="inlineStr"/>
       <c r="E1564" t="inlineStr">
@@ -39939,16 +39939,16 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>ME0545</t>
+          <t>ME0542</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>TUBO COLAP EXFOLIANTE CAPILAR 220GR V1</t>
+          <t>TUBO COLAP ANTOBRONCEADORA 120ML V1</t>
         </is>
       </c>
       <c r="C1565" t="n">
-        <v>1909</v>
+        <v>3493</v>
       </c>
       <c r="D1565" t="inlineStr"/>
       <c r="E1565" t="inlineStr">
@@ -39965,16 +39965,16 @@
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>ME0523</t>
+          <t>ME0545</t>
         </is>
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>ENVASE PVC COLOR BLANCO POCIMA 6ML</t>
+          <t>TUBO COLAP EXFOLIANTE CAPILAR 220GR V1</t>
         </is>
       </c>
       <c r="C1566" t="n">
-        <v>33606</v>
+        <v>1909</v>
       </c>
       <c r="D1566" t="inlineStr"/>
       <c r="E1566" t="inlineStr">
@@ -39991,16 +39991,16 @@
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>ME0513</t>
+          <t>ME1040</t>
         </is>
       </c>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>ENVASE APPLE 28/410 TRANSP P30 M1 300ML</t>
+          <t>TAPA FLIP TOP 28 MM ROSADO FLAMENCO</t>
         </is>
       </c>
       <c r="C1567" t="n">
-        <v>9838</v>
+        <v>17344</v>
       </c>
       <c r="D1567" t="inlineStr"/>
       <c r="E1567" t="inlineStr">
@@ -40017,16 +40017,16 @@
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>ME1040</t>
+          <t>ME0513</t>
         </is>
       </c>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP 28 MM ROSADO FLAMENCO</t>
+          <t>ENVASE APPLE 28/410 TRANSP P30 M1 300ML</t>
         </is>
       </c>
       <c r="C1568" t="n">
-        <v>17344</v>
+        <v>9838</v>
       </c>
       <c r="D1568" t="inlineStr"/>
       <c r="E1568" t="inlineStr">
@@ -41187,16 +41187,16 @@
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>ME0544</t>
+          <t>ME0519</t>
         </is>
       </c>
       <c r="B1613" t="inlineStr">
         <is>
-          <t>TUBO COLAP DERMOACLARANTE 60ML V1</t>
+          <t>ENVASE PARA CREMA FACIAL TENSORA</t>
         </is>
       </c>
       <c r="C1613" t="n">
-        <v>8240</v>
+        <v>10009</v>
       </c>
       <c r="D1613" t="inlineStr"/>
       <c r="E1613" t="inlineStr">
@@ -41213,16 +41213,16 @@
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>ME0519</t>
+          <t>ME1014</t>
         </is>
       </c>
       <c r="B1614" t="inlineStr">
         <is>
-          <t>ENVASE PARA CREMA FACIAL TENSORA</t>
+          <t>SHINE GREEN COLOR PRESS</t>
         </is>
       </c>
       <c r="C1614" t="n">
-        <v>10009</v>
+        <v>6885</v>
       </c>
       <c r="D1614" t="inlineStr"/>
       <c r="E1614" t="inlineStr">
@@ -41239,16 +41239,16 @@
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>ME1014</t>
+          <t>ME0544</t>
         </is>
       </c>
       <c r="B1615" t="inlineStr">
         <is>
-          <t>SHINE GREEN COLOR PRESS</t>
+          <t>TUBO COLAP DERMOACLARANTE 60ML V1</t>
         </is>
       </c>
       <c r="C1615" t="n">
-        <v>6885</v>
+        <v>8240</v>
       </c>
       <c r="D1615" t="inlineStr"/>
       <c r="E1615" t="inlineStr">
@@ -41629,16 +41629,16 @@
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>ME1068</t>
+          <t>ME1012</t>
         </is>
       </c>
       <c r="B1630" t="inlineStr">
         <is>
-          <t>TAPA SPRAY BLANCA R 18/410 (DEPILADOR N)</t>
+          <t>BOMBA ENCASQUE DORADA/BRONCEADORES</t>
         </is>
       </c>
       <c r="C1630" t="n">
-        <v>257740</v>
+        <v>27625</v>
       </c>
       <c r="D1630" t="inlineStr"/>
       <c r="E1630" t="inlineStr">
@@ -41655,21 +41655,21 @@
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>ME1012</t>
+          <t>ET02138</t>
         </is>
       </c>
       <c r="B1631" t="inlineStr">
         <is>
-          <t>BOMBA ENCASQUE DORADA/BRONCEADORES</t>
+          <t>ETIQUETA KERATINA ALISADOR KABA 500 ML</t>
         </is>
       </c>
       <c r="C1631" t="n">
-        <v>27625</v>
+        <v>2868</v>
       </c>
       <c r="D1631" t="inlineStr"/>
       <c r="E1631" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1631" t="inlineStr">
@@ -41681,16 +41681,16 @@
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>ET02138</t>
+          <t>ET02139</t>
         </is>
       </c>
       <c r="B1632" t="inlineStr">
         <is>
-          <t>ETIQUETA KERATINA ALISADOR KABA 500 ML</t>
+          <t>ETIQUETA KERATINA ALISADOR KABA 250 ML</t>
         </is>
       </c>
       <c r="C1632" t="n">
-        <v>2868</v>
+        <v>1368</v>
       </c>
       <c r="D1632" t="inlineStr"/>
       <c r="E1632" t="inlineStr">
@@ -41707,21 +41707,21 @@
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>ET02139</t>
+          <t>ME1068</t>
         </is>
       </c>
       <c r="B1633" t="inlineStr">
         <is>
-          <t>ETIQUETA KERATINA ALISADOR KABA 250 ML</t>
+          <t>TAPA SPRAY BLANCA R 18/410 (DEPILADOR N)</t>
         </is>
       </c>
       <c r="C1633" t="n">
-        <v>1368</v>
+        <v>257740</v>
       </c>
       <c r="D1633" t="inlineStr"/>
       <c r="E1633" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1633" t="inlineStr">
@@ -42587,21 +42587,21 @@
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>190102</t>
+          <t>ET0202CA</t>
         </is>
       </c>
       <c r="B1667" t="inlineStr">
         <is>
-          <t>CARBÓN ACTIVADO</t>
+          <t>ETIQUETA ILUMINADOR GOLD ROSE CARA</t>
         </is>
       </c>
       <c r="C1667" t="n">
-        <v>500</v>
+        <v>3916</v>
       </c>
       <c r="D1667" t="inlineStr"/>
       <c r="E1667" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1667" t="inlineStr">
@@ -42613,21 +42613,21 @@
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>ET0202CA</t>
+          <t>190102</t>
         </is>
       </c>
       <c r="B1668" t="inlineStr">
         <is>
-          <t>ETIQUETA ILUMINADOR GOLD ROSE CARA</t>
+          <t>CARBÓN ACTIVADO</t>
         </is>
       </c>
       <c r="C1668" t="n">
-        <v>3916</v>
+        <v>500</v>
       </c>
       <c r="D1668" t="inlineStr"/>
       <c r="E1668" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1668" t="inlineStr">
@@ -42691,21 +42691,21 @@
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>ME0553</t>
+          <t>ETC0160</t>
         </is>
       </c>
       <c r="B1671" t="inlineStr">
         <is>
-          <t>TUBO COLAP TTO REVITALIZANTE 230ML V1</t>
+          <t>CAJA RUBOR EN CREMA RUBY</t>
         </is>
       </c>
       <c r="C1671" t="n">
-        <v>478</v>
+        <v>10536</v>
       </c>
       <c r="D1671" t="inlineStr"/>
       <c r="E1671" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1671" t="inlineStr">
@@ -42717,16 +42717,16 @@
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>ETC0160</t>
+          <t>ETC0161</t>
         </is>
       </c>
       <c r="B1672" t="inlineStr">
         <is>
-          <t>CAJA RUBOR EN CREMA RUBY</t>
+          <t>CAJA RUBOR EN CREMA SALLY</t>
         </is>
       </c>
       <c r="C1672" t="n">
-        <v>10536</v>
+        <v>10328</v>
       </c>
       <c r="D1672" t="inlineStr"/>
       <c r="E1672" t="inlineStr">
@@ -42743,21 +42743,21 @@
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>ETC0161</t>
+          <t>ME0553</t>
         </is>
       </c>
       <c r="B1673" t="inlineStr">
         <is>
-          <t>CAJA RUBOR EN CREMA SALLY</t>
+          <t>TUBO COLAP TTO REVITALIZANTE 230ML V1</t>
         </is>
       </c>
       <c r="C1673" t="n">
-        <v>10328</v>
+        <v>478</v>
       </c>
       <c r="D1673" t="inlineStr"/>
       <c r="E1673" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1673" t="inlineStr">
@@ -43289,21 +43289,21 @@
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>ME0506</t>
+          <t>ETC0173</t>
         </is>
       </c>
       <c r="B1694" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 260/250 ML</t>
+          <t>CAJA TONICO CAPILAR KABA ROSADA 120ML</t>
         </is>
       </c>
       <c r="C1694" t="n">
-        <v>9784</v>
+        <v>193</v>
       </c>
       <c r="D1694" t="inlineStr"/>
       <c r="E1694" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1694" t="inlineStr">
@@ -43315,21 +43315,21 @@
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>ETC0173</t>
+          <t>ME0506</t>
         </is>
       </c>
       <c r="B1695" t="inlineStr">
         <is>
-          <t>CAJA TONICO CAPILAR KABA ROSADA 120ML</t>
+          <t>BALA TRANSPARENTE 260/250 ML</t>
         </is>
       </c>
       <c r="C1695" t="n">
-        <v>193</v>
+        <v>9784</v>
       </c>
       <c r="D1695" t="inlineStr"/>
       <c r="E1695" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1695" t="inlineStr">
@@ -45157,19 +45157,19 @@
     <row r="1764">
       <c r="A1764" t="inlineStr">
         <is>
-          <t>KM041104</t>
+          <t>K020506</t>
         </is>
       </c>
       <c r="B1764" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS CARAMELO</t>
+          <t>MASCARILLA FACIAL DE CHOCOLATE KABA</t>
         </is>
       </c>
       <c r="C1764" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1764" t="n">
-        <v>217.4427480916031</v>
+        <v>138.7786259541985</v>
       </c>
       <c r="E1764" t="inlineStr">
         <is>
@@ -45185,19 +45185,19 @@
     <row r="1765">
       <c r="A1765" t="inlineStr">
         <is>
-          <t>K020506</t>
+          <t>KM041304</t>
         </is>
       </c>
       <c r="B1765" t="inlineStr">
         <is>
-          <t>MASCARILLA FACIAL DE CHOCOLATE KABA</t>
+          <t>DROPS PINK GOLD</t>
         </is>
       </c>
       <c r="C1765" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D1765" t="n">
-        <v>138.7786259541985</v>
+        <v>178.6259541984733</v>
       </c>
       <c r="E1765" t="inlineStr">
         <is>
@@ -45213,19 +45213,19 @@
     <row r="1766">
       <c r="A1766" t="inlineStr">
         <is>
-          <t>KM041304</t>
+          <t>KM041104</t>
         </is>
       </c>
       <c r="B1766" t="inlineStr">
         <is>
-          <t>DROPS PINK GOLD</t>
+          <t>CORRECTOR DE OJERAS CARAMELO</t>
         </is>
       </c>
       <c r="C1766" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D1766" t="n">
-        <v>178.6259541984733</v>
+        <v>217.4427480916031</v>
       </c>
       <c r="E1766" t="inlineStr">
         <is>
@@ -45269,19 +45269,19 @@
     <row r="1768">
       <c r="A1768" t="inlineStr">
         <is>
-          <t>O030501</t>
+          <t>O030801</t>
         </is>
       </c>
       <c r="B1768" t="inlineStr">
         <is>
-          <t>MANTEQUILLA EXFOLIANTE OMG</t>
+          <t>DEPILADOR INSTANTANEO OMG</t>
         </is>
       </c>
       <c r="C1768" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1768" t="n">
-        <v>4206.641221374046</v>
+        <v>38473.96946564886</v>
       </c>
       <c r="E1768" t="inlineStr">
         <is>
@@ -45297,19 +45297,19 @@
     <row r="1769">
       <c r="A1769" t="inlineStr">
         <is>
-          <t>O030801</t>
+          <t>O030501</t>
         </is>
       </c>
       <c r="B1769" t="inlineStr">
         <is>
-          <t>DEPILADOR INSTANTANEO OMG</t>
+          <t>MANTEQUILLA EXFOLIANTE OMG</t>
         </is>
       </c>
       <c r="C1769" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1769" t="n">
-        <v>38473.96946564886</v>
+        <v>4206.641221374046</v>
       </c>
       <c r="E1769" t="inlineStr">
         <is>
@@ -45549,19 +45549,19 @@
     <row r="1778">
       <c r="A1778" t="inlineStr">
         <is>
-          <t>KM041108</t>
+          <t>K020507</t>
         </is>
       </c>
       <c r="B1778" t="inlineStr">
         <is>
-          <t>GEL FIJADOR DE CEJAS</t>
+          <t>MASCARILLA FACIAL DE FRUTOS ROJOS KABA</t>
         </is>
       </c>
       <c r="C1778" t="n">
         <v>1</v>
       </c>
       <c r="D1778" t="n">
-        <v>4274.312977099236</v>
+        <v>239.0839694656489</v>
       </c>
       <c r="E1778" t="inlineStr">
         <is>
@@ -45577,19 +45577,19 @@
     <row r="1779">
       <c r="A1779" t="inlineStr">
         <is>
-          <t>K020507</t>
+          <t>KM041108</t>
         </is>
       </c>
       <c r="B1779" t="inlineStr">
         <is>
-          <t>MASCARILLA FACIAL DE FRUTOS ROJOS KABA</t>
+          <t>GEL FIJADOR DE CEJAS</t>
         </is>
       </c>
       <c r="C1779" t="n">
         <v>1</v>
       </c>
       <c r="D1779" t="n">
-        <v>239.0839694656489</v>
+        <v>4274.312977099236</v>
       </c>
       <c r="E1779" t="inlineStr">
         <is>

--- a/inventario_operaciones.xlsx
+++ b/inventario_operaciones.xlsx
@@ -15825,21 +15825,21 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>ME1011</t>
+          <t>155301</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>LOTIÓN PUMP 28/410 SILVER/WHITE</t>
+          <t>ESTOGEL M</t>
         </is>
       </c>
       <c r="C566" t="n">
-        <v>326790</v>
+        <v>100000</v>
       </c>
       <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
@@ -15851,21 +15851,21 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>155301</t>
+          <t>ME1011</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>ESTOGEL M</t>
+          <t>LOTIÓN PUMP 28/410 SILVER/WHITE</t>
         </is>
       </c>
       <c r="C567" t="n">
-        <v>100000</v>
+        <v>326790</v>
       </c>
       <c r="D567" t="inlineStr"/>
       <c r="E567" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
@@ -16007,16 +16007,16 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>ME1028</t>
+          <t>ME0507</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>TAPA CON APLICADOR PUNTA PINCEL</t>
+          <t>BALA TRANSPARENTE 30ML</t>
         </is>
       </c>
       <c r="C573" t="n">
-        <v>14930</v>
+        <v>34020</v>
       </c>
       <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr">
@@ -16033,16 +16033,16 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>ME0507</t>
+          <t>ME1028</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 30ML</t>
+          <t>TAPA CON APLICADOR PUNTA PINCEL</t>
         </is>
       </c>
       <c r="C574" t="n">
-        <v>34020</v>
+        <v>14930</v>
       </c>
       <c r="D574" t="inlineStr"/>
       <c r="E574" t="inlineStr">
@@ -36897,21 +36897,21 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>ME1049</t>
+          <t>314208</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>TAPA PUSH PULL DORADA ROSCA 24</t>
+          <t>GEMTONE AMBER G001</t>
         </is>
       </c>
       <c r="C1448" t="n">
-        <v>3386</v>
+        <v>73488</v>
       </c>
       <c r="D1448" t="inlineStr"/>
       <c r="E1448" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1448" t="inlineStr">
@@ -36923,21 +36923,21 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>314208</t>
+          <t>ME1049</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>GEMTONE AMBER G001</t>
+          <t>TAPA PUSH PULL DORADA ROSCA 24</t>
         </is>
       </c>
       <c r="C1449" t="n">
-        <v>73488</v>
+        <v>3386</v>
       </c>
       <c r="D1449" t="inlineStr"/>
       <c r="E1449" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1449" t="inlineStr">
@@ -37287,21 +37287,21 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>ET0202</t>
+          <t>ME0505</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>ETIQUETA PERFUME CABELLO ARRIESGAD 120ML</t>
+          <t>BALA TRANSPARENTE 120ML</t>
         </is>
       </c>
       <c r="C1463" t="n">
-        <v>140</v>
+        <v>2543</v>
       </c>
       <c r="D1463" t="inlineStr"/>
       <c r="E1463" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1463" t="inlineStr">
@@ -37313,21 +37313,21 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>ME0505</t>
+          <t>ET0202</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 120ML</t>
+          <t>ETIQUETA PERFUME CABELLO ARRIESGAD 120ML</t>
         </is>
       </c>
       <c r="C1464" t="n">
-        <v>2543</v>
+        <v>140</v>
       </c>
       <c r="D1464" t="inlineStr"/>
       <c r="E1464" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1464" t="inlineStr">
@@ -38197,21 +38197,21 @@
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>ME1043</t>
+          <t>173501</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
+          <t>ULTRAMAR U-200 AZUL</t>
         </is>
       </c>
       <c r="C1498" t="n">
-        <v>4500</v>
+        <v>5979</v>
       </c>
       <c r="D1498" t="inlineStr"/>
       <c r="E1498" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1498" t="inlineStr">
@@ -38223,16 +38223,16 @@
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>ME1044</t>
+          <t>ME1043</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP PLATEADA ROSCA 18</t>
+          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
         </is>
       </c>
       <c r="C1499" t="n">
-        <v>39551</v>
+        <v>4500</v>
       </c>
       <c r="D1499" t="inlineStr"/>
       <c r="E1499" t="inlineStr">
@@ -38249,21 +38249,21 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>173501</t>
+          <t>ME1044</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>ULTRAMAR U-200 AZUL</t>
+          <t>TAPA FLIP TOP PLATEADA ROSCA 18</t>
         </is>
       </c>
       <c r="C1500" t="n">
-        <v>5979</v>
+        <v>39551</v>
       </c>
       <c r="D1500" t="inlineStr"/>
       <c r="E1500" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1500" t="inlineStr">
@@ -39185,16 +39185,16 @@
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>ME1055</t>
+          <t>ME0578</t>
         </is>
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>TAPA SPRAY VERDE ROSCA 18</t>
+          <t>ENVASE ROJO RUBOR EN CREMA RUBY</t>
         </is>
       </c>
       <c r="C1536" t="n">
-        <v>11362</v>
+        <v>19980</v>
       </c>
       <c r="D1536" t="inlineStr"/>
       <c r="E1536" t="inlineStr">
@@ -39211,16 +39211,16 @@
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>ME0511</t>
+          <t>ME0579</t>
         </is>
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>ENV PEAD KABA B28 500ML</t>
+          <t>ENVASE NARANJA RUBOR EN CREMA SALLY</t>
         </is>
       </c>
       <c r="C1537" t="n">
-        <v>28261</v>
+        <v>19475</v>
       </c>
       <c r="D1537" t="inlineStr"/>
       <c r="E1537" t="inlineStr">
@@ -39237,21 +39237,21 @@
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>ET0253</t>
+          <t>ME1067</t>
         </is>
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>ETIQUETA BRONC DE CHOCOLATE MIEL 45ML</t>
+          <t>TAPA NARANJA RUBOR EN BARRA SALLY</t>
         </is>
       </c>
       <c r="C1538" t="n">
-        <v>22864</v>
+        <v>19440</v>
       </c>
       <c r="D1538" t="inlineStr"/>
       <c r="E1538" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1538" t="inlineStr">
@@ -39263,16 +39263,16 @@
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>ME0578</t>
+          <t>ME1055</t>
         </is>
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>ENVASE ROJO RUBOR EN CREMA RUBY</t>
+          <t>TAPA SPRAY VERDE ROSCA 18</t>
         </is>
       </c>
       <c r="C1539" t="n">
-        <v>19980</v>
+        <v>11362</v>
       </c>
       <c r="D1539" t="inlineStr"/>
       <c r="E1539" t="inlineStr">
@@ -39289,16 +39289,16 @@
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>ME0579</t>
+          <t>ME0511</t>
         </is>
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>ENVASE NARANJA RUBOR EN CREMA SALLY</t>
+          <t>ENV PEAD KABA B28 500ML</t>
         </is>
       </c>
       <c r="C1540" t="n">
-        <v>19475</v>
+        <v>28261</v>
       </c>
       <c r="D1540" t="inlineStr"/>
       <c r="E1540" t="inlineStr">
@@ -39315,21 +39315,21 @@
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>ME1067</t>
+          <t>ET0253</t>
         </is>
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>TAPA NARANJA RUBOR EN BARRA SALLY</t>
+          <t>ETIQUETA BRONC DE CHOCOLATE MIEL 45ML</t>
         </is>
       </c>
       <c r="C1541" t="n">
-        <v>19440</v>
+        <v>22864</v>
       </c>
       <c r="D1541" t="inlineStr"/>
       <c r="E1541" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1541" t="inlineStr">
@@ -39627,16 +39627,16 @@
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>ME1028</t>
+          <t>ME0504</t>
         </is>
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>TAPA CON APLICADOR PUNTA PINCEL</t>
+          <t>BALA NEGRA LARGA 120ML</t>
         </is>
       </c>
       <c r="C1553" t="n">
-        <v>15877</v>
+        <v>9239</v>
       </c>
       <c r="D1553" t="inlineStr"/>
       <c r="E1553" t="inlineStr">
@@ -39653,16 +39653,16 @@
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>ME1059</t>
+          <t>ME0507</t>
         </is>
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>WIPER ( ESCURRIDOR/BARREDOR) NATURAL</t>
+          <t>BALA TRANSPARENTE 30ML</t>
         </is>
       </c>
       <c r="C1554" t="n">
-        <v>30387</v>
+        <v>24300</v>
       </c>
       <c r="D1554" t="inlineStr"/>
       <c r="E1554" t="inlineStr">
@@ -39679,16 +39679,16 @@
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>ME0504</t>
+          <t>ME1028</t>
         </is>
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>BALA NEGRA LARGA 120ML</t>
+          <t>TAPA CON APLICADOR PUNTA PINCEL</t>
         </is>
       </c>
       <c r="C1555" t="n">
-        <v>9239</v>
+        <v>15877</v>
       </c>
       <c r="D1555" t="inlineStr"/>
       <c r="E1555" t="inlineStr">
@@ -39705,16 +39705,16 @@
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>ME0507</t>
+          <t>ME1059</t>
         </is>
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 30ML</t>
+          <t>WIPER ( ESCURRIDOR/BARREDOR) NATURAL</t>
         </is>
       </c>
       <c r="C1556" t="n">
-        <v>24300</v>
+        <v>30387</v>
       </c>
       <c r="D1556" t="inlineStr"/>
       <c r="E1556" t="inlineStr">
@@ -39913,16 +39913,16 @@
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>ME0523</t>
+          <t>ME0542</t>
         </is>
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>ENVASE PVC COLOR BLANCO POCIMA 6ML</t>
+          <t>TUBO COLAP ANTOBRONCEADORA 120ML V1</t>
         </is>
       </c>
       <c r="C1564" t="n">
-        <v>33606</v>
+        <v>3493</v>
       </c>
       <c r="D1564" t="inlineStr"/>
       <c r="E1564" t="inlineStr">
@@ -39939,16 +39939,16 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>ME0542</t>
+          <t>ME0545</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>TUBO COLAP ANTOBRONCEADORA 120ML V1</t>
+          <t>TUBO COLAP EXFOLIANTE CAPILAR 220GR V1</t>
         </is>
       </c>
       <c r="C1565" t="n">
-        <v>3493</v>
+        <v>1909</v>
       </c>
       <c r="D1565" t="inlineStr"/>
       <c r="E1565" t="inlineStr">
@@ -39965,16 +39965,16 @@
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>ME0545</t>
+          <t>ME0523</t>
         </is>
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>TUBO COLAP EXFOLIANTE CAPILAR 220GR V1</t>
+          <t>ENVASE PVC COLOR BLANCO POCIMA 6ML</t>
         </is>
       </c>
       <c r="C1566" t="n">
-        <v>1909</v>
+        <v>33606</v>
       </c>
       <c r="D1566" t="inlineStr"/>
       <c r="E1566" t="inlineStr">
@@ -39991,16 +39991,16 @@
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>ME1040</t>
+          <t>ME0513</t>
         </is>
       </c>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP 28 MM ROSADO FLAMENCO</t>
+          <t>ENVASE APPLE 28/410 TRANSP P30 M1 300ML</t>
         </is>
       </c>
       <c r="C1567" t="n">
-        <v>17344</v>
+        <v>9838</v>
       </c>
       <c r="D1567" t="inlineStr"/>
       <c r="E1567" t="inlineStr">
@@ -40017,16 +40017,16 @@
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>ME0513</t>
+          <t>ME1040</t>
         </is>
       </c>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>ENVASE APPLE 28/410 TRANSP P30 M1 300ML</t>
+          <t>TAPA FLIP TOP 28 MM ROSADO FLAMENCO</t>
         </is>
       </c>
       <c r="C1568" t="n">
-        <v>9838</v>
+        <v>17344</v>
       </c>
       <c r="D1568" t="inlineStr"/>
       <c r="E1568" t="inlineStr">
@@ -41187,16 +41187,16 @@
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>ME0519</t>
+          <t>ME0544</t>
         </is>
       </c>
       <c r="B1613" t="inlineStr">
         <is>
-          <t>ENVASE PARA CREMA FACIAL TENSORA</t>
+          <t>TUBO COLAP DERMOACLARANTE 60ML V1</t>
         </is>
       </c>
       <c r="C1613" t="n">
-        <v>10009</v>
+        <v>8240</v>
       </c>
       <c r="D1613" t="inlineStr"/>
       <c r="E1613" t="inlineStr">
@@ -41213,16 +41213,16 @@
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>ME1014</t>
+          <t>ME0519</t>
         </is>
       </c>
       <c r="B1614" t="inlineStr">
         <is>
-          <t>SHINE GREEN COLOR PRESS</t>
+          <t>ENVASE PARA CREMA FACIAL TENSORA</t>
         </is>
       </c>
       <c r="C1614" t="n">
-        <v>6885</v>
+        <v>10009</v>
       </c>
       <c r="D1614" t="inlineStr"/>
       <c r="E1614" t="inlineStr">
@@ -41239,16 +41239,16 @@
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>ME0544</t>
+          <t>ME1014</t>
         </is>
       </c>
       <c r="B1615" t="inlineStr">
         <is>
-          <t>TUBO COLAP DERMOACLARANTE 60ML V1</t>
+          <t>SHINE GREEN COLOR PRESS</t>
         </is>
       </c>
       <c r="C1615" t="n">
-        <v>8240</v>
+        <v>6885</v>
       </c>
       <c r="D1615" t="inlineStr"/>
       <c r="E1615" t="inlineStr">
@@ -41629,16 +41629,16 @@
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>ME1012</t>
+          <t>ME1068</t>
         </is>
       </c>
       <c r="B1630" t="inlineStr">
         <is>
-          <t>BOMBA ENCASQUE DORADA/BRONCEADORES</t>
+          <t>TAPA SPRAY BLANCA R 18/410 (DEPILADOR N)</t>
         </is>
       </c>
       <c r="C1630" t="n">
-        <v>27625</v>
+        <v>257740</v>
       </c>
       <c r="D1630" t="inlineStr"/>
       <c r="E1630" t="inlineStr">
@@ -41655,21 +41655,21 @@
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>ET02138</t>
+          <t>ME1012</t>
         </is>
       </c>
       <c r="B1631" t="inlineStr">
         <is>
-          <t>ETIQUETA KERATINA ALISADOR KABA 500 ML</t>
+          <t>BOMBA ENCASQUE DORADA/BRONCEADORES</t>
         </is>
       </c>
       <c r="C1631" t="n">
-        <v>2868</v>
+        <v>27625</v>
       </c>
       <c r="D1631" t="inlineStr"/>
       <c r="E1631" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1631" t="inlineStr">
@@ -41681,16 +41681,16 @@
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>ET02139</t>
+          <t>ET02138</t>
         </is>
       </c>
       <c r="B1632" t="inlineStr">
         <is>
-          <t>ETIQUETA KERATINA ALISADOR KABA 250 ML</t>
+          <t>ETIQUETA KERATINA ALISADOR KABA 500 ML</t>
         </is>
       </c>
       <c r="C1632" t="n">
-        <v>1368</v>
+        <v>2868</v>
       </c>
       <c r="D1632" t="inlineStr"/>
       <c r="E1632" t="inlineStr">
@@ -41707,21 +41707,21 @@
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>ME1068</t>
+          <t>ET02139</t>
         </is>
       </c>
       <c r="B1633" t="inlineStr">
         <is>
-          <t>TAPA SPRAY BLANCA R 18/410 (DEPILADOR N)</t>
+          <t>ETIQUETA KERATINA ALISADOR KABA 250 ML</t>
         </is>
       </c>
       <c r="C1633" t="n">
-        <v>257740</v>
+        <v>1368</v>
       </c>
       <c r="D1633" t="inlineStr"/>
       <c r="E1633" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1633" t="inlineStr">
@@ -42587,21 +42587,21 @@
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>ET0202CA</t>
+          <t>190102</t>
         </is>
       </c>
       <c r="B1667" t="inlineStr">
         <is>
-          <t>ETIQUETA ILUMINADOR GOLD ROSE CARA</t>
+          <t>CARBÓN ACTIVADO</t>
         </is>
       </c>
       <c r="C1667" t="n">
-        <v>3916</v>
+        <v>500</v>
       </c>
       <c r="D1667" t="inlineStr"/>
       <c r="E1667" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1667" t="inlineStr">
@@ -42613,21 +42613,21 @@
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>190102</t>
+          <t>ET0202CA</t>
         </is>
       </c>
       <c r="B1668" t="inlineStr">
         <is>
-          <t>CARBÓN ACTIVADO</t>
+          <t>ETIQUETA ILUMINADOR GOLD ROSE CARA</t>
         </is>
       </c>
       <c r="C1668" t="n">
-        <v>500</v>
+        <v>3916</v>
       </c>
       <c r="D1668" t="inlineStr"/>
       <c r="E1668" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1668" t="inlineStr">
@@ -42691,21 +42691,21 @@
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>ETC0160</t>
+          <t>ME0553</t>
         </is>
       </c>
       <c r="B1671" t="inlineStr">
         <is>
-          <t>CAJA RUBOR EN CREMA RUBY</t>
+          <t>TUBO COLAP TTO REVITALIZANTE 230ML V1</t>
         </is>
       </c>
       <c r="C1671" t="n">
-        <v>10536</v>
+        <v>478</v>
       </c>
       <c r="D1671" t="inlineStr"/>
       <c r="E1671" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1671" t="inlineStr">
@@ -42717,16 +42717,16 @@
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>ETC0161</t>
+          <t>ETC0160</t>
         </is>
       </c>
       <c r="B1672" t="inlineStr">
         <is>
-          <t>CAJA RUBOR EN CREMA SALLY</t>
+          <t>CAJA RUBOR EN CREMA RUBY</t>
         </is>
       </c>
       <c r="C1672" t="n">
-        <v>10328</v>
+        <v>10536</v>
       </c>
       <c r="D1672" t="inlineStr"/>
       <c r="E1672" t="inlineStr">
@@ -42743,21 +42743,21 @@
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>ME0553</t>
+          <t>ETC0161</t>
         </is>
       </c>
       <c r="B1673" t="inlineStr">
         <is>
-          <t>TUBO COLAP TTO REVITALIZANTE 230ML V1</t>
+          <t>CAJA RUBOR EN CREMA SALLY</t>
         </is>
       </c>
       <c r="C1673" t="n">
-        <v>478</v>
+        <v>10328</v>
       </c>
       <c r="D1673" t="inlineStr"/>
       <c r="E1673" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1673" t="inlineStr">
@@ -43289,21 +43289,21 @@
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>ETC0173</t>
+          <t>ME0506</t>
         </is>
       </c>
       <c r="B1694" t="inlineStr">
         <is>
-          <t>CAJA TONICO CAPILAR KABA ROSADA 120ML</t>
+          <t>BALA TRANSPARENTE 260/250 ML</t>
         </is>
       </c>
       <c r="C1694" t="n">
-        <v>193</v>
+        <v>9784</v>
       </c>
       <c r="D1694" t="inlineStr"/>
       <c r="E1694" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1694" t="inlineStr">
@@ -43315,21 +43315,21 @@
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>ME0506</t>
+          <t>ETC0173</t>
         </is>
       </c>
       <c r="B1695" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 260/250 ML</t>
+          <t>CAJA TONICO CAPILAR KABA ROSADA 120ML</t>
         </is>
       </c>
       <c r="C1695" t="n">
-        <v>9784</v>
+        <v>193</v>
       </c>
       <c r="D1695" t="inlineStr"/>
       <c r="E1695" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1695" t="inlineStr">

--- a/inventario_operaciones.xlsx
+++ b/inventario_operaciones.xlsx
@@ -1903,19 +1903,19 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>KM041307</t>
+          <t>D031004</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ILUMINADOR LIQUIDO DAILY SHINE</t>
+          <t>MINI BRONCEADOR ZANAHORIA CANELA DLUCHI</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>642</v>
+        <v>326</v>
       </c>
       <c r="D54" t="n">
-        <v>101.6793893129771</v>
+        <v>4990.534351145038</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1931,19 +1931,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>D031004</t>
+          <t>KM041307</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MINI BRONCEADOR ZANAHORIA CANELA DLUCHI</t>
+          <t>ILUMINADOR LIQUIDO DAILY SHINE</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>326</v>
+        <v>642</v>
       </c>
       <c r="D55" t="n">
-        <v>4990.534351145038</v>
+        <v>101.6793893129771</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="D96" t="n">
         <v>8045.038167938931</v>
@@ -11589,18 +11589,20 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>KM041316</t>
+          <t>KITK0302</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>BASE LIQUIDA ALMENDRA</t>
+          <t>KIT AXILAS PERFECTAS KABA</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>1381</v>
-      </c>
-      <c r="D412" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="D412" t="n">
+        <v>324.2748091603053</v>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -11615,20 +11617,18 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>KITK0302</t>
+          <t>KM041316</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>KIT AXILAS PERFECTAS KABA</t>
+          <t>BASE LIQUIDA ALMENDRA</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>36</v>
-      </c>
-      <c r="D413" t="n">
-        <v>324.2748091603053</v>
-      </c>
+        <v>1381</v>
+      </c>
+      <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -12027,16 +12027,16 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>KITC010201</t>
+          <t>C030606</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>KIT VIVIANA GRONDONA</t>
+          <t>GLOW GIRLS SOPHIE ECHEVERRRI</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>2981</v>
+        <v>8160</v>
       </c>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
@@ -12053,16 +12053,16 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>C030606</t>
+          <t>KITC010201</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>GLOW GIRLS SOPHIE ECHEVERRRI</t>
+          <t>KIT VIVIANA GRONDONA</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>8160</v>
+        <v>2981</v>
       </c>
       <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
@@ -14545,21 +14545,21 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>K051701</t>
+          <t>ETC0164</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>CAMARA INSTANTANEA</t>
+          <t>CAJA PR BOX MEXICO</t>
         </is>
       </c>
       <c r="C524" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="D524" t="inlineStr"/>
       <c r="E524" t="inlineStr">
         <is>
-          <t>PRODUCTO MANUFACTURADO</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
@@ -14571,16 +14571,16 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>ETC0164</t>
+          <t>TA0104</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>CAJA PR BOX MEXICO</t>
+          <t>TARJETA KABA MAKEUP</t>
         </is>
       </c>
       <c r="C525" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D525" t="inlineStr"/>
       <c r="E525" t="inlineStr">
@@ -14597,21 +14597,21 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>TA0104</t>
+          <t>K051701</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>TARJETA KABA MAKEUP</t>
+          <t>CAMARA INSTANTANEA</t>
         </is>
       </c>
       <c r="C526" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D526" t="inlineStr"/>
       <c r="E526" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>PRODUCTO MANUFACTURADO</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
@@ -15471,12 +15471,12 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-37</t>
+          <t>VB020103-03-02-M-20</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-AZUL BEBE-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C561" t="n">
@@ -15493,12 +15493,12 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>VB020103-03-02-M-20</t>
+          <t>VB020103-05-01-S-37</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -15739,16 +15739,16 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-16</t>
+          <t>VB020101-01-04-U-06</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C573" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr"/>
@@ -15761,16 +15761,16 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-06</t>
+          <t>VB020101-01-01-S-16</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-AZUL CELESTE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-ROJO</t>
         </is>
       </c>
       <c r="C574" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D574" t="inlineStr"/>
       <c r="E574" t="inlineStr"/>
@@ -16245,19 +16245,23 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>VB020103-03-01-S-20</t>
+          <t>K051501</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
+          <t>COSMETIQUERA GRANDE KABA</t>
         </is>
       </c>
       <c r="C596" t="n">
-        <v>5</v>
+        <v>3813</v>
       </c>
       <c r="D596" t="inlineStr"/>
-      <c r="E596" t="inlineStr"/>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>COMPRA GRAVADA SIN LOTES</t>
+        </is>
+      </c>
       <c r="F596" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -16267,16 +16271,16 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>VB020101-02-02-M-17</t>
+          <t>VB0103-01-01-S-01</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-M-ROSADO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-BLANCO</t>
         </is>
       </c>
       <c r="C597" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D597" t="inlineStr"/>
       <c r="E597" t="inlineStr"/>
@@ -16289,23 +16293,19 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>K051501</t>
+          <t>VB020103-03-01-S-20</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE KABA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C598" t="n">
-        <v>3813</v>
+        <v>5</v>
       </c>
       <c r="D598" t="inlineStr"/>
-      <c r="E598" t="inlineStr">
-        <is>
-          <t>COMPRA GRAVADA SIN LOTES</t>
-        </is>
-      </c>
+      <c r="E598" t="inlineStr"/>
       <c r="F598" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -16315,16 +16315,16 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-01</t>
+          <t>VB020101-02-02-M-17</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-M-ROSADO</t>
         </is>
       </c>
       <c r="C599" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr"/>
@@ -16425,16 +16425,16 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-01</t>
+          <t>VB020205-03-02-M-28</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-PITON BEIGE</t>
         </is>
       </c>
       <c r="C604" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr"/>
@@ -16447,16 +16447,16 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>VB0105-01-01-S-31</t>
+          <t>VB0302-01-01-S-09</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-S-SAFARI</t>
+          <t>PANTALON ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C605" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D605" t="inlineStr"/>
       <c r="E605" t="inlineStr"/>
@@ -16469,16 +16469,16 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-32</t>
+          <t>VB020104-01-01-S-17</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-ROSADO</t>
         </is>
       </c>
       <c r="C606" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr"/>
@@ -16491,16 +16491,16 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>VB020103-01-02-M-26</t>
+          <t>VB020303-01-01-S-26</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
         </is>
       </c>
       <c r="C607" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D607" t="inlineStr"/>
       <c r="E607" t="inlineStr"/>
@@ -16513,16 +16513,16 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-08</t>
+          <t>VB0105-01-03-L-31</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
+          <t>VB ENTERO TANGA-L-SAFARI</t>
         </is>
       </c>
       <c r="C608" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr"/>
@@ -16535,12 +16535,12 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-11</t>
+          <t>VB0103-01-01-S-02</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-NEGRO</t>
         </is>
       </c>
       <c r="C609" t="n">
@@ -16557,16 +16557,16 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-04</t>
+          <t>VB020205-02-02-M-04</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AMARILLO</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-AMARILLO</t>
         </is>
       </c>
       <c r="C610" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr"/>
@@ -16579,16 +16579,16 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>VB020101-03-01-S-01</t>
+          <t>VB020303-01-02-M-25</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-S-BLANCO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C611" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr"/>
@@ -16601,16 +16601,16 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-03</t>
+          <t>VB020204-01-03-L-07</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C612" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr"/>
@@ -16623,16 +16623,16 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>VB020101-03-03-L-01</t>
+          <t>VB020103-02-01-S-03</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C613" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
@@ -16645,16 +16645,16 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-02</t>
+          <t>VB020101-03-03-L-01</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-L-BLANCO</t>
         </is>
       </c>
       <c r="C614" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
@@ -16667,16 +16667,16 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-01</t>
+          <t>VB020105-01-01-S-01</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
         </is>
       </c>
       <c r="C615" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr"/>
@@ -16689,16 +16689,16 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-17</t>
+          <t>VB020202-01-02-M-02</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-ROSADO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C616" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr"/>
@@ -16711,16 +16711,16 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-03</t>
+          <t>VB020203-01-01-S-01</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
         </is>
       </c>
       <c r="C617" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr"/>
@@ -16733,12 +16733,12 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-13</t>
+          <t>VB020101-01-03-L-17</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-ROSADO</t>
         </is>
       </c>
       <c r="C618" t="n">
@@ -16755,16 +16755,16 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-02</t>
+          <t>VB0306-01-01-S-03</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-NEGRO</t>
+          <t>TOP BÁSICO LUISA-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C619" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D619" t="inlineStr"/>
       <c r="E619" t="inlineStr"/>
@@ -16777,16 +16777,16 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-02</t>
+          <t>VB020103-01-02-M-26</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
         </is>
       </c>
       <c r="C620" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D620" t="inlineStr"/>
       <c r="E620" t="inlineStr"/>
@@ -16799,16 +16799,16 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-17</t>
+          <t>VB0105-01-01-S-31</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-ROSADO</t>
+          <t>VB ENTERO TANGA-S-SAFARI</t>
         </is>
       </c>
       <c r="C621" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D621" t="inlineStr"/>
       <c r="E621" t="inlineStr"/>
@@ -16821,16 +16821,16 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>VB020205-03-02-M-28</t>
+          <t>VB0302-01-02-M-01</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-PITON BEIGE</t>
+          <t>PANTALON ALTO-M-BLANCO</t>
         </is>
       </c>
       <c r="C622" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D622" t="inlineStr"/>
       <c r="E622" t="inlineStr"/>
@@ -16843,12 +16843,12 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-09</t>
+          <t>VB020204-01-01-S-11</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-BEIGE</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C623" t="n">
@@ -16865,16 +16865,16 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-26</t>
+          <t>VB0103-01-01-S-32</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C624" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D624" t="inlineStr"/>
       <c r="E624" t="inlineStr"/>
@@ -16887,12 +16887,12 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-17</t>
+          <t>VB020105-01-01-S-08</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
         </is>
       </c>
       <c r="C625" t="n">
@@ -16909,16 +16909,16 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>VB0105-01-03-L-31</t>
+          <t>VB020101-03-01-S-01</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-L-SAFARI</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-S-BLANCO</t>
         </is>
       </c>
       <c r="C626" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D626" t="inlineStr"/>
       <c r="E626" t="inlineStr"/>
@@ -16931,16 +16931,16 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-02</t>
+          <t>VB0306-01-02-M-02</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-NEGRO</t>
+          <t>TOP BÁSICO LUISA-M-NEGRO</t>
         </is>
       </c>
       <c r="C627" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D627" t="inlineStr"/>
       <c r="E627" t="inlineStr"/>
@@ -16953,16 +16953,16 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-04</t>
+          <t>VB020101-01-04-U-03</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-AMARILLO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-AGUAMARINA</t>
         </is>
       </c>
       <c r="C628" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D628" t="inlineStr"/>
       <c r="E628" t="inlineStr"/>
@@ -16975,16 +16975,16 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-25</t>
+          <t>VB0105-02-02-M-02</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS VERDES</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-NEGRO</t>
         </is>
       </c>
       <c r="C629" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D629" t="inlineStr"/>
       <c r="E629" t="inlineStr"/>
@@ -16997,16 +16997,16 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-07</t>
+          <t>VB020105-01-02-M-13</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
         </is>
       </c>
       <c r="C630" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D630" t="inlineStr"/>
       <c r="E630" t="inlineStr"/>
@@ -17019,16 +17019,16 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-03</t>
+          <t>VB020202-01-01-S-04</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AMARILLO</t>
         </is>
       </c>
       <c r="C631" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D631" t="inlineStr"/>
       <c r="E631" t="inlineStr"/>
@@ -17041,12 +17041,12 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-01</t>
+          <t>VB020104-01-01-S-02</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-NEGRO</t>
         </is>
       </c>
       <c r="C632" t="n">
@@ -17063,19 +17063,25 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-02</t>
+          <t>D051601</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-NEGRO</t>
+          <t>CEPILLO APLICADOR AUTOBRONCEADOR DLUCHI</t>
         </is>
       </c>
       <c r="C633" t="n">
-        <v>3</v>
-      </c>
-      <c r="D633" t="inlineStr"/>
-      <c r="E633" t="inlineStr"/>
+        <v>936</v>
+      </c>
+      <c r="D633" t="n">
+        <v>1017.137404580153</v>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>PRODUCTO MANUFACTURADO</t>
+        </is>
+      </c>
       <c r="F633" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -17085,25 +17091,19 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>D051601</t>
+          <t>VB020204-01-01-S-08</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>CEPILLO APLICADOR AUTOBRONCEADOR DLUCHI</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
         </is>
       </c>
       <c r="C634" t="n">
-        <v>936</v>
-      </c>
-      <c r="D634" t="n">
-        <v>1017.137404580153</v>
-      </c>
-      <c r="E634" t="inlineStr">
-        <is>
-          <t>PRODUCTO MANUFACTURADO</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D634" t="inlineStr"/>
+      <c r="E634" t="inlineStr"/>
       <c r="F634" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -17113,16 +17113,16 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-08</t>
+          <t>VB020203-01-01-S-17</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-ROSADO</t>
         </is>
       </c>
       <c r="C635" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr"/>
@@ -17135,16 +17135,16 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-17</t>
+          <t>VB020101-01-04-U-17</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-ROSADO</t>
         </is>
       </c>
       <c r="C636" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D636" t="inlineStr"/>
       <c r="E636" t="inlineStr"/>
@@ -17223,16 +17223,16 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-23</t>
+          <t>VB020205-02-02-M-10</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-FUCSIA</t>
         </is>
       </c>
       <c r="C640" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D640" t="inlineStr"/>
       <c r="E640" t="inlineStr"/>
@@ -17245,16 +17245,16 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-14</t>
+          <t>VB020202-01-03-L-19</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C641" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr"/>
@@ -17267,16 +17267,16 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-19</t>
+          <t>VB0306-01-02-M-14</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-ANIMAL PRINT CAFÉ</t>
+          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C642" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D642" t="inlineStr"/>
       <c r="E642" t="inlineStr"/>
@@ -17289,16 +17289,16 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-10</t>
+          <t>VB0306-01-01-S-01</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-FUCSIA</t>
+          <t>TOP BÁSICO LUISA-S-BLANCO</t>
         </is>
       </c>
       <c r="C643" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D643" t="inlineStr"/>
       <c r="E643" t="inlineStr"/>
@@ -17333,16 +17333,16 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-01</t>
+          <t>VB020105-01-02-M-08</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
         </is>
       </c>
       <c r="C645" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D645" t="inlineStr"/>
       <c r="E645" t="inlineStr"/>
@@ -17355,16 +17355,16 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>VB0104-01-02-M-09</t>
+          <t>VB0104-01-03-L-09</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-BEIGE</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-BEIGE</t>
         </is>
       </c>
       <c r="C646" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D646" t="inlineStr"/>
       <c r="E646" t="inlineStr"/>
@@ -17377,16 +17377,16 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>VB020203-01-03-L-01</t>
+          <t>VB020101-01-03-L-15</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PURPURA</t>
         </is>
       </c>
       <c r="C647" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D647" t="inlineStr"/>
       <c r="E647" t="inlineStr"/>
@@ -17399,16 +17399,16 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>VB020203-01-03-L-02</t>
+          <t>VB020103-02-02-M-03</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C648" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D648" t="inlineStr"/>
       <c r="E648" t="inlineStr"/>
@@ -17421,16 +17421,16 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>VB0303-01-02-M-01</t>
+          <t>VB0104-01-02-M-09</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>SHORT ALTO-M-BLANCO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-BEIGE</t>
         </is>
       </c>
       <c r="C649" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D649" t="inlineStr"/>
       <c r="E649" t="inlineStr"/>
@@ -17443,16 +17443,16 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>VB020205-03-01-S-21</t>
+          <t>VB020203-01-03-L-02</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-ASTRAL</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-NEGRO</t>
         </is>
       </c>
       <c r="C650" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D650" t="inlineStr"/>
       <c r="E650" t="inlineStr"/>
@@ -17465,16 +17465,16 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>VB020101-02-03-L-01</t>
+          <t>VB020203-01-03-L-01</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-BLANCO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-BLANCO</t>
         </is>
       </c>
       <c r="C651" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D651" t="inlineStr"/>
       <c r="E651" t="inlineStr"/>
@@ -17487,16 +17487,16 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>VB020402-01-03-L-31</t>
+          <t>VB0303-01-02-M-01</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS BUSO TALLE ALTO-L-SAFARI</t>
+          <t>SHORT ALTO-M-BLANCO</t>
         </is>
       </c>
       <c r="C652" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr"/>
@@ -17509,16 +17509,16 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>VB0104-01-03-L-09</t>
+          <t>VB020202-01-02-M-23</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-BEIGE</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C653" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D653" t="inlineStr"/>
       <c r="E653" t="inlineStr"/>
@@ -17531,16 +17531,16 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-08</t>
+          <t>VB020101-02-03-L-01</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-BLANCO</t>
         </is>
       </c>
       <c r="C654" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D654" t="inlineStr"/>
       <c r="E654" t="inlineStr"/>
@@ -17553,16 +17553,16 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-15</t>
+          <t>VB020205-03-01-S-21</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PURPURA</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-ASTRAL</t>
         </is>
       </c>
       <c r="C655" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D655" t="inlineStr"/>
       <c r="E655" t="inlineStr"/>
@@ -17575,16 +17575,16 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>VB020103-02-02-M-03</t>
+          <t>VB020402-01-03-L-31</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
+          <t>VB DOS PIEZAS BUSO TALLE ALTO-L-SAFARI</t>
         </is>
       </c>
       <c r="C656" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D656" t="inlineStr"/>
       <c r="E656" t="inlineStr"/>
@@ -17663,16 +17663,16 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>VB020101-02-03-L-17</t>
+          <t>VB0305-01-04-U-02</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-ROSADO</t>
+          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-NEGRO</t>
         </is>
       </c>
       <c r="C660" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D660" t="inlineStr"/>
       <c r="E660" t="inlineStr"/>
@@ -17685,16 +17685,16 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>VB0305-01-04-U-02</t>
+          <t>VB020101-02-03-L-17</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-ROSADO</t>
         </is>
       </c>
       <c r="C661" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D661" t="inlineStr"/>
       <c r="E661" t="inlineStr"/>
@@ -17729,16 +17729,16 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-37</t>
+          <t>VB020103-05-03-L-36</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-AZUL BEBE-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C663" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr"/>
@@ -17751,16 +17751,16 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-01</t>
+          <t>VB0105-01-02-M-31</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-BLANCO</t>
+          <t>VB ENTERO TANGA-M-SAFARI</t>
         </is>
       </c>
       <c r="C664" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D664" t="inlineStr"/>
       <c r="E664" t="inlineStr"/>
@@ -17773,16 +17773,16 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-36</t>
+          <t>VB020204-01-03-L-11</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C665" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D665" t="inlineStr"/>
       <c r="E665" t="inlineStr"/>
@@ -17795,16 +17795,16 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>VB0105-01-02-M-31</t>
+          <t>VB020101-01-04-U-01</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-M-SAFARI</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-BLANCO</t>
         </is>
       </c>
       <c r="C666" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D666" t="inlineStr"/>
       <c r="E666" t="inlineStr"/>
@@ -17817,16 +17817,16 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-11</t>
+          <t>VB020103-05-03-L-37</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C667" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D667" t="inlineStr"/>
       <c r="E667" t="inlineStr"/>
@@ -17839,16 +17839,16 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>VB020205-03-03-L-21</t>
+          <t>VB020202-01-01-S-08</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-ASTRAL</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL REY</t>
         </is>
       </c>
       <c r="C668" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D668" t="inlineStr"/>
       <c r="E668" t="inlineStr"/>
@@ -17861,16 +17861,16 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-08</t>
+          <t>VB020205-03-03-L-21</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-ASTRAL</t>
         </is>
       </c>
       <c r="C669" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D669" t="inlineStr"/>
       <c r="E669" t="inlineStr"/>
@@ -17927,16 +17927,16 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-03</t>
+          <t>VB020303-01-03-L-19</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C672" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D672" t="inlineStr"/>
       <c r="E672" t="inlineStr"/>
@@ -17949,16 +17949,16 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>VB0105-01-03-L-23</t>
+          <t>VB020203-01-02-M-01</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-L-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-BLANCO</t>
         </is>
       </c>
       <c r="C673" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D673" t="inlineStr"/>
       <c r="E673" t="inlineStr"/>
@@ -17971,16 +17971,16 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-33</t>
+          <t>VB020202-01-02-M-04</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-TIE DYE</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AMARILLO</t>
         </is>
       </c>
       <c r="C674" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D674" t="inlineStr"/>
       <c r="E674" t="inlineStr"/>
@@ -17993,12 +17993,12 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-08</t>
+          <t>VB020104-01-03-L-03</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C675" t="n">
@@ -18015,16 +18015,16 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-16</t>
+          <t>VB020101-01-01-S-06</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C676" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D676" t="inlineStr"/>
       <c r="E676" t="inlineStr"/>
@@ -18037,16 +18037,16 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-19</t>
+          <t>VB020203-01-02-M-17</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-ROSADO</t>
         </is>
       </c>
       <c r="C677" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D677" t="inlineStr"/>
       <c r="E677" t="inlineStr"/>
@@ -18059,16 +18059,16 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>VB020203-01-02-M-01</t>
+          <t>VB020202-01-01-S-23</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C678" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D678" t="inlineStr"/>
       <c r="E678" t="inlineStr"/>
@@ -18081,12 +18081,12 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-04</t>
+          <t>VB020105-01-01-S-16</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AMARILLO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
         </is>
       </c>
       <c r="C679" t="n">
@@ -18103,16 +18103,16 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-03</t>
+          <t>VB020202-01-02-M-19</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C680" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D680" t="inlineStr"/>
       <c r="E680" t="inlineStr"/>
@@ -18125,16 +18125,16 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-06</t>
+          <t>VB0302-01-03-L-02</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AZUL CELESTE</t>
+          <t>PANTALON ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C681" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
@@ -18147,16 +18147,16 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>VB020203-01-02-M-17</t>
+          <t>VB020205-02-01-S-22</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-ROSADO</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-FLORES</t>
         </is>
       </c>
       <c r="C682" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr"/>
@@ -18169,16 +18169,16 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-23</t>
+          <t>VB0105-02-01-S-17</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-ROSADO</t>
         </is>
       </c>
       <c r="C683" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
@@ -18191,16 +18191,16 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-16</t>
+          <t>VB020103-04-03-L-09</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-BEIGE</t>
         </is>
       </c>
       <c r="C684" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D684" t="inlineStr"/>
       <c r="E684" t="inlineStr"/>
@@ -18213,16 +18213,16 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-19</t>
+          <t>VB020203-01-01-S-02</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-NEGRO</t>
         </is>
       </c>
       <c r="C685" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
@@ -18235,16 +18235,16 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-02</t>
+          <t>VB020103-01-01-S-26</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-S-MISTICO</t>
         </is>
       </c>
       <c r="C686" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D686" t="inlineStr"/>
       <c r="E686" t="inlineStr"/>
@@ -18257,12 +18257,12 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-09</t>
+          <t>VB020103-01-03-L-26</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-L-MISTICO</t>
         </is>
       </c>
       <c r="C687" t="n">
@@ -18279,12 +18279,12 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-22</t>
+          <t>VB020103-03-03-L-20</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-FLORES</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C688" t="n">
@@ -18301,16 +18301,16 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>VB020103-03-03-L-20</t>
+          <t>VB020204-01-02-M-13</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
         </is>
       </c>
       <c r="C689" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D689" t="inlineStr"/>
       <c r="E689" t="inlineStr"/>
@@ -18323,16 +18323,16 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>VB0103-01-02-M-01</t>
+          <t>VB020101-01-02-M-16</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ROJO</t>
         </is>
       </c>
       <c r="C690" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D690" t="inlineStr"/>
       <c r="E690" t="inlineStr"/>
@@ -18345,16 +18345,16 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>VB020103-01-01-S-26</t>
+          <t>VB020101-01-02-M-17</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-S-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ROSADO</t>
         </is>
       </c>
       <c r="C691" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D691" t="inlineStr"/>
       <c r="E691" t="inlineStr"/>
@@ -18367,16 +18367,16 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-02</t>
+          <t>VB020103-02-03-L-17</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-ROSADO</t>
         </is>
       </c>
       <c r="C692" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D692" t="inlineStr"/>
       <c r="E692" t="inlineStr"/>
@@ -18389,16 +18389,16 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-17</t>
+          <t>VB020101-01-01-S-14</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C693" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D693" t="inlineStr"/>
       <c r="E693" t="inlineStr"/>
@@ -18411,16 +18411,16 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>VB020103-01-03-L-26</t>
+          <t>VB0103-01-02-M-01</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-L-MISTICO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-BLANCO</t>
         </is>
       </c>
       <c r="C694" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D694" t="inlineStr"/>
       <c r="E694" t="inlineStr"/>
@@ -18433,16 +18433,16 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-13</t>
+          <t>VB020205-02-02-M-22</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-FLORES</t>
         </is>
       </c>
       <c r="C695" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D695" t="inlineStr"/>
       <c r="E695" t="inlineStr"/>
@@ -18455,12 +18455,12 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-16</t>
+          <t>VB020205-02-03-L-04</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ROJO</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-AMARILLO</t>
         </is>
       </c>
       <c r="C696" t="n">
@@ -18477,16 +18477,16 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-09</t>
+          <t>VB020101-01-03-L-01</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-BLANCO</t>
         </is>
       </c>
       <c r="C697" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D697" t="inlineStr"/>
       <c r="E697" t="inlineStr"/>
@@ -18499,16 +18499,16 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>VB020205-03-02-M-21</t>
+          <t>VB020303-01-03-L-34</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-ASTRAL</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-FAUNA</t>
         </is>
       </c>
       <c r="C698" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D698" t="inlineStr"/>
       <c r="E698" t="inlineStr"/>
@@ -18521,12 +18521,12 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-15</t>
+          <t>VB020103-02-03-L-03</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C699" t="n">
@@ -18543,16 +18543,16 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-25</t>
+          <t>VB0105-02-01-S-33</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-HOJAS VERDES</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-TIE DYE</t>
         </is>
       </c>
       <c r="C700" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D700" t="inlineStr"/>
       <c r="E700" t="inlineStr"/>
@@ -18565,12 +18565,12 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-09</t>
+          <t>VB0105-02-01-S-02</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-BEIGE</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-NEGRO</t>
         </is>
       </c>
       <c r="C701" t="n">
@@ -18587,16 +18587,16 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>VB0305-01-04-U-09</t>
+          <t>VB0306-01-03-L-16</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-BEIGE</t>
+          <t>TOP BÁSICO LUISA-L-ROJO</t>
         </is>
       </c>
       <c r="C702" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D702" t="inlineStr"/>
       <c r="E702" t="inlineStr"/>
@@ -18609,16 +18609,16 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-30</t>
+          <t>VB020202-01-02-M-08</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AZUL REY</t>
         </is>
       </c>
       <c r="C703" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr"/>
@@ -18631,16 +18631,16 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-06</t>
+          <t>VB0306-01-01-S-16</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AZUL CELESTE</t>
+          <t>TOP BÁSICO LUISA-S-ROJO</t>
         </is>
       </c>
       <c r="C704" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D704" t="inlineStr"/>
       <c r="E704" t="inlineStr"/>
@@ -18653,16 +18653,16 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>VB0301-01-04-U-09</t>
+          <t>VB020103-04-02-M-28</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>FALDA GAIA MACRAME-U-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-PITON BEIGE</t>
         </is>
       </c>
       <c r="C705" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr"/>
@@ -18675,16 +18675,16 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>VB0105-02-03-L-18</t>
+          <t>VB020202-01-03-L-08</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-VERDE MENTA</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL REY</t>
         </is>
       </c>
       <c r="C706" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D706" t="inlineStr"/>
       <c r="E706" t="inlineStr"/>
@@ -18697,12 +18697,12 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-25</t>
+          <t>VB0303-01-01-S-09</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS VERDES</t>
+          <t>SHORT ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C707" t="n">
@@ -18719,16 +18719,16 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-19</t>
+          <t>VB020205-02-03-L-07</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C708" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D708" t="inlineStr"/>
       <c r="E708" t="inlineStr"/>
@@ -18741,16 +18741,16 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-03</t>
+          <t>VB0103-01-03-L-16</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AGUAMARINA</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-ROJO</t>
         </is>
       </c>
       <c r="C709" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D709" t="inlineStr"/>
       <c r="E709" t="inlineStr"/>
@@ -18763,16 +18763,16 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-28</t>
+          <t>VB0103-01-03-L-32</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-PITON BEIGE</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C710" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D710" t="inlineStr"/>
       <c r="E710" t="inlineStr"/>
@@ -18785,16 +18785,16 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-08</t>
+          <t>VB020204-01-03-L-08</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
         </is>
       </c>
       <c r="C711" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D711" t="inlineStr"/>
       <c r="E711" t="inlineStr"/>
@@ -18807,16 +18807,16 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-16</t>
+          <t>VB020103-05-01-S-36</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C712" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D712" t="inlineStr"/>
       <c r="E712" t="inlineStr"/>
@@ -18829,16 +18829,16 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-02</t>
+          <t>VB0105-01-03-L-23</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-NEGRO</t>
+          <t>VB ENTERO TANGA-L-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C713" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D713" t="inlineStr"/>
       <c r="E713" t="inlineStr"/>
@@ -18851,16 +18851,16 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>VB0303-01-01-S-09</t>
+          <t>VB0304-01-03-L-02</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>SHORT ALTO-S-BEIGE</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-L-NEGRO</t>
         </is>
       </c>
       <c r="C714" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D714" t="inlineStr"/>
       <c r="E714" t="inlineStr"/>
@@ -18873,16 +18873,16 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>VB0104-01-03-L-02</t>
+          <t>VB020202-01-03-L-02</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C715" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D715" t="inlineStr"/>
       <c r="E715" t="inlineStr"/>
@@ -18895,16 +18895,16 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-24</t>
+          <t>VB0104-01-03-L-02</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS NEGRO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-NEGRO</t>
         </is>
       </c>
       <c r="C716" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr"/>
@@ -18917,16 +18917,16 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-12</t>
+          <t>VB020303-01-01-S-24</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-MORADO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C717" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D717" t="inlineStr"/>
       <c r="E717" t="inlineStr"/>
@@ -18939,16 +18939,16 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-09</t>
+          <t>VB020205-02-01-S-12</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-BEIGE</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-MORADO</t>
         </is>
       </c>
       <c r="C718" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D718" t="inlineStr"/>
       <c r="E718" t="inlineStr"/>
@@ -18961,16 +18961,16 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-16</t>
+          <t>VB020204-01-02-M-08</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-ROJO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
         </is>
       </c>
       <c r="C719" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D719" t="inlineStr"/>
       <c r="E719" t="inlineStr"/>
@@ -18983,16 +18983,16 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-08</t>
+          <t>VB0302-01-03-L-09</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
+          <t>PANTALON ALTO-L-BEIGE</t>
         </is>
       </c>
       <c r="C720" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D720" t="inlineStr"/>
       <c r="E720" t="inlineStr"/>
@@ -19027,16 +19027,16 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-07</t>
+          <t>VB0105-02-03-L-18</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-AZUL CIAN</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-VERDE MENTA</t>
         </is>
       </c>
       <c r="C722" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D722" t="inlineStr"/>
       <c r="E722" t="inlineStr"/>
@@ -19049,16 +19049,16 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-14</t>
+          <t>VB020205-02-02-M-07</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-AZUL CIAN</t>
         </is>
       </c>
       <c r="C723" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="inlineStr"/>
@@ -19071,16 +19071,16 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-17</t>
+          <t>VB020101-01-03-L-06</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C724" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D724" t="inlineStr"/>
       <c r="E724" t="inlineStr"/>
@@ -19093,16 +19093,16 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-17</t>
+          <t>VB020101-01-02-M-14</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C725" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D725" t="inlineStr"/>
       <c r="E725" t="inlineStr"/>
@@ -19115,16 +19115,16 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-14</t>
+          <t>VB020303-01-03-L-30</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
         </is>
       </c>
       <c r="C726" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr"/>
@@ -19137,16 +19137,16 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-22</t>
+          <t>VB0301-01-04-U-09</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-FLORES</t>
+          <t>FALDA GAIA MACRAME-U-BEIGE</t>
         </is>
       </c>
       <c r="C727" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr"/>
@@ -19159,16 +19159,16 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-04</t>
+          <t>VB020101-02-01-S-01</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-AMARILLO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-S-BLANCO</t>
         </is>
       </c>
       <c r="C728" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr"/>
@@ -19181,16 +19181,16 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>VB020101-02-01-S-01</t>
+          <t>VB020104-01-03-L-17</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-ROSADO</t>
         </is>
       </c>
       <c r="C729" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D729" t="inlineStr"/>
       <c r="E729" t="inlineStr"/>
@@ -19203,12 +19203,12 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-17</t>
+          <t>VB0304-01-02-M-02</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-ROSADO</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-M-NEGRO</t>
         </is>
       </c>
       <c r="C730" t="n">
@@ -19225,12 +19225,12 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>VB0304-01-02-M-02</t>
+          <t>VB020204-01-03-L-15</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-M-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
         </is>
       </c>
       <c r="C731" t="n">
@@ -19269,16 +19269,16 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-15</t>
+          <t>VB020101-01-04-U-14</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C733" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D733" t="inlineStr"/>
       <c r="E733" t="inlineStr"/>
@@ -19291,16 +19291,16 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-14</t>
+          <t>VB020205-03-02-M-21</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-ASTRAL</t>
         </is>
       </c>
       <c r="C734" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D734" t="inlineStr"/>
       <c r="E734" t="inlineStr"/>
@@ -19379,16 +19379,16 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>VB0303-01-02-M-09</t>
+          <t>VB020103-04-02-M-09</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>SHORT ALTO-M-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-BEIGE</t>
         </is>
       </c>
       <c r="C738" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D738" t="inlineStr"/>
       <c r="E738" t="inlineStr"/>
@@ -19401,16 +19401,16 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-09</t>
+          <t>VB0303-01-02-M-09</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-BEIGE</t>
+          <t>SHORT ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C739" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D739" t="inlineStr"/>
       <c r="E739" t="inlineStr"/>
@@ -19423,16 +19423,16 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-07</t>
+          <t>VB020204-01-01-S-15</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-PURPURA</t>
         </is>
       </c>
       <c r="C740" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D740" t="inlineStr"/>
       <c r="E740" t="inlineStr"/>
@@ -19445,16 +19445,16 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-34</t>
+          <t>VB0305-01-04-U-09</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-FAUNA</t>
+          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-BEIGE</t>
         </is>
       </c>
       <c r="C741" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D741" t="inlineStr"/>
       <c r="E741" t="inlineStr"/>
@@ -19467,12 +19467,12 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-01</t>
+          <t>VB020101-01-01-S-25</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C742" t="n">
@@ -19489,16 +19489,16 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>VB0304-01-03-L-02</t>
+          <t>VB0302-01-02-M-09</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-L-NEGRO</t>
+          <t>PANTALON ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C743" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D743" t="inlineStr"/>
       <c r="E743" t="inlineStr"/>
@@ -19511,16 +19511,16 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-02</t>
+          <t>VB020103-04-01-S-09</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-BEIGE</t>
         </is>
       </c>
       <c r="C744" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D744" t="inlineStr"/>
       <c r="E744" t="inlineStr"/>
@@ -19533,12 +19533,12 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-36</t>
+          <t>VB020303-01-01-S-19</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C745" t="n">
@@ -19555,12 +19555,12 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-32</t>
+          <t>VB020303-01-01-S-25</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C746" t="n">
@@ -19577,16 +19577,16 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-08</t>
+          <t>VB020101-01-01-S-03</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C747" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D747" t="inlineStr"/>
       <c r="E747" t="inlineStr"/>
@@ -19599,16 +19599,16 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>VB0104-01-01-S-09</t>
+          <t>VB020105-01-03-L-15</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-PURPURA</t>
         </is>
       </c>
       <c r="C748" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D748" t="inlineStr"/>
       <c r="E748" t="inlineStr"/>
@@ -19621,23 +19621,19 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>DISACK010101</t>
+          <t>VB020101-01-02-M-08</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>DISPLEY SACHET DE SHAMPO DE CEBOLLA KABA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AZUL REY</t>
         </is>
       </c>
       <c r="C749" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D749" t="inlineStr"/>
-      <c r="E749" t="inlineStr">
-        <is>
-          <t>PRODUCTO MANUFACTURADO</t>
-        </is>
-      </c>
+      <c r="E749" t="inlineStr"/>
       <c r="F749" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -19647,12 +19643,12 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-19</t>
+          <t>VB020101-01-02-M-05</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C750" t="n">
@@ -19669,12 +19665,12 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>VB0105-02-03-L-17</t>
+          <t>VB020103-04-03-L-28</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-PITON BEIGE</t>
         </is>
       </c>
       <c r="C751" t="n">
@@ -19691,16 +19687,16 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-25</t>
+          <t>VB020101-01-02-M-15</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PURPURA</t>
         </is>
       </c>
       <c r="C752" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D752" t="inlineStr"/>
       <c r="E752" t="inlineStr"/>
@@ -19713,16 +19709,16 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-15</t>
+          <t>VB020101-02-03-L-18</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-VERDE MENTA</t>
         </is>
       </c>
       <c r="C753" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D753" t="inlineStr"/>
       <c r="E753" t="inlineStr"/>
@@ -19735,16 +19731,16 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-08</t>
+          <t>VB0306-01-03-L-03</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AZUL REY</t>
+          <t>TOP BÁSICO LUISA-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C754" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D754" t="inlineStr"/>
       <c r="E754" t="inlineStr"/>
@@ -19757,16 +19753,16 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-05</t>
+          <t>VB0104-01-01-S-09</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AMARILLO NEON</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-BEIGE</t>
         </is>
       </c>
       <c r="C755" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D755" t="inlineStr"/>
       <c r="E755" t="inlineStr"/>
@@ -19779,19 +19775,23 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-28</t>
+          <t>DISACK010101</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-PITON BEIGE</t>
+          <t>DISPLEY SACHET DE SHAMPO DE CEBOLLA KABA</t>
         </is>
       </c>
       <c r="C756" t="n">
         <v>2</v>
       </c>
       <c r="D756" t="inlineStr"/>
-      <c r="E756" t="inlineStr"/>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>PRODUCTO MANUFACTURADO</t>
+        </is>
+      </c>
       <c r="F756" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -19801,16 +19801,16 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-15</t>
+          <t>VB020101-01-02-M-25</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C757" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D757" t="inlineStr"/>
       <c r="E757" t="inlineStr"/>
@@ -19823,16 +19823,16 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>VB020101-02-03-L-18</t>
+          <t>VB0105-02-03-L-17</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-VERDE MENTA</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-ROSADO</t>
         </is>
       </c>
       <c r="C758" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D758" t="inlineStr"/>
       <c r="E758" t="inlineStr"/>
@@ -19845,16 +19845,16 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-03</t>
+          <t>VB020202-01-01-S-19</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C759" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D759" t="inlineStr"/>
       <c r="E759" t="inlineStr"/>
@@ -19889,16 +19889,16 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-24</t>
+          <t>VB020105-01-03-L-13</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
         </is>
       </c>
       <c r="C761" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D761" t="inlineStr"/>
       <c r="E761" t="inlineStr"/>
@@ -19933,16 +19933,16 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-13</t>
+          <t>VB020303-01-03-L-24</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C763" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D763" t="inlineStr"/>
       <c r="E763" t="inlineStr"/>
@@ -20087,16 +20087,16 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-04</t>
+          <t>VB0104-01-01-S-02</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AMARILLO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-NEGRO</t>
         </is>
       </c>
       <c r="C770" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D770" t="inlineStr"/>
       <c r="E770" t="inlineStr"/>
@@ -20109,16 +20109,16 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>VB0104-01-01-S-02</t>
+          <t>VB020202-01-03-L-04</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AMARILLO</t>
         </is>
       </c>
       <c r="C771" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D771" t="inlineStr"/>
       <c r="E771" t="inlineStr"/>
@@ -20329,16 +20329,16 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-05</t>
+          <t>VB020202-01-01-S-02</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
         </is>
       </c>
       <c r="C781" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D781" t="inlineStr"/>
       <c r="E781" t="inlineStr"/>
@@ -20351,16 +20351,16 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-02</t>
+          <t>VB020105-01-01-S-05</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C782" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D782" t="inlineStr"/>
       <c r="E782" t="inlineStr"/>
@@ -21623,16 +21623,16 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>VB0304-01-02-M-09</t>
+          <t>VB0103-01-03-L-16</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-M-BEIGE</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-ROJO</t>
         </is>
       </c>
       <c r="C831" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D831" t="inlineStr"/>
       <c r="E831" t="inlineStr"/>
@@ -21645,16 +21645,16 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-16</t>
+          <t>VB0304-01-02-M-09</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-ROJO</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-M-BEIGE</t>
         </is>
       </c>
       <c r="C832" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D832" t="inlineStr"/>
       <c r="E832" t="inlineStr"/>
@@ -21755,16 +21755,16 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>VB0105-01-03-L-31</t>
+          <t>VB0306-01-02-M-02</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-L-SAFARI</t>
+          <t>TOP BÁSICO LUISA-M-NEGRO</t>
         </is>
       </c>
       <c r="C837" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D837" t="inlineStr"/>
       <c r="E837" t="inlineStr"/>
@@ -21777,16 +21777,16 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-02</t>
+          <t>VB0105-01-03-L-31</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-NEGRO</t>
+          <t>VB ENTERO TANGA-L-SAFARI</t>
         </is>
       </c>
       <c r="C838" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D838" t="inlineStr"/>
       <c r="E838" t="inlineStr"/>
@@ -22107,16 +22107,16 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>VB0303-01-03-L-09</t>
+          <t>VB0104-01-02-M-09</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>SHORT ALTO-L-BEIGE</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-BEIGE</t>
         </is>
       </c>
       <c r="C853" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D853" t="inlineStr"/>
       <c r="E853" t="inlineStr"/>
@@ -22129,16 +22129,16 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>VB0104-01-02-M-09</t>
+          <t>VB0303-01-03-L-09</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-BEIGE</t>
+          <t>SHORT ALTO-L-BEIGE</t>
         </is>
       </c>
       <c r="C854" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D854" t="inlineStr"/>
       <c r="E854" t="inlineStr"/>
@@ -22393,16 +22393,16 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-17</t>
+          <t>VB0306-01-03-L-03</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-ROSADO</t>
+          <t>TOP BÁSICO LUISA-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C866" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D866" t="inlineStr"/>
       <c r="E866" t="inlineStr"/>
@@ -22415,16 +22415,16 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-03</t>
+          <t>VB0105-02-01-S-17</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-AGUAMARINA</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-ROSADO</t>
         </is>
       </c>
       <c r="C867" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D867" t="inlineStr"/>
       <c r="E867" t="inlineStr"/>
@@ -22679,16 +22679,16 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-05</t>
+          <t>VB0302-01-01-S-09</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AMARILLO NEON</t>
+          <t>PANTALON ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C879" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D879" t="inlineStr"/>
       <c r="E879" t="inlineStr"/>
@@ -22701,16 +22701,16 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-09</t>
+          <t>VB020105-01-01-S-05</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C880" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D880" t="inlineStr"/>
       <c r="E880" t="inlineStr"/>
@@ -22811,16 +22811,16 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>VB0301-01-04-U-09</t>
+          <t>VB0302-01-02-M-02</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>FALDA GAIA MACRAME-U-BEIGE</t>
+          <t>PANTALON ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C885" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D885" t="inlineStr"/>
       <c r="E885" t="inlineStr"/>
@@ -22833,16 +22833,16 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-02</t>
+          <t>VB0301-01-04-U-09</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-NEGRO</t>
+          <t>FALDA GAIA MACRAME-U-BEIGE</t>
         </is>
       </c>
       <c r="C886" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D886" t="inlineStr"/>
       <c r="E886" t="inlineStr"/>
@@ -22965,16 +22965,16 @@
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-09</t>
+          <t>VB0105-01-02-M-23</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-BEIGE</t>
+          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C892" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D892" t="inlineStr"/>
       <c r="E892" t="inlineStr"/>
@@ -22987,16 +22987,16 @@
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-08</t>
+          <t>VB020204-01-01-S-07</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL CIAN</t>
         </is>
       </c>
       <c r="C893" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D893" t="inlineStr"/>
       <c r="E893" t="inlineStr"/>
@@ -23009,16 +23009,16 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-22</t>
+          <t>VB020105-01-02-M-08</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-FLORES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
         </is>
       </c>
       <c r="C894" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D894" t="inlineStr"/>
       <c r="E894" t="inlineStr"/>
@@ -23031,16 +23031,16 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>VB0301-01-04-U-02</t>
+          <t>VB020202-01-03-L-04</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>FALDA GAIA MACRAME-U-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AMARILLO</t>
         </is>
       </c>
       <c r="C895" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D895" t="inlineStr"/>
       <c r="E895" t="inlineStr"/>
@@ -23053,16 +23053,16 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-37</t>
+          <t>VB020202-01-02-M-23</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-AZUL BEBE-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C896" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D896" t="inlineStr"/>
       <c r="E896" t="inlineStr"/>
@@ -23075,16 +23075,16 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-08</t>
+          <t>VB0103-01-03-L-32</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL REY</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C897" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D897" t="inlineStr"/>
       <c r="E897" t="inlineStr"/>
@@ -23097,16 +23097,16 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-35</t>
+          <t>VB020202-01-02-M-22</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-NEGRO-BLANCO HUESO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-FLORES</t>
         </is>
       </c>
       <c r="C898" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D898" t="inlineStr"/>
       <c r="E898" t="inlineStr"/>
@@ -23119,16 +23119,16 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>VB0303-01-01-S-09</t>
+          <t>VB0301-01-04-U-02</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>SHORT ALTO-S-BEIGE</t>
+          <t>FALDA GAIA MACRAME-U-NEGRO</t>
         </is>
       </c>
       <c r="C899" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D899" t="inlineStr"/>
       <c r="E899" t="inlineStr"/>
@@ -23141,16 +23141,16 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>VB020103-01-02-M-26</t>
+          <t>VB020103-05-03-L-37</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C900" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D900" t="inlineStr"/>
       <c r="E900" t="inlineStr"/>
@@ -23163,16 +23163,16 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-09</t>
+          <t>VB020202-01-01-S-08</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-BEIGE</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL REY</t>
         </is>
       </c>
       <c r="C901" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D901" t="inlineStr"/>
       <c r="E901" t="inlineStr"/>
@@ -23185,16 +23185,16 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-04</t>
+          <t>VB0103-01-02-M-16</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AMARILLO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-ROJO</t>
         </is>
       </c>
       <c r="C902" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D902" t="inlineStr"/>
       <c r="E902" t="inlineStr"/>
@@ -23207,16 +23207,16 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>VB0103-01-02-M-16</t>
+          <t>VB020202-01-01-S-04</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-ROJO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AMARILLO</t>
         </is>
       </c>
       <c r="C903" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D903" t="inlineStr"/>
       <c r="E903" t="inlineStr"/>
@@ -23229,12 +23229,12 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-11</t>
+          <t>VB0303-01-01-S-09</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-FUCSIA NEON</t>
+          <t>SHORT ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C904" t="n">
@@ -23251,16 +23251,16 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>VB0304-01-03-L-02</t>
+          <t>VB020205-02-02-M-04</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-AMARILLO</t>
         </is>
       </c>
       <c r="C905" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D905" t="inlineStr"/>
       <c r="E905" t="inlineStr"/>
@@ -23273,16 +23273,16 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-07</t>
+          <t>VB0302-01-02-M-09</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-AZUL CIAN</t>
+          <t>PANTALON ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C906" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D906" t="inlineStr"/>
       <c r="E906" t="inlineStr"/>
@@ -23295,16 +23295,16 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-04</t>
+          <t>VB020103-01-02-M-26</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-AMARILLO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
         </is>
       </c>
       <c r="C907" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D907" t="inlineStr"/>
       <c r="E907" t="inlineStr"/>
@@ -23317,16 +23317,16 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-25</t>
+          <t>VB020103-05-03-L-35</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-NEGRO-BLANCO HUESO</t>
         </is>
       </c>
       <c r="C908" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D908" t="inlineStr"/>
       <c r="E908" t="inlineStr"/>
@@ -23339,16 +23339,16 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-08</t>
+          <t>VB020105-01-01-S-11</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C909" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D909" t="inlineStr"/>
       <c r="E909" t="inlineStr"/>
@@ -23361,16 +23361,16 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-07</t>
+          <t>VB0304-01-03-L-02</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL CIAN</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-L-NEGRO</t>
         </is>
       </c>
       <c r="C910" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D910" t="inlineStr"/>
       <c r="E910" t="inlineStr"/>
@@ -23383,16 +23383,16 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-32</t>
+          <t>VB020205-02-01-S-07</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-AZUL CIAN</t>
         </is>
       </c>
       <c r="C911" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D911" t="inlineStr"/>
       <c r="E911" t="inlineStr"/>
@@ -23405,16 +23405,16 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>VB0105-02-03-L-18</t>
+          <t>VB020303-01-02-M-25</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-VERDE MENTA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C912" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D912" t="inlineStr"/>
       <c r="E912" t="inlineStr"/>
@@ -23427,16 +23427,16 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-07</t>
+          <t>VB0105-02-03-L-18</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-AZUL CIAN</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-VERDE MENTA</t>
         </is>
       </c>
       <c r="C913" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D913" t="inlineStr"/>
       <c r="E913" t="inlineStr"/>
@@ -23471,16 +23471,16 @@
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-23</t>
+          <t>VB020205-02-03-L-07</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C915" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D915" t="inlineStr"/>
       <c r="E915" t="inlineStr"/>
@@ -23493,16 +23493,16 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-02</t>
+          <t>VB020103-04-01-S-09</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-BEIGE</t>
         </is>
       </c>
       <c r="C916" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D916" t="inlineStr"/>
       <c r="E916" t="inlineStr"/>
@@ -23515,16 +23515,16 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>VB0105-01-02-M-31</t>
+          <t>VB020204-01-03-L-13</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-M-SAFARI</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-NARANJA</t>
         </is>
       </c>
       <c r="C917" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D917" t="inlineStr"/>
       <c r="E917" t="inlineStr"/>
@@ -23537,16 +23537,16 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-13</t>
+          <t>VB0103-01-01-S-02</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-NARANJA</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-NEGRO</t>
         </is>
       </c>
       <c r="C918" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D918" t="inlineStr"/>
       <c r="E918" t="inlineStr"/>
@@ -23559,16 +23559,16 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-36</t>
+          <t>VB020202-01-03-L-23</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C919" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D919" t="inlineStr"/>
       <c r="E919" t="inlineStr"/>
@@ -23581,16 +23581,16 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-34</t>
+          <t>VB0105-01-02-M-31</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-FAUNA</t>
+          <t>VB ENTERO TANGA-M-SAFARI</t>
         </is>
       </c>
       <c r="C920" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D920" t="inlineStr"/>
       <c r="E920" t="inlineStr"/>
@@ -23603,16 +23603,16 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-19</t>
+          <t>VB020103-05-03-L-36</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C921" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D921" t="inlineStr"/>
       <c r="E921" t="inlineStr"/>
@@ -23625,16 +23625,16 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-11</t>
+          <t>VB020303-01-01-S-34</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-FAUNA</t>
         </is>
       </c>
       <c r="C922" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D922" t="inlineStr"/>
       <c r="E922" t="inlineStr"/>
@@ -23647,16 +23647,16 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-29</t>
+          <t>VB020303-01-01-S-19</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PITON ROSADO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C923" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D923" t="inlineStr"/>
       <c r="E923" t="inlineStr"/>
@@ -23669,16 +23669,16 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-11</t>
+          <t>VB020105-01-03-L-11</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C924" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D924" t="inlineStr"/>
       <c r="E924" t="inlineStr"/>
@@ -23691,16 +23691,16 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-09</t>
+          <t>VB020101-01-03-L-29</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PITON ROSADO</t>
         </is>
       </c>
       <c r="C925" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D925" t="inlineStr"/>
       <c r="E925" t="inlineStr"/>
@@ -23713,16 +23713,16 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-01</t>
+          <t>VB020203-01-02-M-01</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-BLANCO</t>
         </is>
       </c>
       <c r="C926" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D926" t="inlineStr"/>
       <c r="E926" t="inlineStr"/>
@@ -23735,16 +23735,16 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-05</t>
+          <t>VB020204-01-02-M-11</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C927" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D927" t="inlineStr"/>
       <c r="E927" t="inlineStr"/>
@@ -23757,16 +23757,16 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>VB020203-01-02-M-01</t>
+          <t>VB020202-01-02-M-09</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C928" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D928" t="inlineStr"/>
       <c r="E928" t="inlineStr"/>
@@ -23779,16 +23779,16 @@
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-13</t>
+          <t>VB0306-01-01-S-01</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
+          <t>TOP BÁSICO LUISA-S-BLANCO</t>
         </is>
       </c>
       <c r="C929" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D929" t="inlineStr"/>
       <c r="E929" t="inlineStr"/>
@@ -23801,16 +23801,16 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-01</t>
+          <t>VB020204-01-02-M-05</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C930" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D930" t="inlineStr"/>
       <c r="E930" t="inlineStr"/>
@@ -23823,16 +23823,16 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-12</t>
+          <t>VB0103-01-01-S-01</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-MORADO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-BLANCO</t>
         </is>
       </c>
       <c r="C931" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D931" t="inlineStr"/>
       <c r="E931" t="inlineStr"/>
@@ -23845,16 +23845,16 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-07</t>
+          <t>VB020204-01-02-M-13</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
         </is>
       </c>
       <c r="C932" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D932" t="inlineStr"/>
       <c r="E932" t="inlineStr"/>
@@ -23867,16 +23867,16 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-13</t>
+          <t>VB020205-02-01-S-12</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-NARANJA</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-MORADO</t>
         </is>
       </c>
       <c r="C933" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D933" t="inlineStr"/>
       <c r="E933" t="inlineStr"/>
@@ -23889,16 +23889,16 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-29</t>
+          <t>VB020204-01-03-L-07</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PITON ROSADO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C934" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D934" t="inlineStr"/>
       <c r="E934" t="inlineStr"/>
@@ -23911,16 +23911,16 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-15</t>
+          <t>VB020105-01-01-S-13</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-NARANJA</t>
         </is>
       </c>
       <c r="C935" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D935" t="inlineStr"/>
       <c r="E935" t="inlineStr"/>
@@ -23933,16 +23933,16 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-26</t>
+          <t>VB020101-01-02-M-29</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PITON ROSADO</t>
         </is>
       </c>
       <c r="C936" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="D936" t="inlineStr"/>
       <c r="E936" t="inlineStr"/>
@@ -23955,16 +23955,16 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-30</t>
+          <t>VB020105-01-02-M-15</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-PURPURA</t>
         </is>
       </c>
       <c r="C937" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D937" t="inlineStr"/>
       <c r="E937" t="inlineStr"/>
@@ -23977,16 +23977,16 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-16</t>
+          <t>VB020303-01-03-L-26</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-ROJO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-MISTICO</t>
         </is>
       </c>
       <c r="C938" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D938" t="inlineStr"/>
       <c r="E938" t="inlineStr"/>
@@ -23999,16 +23999,16 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>VB020104-01-02-M-03</t>
+          <t>VB020303-01-03-L-34</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-M-AGUAMARINA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-FAUNA</t>
         </is>
       </c>
       <c r="C939" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D939" t="inlineStr"/>
       <c r="E939" t="inlineStr"/>
@@ -24021,16 +24021,16 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>VB0104-01-01-S-09</t>
+          <t>VB020103-03-01-S-20</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C940" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="D940" t="inlineStr"/>
       <c r="E940" t="inlineStr"/>
@@ -24043,16 +24043,16 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-36</t>
+          <t>VB020202-01-03-L-08</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL REY</t>
         </is>
       </c>
       <c r="C941" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D941" t="inlineStr"/>
       <c r="E941" t="inlineStr"/>
@@ -24065,16 +24065,16 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>VB0105-02-03-L-02</t>
+          <t>VB0303-01-02-M-02</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-NEGRO</t>
+          <t>SHORT ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C942" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D942" t="inlineStr"/>
       <c r="E942" t="inlineStr"/>
@@ -24087,16 +24087,16 @@
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-23</t>
+          <t>VB020104-01-01-S-02</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-NEGRO</t>
         </is>
       </c>
       <c r="C943" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D943" t="inlineStr"/>
       <c r="E943" t="inlineStr"/>
@@ -24109,16 +24109,16 @@
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-04</t>
+          <t>VB020205-03-03-L-21</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AMARILLO</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-ASTRAL</t>
         </is>
       </c>
       <c r="C944" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D944" t="inlineStr"/>
       <c r="E944" t="inlineStr"/>
@@ -24131,16 +24131,16 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-34</t>
+          <t>VB020204-01-02-M-08</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-FAUNA</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
         </is>
       </c>
       <c r="C945" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D945" t="inlineStr"/>
       <c r="E945" t="inlineStr"/>
@@ -24153,16 +24153,16 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>VB020103-03-01-S-20</t>
+          <t>VB020105-01-03-L-08</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AZUL REY</t>
         </is>
       </c>
       <c r="C946" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D946" t="inlineStr"/>
       <c r="E946" t="inlineStr"/>
@@ -24175,16 +24175,16 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>VB0105-01-02-M-23</t>
+          <t>VB0103-01-01-S-16</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-ROJO</t>
         </is>
       </c>
       <c r="C947" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D947" t="inlineStr"/>
       <c r="E947" t="inlineStr"/>
@@ -24197,16 +24197,16 @@
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>VB0303-01-02-M-02</t>
+          <t>VB020104-01-02-M-03</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>SHORT ALTO-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C948" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D948" t="inlineStr"/>
       <c r="E948" t="inlineStr"/>
@@ -24219,16 +24219,16 @@
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-02</t>
+          <t>VB020103-05-01-S-36</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C949" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D949" t="inlineStr"/>
       <c r="E949" t="inlineStr"/>
@@ -24241,16 +24241,16 @@
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>VB020205-03-03-L-21</t>
+          <t>VB0104-01-01-S-09</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-ASTRAL</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-BEIGE</t>
         </is>
       </c>
       <c r="C950" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D950" t="inlineStr"/>
       <c r="E950" t="inlineStr"/>
@@ -24263,16 +24263,16 @@
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-08</t>
+          <t>VB020303-01-03-L-30</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
         </is>
       </c>
       <c r="C951" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D951" t="inlineStr"/>
       <c r="E951" t="inlineStr"/>
@@ -24285,16 +24285,16 @@
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-08</t>
+          <t>VB0105-02-03-L-02</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AZUL REY</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-NEGRO</t>
         </is>
       </c>
       <c r="C952" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D952" t="inlineStr"/>
       <c r="E952" t="inlineStr"/>
@@ -24307,16 +24307,16 @@
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-22</t>
+          <t>VB0104-01-03-L-02</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-FLORES</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-NEGRO</t>
         </is>
       </c>
       <c r="C953" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D953" t="inlineStr"/>
       <c r="E953" t="inlineStr"/>
@@ -24329,16 +24329,16 @@
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-05</t>
+          <t>VB0305-01-04-U-09</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AMARILLO NEON</t>
+          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-BEIGE</t>
         </is>
       </c>
       <c r="C954" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D954" t="inlineStr"/>
       <c r="E954" t="inlineStr"/>
@@ -24351,16 +24351,16 @@
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-05</t>
+          <t>VB020101-01-02-M-05</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C955" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D955" t="inlineStr"/>
       <c r="E955" t="inlineStr"/>
@@ -24373,16 +24373,16 @@
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-15</t>
+          <t>VB020204-01-02-M-07</t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AZUL CIAN</t>
         </is>
       </c>
       <c r="C956" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D956" t="inlineStr"/>
       <c r="E956" t="inlineStr"/>
@@ -24395,16 +24395,16 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-14</t>
+          <t>VB020303-01-01-S-25</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C957" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D957" t="inlineStr"/>
       <c r="E957" t="inlineStr"/>
@@ -24417,16 +24417,16 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-01</t>
+          <t>VB020303-01-01-S-30</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-BLANCO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-PLUMAS</t>
         </is>
       </c>
       <c r="C958" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D958" t="inlineStr"/>
       <c r="E958" t="inlineStr"/>
@@ -24439,16 +24439,16 @@
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>VB0305-01-04-U-02</t>
+          <t>VB020204-01-01-S-08</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
         </is>
       </c>
       <c r="C959" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D959" t="inlineStr"/>
       <c r="E959" t="inlineStr"/>
@@ -24461,16 +24461,16 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>VB0104-01-03-L-02</t>
+          <t>VB0306-01-01-S-16</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-NEGRO</t>
+          <t>TOP BÁSICO LUISA-S-ROJO</t>
         </is>
       </c>
       <c r="C960" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D960" t="inlineStr"/>
       <c r="E960" t="inlineStr"/>
@@ -24483,16 +24483,16 @@
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>VB0305-01-04-U-09</t>
+          <t>VB020205-02-01-S-10</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-BEIGE</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-FUCSIA</t>
         </is>
       </c>
       <c r="C961" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D961" t="inlineStr"/>
       <c r="E961" t="inlineStr"/>
@@ -24505,16 +24505,16 @@
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-07</t>
+          <t>VB020103-03-03-L-20</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C962" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D962" t="inlineStr"/>
       <c r="E962" t="inlineStr"/>
@@ -24527,16 +24527,16 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-05</t>
+          <t>VB020101-01-02-M-19</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C963" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D963" t="inlineStr"/>
       <c r="E963" t="inlineStr"/>
@@ -24549,16 +24549,16 @@
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>VB020103-01-03-L-26</t>
+          <t>VB0105-02-01-S-18</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-L-MISTICO</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-VERDE MENTA</t>
         </is>
       </c>
       <c r="C964" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D964" t="inlineStr"/>
       <c r="E964" t="inlineStr"/>
@@ -24571,16 +24571,16 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-08</t>
+          <t>VB020204-01-01-S-13</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
         </is>
       </c>
       <c r="C965" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D965" t="inlineStr"/>
       <c r="E965" t="inlineStr"/>
@@ -24593,16 +24593,16 @@
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-16</t>
+          <t>VB020103-01-03-L-26</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-L-MISTICO</t>
         </is>
       </c>
       <c r="C966" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D966" t="inlineStr"/>
       <c r="E966" t="inlineStr"/>
@@ -24615,16 +24615,16 @@
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-30</t>
+          <t>VB020103-05-01-S-37</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C967" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D967" t="inlineStr"/>
       <c r="E967" t="inlineStr"/>
@@ -24637,16 +24637,16 @@
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-10</t>
+          <t>VB020103-03-03-L-32</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-FUCSIA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C968" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D968" t="inlineStr"/>
       <c r="E968" t="inlineStr"/>
@@ -24659,16 +24659,16 @@
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>VB020103-03-03-L-20</t>
+          <t>VB0306-01-01-S-03</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-ANIMAL PRINT FLORES</t>
+          <t>TOP BÁSICO LUISA-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C969" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="D969" t="inlineStr"/>
       <c r="E969" t="inlineStr"/>
@@ -24681,16 +24681,16 @@
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-19</t>
+          <t>VB020202-01-01-S-09</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C970" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D970" t="inlineStr"/>
       <c r="E970" t="inlineStr"/>
@@ -24703,16 +24703,16 @@
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-13</t>
+          <t>VB020203-01-01-S-02</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-NEGRO</t>
         </is>
       </c>
       <c r="C971" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D971" t="inlineStr"/>
       <c r="E971" t="inlineStr"/>
@@ -24725,16 +24725,16 @@
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-18</t>
+          <t>VB0304-01-02-M-02</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-VERDE MENTA</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-M-NEGRO</t>
         </is>
       </c>
       <c r="C972" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D972" t="inlineStr"/>
       <c r="E972" t="inlineStr"/>
@@ -24747,16 +24747,16 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-37</t>
+          <t>VB020202-01-03-L-19</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-AZUL BEBE-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C973" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D973" t="inlineStr"/>
       <c r="E973" t="inlineStr"/>
@@ -24769,16 +24769,16 @@
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>VB020103-03-03-L-32</t>
+          <t>VB0304-01-03-L-09</t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-SELVA PAJAROS</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-L-BEIGE</t>
         </is>
       </c>
       <c r="C974" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D974" t="inlineStr"/>
       <c r="E974" t="inlineStr"/>
@@ -24813,16 +24813,16 @@
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-19</t>
+          <t>VB020103-02-02-M-17</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-ROSADO</t>
         </is>
       </c>
       <c r="C976" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D976" t="inlineStr"/>
       <c r="E976" t="inlineStr"/>
@@ -24835,16 +24835,16 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>VB0304-01-03-L-09</t>
+          <t>VB020103-04-03-L-19</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-L-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C977" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D977" t="inlineStr"/>
       <c r="E977" t="inlineStr"/>
@@ -24857,16 +24857,16 @@
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>VB0304-01-02-M-02</t>
+          <t>VB0104-01-02-M-02</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-M-NEGRO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-NEGRO</t>
         </is>
       </c>
       <c r="C978" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D978" t="inlineStr"/>
       <c r="E978" t="inlineStr"/>
@@ -24879,16 +24879,16 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-02</t>
+          <t>VB020103-05-02-M-37</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C979" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D979" t="inlineStr"/>
       <c r="E979" t="inlineStr"/>
@@ -24901,16 +24901,16 @@
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-19</t>
+          <t>VB020103-02-01-S-03</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C980" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D980" t="inlineStr"/>
       <c r="E980" t="inlineStr"/>
@@ -24923,16 +24923,16 @@
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>VB020103-02-02-M-17</t>
+          <t>VB020204-01-02-M-15</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-ROSADO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-PURPURA</t>
         </is>
       </c>
       <c r="C981" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D981" t="inlineStr"/>
       <c r="E981" t="inlineStr"/>
@@ -24945,16 +24945,16 @@
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-25</t>
+          <t>VB020202-01-02-M-19</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C982" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D982" t="inlineStr"/>
       <c r="E982" t="inlineStr"/>
@@ -24967,16 +24967,16 @@
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-09</t>
+          <t>VB020204-01-03-L-11</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-BEIGE</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C983" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D983" t="inlineStr"/>
       <c r="E983" t="inlineStr"/>
@@ -24989,16 +24989,16 @@
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-03</t>
+          <t>VB0105-02-02-M-33</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-AGUAMARINA</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-TIE DYE</t>
         </is>
       </c>
       <c r="C984" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D984" t="inlineStr"/>
       <c r="E984" t="inlineStr"/>
@@ -25011,16 +25011,16 @@
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>VB0304-01-01-S-09</t>
+          <t>VB020103-02-01-S-17</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-S-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-ROSADO</t>
         </is>
       </c>
       <c r="C985" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D985" t="inlineStr"/>
       <c r="E985" t="inlineStr"/>
@@ -25033,16 +25033,16 @@
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-28</t>
+          <t>VB0103-01-03-L-01</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-PITON BEIGE</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-BLANCO</t>
         </is>
       </c>
       <c r="C986" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D986" t="inlineStr"/>
       <c r="E986" t="inlineStr"/>
@@ -25055,16 +25055,16 @@
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-11</t>
+          <t>VB020103-04-01-S-28</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-PITON BEIGE</t>
         </is>
       </c>
       <c r="C987" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D987" t="inlineStr"/>
       <c r="E987" t="inlineStr"/>
@@ -25077,16 +25077,16 @@
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-16</t>
+          <t>VB020101-01-03-L-27</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PITON AZUL</t>
         </is>
       </c>
       <c r="C988" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D988" t="inlineStr"/>
       <c r="E988" t="inlineStr"/>
@@ -25099,16 +25099,16 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>VB020103-03-02-M-20</t>
+          <t>VB020105-01-01-S-08</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
         </is>
       </c>
       <c r="C989" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="D989" t="inlineStr"/>
       <c r="E989" t="inlineStr"/>
@@ -25121,16 +25121,16 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>VB0103-01-02-M-32</t>
+          <t>VB0105-02-01-S-33</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-TIE DYE</t>
         </is>
       </c>
       <c r="C990" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D990" t="inlineStr"/>
       <c r="E990" t="inlineStr"/>
@@ -25143,16 +25143,16 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-33</t>
+          <t>VB020202-01-02-M-04</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-TIE DYE</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AMARILLO</t>
         </is>
       </c>
       <c r="C991" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D991" t="inlineStr"/>
       <c r="E991" t="inlineStr"/>
@@ -25187,16 +25187,16 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>VB020103-02-02-M-03</t>
+          <t>VB020204-01-03-L-05</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C993" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D993" t="inlineStr"/>
       <c r="E993" t="inlineStr"/>
@@ -25209,16 +25209,16 @@
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>VB020205-03-01-S-28</t>
+          <t>VB020204-01-03-L-15</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
         </is>
       </c>
       <c r="C994" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D994" t="inlineStr"/>
       <c r="E994" t="inlineStr"/>
@@ -25231,16 +25231,16 @@
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-35</t>
+          <t>VB0306-01-02-M-14</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-NEGRO-BLANCO HUESO</t>
+          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C995" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D995" t="inlineStr"/>
       <c r="E995" t="inlineStr"/>
@@ -25253,12 +25253,12 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-18</t>
+          <t>VB020101-01-03-L-05</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-VERDE MENTA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C996" t="n">
@@ -25275,16 +25275,16 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-02</t>
+          <t>VB020205-02-03-L-22</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-FLORES</t>
         </is>
       </c>
       <c r="C997" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D997" t="inlineStr"/>
       <c r="E997" t="inlineStr"/>
@@ -25297,16 +25297,16 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-01</t>
+          <t>VB0302-01-02-M-01</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
+          <t>PANTALON ALTO-M-BLANCO</t>
         </is>
       </c>
       <c r="C998" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D998" t="inlineStr"/>
       <c r="E998" t="inlineStr"/>
@@ -25319,16 +25319,16 @@
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-04</t>
+          <t>VB0305-01-04-U-02</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AMARILLO</t>
+          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-NEGRO</t>
         </is>
       </c>
       <c r="C999" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D999" t="inlineStr"/>
       <c r="E999" t="inlineStr"/>
@@ -25341,16 +25341,16 @@
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-16</t>
+          <t>VB0103-01-02-M-32</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C1000" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D1000" t="inlineStr"/>
       <c r="E1000" t="inlineStr"/>
@@ -25363,16 +25363,16 @@
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-13</t>
+          <t>VB020103-03-02-M-20</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C1001" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="D1001" t="inlineStr"/>
       <c r="E1001" t="inlineStr"/>
@@ -25385,16 +25385,16 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>VB0104-01-02-M-02</t>
+          <t>VB020205-03-01-S-28</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-PITON BEIGE</t>
         </is>
       </c>
       <c r="C1002" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D1002" t="inlineStr"/>
       <c r="E1002" t="inlineStr"/>
@@ -25407,16 +25407,16 @@
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>VB020103-05-02-M-37</t>
+          <t>VB020103-05-01-S-35</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-AZUL BEBE-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-NEGRO-BLANCO HUESO</t>
         </is>
       </c>
       <c r="C1003" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D1003" t="inlineStr"/>
       <c r="E1003" t="inlineStr"/>
@@ -25429,16 +25429,16 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-03</t>
+          <t>VB020103-02-02-M-03</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1004" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D1004" t="inlineStr"/>
       <c r="E1004" t="inlineStr"/>
@@ -25451,16 +25451,16 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-15</t>
+          <t>VB020105-01-03-L-01</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
         </is>
       </c>
       <c r="C1005" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D1005" t="inlineStr"/>
       <c r="E1005" t="inlineStr"/>
@@ -25473,16 +25473,16 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-19</t>
+          <t>VB020202-01-02-M-02</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C1006" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D1006" t="inlineStr"/>
       <c r="E1006" t="inlineStr"/>
@@ -25495,16 +25495,16 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-22</t>
+          <t>VB0105-02-02-M-18</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-FLORES</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-VERDE MENTA</t>
         </is>
       </c>
       <c r="C1007" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="D1007" t="inlineStr"/>
       <c r="E1007" t="inlineStr"/>
@@ -25517,16 +25517,16 @@
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>VB020205-03-02-M-21</t>
+          <t>VB020205-02-01-S-22</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-ASTRAL</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-FLORES</t>
         </is>
       </c>
       <c r="C1008" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="D1008" t="inlineStr"/>
       <c r="E1008" t="inlineStr"/>
@@ -25539,16 +25539,16 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-07</t>
+          <t>VB020205-03-02-M-21</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-ASTRAL</t>
         </is>
       </c>
       <c r="C1009" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D1009" t="inlineStr"/>
       <c r="E1009" t="inlineStr"/>
@@ -25561,16 +25561,16 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-16</t>
+          <t>VB020205-02-02-M-07</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-ROJO</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1010" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D1010" t="inlineStr"/>
       <c r="E1010" t="inlineStr"/>
@@ -25583,16 +25583,16 @@
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-07</t>
+          <t>VB020105-01-03-L-16</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-ROJO</t>
         </is>
       </c>
       <c r="C1011" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D1011" t="inlineStr"/>
       <c r="E1011" t="inlineStr"/>
@@ -25605,16 +25605,16 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-19</t>
+          <t>VB020105-01-03-L-07</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1012" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D1012" t="inlineStr"/>
       <c r="E1012" t="inlineStr"/>
@@ -25627,16 +25627,16 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-05</t>
+          <t>VB020202-01-01-S-19</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1013" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D1013" t="inlineStr"/>
       <c r="E1013" t="inlineStr"/>
@@ -25649,16 +25649,16 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-33</t>
+          <t>VB020105-01-02-M-05</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-TIE DYE</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C1014" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D1014" t="inlineStr"/>
       <c r="E1014" t="inlineStr"/>
@@ -25671,16 +25671,16 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-11</t>
+          <t>VB020105-01-02-M-16</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-ROJO</t>
         </is>
       </c>
       <c r="C1015" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D1015" t="inlineStr"/>
       <c r="E1015" t="inlineStr"/>
@@ -25693,16 +25693,16 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-17</t>
+          <t>VB020105-01-03-L-13</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
         </is>
       </c>
       <c r="C1016" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D1016" t="inlineStr"/>
       <c r="E1016" t="inlineStr"/>
@@ -25715,16 +25715,16 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-27</t>
+          <t>VB020105-01-01-S-16</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PITON AZUL</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
         </is>
       </c>
       <c r="C1017" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D1017" t="inlineStr"/>
       <c r="E1017" t="inlineStr"/>
@@ -25737,16 +25737,16 @@
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-01</t>
+          <t>VB0304-01-01-S-09</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-BLANCO</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-S-BEIGE</t>
         </is>
       </c>
       <c r="C1018" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D1018" t="inlineStr"/>
       <c r="E1018" t="inlineStr"/>
@@ -25759,16 +25759,16 @@
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-08</t>
+          <t>VB020103-04-03-L-28</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-PITON BEIGE</t>
         </is>
       </c>
       <c r="C1019" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D1019" t="inlineStr"/>
       <c r="E1019" t="inlineStr"/>
@@ -25781,16 +25781,16 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-28</t>
+          <t>VB020105-01-02-M-11</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C1020" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D1020" t="inlineStr"/>
       <c r="E1020" t="inlineStr"/>
@@ -25847,16 +25847,16 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-08</t>
+          <t>VB020101-01-01-S-15</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PURPURA</t>
         </is>
       </c>
       <c r="C1023" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D1023" t="inlineStr"/>
       <c r="E1023" t="inlineStr"/>
@@ -25913,16 +25913,16 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-15</t>
+          <t>VB020103-03-01-S-32</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C1026" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="D1026" t="inlineStr"/>
       <c r="E1026" t="inlineStr"/>
@@ -25935,16 +25935,16 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>VB020103-03-01-S-32</t>
+          <t>VB0302-01-03-L-01</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-SELVA PAJAROS</t>
+          <t>PANTALON ALTO-L-BLANCO</t>
         </is>
       </c>
       <c r="C1027" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D1027" t="inlineStr"/>
       <c r="E1027" t="inlineStr"/>
@@ -25957,16 +25957,16 @@
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-01</t>
+          <t>VB020101-01-01-S-29</t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PITON ROSADO</t>
         </is>
       </c>
       <c r="C1028" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D1028" t="inlineStr"/>
       <c r="E1028" t="inlineStr"/>
@@ -25979,16 +25979,16 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-29</t>
+          <t>VB020104-01-03-L-02</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PITON ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-NEGRO</t>
         </is>
       </c>
       <c r="C1029" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1029" t="inlineStr"/>
       <c r="E1029" t="inlineStr"/>
@@ -26001,16 +26001,16 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-02</t>
+          <t>VB020204-01-03-L-08</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
         </is>
       </c>
       <c r="C1030" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D1030" t="inlineStr"/>
       <c r="E1030" t="inlineStr"/>
@@ -26089,16 +26089,16 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-04</t>
+          <t>VB0104-01-03-L-09</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-AMARILLO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-BEIGE</t>
         </is>
       </c>
       <c r="C1034" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D1034" t="inlineStr"/>
       <c r="E1034" t="inlineStr"/>
@@ -26111,16 +26111,16 @@
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>VB0104-01-03-L-09</t>
+          <t>VB020205-02-01-S-04</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-BEIGE</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-AMARILLO</t>
         </is>
       </c>
       <c r="C1035" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D1035" t="inlineStr"/>
       <c r="E1035" t="inlineStr"/>
@@ -26309,16 +26309,16 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-30</t>
+          <t>VB020103-04-02-M-19</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1044" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="D1044" t="inlineStr"/>
       <c r="E1044" t="inlineStr"/>
@@ -26331,16 +26331,16 @@
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-19</t>
+          <t>VB020303-01-02-M-30</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-PLUMAS</t>
         </is>
       </c>
       <c r="C1045" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="D1045" t="inlineStr"/>
       <c r="E1045" t="inlineStr"/>
@@ -26507,16 +26507,16 @@
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-05</t>
+          <t>VB0303-01-02-M-09</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AMARILLO NEON</t>
+          <t>SHORT ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C1053" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D1053" t="inlineStr"/>
       <c r="E1053" t="inlineStr"/>
@@ -26529,16 +26529,16 @@
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>VB0303-01-02-M-09</t>
+          <t>VB020105-01-03-L-05</t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>SHORT ALTO-M-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C1054" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D1054" t="inlineStr"/>
       <c r="E1054" t="inlineStr"/>
@@ -26639,16 +26639,16 @@
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>VB0105-01-01-S-23</t>
+          <t>VB020402-01-02-M-31</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-S-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS BUSO TALLE ALTO-M-SAFARI</t>
         </is>
       </c>
       <c r="C1059" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D1059" t="inlineStr"/>
       <c r="E1059" t="inlineStr"/>
@@ -26661,16 +26661,16 @@
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>VB020402-01-02-M-31</t>
+          <t>VB0105-01-01-S-23</t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS BUSO TALLE ALTO-M-SAFARI</t>
+          <t>VB ENTERO TANGA-S-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C1060" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D1060" t="inlineStr"/>
       <c r="E1060" t="inlineStr"/>
@@ -28835,16 +28835,16 @@
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>344102</t>
+          <t>230103</t>
         </is>
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>MATRIFUSE S-1</t>
+          <t>230103</t>
         </is>
       </c>
       <c r="C1145" t="n">
-        <v>9840</v>
+        <v>22380</v>
       </c>
       <c r="D1145" t="inlineStr"/>
       <c r="E1145" t="inlineStr">
@@ -28861,16 +28861,16 @@
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>230103</t>
+          <t>344102</t>
         </is>
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>230103</t>
+          <t>MATRIFUSE S-1</t>
         </is>
       </c>
       <c r="C1146" t="n">
-        <v>22380</v>
+        <v>9840</v>
       </c>
       <c r="D1146" t="inlineStr"/>
       <c r="E1146" t="inlineStr">
@@ -31955,16 +31955,16 @@
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>163804</t>
+          <t>163803</t>
         </is>
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>163804</t>
+          <t>163803</t>
         </is>
       </c>
       <c r="C1265" t="n">
-        <v>64285</v>
+        <v>54785</v>
       </c>
       <c r="D1265" t="inlineStr"/>
       <c r="E1265" t="inlineStr">
@@ -31981,16 +31981,16 @@
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>163803</t>
+          <t>163804</t>
         </is>
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>163803</t>
+          <t>163804</t>
         </is>
       </c>
       <c r="C1266" t="n">
-        <v>54785</v>
+        <v>64285</v>
       </c>
       <c r="D1266" t="inlineStr"/>
       <c r="E1266" t="inlineStr">
@@ -36219,21 +36219,21 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>ME0524</t>
+          <t>ETC0104</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>ENVASE VIDRIO AMARILLO SOÑADORA 120ML</t>
+          <t>CAJA CORRECTOR ARENA</t>
         </is>
       </c>
       <c r="C1429" t="n">
-        <v>1447</v>
+        <v>5510</v>
       </c>
       <c r="D1429" t="inlineStr"/>
       <c r="E1429" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1429" t="inlineStr">
@@ -36245,21 +36245,21 @@
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>ETC0104</t>
+          <t>ME0524</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>CAJA CORRECTOR ARENA</t>
+          <t>ENVASE VIDRIO AMARILLO SOÑADORA 120ML</t>
         </is>
       </c>
       <c r="C1430" t="n">
-        <v>5510</v>
+        <v>1447</v>
       </c>
       <c r="D1430" t="inlineStr"/>
       <c r="E1430" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1430" t="inlineStr">
@@ -36557,16 +36557,16 @@
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>ME0511</t>
+          <t>ME1067</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>ENV PEAD KABA B28 500ML</t>
+          <t>TAPA NARANJA RUBOR EN BARRA SALLY</t>
         </is>
       </c>
       <c r="C1442" t="n">
-        <v>28261</v>
+        <v>19440</v>
       </c>
       <c r="D1442" t="inlineStr"/>
       <c r="E1442" t="inlineStr">
@@ -36583,16 +36583,16 @@
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>ME1067</t>
+          <t>ME0511</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>TAPA NARANJA RUBOR EN BARRA SALLY</t>
+          <t>ENV PEAD KABA B28 500ML</t>
         </is>
       </c>
       <c r="C1443" t="n">
-        <v>19440</v>
+        <v>28261</v>
       </c>
       <c r="D1443" t="inlineStr"/>
       <c r="E1443" t="inlineStr">
@@ -37025,16 +37025,16 @@
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>ME1028</t>
+          <t>ME0507</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>TAPA CON APLICADOR PUNTA PINCEL</t>
+          <t>BALA TRANSPARENTE 30ML</t>
         </is>
       </c>
       <c r="C1460" t="n">
-        <v>15877</v>
+        <v>24300</v>
       </c>
       <c r="D1460" t="inlineStr"/>
       <c r="E1460" t="inlineStr">
@@ -37051,16 +37051,16 @@
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>ME0507</t>
+          <t>ME1028</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 30ML</t>
+          <t>TAPA CON APLICADOR PUNTA PINCEL</t>
         </is>
       </c>
       <c r="C1461" t="n">
-        <v>24300</v>
+        <v>15877</v>
       </c>
       <c r="D1461" t="inlineStr"/>
       <c r="E1461" t="inlineStr">
@@ -39621,16 +39621,16 @@
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>ETC0138USA</t>
+          <t>ETC0136USA</t>
         </is>
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>CAJA FACIAL TONER BRIGHTENING ILLUMINATO</t>
+          <t>CAJA HAIR TONIC KABA</t>
         </is>
       </c>
       <c r="C1560" t="n">
-        <v>5400</v>
+        <v>680</v>
       </c>
       <c r="D1560" t="inlineStr"/>
       <c r="E1560" t="inlineStr">
@@ -39647,16 +39647,16 @@
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>ETC0136USA</t>
+          <t>ETC0138USA</t>
         </is>
       </c>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>CAJA HAIR TONIC KABA</t>
+          <t>CAJA FACIAL TONER BRIGHTENING ILLUMINATO</t>
         </is>
       </c>
       <c r="C1561" t="n">
-        <v>680</v>
+        <v>5400</v>
       </c>
       <c r="D1561" t="inlineStr"/>
       <c r="E1561" t="inlineStr">
@@ -40193,16 +40193,16 @@
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>ET0205VG</t>
+          <t>ETC0157</t>
         </is>
       </c>
       <c r="B1582" t="inlineStr">
         <is>
-          <t>ETIQ TAPA BRONCEADOR VIVANA GRONDONA D1</t>
+          <t>CAJA BASE LIQUIDA MIEL</t>
         </is>
       </c>
       <c r="C1582" t="n">
-        <v>6992</v>
+        <v>3978</v>
       </c>
       <c r="D1582" t="inlineStr"/>
       <c r="E1582" t="inlineStr">
@@ -40219,16 +40219,16 @@
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>ETC0157</t>
+          <t>ET0205VG</t>
         </is>
       </c>
       <c r="B1583" t="inlineStr">
         <is>
-          <t>CAJA BASE LIQUIDA MIEL</t>
+          <t>ETIQ TAPA BRONCEADOR VIVANA GRONDONA D1</t>
         </is>
       </c>
       <c r="C1583" t="n">
-        <v>3978</v>
+        <v>6992</v>
       </c>
       <c r="D1583" t="inlineStr"/>
       <c r="E1583" t="inlineStr">
@@ -41025,16 +41025,16 @@
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>ET0250USA</t>
+          <t>ET02128USA</t>
         </is>
       </c>
       <c r="B1614" t="inlineStr">
         <is>
-          <t>ETIQUETA BIO HAIR MASK KABA</t>
+          <t>ETIQ BIPHASIC MAKE UP REMOVER 30ML</t>
         </is>
       </c>
       <c r="C1614" t="n">
-        <v>7207</v>
+        <v>5500</v>
       </c>
       <c r="D1614" t="inlineStr"/>
       <c r="E1614" t="inlineStr">
@@ -41051,16 +41051,16 @@
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>ET0296USA</t>
+          <t>ET0250USA</t>
         </is>
       </c>
       <c r="B1615" t="inlineStr">
         <is>
-          <t>ETIQUETA EYELASH GROWTH SERUM KABA</t>
+          <t>ETIQUETA BIO HAIR MASK KABA</t>
         </is>
       </c>
       <c r="C1615" t="n">
-        <v>5250</v>
+        <v>7207</v>
       </c>
       <c r="D1615" t="inlineStr"/>
       <c r="E1615" t="inlineStr">
@@ -41077,16 +41077,16 @@
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>ET02110USA</t>
+          <t>ET0296USA</t>
         </is>
       </c>
       <c r="B1616" t="inlineStr">
         <is>
-          <t>ETIQUETA ONION SHAMPOO KABA</t>
+          <t>ETIQUETA EYELASH GROWTH SERUM KABA</t>
         </is>
       </c>
       <c r="C1616" t="n">
-        <v>21403</v>
+        <v>5250</v>
       </c>
       <c r="D1616" t="inlineStr"/>
       <c r="E1616" t="inlineStr">
@@ -41103,16 +41103,16 @@
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>ET02128USA</t>
+          <t>ET02110USA</t>
         </is>
       </c>
       <c r="B1617" t="inlineStr">
         <is>
-          <t>ETIQ BIPHASIC MAKE UP REMOVER 30ML</t>
+          <t>ETIQUETA ONION SHAMPOO KABA</t>
         </is>
       </c>
       <c r="C1617" t="n">
-        <v>5500</v>
+        <v>21403</v>
       </c>
       <c r="D1617" t="inlineStr"/>
       <c r="E1617" t="inlineStr">
@@ -43087,16 +43087,16 @@
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>K051505</t>
+          <t>K051501</t>
         </is>
       </c>
       <c r="B1690" t="inlineStr">
         <is>
-          <t>COSMETIQUERA FACIAL GRANDE KABA</t>
+          <t>COSMETIQUERA GRANDE KABA</t>
         </is>
       </c>
       <c r="C1690" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D1690" t="inlineStr"/>
       <c r="E1690" t="inlineStr">
@@ -43113,16 +43113,16 @@
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>K051501</t>
+          <t>K051505</t>
         </is>
       </c>
       <c r="B1691" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE KABA</t>
+          <t>COSMETIQUERA FACIAL GRANDE KABA</t>
         </is>
       </c>
       <c r="C1691" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D1691" t="inlineStr"/>
       <c r="E1691" t="inlineStr">

--- a/inventario_operaciones.xlsx
+++ b/inventario_operaciones.xlsx
@@ -1207,19 +1207,19 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R010302</t>
+          <t>K010102</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TONICO CAPILAR LA RECETA</t>
+          <t>SHAMPO KIDS KABA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>184</v>
+        <v>120</v>
       </c>
       <c r="D29" t="n">
-        <v>3218.702290076336</v>
+        <v>2141.106870229008</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1235,19 +1235,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>K010102</t>
+          <t>R010302</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SHAMPO KIDS KABA</t>
+          <t>TONICO CAPILAR LA RECETA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>120</v>
+        <v>184</v>
       </c>
       <c r="D30" t="n">
-        <v>2141.106870229008</v>
+        <v>3218.702290076336</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -8195,19 +8195,19 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>R010302</t>
+          <t>K010102</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>TONICO CAPILAR LA RECETA</t>
+          <t>SHAMPO KIDS KABA</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>13873</v>
+        <v>2891</v>
       </c>
       <c r="D285" t="n">
-        <v>3218.702290076336</v>
+        <v>2141.106870229008</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -8223,19 +8223,19 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>K010101</t>
+          <t>R010302</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>SHAMPO DE CEBOLLA KABA</t>
+          <t>TONICO CAPILAR LA RECETA</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>176638</v>
+        <v>13873</v>
       </c>
       <c r="D286" t="n">
-        <v>81409.46564885495</v>
+        <v>3218.702290076336</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -8251,19 +8251,19 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>K010102</t>
+          <t>K010101</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>SHAMPO KIDS KABA</t>
+          <t>SHAMPO DE CEBOLLA KABA</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>2891</v>
+        <v>176638</v>
       </c>
       <c r="D287" t="n">
-        <v>2141.106870229008</v>
+        <v>81409.46564885495</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -13589,21 +13589,21 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>155301</t>
+          <t>ME1011</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>ESTOGEL M</t>
+          <t>LOTIÓN PUMP 28/410 SILVER/WHITE</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>100000</v>
+        <v>326790</v>
       </c>
       <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -13615,21 +13615,21 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>ME1011</t>
+          <t>155301</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>LOTIÓN PUMP 28/410 SILVER/WHITE</t>
+          <t>ESTOGEL M</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>326790</v>
+        <v>100000</v>
       </c>
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -34791,21 +34791,21 @@
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>314208</t>
+          <t>ME1049</t>
         </is>
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>GEMTONE AMBER G001</t>
+          <t>TAPA PUSH PULL DORADA ROSCA 24</t>
         </is>
       </c>
       <c r="C1373" t="n">
-        <v>73488</v>
+        <v>3386</v>
       </c>
       <c r="D1373" t="inlineStr"/>
       <c r="E1373" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1373" t="inlineStr">
@@ -34817,21 +34817,21 @@
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>ME1049</t>
+          <t>314208</t>
         </is>
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>TAPA PUSH PULL DORADA ROSCA 24</t>
+          <t>GEMTONE AMBER G001</t>
         </is>
       </c>
       <c r="C1374" t="n">
-        <v>3386</v>
+        <v>73488</v>
       </c>
       <c r="D1374" t="inlineStr"/>
       <c r="E1374" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1374" t="inlineStr">
@@ -35207,21 +35207,21 @@
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>ME0505</t>
+          <t>ET0202</t>
         </is>
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 120ML</t>
+          <t>ETIQUETA PERFUME CABELLO ARRIESGAD 120ML</t>
         </is>
       </c>
       <c r="C1389" t="n">
-        <v>2543</v>
+        <v>140</v>
       </c>
       <c r="D1389" t="inlineStr"/>
       <c r="E1389" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1389" t="inlineStr">
@@ -35233,21 +35233,21 @@
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>ET0202</t>
+          <t>ME0505</t>
         </is>
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>ETIQUETA PERFUME CABELLO ARRIESGAD 120ML</t>
+          <t>BALA TRANSPARENTE 120ML</t>
         </is>
       </c>
       <c r="C1390" t="n">
-        <v>140</v>
+        <v>2543</v>
       </c>
       <c r="D1390" t="inlineStr"/>
       <c r="E1390" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1390" t="inlineStr">
@@ -36143,21 +36143,21 @@
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>173501</t>
+          <t>ME1043</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>ULTRAMAR U-200 AZUL</t>
+          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
         </is>
       </c>
       <c r="C1425" t="n">
-        <v>5310</v>
+        <v>2731</v>
       </c>
       <c r="D1425" t="inlineStr"/>
       <c r="E1425" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1425" t="inlineStr">
@@ -36169,16 +36169,16 @@
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>ME1043</t>
+          <t>ME1044</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
+          <t>TAPA FLIP TOP PLATEADA ROSCA 18</t>
         </is>
       </c>
       <c r="C1426" t="n">
-        <v>2731</v>
+        <v>39551</v>
       </c>
       <c r="D1426" t="inlineStr"/>
       <c r="E1426" t="inlineStr">
@@ -36195,21 +36195,21 @@
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>ME1044</t>
+          <t>173501</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP PLATEADA ROSCA 18</t>
+          <t>ULTRAMAR U-200 AZUL</t>
         </is>
       </c>
       <c r="C1427" t="n">
-        <v>39551</v>
+        <v>5310</v>
       </c>
       <c r="D1427" t="inlineStr"/>
       <c r="E1427" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1427" t="inlineStr">
@@ -37131,16 +37131,16 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>ME0578</t>
+          <t>ME0511</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>ENVASE ROJO RUBOR EN CREMA RUBY</t>
+          <t>ENV PEAD KABA B28 500ML</t>
         </is>
       </c>
       <c r="C1463" t="n">
-        <v>19980</v>
+        <v>28261</v>
       </c>
       <c r="D1463" t="inlineStr"/>
       <c r="E1463" t="inlineStr">
@@ -37157,21 +37157,21 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>ME0579</t>
+          <t>ET0253</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>ENVASE NARANJA RUBOR EN CREMA SALLY</t>
+          <t>ETIQUETA BRONC DE CHOCOLATE MIEL 45ML</t>
         </is>
       </c>
       <c r="C1464" t="n">
-        <v>19475</v>
+        <v>22864</v>
       </c>
       <c r="D1464" t="inlineStr"/>
       <c r="E1464" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1464" t="inlineStr">
@@ -37183,16 +37183,16 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>ME1055</t>
+          <t>ME0578</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>TAPA SPRAY VERDE ROSCA 18</t>
+          <t>ENVASE ROJO RUBOR EN CREMA RUBY</t>
         </is>
       </c>
       <c r="C1465" t="n">
-        <v>11362</v>
+        <v>19980</v>
       </c>
       <c r="D1465" t="inlineStr"/>
       <c r="E1465" t="inlineStr">
@@ -37209,16 +37209,16 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>ME1067</t>
+          <t>ME0579</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>TAPA NARANJA RUBOR EN BARRA SALLY</t>
+          <t>ENVASE NARANJA RUBOR EN CREMA SALLY</t>
         </is>
       </c>
       <c r="C1466" t="n">
-        <v>19440</v>
+        <v>19475</v>
       </c>
       <c r="D1466" t="inlineStr"/>
       <c r="E1466" t="inlineStr">
@@ -37235,16 +37235,16 @@
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>ME0511</t>
+          <t>ME1055</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>ENV PEAD KABA B28 500ML</t>
+          <t>TAPA SPRAY VERDE ROSCA 18</t>
         </is>
       </c>
       <c r="C1467" t="n">
-        <v>28261</v>
+        <v>11362</v>
       </c>
       <c r="D1467" t="inlineStr"/>
       <c r="E1467" t="inlineStr">
@@ -37261,21 +37261,21 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>ET0253</t>
+          <t>ME1067</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>ETIQUETA BRONC DE CHOCOLATE MIEL 45ML</t>
+          <t>TAPA NARANJA RUBOR EN BARRA SALLY</t>
         </is>
       </c>
       <c r="C1468" t="n">
-        <v>22864</v>
+        <v>19440</v>
       </c>
       <c r="D1468" t="inlineStr"/>
       <c r="E1468" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1468" t="inlineStr">
@@ -37755,16 +37755,16 @@
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>ME1501</t>
+          <t>ME1039</t>
         </is>
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>TAPON DE VIDRIO ROSCA 28</t>
+          <t>TAPA FLIP TOP 28 MM MORADO SANGRIA</t>
         </is>
       </c>
       <c r="C1487" t="n">
-        <v>17477</v>
+        <v>39454</v>
       </c>
       <c r="D1487" t="inlineStr"/>
       <c r="E1487" t="inlineStr">
@@ -37781,21 +37781,21 @@
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>ME1039</t>
+          <t>ET02124</t>
         </is>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP 28 MM MORADO SANGRIA</t>
+          <t>ETIQUETA UNGUENTO GRANDE 120GR</t>
         </is>
       </c>
       <c r="C1488" t="n">
-        <v>39454</v>
+        <v>299</v>
       </c>
       <c r="D1488" t="inlineStr"/>
       <c r="E1488" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1488" t="inlineStr">
@@ -37807,21 +37807,21 @@
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>ET02124</t>
+          <t>ME1501</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>ETIQUETA UNGUENTO GRANDE 120GR</t>
+          <t>TAPON DE VIDRIO ROSCA 28</t>
         </is>
       </c>
       <c r="C1489" t="n">
-        <v>299</v>
+        <v>17477</v>
       </c>
       <c r="D1489" t="inlineStr"/>
       <c r="E1489" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1489" t="inlineStr">
@@ -39185,21 +39185,21 @@
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>ME0543</t>
+          <t>ET0204</t>
         </is>
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>TUBO COLAP CONTORNO DE OJOS 15ML V1</t>
+          <t>ETIQUETA PERFUME CABELLO SOÑADORA 120ML</t>
         </is>
       </c>
       <c r="C1542" t="n">
-        <v>22670</v>
+        <v>184</v>
       </c>
       <c r="D1542" t="inlineStr"/>
       <c r="E1542" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1542" t="inlineStr">
@@ -39211,21 +39211,21 @@
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>ET0204</t>
+          <t>ME0543</t>
         </is>
       </c>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>ETIQUETA PERFUME CABELLO SOÑADORA 120ML</t>
+          <t>TUBO COLAP CONTORNO DE OJOS 15ML V1</t>
         </is>
       </c>
       <c r="C1543" t="n">
-        <v>184</v>
+        <v>22670</v>
       </c>
       <c r="D1543" t="inlineStr"/>
       <c r="E1543" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1543" t="inlineStr">
@@ -39497,16 +39497,16 @@
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>ME1068</t>
+          <t>ME1012</t>
         </is>
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>TAPA SPRAY BLANCA R 18/410 (DEPILADOR N)</t>
+          <t>BOMBA ENCASQUE DORADA/BRONCEADORES</t>
         </is>
       </c>
       <c r="C1554" t="n">
-        <v>257740</v>
+        <v>17600</v>
       </c>
       <c r="D1554" t="inlineStr"/>
       <c r="E1554" t="inlineStr">
@@ -39523,21 +39523,21 @@
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>ME1012</t>
+          <t>ET02138</t>
         </is>
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>BOMBA ENCASQUE DORADA/BRONCEADORES</t>
+          <t>ETIQUETA KERATINA ALISADOR KABA 500 ML</t>
         </is>
       </c>
       <c r="C1555" t="n">
-        <v>17600</v>
+        <v>2868</v>
       </c>
       <c r="D1555" t="inlineStr"/>
       <c r="E1555" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1555" t="inlineStr">
@@ -39549,16 +39549,16 @@
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>ET02138</t>
+          <t>ET02139</t>
         </is>
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>ETIQUETA KERATINA ALISADOR KABA 500 ML</t>
+          <t>ETIQUETA KERATINA ALISADOR KABA 250 ML</t>
         </is>
       </c>
       <c r="C1556" t="n">
-        <v>2868</v>
+        <v>1368</v>
       </c>
       <c r="D1556" t="inlineStr"/>
       <c r="E1556" t="inlineStr">
@@ -39575,21 +39575,21 @@
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>ET02139</t>
+          <t>ME1068</t>
         </is>
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>ETIQUETA KERATINA ALISADOR KABA 250 ML</t>
+          <t>TAPA SPRAY BLANCA R 18/410 (DEPILADOR N)</t>
         </is>
       </c>
       <c r="C1557" t="n">
-        <v>1368</v>
+        <v>257740</v>
       </c>
       <c r="D1557" t="inlineStr"/>
       <c r="E1557" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1557" t="inlineStr">
@@ -40065,21 +40065,21 @@
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>314202</t>
+          <t>ME0527</t>
         </is>
       </c>
       <c r="B1576" t="inlineStr">
         <is>
-          <t>CLOISONNE ROUGE FLAMBE 440X</t>
+          <t>ENVASE VIDRIO ROSADO MARCADO 30ML</t>
         </is>
       </c>
       <c r="C1576" t="n">
-        <v>6266</v>
+        <v>46</v>
       </c>
       <c r="D1576" t="inlineStr"/>
       <c r="E1576" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1576" t="inlineStr">
@@ -40091,21 +40091,21 @@
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>ME0527</t>
+          <t>314202</t>
         </is>
       </c>
       <c r="B1577" t="inlineStr">
         <is>
-          <t>ENVASE VIDRIO ROSADO MARCADO 30ML</t>
+          <t>CLOISONNE ROUGE FLAMBE 440X</t>
         </is>
       </c>
       <c r="C1577" t="n">
-        <v>46</v>
+        <v>6266</v>
       </c>
       <c r="D1577" t="inlineStr"/>
       <c r="E1577" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1577" t="inlineStr">
@@ -40403,21 +40403,21 @@
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>190102</t>
+          <t>ET0202CA</t>
         </is>
       </c>
       <c r="B1589" t="inlineStr">
         <is>
-          <t>CARBÓN ACTIVADO</t>
+          <t>ETIQUETA ILUMINADOR GOLD ROSE CARA</t>
         </is>
       </c>
       <c r="C1589" t="n">
-        <v>500</v>
+        <v>3916</v>
       </c>
       <c r="D1589" t="inlineStr"/>
       <c r="E1589" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1589" t="inlineStr">
@@ -40429,21 +40429,21 @@
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>ET0202CA</t>
+          <t>190102</t>
         </is>
       </c>
       <c r="B1590" t="inlineStr">
         <is>
-          <t>ETIQUETA ILUMINADOR GOLD ROSE CARA</t>
+          <t>CARBÓN ACTIVADO</t>
         </is>
       </c>
       <c r="C1590" t="n">
-        <v>3916</v>
+        <v>500</v>
       </c>
       <c r="D1590" t="inlineStr"/>
       <c r="E1590" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1590" t="inlineStr">
@@ -40507,21 +40507,21 @@
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>ME0553</t>
+          <t>ETC0160</t>
         </is>
       </c>
       <c r="B1593" t="inlineStr">
         <is>
-          <t>TUBO COLAP TTO REVITALIZANTE 230ML V1</t>
+          <t>CAJA RUBOR EN CREMA RUBY</t>
         </is>
       </c>
       <c r="C1593" t="n">
-        <v>478</v>
+        <v>10536</v>
       </c>
       <c r="D1593" t="inlineStr"/>
       <c r="E1593" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1593" t="inlineStr">
@@ -40533,16 +40533,16 @@
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>ETC0160</t>
+          <t>ETC0161</t>
         </is>
       </c>
       <c r="B1594" t="inlineStr">
         <is>
-          <t>CAJA RUBOR EN CREMA RUBY</t>
+          <t>CAJA RUBOR EN CREMA SALLY</t>
         </is>
       </c>
       <c r="C1594" t="n">
-        <v>10536</v>
+        <v>10328</v>
       </c>
       <c r="D1594" t="inlineStr"/>
       <c r="E1594" t="inlineStr">
@@ -40559,21 +40559,21 @@
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>ETC0161</t>
+          <t>ME0553</t>
         </is>
       </c>
       <c r="B1595" t="inlineStr">
         <is>
-          <t>CAJA RUBOR EN CREMA SALLY</t>
+          <t>TUBO COLAP TTO REVITALIZANTE 230ML V1</t>
         </is>
       </c>
       <c r="C1595" t="n">
-        <v>10328</v>
+        <v>478</v>
       </c>
       <c r="D1595" t="inlineStr"/>
       <c r="E1595" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1595" t="inlineStr">
@@ -41105,21 +41105,21 @@
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>ME0506</t>
+          <t>ETC0173</t>
         </is>
       </c>
       <c r="B1616" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 260/250 ML</t>
+          <t>CAJA TONICO CAPILAR KABA ROSADA 120ML</t>
         </is>
       </c>
       <c r="C1616" t="n">
-        <v>4464</v>
+        <v>193</v>
       </c>
       <c r="D1616" t="inlineStr"/>
       <c r="E1616" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1616" t="inlineStr">
@@ -41131,21 +41131,21 @@
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>ETC0173</t>
+          <t>ME0506</t>
         </is>
       </c>
       <c r="B1617" t="inlineStr">
         <is>
-          <t>CAJA TONICO CAPILAR KABA ROSADA 120ML</t>
+          <t>BALA TRANSPARENTE 260/250 ML</t>
         </is>
       </c>
       <c r="C1617" t="n">
-        <v>193</v>
+        <v>4464</v>
       </c>
       <c r="D1617" t="inlineStr"/>
       <c r="E1617" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1617" t="inlineStr">
@@ -41261,16 +41261,16 @@
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>ME0515VG</t>
+          <t>ME1001VG</t>
         </is>
       </c>
       <c r="B1622" t="inlineStr">
         <is>
-          <t>ENVASE CAPSULA BRONCEADOR VIVIANA GRONDO</t>
+          <t>TAPA BRONCEADOR R/24 VIVIANA GRONDONA</t>
         </is>
       </c>
       <c r="C1622" t="n">
-        <v>11568</v>
+        <v>12219</v>
       </c>
       <c r="D1622" t="inlineStr"/>
       <c r="E1622" t="inlineStr">
@@ -41287,16 +41287,16 @@
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>ME1001VG</t>
+          <t>ME0533VG</t>
         </is>
       </c>
       <c r="B1623" t="inlineStr">
         <is>
-          <t>TAPA BRONCEADOR R/24 VIVIANA GRONDONA</t>
+          <t>ENVASE Y TAPA APLICADOR VIVIANA GRONDONA</t>
         </is>
       </c>
       <c r="C1623" t="n">
-        <v>12219</v>
+        <v>11568</v>
       </c>
       <c r="D1623" t="inlineStr"/>
       <c r="E1623" t="inlineStr">
@@ -41313,12 +41313,12 @@
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>ME0533VG</t>
+          <t>ME0515VG</t>
         </is>
       </c>
       <c r="B1624" t="inlineStr">
         <is>
-          <t>ENVASE Y TAPA APLICADOR VIVIANA GRONDONA</t>
+          <t>ENVASE CAPSULA BRONCEADOR VIVIANA GRONDO</t>
         </is>
       </c>
       <c r="C1624" t="n">
@@ -45285,21 +45285,21 @@
     <row r="1773">
       <c r="A1773" t="inlineStr">
         <is>
-          <t>144301</t>
+          <t>ET0204VG</t>
         </is>
       </c>
       <c r="B1773" t="inlineStr">
         <is>
-          <t>ALCOHOL CETOESTEARÍLICO 30/70</t>
+          <t>ETIQUETA LIP GLOSS VIVIANA GRONDONA D2</t>
         </is>
       </c>
       <c r="C1773" t="n">
-        <v>96090</v>
+        <v>2500</v>
       </c>
       <c r="D1773" t="inlineStr"/>
       <c r="E1773" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1773" t="inlineStr">
@@ -45311,12 +45311,12 @@
     <row r="1774">
       <c r="A1774" t="inlineStr">
         <is>
-          <t>ET0204VG</t>
+          <t>ET0203VG</t>
         </is>
       </c>
       <c r="B1774" t="inlineStr">
         <is>
-          <t>ETIQUETA LIP GLOSS VIVIANA GRONDONA D2</t>
+          <t>ETIQUETA LIP GLOSS VIVIANA GRONDONA D1</t>
         </is>
       </c>
       <c r="C1774" t="n">
@@ -45337,21 +45337,21 @@
     <row r="1775">
       <c r="A1775" t="inlineStr">
         <is>
-          <t>ET0203VG</t>
+          <t>144301</t>
         </is>
       </c>
       <c r="B1775" t="inlineStr">
         <is>
-          <t>ETIQUETA LIP GLOSS VIVIANA GRONDONA D1</t>
+          <t>ALCOHOL CETOESTEARÍLICO 30/70</t>
         </is>
       </c>
       <c r="C1775" t="n">
-        <v>2500</v>
+        <v>96090</v>
       </c>
       <c r="D1775" t="inlineStr"/>
       <c r="E1775" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1775" t="inlineStr">
@@ -46767,16 +46767,16 @@
     <row r="1830">
       <c r="A1830" t="inlineStr">
         <is>
-          <t>ME0544</t>
+          <t>ME0572</t>
         </is>
       </c>
       <c r="B1830" t="inlineStr">
         <is>
-          <t>TUBO COLAP DERMOACLARANTE 60ML V1</t>
+          <t>COLAPSIBLE AZUL CREMA CORPORAL ACLARANTE</t>
         </is>
       </c>
       <c r="C1830" t="n">
-        <v>815</v>
+        <v>6750</v>
       </c>
       <c r="D1830" t="inlineStr"/>
       <c r="E1830" t="inlineStr">
@@ -46793,16 +46793,16 @@
     <row r="1831">
       <c r="A1831" t="inlineStr">
         <is>
-          <t>ME0572</t>
+          <t>ME0544</t>
         </is>
       </c>
       <c r="B1831" t="inlineStr">
         <is>
-          <t>COLAPSIBLE AZUL CREMA CORPORAL ACLARANTE</t>
+          <t>TUBO COLAP DERMOACLARANTE 60ML V1</t>
         </is>
       </c>
       <c r="C1831" t="n">
-        <v>6750</v>
+        <v>815</v>
       </c>
       <c r="D1831" t="inlineStr"/>
       <c r="E1831" t="inlineStr">

--- a/inventario_operaciones.xlsx
+++ b/inventario_operaciones.xlsx
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="D6" t="n">
         <v>423.8931297709924</v>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="D8" t="n">
         <v>171.412213740458</v>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D9" t="n">
         <v>531.7557251908397</v>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D14" t="n">
         <v>1100.954198473282</v>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-46</v>
+        <v>-54</v>
       </c>
       <c r="D15" t="n">
         <v>1163.473282442748</v>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="D21" t="n">
         <v>1723.396946564885</v>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="D22" t="n">
         <v>1647.137404580153</v>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-1572</v>
+        <v>-1587</v>
       </c>
       <c r="D23" t="n">
         <v>23981.2213740458</v>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D25" t="n">
         <v>21.87022900763359</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D30" t="n">
         <v>3218.702290076336</v>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D32" t="n">
         <v>33819.04580152671</v>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D35" t="n">
         <v>8401.603053435116</v>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="D38" t="n">
         <v>574.0076335877862</v>
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="D41" t="n">
         <v>1825.763358778626</v>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="D51" t="n">
         <v>162.824427480916</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="D52" t="n">
         <v>101.6793893129771</v>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="D66" t="n">
         <v>15285.91603053435</v>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D75" t="n">
         <v>4484.885496183206</v>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="D77" t="n">
         <v>11863.1679389313</v>
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D82" t="n">
         <v>239.0839694656489</v>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D96" t="n">
         <v>8045.038167938931</v>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D100" t="n">
         <v>6729.73282442748</v>
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D103" t="n">
         <v>230.7251908396946</v>
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D107" t="n">
         <v>1616.908396946565</v>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D110" t="n">
         <v>4274.312977099236</v>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D117" t="n">
         <v>324.2748091603053</v>
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D122" t="n">
         <v>87.25190839694656</v>
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D129" t="n">
         <v>260.9541984732824</v>
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D130" t="n">
         <v>196.8320610687023</v>
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>-807</v>
+        <v>-823</v>
       </c>
       <c r="D136" t="n">
         <v>38473.96946564886</v>
@@ -4204,7 +4204,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D137" t="n">
         <v>408.7786259541984</v>
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D142" t="n">
         <v>5048.244274809161</v>
@@ -4364,7 +4364,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D143" t="n">
         <v>98.58778625954199</v>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D148" t="n">
         <v>383.3587786259542</v>
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D150" t="n">
         <v>118.5114503816794</v>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D151" t="n">
         <v>82.32824427480917</v>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D155" t="n">
         <v>164.7709923664122</v>
@@ -4884,7 +4884,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D162" t="n">
         <v>722.9770992366413</v>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D165" t="n">
         <v>64.58015267175571</v>
@@ -5024,7 +5024,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
@@ -5774,7 +5774,7 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="D195" t="n">
         <v>39274.69465648855</v>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>2259</v>
+        <v>2256</v>
       </c>
       <c r="D196" t="n">
         <v>32942.74809160305</v>
@@ -13589,21 +13589,21 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>ME1011</t>
+          <t>155301</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>LOTIÓN PUMP 28/410 SILVER/WHITE</t>
+          <t>ESTOGEL M</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>326790</v>
+        <v>100000</v>
       </c>
       <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -13615,21 +13615,21 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>155301</t>
+          <t>ME1011</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>ESTOGEL M</t>
+          <t>LOTIÓN PUMP 28/410 SILVER/WHITE</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>100000</v>
+        <v>326790</v>
       </c>
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -25192,7 +25192,7 @@
         </is>
       </c>
       <c r="C987" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D987" t="inlineStr"/>
       <c r="E987" t="inlineStr"/>
@@ -34791,21 +34791,21 @@
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>ME1049</t>
+          <t>314208</t>
         </is>
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>TAPA PUSH PULL DORADA ROSCA 24</t>
+          <t>GEMTONE AMBER G001</t>
         </is>
       </c>
       <c r="C1373" t="n">
-        <v>3386</v>
+        <v>73488</v>
       </c>
       <c r="D1373" t="inlineStr"/>
       <c r="E1373" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1373" t="inlineStr">
@@ -34817,21 +34817,21 @@
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>314208</t>
+          <t>ME1049</t>
         </is>
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>GEMTONE AMBER G001</t>
+          <t>TAPA PUSH PULL DORADA ROSCA 24</t>
         </is>
       </c>
       <c r="C1374" t="n">
-        <v>73488</v>
+        <v>3386</v>
       </c>
       <c r="D1374" t="inlineStr"/>
       <c r="E1374" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1374" t="inlineStr">
@@ -35207,21 +35207,21 @@
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>ET0202</t>
+          <t>ME0505</t>
         </is>
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>ETIQUETA PERFUME CABELLO ARRIESGAD 120ML</t>
+          <t>BALA TRANSPARENTE 120ML</t>
         </is>
       </c>
       <c r="C1389" t="n">
-        <v>140</v>
+        <v>2543</v>
       </c>
       <c r="D1389" t="inlineStr"/>
       <c r="E1389" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1389" t="inlineStr">
@@ -35233,21 +35233,21 @@
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>ME0505</t>
+          <t>ET0202</t>
         </is>
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 120ML</t>
+          <t>ETIQUETA PERFUME CABELLO ARRIESGAD 120ML</t>
         </is>
       </c>
       <c r="C1390" t="n">
-        <v>2543</v>
+        <v>140</v>
       </c>
       <c r="D1390" t="inlineStr"/>
       <c r="E1390" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1390" t="inlineStr">
@@ -36143,21 +36143,21 @@
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>ME1043</t>
+          <t>173501</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
+          <t>ULTRAMAR U-200 AZUL</t>
         </is>
       </c>
       <c r="C1425" t="n">
-        <v>2731</v>
+        <v>5310</v>
       </c>
       <c r="D1425" t="inlineStr"/>
       <c r="E1425" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1425" t="inlineStr">
@@ -36169,16 +36169,16 @@
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>ME1044</t>
+          <t>ME1043</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP PLATEADA ROSCA 18</t>
+          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
         </is>
       </c>
       <c r="C1426" t="n">
-        <v>39551</v>
+        <v>2731</v>
       </c>
       <c r="D1426" t="inlineStr"/>
       <c r="E1426" t="inlineStr">
@@ -36195,21 +36195,21 @@
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>173501</t>
+          <t>ME1044</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>ULTRAMAR U-200 AZUL</t>
+          <t>TAPA FLIP TOP PLATEADA ROSCA 18</t>
         </is>
       </c>
       <c r="C1427" t="n">
-        <v>5310</v>
+        <v>39551</v>
       </c>
       <c r="D1427" t="inlineStr"/>
       <c r="E1427" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1427" t="inlineStr">
@@ -37131,16 +37131,16 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>ME0511</t>
+          <t>ME0578</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>ENV PEAD KABA B28 500ML</t>
+          <t>ENVASE ROJO RUBOR EN CREMA RUBY</t>
         </is>
       </c>
       <c r="C1463" t="n">
-        <v>28261</v>
+        <v>19980</v>
       </c>
       <c r="D1463" t="inlineStr"/>
       <c r="E1463" t="inlineStr">
@@ -37157,21 +37157,21 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>ET0253</t>
+          <t>ME0579</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>ETIQUETA BRONC DE CHOCOLATE MIEL 45ML</t>
+          <t>ENVASE NARANJA RUBOR EN CREMA SALLY</t>
         </is>
       </c>
       <c r="C1464" t="n">
-        <v>22864</v>
+        <v>19475</v>
       </c>
       <c r="D1464" t="inlineStr"/>
       <c r="E1464" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1464" t="inlineStr">
@@ -37183,16 +37183,16 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>ME0578</t>
+          <t>ME1055</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>ENVASE ROJO RUBOR EN CREMA RUBY</t>
+          <t>TAPA SPRAY VERDE ROSCA 18</t>
         </is>
       </c>
       <c r="C1465" t="n">
-        <v>19980</v>
+        <v>11362</v>
       </c>
       <c r="D1465" t="inlineStr"/>
       <c r="E1465" t="inlineStr">
@@ -37209,16 +37209,16 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>ME0579</t>
+          <t>ME1067</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>ENVASE NARANJA RUBOR EN CREMA SALLY</t>
+          <t>TAPA NARANJA RUBOR EN BARRA SALLY</t>
         </is>
       </c>
       <c r="C1466" t="n">
-        <v>19475</v>
+        <v>19440</v>
       </c>
       <c r="D1466" t="inlineStr"/>
       <c r="E1466" t="inlineStr">
@@ -37235,16 +37235,16 @@
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>ME1055</t>
+          <t>ME0511</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>TAPA SPRAY VERDE ROSCA 18</t>
+          <t>ENV PEAD KABA B28 500ML</t>
         </is>
       </c>
       <c r="C1467" t="n">
-        <v>11362</v>
+        <v>28261</v>
       </c>
       <c r="D1467" t="inlineStr"/>
       <c r="E1467" t="inlineStr">
@@ -37261,21 +37261,21 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>ME1067</t>
+          <t>ET0253</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>TAPA NARANJA RUBOR EN BARRA SALLY</t>
+          <t>ETIQUETA BRONC DE CHOCOLATE MIEL 45ML</t>
         </is>
       </c>
       <c r="C1468" t="n">
-        <v>19440</v>
+        <v>22864</v>
       </c>
       <c r="D1468" t="inlineStr"/>
       <c r="E1468" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1468" t="inlineStr">
@@ -37755,16 +37755,16 @@
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>ME1039</t>
+          <t>ME1501</t>
         </is>
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP 28 MM MORADO SANGRIA</t>
+          <t>TAPON DE VIDRIO ROSCA 28</t>
         </is>
       </c>
       <c r="C1487" t="n">
-        <v>39454</v>
+        <v>17477</v>
       </c>
       <c r="D1487" t="inlineStr"/>
       <c r="E1487" t="inlineStr">
@@ -37781,21 +37781,21 @@
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>ET02124</t>
+          <t>ME1039</t>
         </is>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>ETIQUETA UNGUENTO GRANDE 120GR</t>
+          <t>TAPA FLIP TOP 28 MM MORADO SANGRIA</t>
         </is>
       </c>
       <c r="C1488" t="n">
-        <v>299</v>
+        <v>39454</v>
       </c>
       <c r="D1488" t="inlineStr"/>
       <c r="E1488" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1488" t="inlineStr">
@@ -37807,21 +37807,21 @@
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>ME1501</t>
+          <t>ET02124</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>TAPON DE VIDRIO ROSCA 28</t>
+          <t>ETIQUETA UNGUENTO GRANDE 120GR</t>
         </is>
       </c>
       <c r="C1489" t="n">
-        <v>17477</v>
+        <v>299</v>
       </c>
       <c r="D1489" t="inlineStr"/>
       <c r="E1489" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1489" t="inlineStr">
@@ -39185,21 +39185,21 @@
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>ET0204</t>
+          <t>ME0543</t>
         </is>
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>ETIQUETA PERFUME CABELLO SOÑADORA 120ML</t>
+          <t>TUBO COLAP CONTORNO DE OJOS 15ML V1</t>
         </is>
       </c>
       <c r="C1542" t="n">
-        <v>184</v>
+        <v>22670</v>
       </c>
       <c r="D1542" t="inlineStr"/>
       <c r="E1542" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1542" t="inlineStr">
@@ -39211,21 +39211,21 @@
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>ME0543</t>
+          <t>ET0204</t>
         </is>
       </c>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>TUBO COLAP CONTORNO DE OJOS 15ML V1</t>
+          <t>ETIQUETA PERFUME CABELLO SOÑADORA 120ML</t>
         </is>
       </c>
       <c r="C1543" t="n">
-        <v>22670</v>
+        <v>184</v>
       </c>
       <c r="D1543" t="inlineStr"/>
       <c r="E1543" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1543" t="inlineStr">
@@ -39497,16 +39497,16 @@
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>ME1012</t>
+          <t>ME1068</t>
         </is>
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>BOMBA ENCASQUE DORADA/BRONCEADORES</t>
+          <t>TAPA SPRAY BLANCA R 18/410 (DEPILADOR N)</t>
         </is>
       </c>
       <c r="C1554" t="n">
-        <v>17600</v>
+        <v>257740</v>
       </c>
       <c r="D1554" t="inlineStr"/>
       <c r="E1554" t="inlineStr">
@@ -39523,21 +39523,21 @@
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>ET02138</t>
+          <t>ME1012</t>
         </is>
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>ETIQUETA KERATINA ALISADOR KABA 500 ML</t>
+          <t>BOMBA ENCASQUE DORADA/BRONCEADORES</t>
         </is>
       </c>
       <c r="C1555" t="n">
-        <v>2868</v>
+        <v>17600</v>
       </c>
       <c r="D1555" t="inlineStr"/>
       <c r="E1555" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1555" t="inlineStr">
@@ -39549,16 +39549,16 @@
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>ET02139</t>
+          <t>ET02138</t>
         </is>
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>ETIQUETA KERATINA ALISADOR KABA 250 ML</t>
+          <t>ETIQUETA KERATINA ALISADOR KABA 500 ML</t>
         </is>
       </c>
       <c r="C1556" t="n">
-        <v>1368</v>
+        <v>2868</v>
       </c>
       <c r="D1556" t="inlineStr"/>
       <c r="E1556" t="inlineStr">
@@ -39575,21 +39575,21 @@
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>ME1068</t>
+          <t>ET02139</t>
         </is>
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>TAPA SPRAY BLANCA R 18/410 (DEPILADOR N)</t>
+          <t>ETIQUETA KERATINA ALISADOR KABA 250 ML</t>
         </is>
       </c>
       <c r="C1557" t="n">
-        <v>257740</v>
+        <v>1368</v>
       </c>
       <c r="D1557" t="inlineStr"/>
       <c r="E1557" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1557" t="inlineStr">
@@ -40065,21 +40065,21 @@
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>ME0527</t>
+          <t>314202</t>
         </is>
       </c>
       <c r="B1576" t="inlineStr">
         <is>
-          <t>ENVASE VIDRIO ROSADO MARCADO 30ML</t>
+          <t>CLOISONNE ROUGE FLAMBE 440X</t>
         </is>
       </c>
       <c r="C1576" t="n">
-        <v>46</v>
+        <v>6266</v>
       </c>
       <c r="D1576" t="inlineStr"/>
       <c r="E1576" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1576" t="inlineStr">
@@ -40091,21 +40091,21 @@
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>314202</t>
+          <t>ME0527</t>
         </is>
       </c>
       <c r="B1577" t="inlineStr">
         <is>
-          <t>CLOISONNE ROUGE FLAMBE 440X</t>
+          <t>ENVASE VIDRIO ROSADO MARCADO 30ML</t>
         </is>
       </c>
       <c r="C1577" t="n">
-        <v>6266</v>
+        <v>46</v>
       </c>
       <c r="D1577" t="inlineStr"/>
       <c r="E1577" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1577" t="inlineStr">
@@ -40403,21 +40403,21 @@
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>ET0202CA</t>
+          <t>190102</t>
         </is>
       </c>
       <c r="B1589" t="inlineStr">
         <is>
-          <t>ETIQUETA ILUMINADOR GOLD ROSE CARA</t>
+          <t>CARBÓN ACTIVADO</t>
         </is>
       </c>
       <c r="C1589" t="n">
-        <v>3916</v>
+        <v>500</v>
       </c>
       <c r="D1589" t="inlineStr"/>
       <c r="E1589" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1589" t="inlineStr">
@@ -40429,21 +40429,21 @@
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>190102</t>
+          <t>ET0202CA</t>
         </is>
       </c>
       <c r="B1590" t="inlineStr">
         <is>
-          <t>CARBÓN ACTIVADO</t>
+          <t>ETIQUETA ILUMINADOR GOLD ROSE CARA</t>
         </is>
       </c>
       <c r="C1590" t="n">
-        <v>500</v>
+        <v>3916</v>
       </c>
       <c r="D1590" t="inlineStr"/>
       <c r="E1590" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1590" t="inlineStr">
@@ -40507,21 +40507,21 @@
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>ETC0160</t>
+          <t>ME0553</t>
         </is>
       </c>
       <c r="B1593" t="inlineStr">
         <is>
-          <t>CAJA RUBOR EN CREMA RUBY</t>
+          <t>TUBO COLAP TTO REVITALIZANTE 230ML V1</t>
         </is>
       </c>
       <c r="C1593" t="n">
-        <v>10536</v>
+        <v>478</v>
       </c>
       <c r="D1593" t="inlineStr"/>
       <c r="E1593" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1593" t="inlineStr">
@@ -40533,16 +40533,16 @@
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>ETC0161</t>
+          <t>ETC0160</t>
         </is>
       </c>
       <c r="B1594" t="inlineStr">
         <is>
-          <t>CAJA RUBOR EN CREMA SALLY</t>
+          <t>CAJA RUBOR EN CREMA RUBY</t>
         </is>
       </c>
       <c r="C1594" t="n">
-        <v>10328</v>
+        <v>10536</v>
       </c>
       <c r="D1594" t="inlineStr"/>
       <c r="E1594" t="inlineStr">
@@ -40559,21 +40559,21 @@
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>ME0553</t>
+          <t>ETC0161</t>
         </is>
       </c>
       <c r="B1595" t="inlineStr">
         <is>
-          <t>TUBO COLAP TTO REVITALIZANTE 230ML V1</t>
+          <t>CAJA RUBOR EN CREMA SALLY</t>
         </is>
       </c>
       <c r="C1595" t="n">
-        <v>478</v>
+        <v>10328</v>
       </c>
       <c r="D1595" t="inlineStr"/>
       <c r="E1595" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1595" t="inlineStr">
@@ -41105,21 +41105,21 @@
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>ETC0173</t>
+          <t>ME0506</t>
         </is>
       </c>
       <c r="B1616" t="inlineStr">
         <is>
-          <t>CAJA TONICO CAPILAR KABA ROSADA 120ML</t>
+          <t>BALA TRANSPARENTE 260/250 ML</t>
         </is>
       </c>
       <c r="C1616" t="n">
-        <v>193</v>
+        <v>4464</v>
       </c>
       <c r="D1616" t="inlineStr"/>
       <c r="E1616" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1616" t="inlineStr">
@@ -41131,21 +41131,21 @@
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>ME0506</t>
+          <t>ETC0173</t>
         </is>
       </c>
       <c r="B1617" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 260/250 ML</t>
+          <t>CAJA TONICO CAPILAR KABA ROSADA 120ML</t>
         </is>
       </c>
       <c r="C1617" t="n">
-        <v>4464</v>
+        <v>193</v>
       </c>
       <c r="D1617" t="inlineStr"/>
       <c r="E1617" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1617" t="inlineStr">
@@ -41261,16 +41261,16 @@
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>ME1001VG</t>
+          <t>ME0515VG</t>
         </is>
       </c>
       <c r="B1622" t="inlineStr">
         <is>
-          <t>TAPA BRONCEADOR R/24 VIVIANA GRONDONA</t>
+          <t>ENVASE CAPSULA BRONCEADOR VIVIANA GRONDO</t>
         </is>
       </c>
       <c r="C1622" t="n">
-        <v>12219</v>
+        <v>11568</v>
       </c>
       <c r="D1622" t="inlineStr"/>
       <c r="E1622" t="inlineStr">
@@ -41287,16 +41287,16 @@
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>ME0533VG</t>
+          <t>ME1001VG</t>
         </is>
       </c>
       <c r="B1623" t="inlineStr">
         <is>
-          <t>ENVASE Y TAPA APLICADOR VIVIANA GRONDONA</t>
+          <t>TAPA BRONCEADOR R/24 VIVIANA GRONDONA</t>
         </is>
       </c>
       <c r="C1623" t="n">
-        <v>11568</v>
+        <v>12219</v>
       </c>
       <c r="D1623" t="inlineStr"/>
       <c r="E1623" t="inlineStr">
@@ -41313,12 +41313,12 @@
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>ME0515VG</t>
+          <t>ME0533VG</t>
         </is>
       </c>
       <c r="B1624" t="inlineStr">
         <is>
-          <t>ENVASE CAPSULA BRONCEADOR VIVIANA GRONDO</t>
+          <t>ENVASE Y TAPA APLICADOR VIVIANA GRONDONA</t>
         </is>
       </c>
       <c r="C1624" t="n">
@@ -45285,21 +45285,21 @@
     <row r="1773">
       <c r="A1773" t="inlineStr">
         <is>
-          <t>ET0204VG</t>
+          <t>144301</t>
         </is>
       </c>
       <c r="B1773" t="inlineStr">
         <is>
-          <t>ETIQUETA LIP GLOSS VIVIANA GRONDONA D2</t>
+          <t>ALCOHOL CETOESTEARÍLICO 30/70</t>
         </is>
       </c>
       <c r="C1773" t="n">
-        <v>2500</v>
+        <v>96090</v>
       </c>
       <c r="D1773" t="inlineStr"/>
       <c r="E1773" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1773" t="inlineStr">
@@ -45311,12 +45311,12 @@
     <row r="1774">
       <c r="A1774" t="inlineStr">
         <is>
-          <t>ET0203VG</t>
+          <t>ET0204VG</t>
         </is>
       </c>
       <c r="B1774" t="inlineStr">
         <is>
-          <t>ETIQUETA LIP GLOSS VIVIANA GRONDONA D1</t>
+          <t>ETIQUETA LIP GLOSS VIVIANA GRONDONA D2</t>
         </is>
       </c>
       <c r="C1774" t="n">
@@ -45337,21 +45337,21 @@
     <row r="1775">
       <c r="A1775" t="inlineStr">
         <is>
-          <t>144301</t>
+          <t>ET0203VG</t>
         </is>
       </c>
       <c r="B1775" t="inlineStr">
         <is>
-          <t>ALCOHOL CETOESTEARÍLICO 30/70</t>
+          <t>ETIQUETA LIP GLOSS VIVIANA GRONDONA D1</t>
         </is>
       </c>
       <c r="C1775" t="n">
-        <v>96090</v>
+        <v>2500</v>
       </c>
       <c r="D1775" t="inlineStr"/>
       <c r="E1775" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1775" t="inlineStr">
@@ -46767,16 +46767,16 @@
     <row r="1830">
       <c r="A1830" t="inlineStr">
         <is>
-          <t>ME0572</t>
+          <t>ME0544</t>
         </is>
       </c>
       <c r="B1830" t="inlineStr">
         <is>
-          <t>COLAPSIBLE AZUL CREMA CORPORAL ACLARANTE</t>
+          <t>TUBO COLAP DERMOACLARANTE 60ML V1</t>
         </is>
       </c>
       <c r="C1830" t="n">
-        <v>6750</v>
+        <v>815</v>
       </c>
       <c r="D1830" t="inlineStr"/>
       <c r="E1830" t="inlineStr">
@@ -46793,16 +46793,16 @@
     <row r="1831">
       <c r="A1831" t="inlineStr">
         <is>
-          <t>ME0544</t>
+          <t>ME0572</t>
         </is>
       </c>
       <c r="B1831" t="inlineStr">
         <is>
-          <t>TUBO COLAP DERMOACLARANTE 60ML V1</t>
+          <t>COLAPSIBLE AZUL CREMA CORPORAL ACLARANTE</t>
         </is>
       </c>
       <c r="C1831" t="n">
-        <v>815</v>
+        <v>6750</v>
       </c>
       <c r="D1831" t="inlineStr"/>
       <c r="E1831" t="inlineStr">

--- a/inventario_operaciones.xlsx
+++ b/inventario_operaciones.xlsx
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-128</v>
+        <v>140</v>
       </c>
       <c r="D18" t="n">
         <v>1701.068702290076</v>
@@ -7333,19 +7333,19 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>K010402</t>
+          <t>D030601</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO CONFIDENTE KABA</t>
+          <t>FRESHING POP AFTER SUN DLUCHI</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>2016</v>
+        <v>20136</v>
       </c>
       <c r="D253" t="n">
-        <v>1163.473282442748</v>
+        <v>267.9389312977099</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -7361,19 +7361,19 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>D030601</t>
+          <t>K010402</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>FRESHING POP AFTER SUN DLUCHI</t>
+          <t>PERFUME PARA EL CABELLO CONFIDENTE KABA</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>20136</v>
+        <v>2016</v>
       </c>
       <c r="D254" t="n">
-        <v>267.9389312977099</v>
+        <v>1163.473282442748</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>

--- a/inventario_operaciones.xlsx
+++ b/inventario_operaciones.xlsx
@@ -9089,21 +9089,21 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>340302</t>
+          <t>ME0546</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>340302</t>
+          <t>TUBO COLAP FOTOPROTECTOR 60ML V1</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>44000</v>
+        <v>4514</v>
       </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -9115,21 +9115,21 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ME0546</t>
+          <t>340302</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>TUBO COLAP FOTOPROTECTOR 60ML V1</t>
+          <t>340302</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>4514</v>
+        <v>44000</v>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -36139,21 +36139,21 @@
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>314208</t>
+          <t>ME1049</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>GEMTONE AMBER G001</t>
+          <t>TAPA PUSH PULL DORADA ROSCA 24</t>
         </is>
       </c>
       <c r="C1425" t="n">
-        <v>73488</v>
+        <v>3386</v>
       </c>
       <c r="D1425" t="inlineStr"/>
       <c r="E1425" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1425" t="inlineStr">
@@ -36165,21 +36165,21 @@
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>ME1049</t>
+          <t>314208</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>TAPA PUSH PULL DORADA ROSCA 24</t>
+          <t>GEMTONE AMBER G001</t>
         </is>
       </c>
       <c r="C1426" t="n">
-        <v>3386</v>
+        <v>73488</v>
       </c>
       <c r="D1426" t="inlineStr"/>
       <c r="E1426" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1426" t="inlineStr">
@@ -37517,21 +37517,21 @@
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>173501</t>
+          <t>ME1043</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>ULTRAMAR U-200 AZUL</t>
+          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
         </is>
       </c>
       <c r="C1478" t="n">
-        <v>5025</v>
+        <v>2731</v>
       </c>
       <c r="D1478" t="inlineStr"/>
       <c r="E1478" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1478" t="inlineStr">
@@ -37543,16 +37543,16 @@
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>ME1043</t>
+          <t>ME1044</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
+          <t>TAPA FLIP TOP PLATEADA ROSCA 18</t>
         </is>
       </c>
       <c r="C1479" t="n">
-        <v>2731</v>
+        <v>39166</v>
       </c>
       <c r="D1479" t="inlineStr"/>
       <c r="E1479" t="inlineStr">
@@ -37569,21 +37569,21 @@
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>ME1044</t>
+          <t>173501</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP PLATEADA ROSCA 18</t>
+          <t>ULTRAMAR U-200 AZUL</t>
         </is>
       </c>
       <c r="C1480" t="n">
-        <v>39166</v>
+        <v>5025</v>
       </c>
       <c r="D1480" t="inlineStr"/>
       <c r="E1480" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1480" t="inlineStr">
@@ -38921,16 +38921,16 @@
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>ME0507</t>
+          <t>ME0504</t>
         </is>
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 30ML</t>
+          <t>BALA NEGRA LARGA 120ML</t>
         </is>
       </c>
       <c r="C1532" t="n">
-        <v>24300</v>
+        <v>9239</v>
       </c>
       <c r="D1532" t="inlineStr"/>
       <c r="E1532" t="inlineStr">
@@ -38947,16 +38947,16 @@
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>ME0504</t>
+          <t>ME1028</t>
         </is>
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>BALA NEGRA LARGA 120ML</t>
+          <t>TAPA CON APLICADOR PUNTA PINCEL</t>
         </is>
       </c>
       <c r="C1533" t="n">
-        <v>9239</v>
+        <v>15877</v>
       </c>
       <c r="D1533" t="inlineStr"/>
       <c r="E1533" t="inlineStr">
@@ -38973,16 +38973,16 @@
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>ME1028</t>
+          <t>ME1059</t>
         </is>
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>TAPA CON APLICADOR PUNTA PINCEL</t>
+          <t>WIPER ( ESCURRIDOR/BARREDOR) NATURAL</t>
         </is>
       </c>
       <c r="C1534" t="n">
-        <v>15877</v>
+        <v>30387</v>
       </c>
       <c r="D1534" t="inlineStr"/>
       <c r="E1534" t="inlineStr">
@@ -38999,16 +38999,16 @@
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>ME1059</t>
+          <t>ME0507</t>
         </is>
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>WIPER ( ESCURRIDOR/BARREDOR) NATURAL</t>
+          <t>BALA TRANSPARENTE 30ML</t>
         </is>
       </c>
       <c r="C1535" t="n">
-        <v>30387</v>
+        <v>24300</v>
       </c>
       <c r="D1535" t="inlineStr"/>
       <c r="E1535" t="inlineStr">
@@ -41543,21 +41543,21 @@
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>314202</t>
+          <t>ME0527</t>
         </is>
       </c>
       <c r="B1633" t="inlineStr">
         <is>
-          <t>CLOISONNE ROUGE FLAMBE 440X</t>
+          <t>ENVASE VIDRIO ROSADO MARCADO 30ML</t>
         </is>
       </c>
       <c r="C1633" t="n">
-        <v>6266</v>
+        <v>46</v>
       </c>
       <c r="D1633" t="inlineStr"/>
       <c r="E1633" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1633" t="inlineStr">
@@ -41569,21 +41569,21 @@
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>ME0527</t>
+          <t>314202</t>
         </is>
       </c>
       <c r="B1634" t="inlineStr">
         <is>
-          <t>ENVASE VIDRIO ROSADO MARCADO 30ML</t>
+          <t>CLOISONNE ROUGE FLAMBE 440X</t>
         </is>
       </c>
       <c r="C1634" t="n">
-        <v>46</v>
+        <v>6266</v>
       </c>
       <c r="D1634" t="inlineStr"/>
       <c r="E1634" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1634" t="inlineStr">
@@ -51551,21 +51551,21 @@
     <row r="2011">
       <c r="A2011" t="inlineStr">
         <is>
-          <t>173501</t>
+          <t>ME1043</t>
         </is>
       </c>
       <c r="B2011" t="inlineStr">
         <is>
-          <t>ULTRAMAR U-200 AZUL</t>
+          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
         </is>
       </c>
       <c r="C2011" t="n">
-        <v>309</v>
+        <v>3588</v>
       </c>
       <c r="D2011" t="inlineStr"/>
       <c r="E2011" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F2011" t="inlineStr">
@@ -51577,21 +51577,21 @@
     <row r="2012">
       <c r="A2012" t="inlineStr">
         <is>
-          <t>ME1043</t>
+          <t>173501</t>
         </is>
       </c>
       <c r="B2012" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
+          <t>ULTRAMAR U-200 AZUL</t>
         </is>
       </c>
       <c r="C2012" t="n">
-        <v>3588</v>
+        <v>309</v>
       </c>
       <c r="D2012" t="inlineStr"/>
       <c r="E2012" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F2012" t="inlineStr">

--- a/inventario_operaciones.xlsx
+++ b/inventario_operaciones.xlsx
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1138</v>
+        <v>1118</v>
       </c>
       <c r="D19" t="n">
         <v>1647.137404580153</v>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1168</v>
+        <v>1112</v>
       </c>
       <c r="D25" t="n">
         <v>33819.04580152671</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="D30" t="n">
         <v>1492.557251908397</v>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="D32" t="n">
         <v>23981.2213740458</v>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D81" t="n">
         <v>8.931297709923664</v>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-1304</v>
+        <v>541</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D93" t="n">
         <v>93.09160305343511</v>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1217</v>
+        <v>1199</v>
       </c>
       <c r="D96" t="n">
         <v>11863.1679389313</v>
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D101" t="n">
         <v>20.72519083969465</v>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D103" t="n">
         <v>95.95419847328245</v>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D105" t="n">
         <v>15285.91603053435</v>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="D106" t="n">
         <v>5497.900763358779</v>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="D111" t="n">
         <v>1155.229007633588</v>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D117" t="n">
         <v>87.25190839694656</v>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D124" t="n">
         <v>383.3587786259542</v>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D137" t="n">
         <v>7602.595419847328</v>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D139" t="n">
         <v>1701.068702290076</v>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D149" t="n">
         <v>116.9083969465649</v>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>3698</v>
+        <v>3691</v>
       </c>
       <c r="D184" t="n">
         <v>81409.46564885495</v>
@@ -5622,7 +5622,7 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="D189" t="n">
         <v>32942.74809160305</v>
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>2127</v>
+        <v>2120</v>
       </c>
       <c r="D191" t="n">
         <v>39274.69465648855</v>
@@ -8821,21 +8821,21 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>340302</t>
+          <t>ME0546</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>340302</t>
+          <t>TUBO COLAP FOTOPROTECTOR 60ML V1</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>44000</v>
+        <v>4514</v>
       </c>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -8847,21 +8847,21 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ME0546</t>
+          <t>340302</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>TUBO COLAP FOTOPROTECTOR 60ML V1</t>
+          <t>340302</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>4514</v>
+        <v>44000</v>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -13297,16 +13297,16 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>ETC0117</t>
+          <t>ETC0118</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>CAJA ILUMINADOR DAILY SHINE</t>
+          <t>CAJA ILUMINADOR LIGHTS UP</t>
         </is>
       </c>
       <c r="C475" t="n">
-        <v>14307</v>
+        <v>18741</v>
       </c>
       <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
@@ -13323,16 +13323,16 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>ETC0118</t>
+          <t>ETC0117</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>CAJA ILUMINADOR LIGHTS UP</t>
+          <t>CAJA ILUMINADOR DAILY SHINE</t>
         </is>
       </c>
       <c r="C476" t="n">
-        <v>18741</v>
+        <v>14307</v>
       </c>
       <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
@@ -13375,16 +13375,16 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>ETC0106</t>
+          <t>ETC0105</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>CAJA CORRECTOR CARAMELO</t>
+          <t>CAJA CORRECTOR AVELLANA</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>24356</v>
+        <v>28376</v>
       </c>
       <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
@@ -13401,16 +13401,16 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>ETC0105</t>
+          <t>ETC0106</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>CAJA CORRECTOR AVELLANA</t>
+          <t>CAJA CORRECTOR CARAMELO</t>
         </is>
       </c>
       <c r="C479" t="n">
-        <v>28376</v>
+        <v>24356</v>
       </c>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
@@ -13505,16 +13505,16 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>ME0514</t>
+          <t>MR0509</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>ENVASE BLA ESPUMA AUTOBRONCEASORA 150ML</t>
+          <t>BOTELLAS ESPUMA TRANS CON BOMBA 150ML</t>
         </is>
       </c>
       <c r="C483" t="n">
-        <v>62528</v>
+        <v>17440</v>
       </c>
       <c r="D483" t="inlineStr"/>
       <c r="E483" t="inlineStr">
@@ -13531,16 +13531,16 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>MR0509</t>
+          <t>ME0514</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>BOTELLAS ESPUMA TRANS CON BOMBA 150ML</t>
+          <t>ENVASE BLA ESPUMA AUTOBRONCEASORA 150ML</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>17440</v>
+        <v>62528</v>
       </c>
       <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr">
@@ -13739,16 +13739,16 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>ME0571</t>
+          <t>ME0505</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>TUBO COLAPSIBLE 50X175X5 MATE SIN IMPR</t>
+          <t>BALA TRANSPARENTE 120ML</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>509</v>
+        <v>4320</v>
       </c>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr">
@@ -13765,16 +13765,16 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>ME0505</t>
+          <t>ME0571</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 120ML</t>
+          <t>TUBO COLAPSIBLE 50X175X5 MATE SIN IMPR</t>
         </is>
       </c>
       <c r="C493" t="n">
-        <v>4320</v>
+        <v>509</v>
       </c>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr">
@@ -13843,16 +13843,16 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>ME1009</t>
+          <t>ME0532</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>GOTERO ROSADO PARA ENVASE MARCA ROSCA 19</t>
+          <t>ENVASE VIDRIO VERDE MARCADO 30ML</t>
         </is>
       </c>
       <c r="C496" t="n">
-        <v>245322</v>
+        <v>56700</v>
       </c>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr">
@@ -13869,16 +13869,16 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>ME0529</t>
+          <t>ME1009</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>ENVASE VIDRIO ROSADO TONICO ROSAS 120ML</t>
+          <t>GOTERO ROSADO PARA ENVASE MARCA ROSCA 19</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>3696</v>
+        <v>245322</v>
       </c>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
@@ -13895,16 +13895,16 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>ME0532</t>
+          <t>ME0529</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>ENVASE VIDRIO VERDE MARCADO 30ML</t>
+          <t>ENVASE VIDRIO ROSADO TONICO ROSAS 120ML</t>
         </is>
       </c>
       <c r="C498" t="n">
-        <v>56700</v>
+        <v>3696</v>
       </c>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr">
@@ -13947,16 +13947,16 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>ME0507</t>
+          <t>ME1028</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 30ML</t>
+          <t>TAPA CON APLICADOR PUNTA PINCEL</t>
         </is>
       </c>
       <c r="C500" t="n">
-        <v>34020</v>
+        <v>109430</v>
       </c>
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
@@ -13973,16 +13973,16 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>ME1028</t>
+          <t>ME0507</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>TAPA CON APLICADOR PUNTA PINCEL</t>
+          <t>BALA TRANSPARENTE 30ML</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>109430</v>
+        <v>34020</v>
       </c>
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
@@ -14051,16 +14051,16 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>ME1040</t>
+          <t>ME1501</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP 28 MM ROSADO FLAMENCO</t>
+          <t>TAPON DE VIDRIO ROSCA 28</t>
         </is>
       </c>
       <c r="C504" t="n">
-        <v>303250</v>
+        <v>828000</v>
       </c>
       <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr">
@@ -14077,16 +14077,16 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>ME1501</t>
+          <t>ME1040</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>TAPON DE VIDRIO ROSCA 28</t>
+          <t>TAPA FLIP TOP 28 MM ROSADO FLAMENCO</t>
         </is>
       </c>
       <c r="C505" t="n">
-        <v>828000</v>
+        <v>303250</v>
       </c>
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
@@ -14233,21 +14233,21 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>ETC0136</t>
+          <t>ME0518</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>CAJA TONICO CAPILAR KABA ROSADA 30ML</t>
+          <t>ENVASE CON TAPA FUCSIA KABA MAKEUP 10ML</t>
         </is>
       </c>
       <c r="C511" t="n">
-        <v>77733</v>
+        <v>32340</v>
       </c>
       <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
@@ -14259,21 +14259,21 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>ME0518</t>
+          <t>ETC0136</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>ENVASE CON TAPA FUCSIA KABA MAKEUP 10ML</t>
+          <t>CAJA TONICO CAPILAR KABA ROSADA 30ML</t>
         </is>
       </c>
       <c r="C512" t="n">
-        <v>32340</v>
+        <v>77733</v>
       </c>
       <c r="D512" t="inlineStr"/>
       <c r="E512" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
@@ -14649,16 +14649,16 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>ME0575</t>
+          <t>ME1071</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>ENVASE PET SPRAY AMARILLO 200ML</t>
+          <t>TAPA AIRLESS NEGRO CON ARO PLATA</t>
         </is>
       </c>
       <c r="C527" t="n">
-        <v>9878</v>
+        <v>34496</v>
       </c>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr">
@@ -14675,16 +14675,16 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>ME1071</t>
+          <t>ME0502</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>TAPA AIRLESS NEGRO CON ARO PLATA</t>
+          <t>AIRLESS NEGRO CON ARO PLATA 30ML</t>
         </is>
       </c>
       <c r="C528" t="n">
-        <v>34496</v>
+        <v>34320</v>
       </c>
       <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr">
@@ -14701,16 +14701,16 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>ME0502</t>
+          <t>ME0575</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>AIRLESS NEGRO CON ARO PLATA 30ML</t>
+          <t>ENVASE PET SPRAY AMARILLO 200ML</t>
         </is>
       </c>
       <c r="C529" t="n">
-        <v>34320</v>
+        <v>9878</v>
       </c>
       <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr">
@@ -15065,23 +15065,19 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>ETC0164</t>
+          <t>VB0307-04-04-U-13</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>CAJA PR BOX MEXICO</t>
+          <t>TOALLA DLUCHI GRANDE-U-NARANJA</t>
         </is>
       </c>
       <c r="C543" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D543" t="inlineStr"/>
-      <c r="E543" t="inlineStr">
-        <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
-        </is>
-      </c>
+      <c r="E543" t="inlineStr"/>
       <c r="F543" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -15091,23 +15087,19 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>TA0101</t>
+          <t>VB0307-05-04-U-01</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>TARJETA IMPERIO LUISA CHIMA</t>
+          <t>TOALLA KABA PEQUEÑA-U-BLANCO</t>
         </is>
       </c>
       <c r="C544" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="D544" t="inlineStr"/>
-      <c r="E544" t="inlineStr">
-        <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
-        </is>
-      </c>
+      <c r="E544" t="inlineStr"/>
       <c r="F544" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -15117,16 +15109,16 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>TA0102</t>
+          <t>ETC0146</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>TARJETA DREAM BAG</t>
+          <t>CAJA PR KABA MAKEUP</t>
         </is>
       </c>
       <c r="C545" t="n">
-        <v>1424</v>
+        <v>37</v>
       </c>
       <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr">
@@ -15143,16 +15135,16 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>TA0103</t>
+          <t>ETC0147</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>TARJETA DESCUENTO VB</t>
+          <t>CAJA PR PANAL DLUCHI</t>
         </is>
       </c>
       <c r="C546" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr">
@@ -15169,16 +15161,16 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>TA0104</t>
+          <t>ETC0148</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>TARJETA KABA MAKEUP</t>
+          <t>CAJA PR KABA SOS</t>
         </is>
       </c>
       <c r="C547" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D547" t="inlineStr"/>
       <c r="E547" t="inlineStr">
@@ -15195,16 +15187,16 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>ETC0140</t>
+          <t>ETC0164</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>CAJAS SACHET KABA</t>
+          <t>CAJA PR BOX MEXICO</t>
         </is>
       </c>
       <c r="C548" t="n">
-        <v>420</v>
+        <v>42</v>
       </c>
       <c r="D548" t="inlineStr"/>
       <c r="E548" t="inlineStr">
@@ -15221,16 +15213,16 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>ETC0139</t>
+          <t>ETC0140</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>CAJAS SACHET DLUCHI</t>
+          <t>CAJAS SACHET KABA</t>
         </is>
       </c>
       <c r="C549" t="n">
-        <v>13</v>
+        <v>420</v>
       </c>
       <c r="D549" t="inlineStr"/>
       <c r="E549" t="inlineStr">
@@ -15247,16 +15239,16 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>ETC0141</t>
+          <t>ETC0139</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>CAJAS SACHET RECETA</t>
+          <t>CAJAS SACHET DLUCHI</t>
         </is>
       </c>
       <c r="C550" t="n">
-        <v>1226</v>
+        <v>13</v>
       </c>
       <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr">
@@ -15273,19 +15265,23 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>VB0307-04-04-U-13</t>
+          <t>ETC0141</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>TOALLA DLUCHI GRANDE-U-NARANJA</t>
+          <t>CAJAS SACHET RECETA</t>
         </is>
       </c>
       <c r="C551" t="n">
-        <v>47</v>
+        <v>1226</v>
       </c>
       <c r="D551" t="inlineStr"/>
-      <c r="E551" t="inlineStr"/>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+        </is>
+      </c>
       <c r="F551" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -15295,19 +15291,23 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>VB0307-05-04-U-01</t>
+          <t>TA0101</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>TOALLA KABA PEQUEÑA-U-BLANCO</t>
+          <t>TARJETA IMPERIO LUISA CHIMA</t>
         </is>
       </c>
       <c r="C552" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="D552" t="inlineStr"/>
-      <c r="E552" t="inlineStr"/>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+        </is>
+      </c>
       <c r="F552" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -15317,16 +15317,16 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>ETC0146</t>
+          <t>TA0102</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>CAJA PR KABA MAKEUP</t>
+          <t>TARJETA DREAM BAG</t>
         </is>
       </c>
       <c r="C553" t="n">
-        <v>37</v>
+        <v>1424</v>
       </c>
       <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
@@ -15343,16 +15343,16 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>ETC0147</t>
+          <t>TA0103</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>CAJA PR PANAL DLUCHI</t>
+          <t>TARJETA DESCUENTO VB</t>
         </is>
       </c>
       <c r="C554" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
@@ -15369,16 +15369,16 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>ETC0148</t>
+          <t>TA0104</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>CAJA PR KABA SOS</t>
+          <t>TARJETA KABA MAKEUP</t>
         </is>
       </c>
       <c r="C555" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D555" t="inlineStr"/>
       <c r="E555" t="inlineStr">
@@ -15629,21 +15629,21 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>C051601</t>
+          <t>ME0540</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>ESTUCHE LIP GLOSS VIVIANA GRONDONA</t>
+          <t>POTE NEGRO TAPA PLATA UNGÜENTO 60ML</t>
         </is>
       </c>
       <c r="C565" t="n">
-        <v>6878</v>
+        <v>4844</v>
       </c>
       <c r="D565" t="inlineStr"/>
       <c r="E565" t="inlineStr">
         <is>
-          <t>COMPRA GRAVADA SIN LOTES</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
@@ -15655,21 +15655,21 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>C051501</t>
+          <t>ME0539</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>COSMETIQUERA VIVIANA GRONDONA</t>
+          <t>POTE NEGRO TAPA PLATA UNGÜENTO 200ML</t>
         </is>
       </c>
       <c r="C566" t="n">
-        <v>11573</v>
+        <v>2259</v>
       </c>
       <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr">
         <is>
-          <t>COMPRA GRAVADA SIN LOTES</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
@@ -15681,21 +15681,21 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>ME0540</t>
+          <t>C051501</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>POTE NEGRO TAPA PLATA UNGÜENTO 60ML</t>
+          <t>COSMETIQUERA VIVIANA GRONDONA</t>
         </is>
       </c>
       <c r="C567" t="n">
-        <v>4844</v>
+        <v>11573</v>
       </c>
       <c r="D567" t="inlineStr"/>
       <c r="E567" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>COMPRA GRAVADA SIN LOTES</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
@@ -15707,21 +15707,21 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>ME0539</t>
+          <t>C051601</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>POTE NEGRO TAPA PLATA UNGÜENTO 200ML</t>
+          <t>ESTUCHE LIP GLOSS VIVIANA GRONDONA</t>
         </is>
       </c>
       <c r="C568" t="n">
-        <v>2259</v>
+        <v>6878</v>
       </c>
       <c r="D568" t="inlineStr"/>
       <c r="E568" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>COMPRA GRAVADA SIN LOTES</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
@@ -16225,16 +16225,16 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>ME0567</t>
+          <t>ME1034</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>BALA NEGRA LARGA 120 ML</t>
+          <t>TAPA DISC TOP BLANCA ROSCA 28</t>
         </is>
       </c>
       <c r="C589" t="n">
-        <v>127</v>
+        <v>282</v>
       </c>
       <c r="D589" t="inlineStr"/>
       <c r="E589" t="inlineStr">
@@ -16251,16 +16251,16 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>ME0568</t>
+          <t>ME0567</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>BALA NEGRA 260 ML</t>
+          <t>BALA NEGRA LARGA 120 ML</t>
         </is>
       </c>
       <c r="C590" t="n">
-        <v>1016</v>
+        <v>127</v>
       </c>
       <c r="D590" t="inlineStr"/>
       <c r="E590" t="inlineStr">
@@ -16277,16 +16277,16 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>ME1034</t>
+          <t>ME0568</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>TAPA DISC TOP BLANCA ROSCA 28</t>
+          <t>BALA NEGRA 260 ML</t>
         </is>
       </c>
       <c r="C591" t="n">
-        <v>282</v>
+        <v>1016</v>
       </c>
       <c r="D591" t="inlineStr"/>
       <c r="E591" t="inlineStr">
@@ -16533,12 +16533,12 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>VB0104-01-03-L-02</t>
+          <t>VB0104-01-01-S-02</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-NEGRO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-NEGRO</t>
         </is>
       </c>
       <c r="C601" t="n">
@@ -16555,12 +16555,12 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>VB0104-01-01-S-02</t>
+          <t>VB0104-01-03-L-02</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-NEGRO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-NEGRO</t>
         </is>
       </c>
       <c r="C602" t="n">
@@ -16599,12 +16599,12 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-11</t>
+          <t>VB020103-03-03-L-20</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C604" t="n">
@@ -16621,16 +16621,16 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-06</t>
+          <t>VB020105-01-03-L-11</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AZUL CELESTE</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C605" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D605" t="inlineStr"/>
       <c r="E605" t="inlineStr"/>
@@ -16643,16 +16643,16 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>VB020103-03-03-L-20</t>
+          <t>VB020101-01-01-S-06</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C606" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr"/>
@@ -16687,16 +16687,16 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-13</t>
+          <t>VB020105-01-02-M-13</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
         </is>
       </c>
       <c r="C608" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr"/>
@@ -16709,23 +16709,19 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>DISACK010101</t>
+          <t>VB020105-01-03-L-13</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>DISPLEY SACHET DE SHAMPO DE CEBOLLA KABA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
         </is>
       </c>
       <c r="C609" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D609" t="inlineStr"/>
-      <c r="E609" t="inlineStr">
-        <is>
-          <t>PRODUCTO MANUFACTURADO</t>
-        </is>
-      </c>
+      <c r="E609" t="inlineStr"/>
       <c r="F609" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -16735,19 +16731,23 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-13</t>
+          <t>DISACK010101</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
+          <t>DISPLEY SACHET DE SHAMPO DE CEBOLLA KABA</t>
         </is>
       </c>
       <c r="C610" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D610" t="inlineStr"/>
-      <c r="E610" t="inlineStr"/>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>PRODUCTO MANUFACTURADO</t>
+        </is>
+      </c>
       <c r="F610" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -16757,12 +16757,12 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-24</t>
+          <t>VB020103-01-02-M-26</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -16779,16 +16779,16 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>VB020103-01-02-M-26</t>
+          <t>VB020303-01-03-L-25</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C612" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr"/>
@@ -16801,16 +16801,16 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-08</t>
+          <t>VB020303-01-03-L-24</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C613" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
@@ -16823,16 +16823,16 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-25</t>
+          <t>VB020105-01-01-S-08</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
         </is>
       </c>
       <c r="C614" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
@@ -16845,12 +16845,12 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-14</t>
+          <t>VB020105-01-01-S-13</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-NARANJA</t>
         </is>
       </c>
       <c r="C615" t="n">
@@ -16867,12 +16867,12 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>VB020103-03-02-M-20</t>
+          <t>VB020101-01-01-S-14</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C616" t="n">
@@ -16889,16 +16889,16 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-24</t>
+          <t>VB020103-03-02-M-20</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C617" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr"/>
@@ -16911,16 +16911,16 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-13</t>
+          <t>VB020303-01-02-M-25</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-NARANJA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C618" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D618" t="inlineStr"/>
       <c r="E618" t="inlineStr"/>
@@ -16933,16 +16933,16 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-25</t>
+          <t>VB020101-01-02-M-06</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C619" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D619" t="inlineStr"/>
       <c r="E619" t="inlineStr"/>
@@ -16955,16 +16955,16 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-06</t>
+          <t>VB020101-01-01-S-25</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AZUL CELESTE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C620" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D620" t="inlineStr"/>
       <c r="E620" t="inlineStr"/>
@@ -16977,12 +16977,12 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-06</t>
+          <t>VB020101-01-03-L-25</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AZUL CELESTE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C621" t="n">
@@ -16999,16 +16999,16 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-11</t>
+          <t>VB020303-01-01-S-25</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C622" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D622" t="inlineStr"/>
       <c r="E622" t="inlineStr"/>
@@ -17021,16 +17021,16 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-05</t>
+          <t>VB020101-01-02-M-25</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C623" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D623" t="inlineStr"/>
       <c r="E623" t="inlineStr"/>
@@ -17043,16 +17043,16 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-05</t>
+          <t>VB020303-01-02-M-24</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C624" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D624" t="inlineStr"/>
       <c r="E624" t="inlineStr"/>
@@ -17065,16 +17065,16 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-25</t>
+          <t>VB020105-01-02-M-11</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C625" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D625" t="inlineStr"/>
       <c r="E625" t="inlineStr"/>
@@ -17087,16 +17087,16 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-25</t>
+          <t>VB020101-01-03-L-06</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C626" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D626" t="inlineStr"/>
       <c r="E626" t="inlineStr"/>
@@ -17109,12 +17109,12 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-25</t>
+          <t>VB020105-01-02-M-05</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C627" t="n">
@@ -17131,16 +17131,16 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-25</t>
+          <t>VB020105-01-01-S-05</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C628" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D628" t="inlineStr"/>
       <c r="E628" t="inlineStr"/>
@@ -20555,19 +20555,23 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-14</t>
+          <t>KITN0103</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-PALO DE ROSA</t>
+          <t>KIT FULL CARE</t>
         </is>
       </c>
       <c r="C783" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D783" t="inlineStr"/>
-      <c r="E783" t="inlineStr"/>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>PRODUCTO MANUFACTURADO</t>
+        </is>
+      </c>
       <c r="F783" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -20577,12 +20581,12 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-16</t>
+          <t>VB0306-01-03-L-16</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-ROJO</t>
+          <t>TOP BÁSICO LUISA-L-ROJO</t>
         </is>
       </c>
       <c r="C784" t="n">
@@ -20599,12 +20603,12 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-14</t>
+          <t>VB0306-01-02-M-16</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-PALO DE ROSA</t>
+          <t>TOP BÁSICO LUISA-M-ROJO</t>
         </is>
       </c>
       <c r="C785" t="n">
@@ -20621,12 +20625,12 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-14</t>
+          <t>VB0306-01-03-L-14</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
+          <t>TOP BÁSICO LUISA-L-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C786" t="n">
@@ -20643,12 +20647,12 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-16</t>
+          <t>VB0306-01-01-S-16</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-ROJO</t>
+          <t>TOP BÁSICO LUISA-S-ROJO</t>
         </is>
       </c>
       <c r="C787" t="n">
@@ -20665,23 +20669,19 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>KITN0103</t>
+          <t>VB0306-01-01-S-14</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>KIT FULL CARE</t>
+          <t>TOP BÁSICO LUISA-S-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C788" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D788" t="inlineStr"/>
-      <c r="E788" t="inlineStr">
-        <is>
-          <t>PRODUCTO MANUFACTURADO</t>
-        </is>
-      </c>
+      <c r="E788" t="inlineStr"/>
       <c r="F788" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -20691,12 +20691,12 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-16</t>
+          <t>VB0306-01-02-M-14</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-ROJO</t>
+          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -20999,16 +20999,16 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-16</t>
+          <t>VB020101-01-01-S-16</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-ROJO</t>
         </is>
       </c>
       <c r="C803" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D803" t="inlineStr"/>
       <c r="E803" t="inlineStr"/>
@@ -21021,16 +21021,16 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-16</t>
+          <t>VB020101-01-03-L-17</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-ROSADO</t>
         </is>
       </c>
       <c r="C804" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D804" t="inlineStr"/>
       <c r="E804" t="inlineStr"/>
@@ -21043,16 +21043,16 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-17</t>
+          <t>VB020101-01-02-M-17</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ROSADO</t>
         </is>
       </c>
       <c r="C805" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D805" t="inlineStr"/>
       <c r="E805" t="inlineStr"/>
@@ -21065,16 +21065,16 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-17</t>
+          <t>VB020104-01-01-S-02</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-NEGRO</t>
         </is>
       </c>
       <c r="C806" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D806" t="inlineStr"/>
       <c r="E806" t="inlineStr"/>
@@ -21087,16 +21087,16 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-02</t>
+          <t>VB020101-01-02-M-16</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ROJO</t>
         </is>
       </c>
       <c r="C807" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D807" t="inlineStr"/>
       <c r="E807" t="inlineStr"/>
@@ -21703,16 +21703,16 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>VB0105-01-03-L-31</t>
+          <t>VB0105-01-02-M-31</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-L-SAFARI</t>
+          <t>VB ENTERO TANGA-M-SAFARI</t>
         </is>
       </c>
       <c r="C835" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D835" t="inlineStr"/>
       <c r="E835" t="inlineStr"/>
@@ -21725,16 +21725,16 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>VB020402-01-03-L-31</t>
+          <t>VB0105-01-03-L-31</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS BUSO TALLE ALTO-L-SAFARI</t>
+          <t>VB ENTERO TANGA-L-SAFARI</t>
         </is>
       </c>
       <c r="C836" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D836" t="inlineStr"/>
       <c r="E836" t="inlineStr"/>
@@ -21747,12 +21747,12 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-08</t>
+          <t>VB020402-01-03-L-31</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AZUL REY</t>
+          <t>VB DOS PIEZAS BUSO TALLE ALTO-L-SAFARI</t>
         </is>
       </c>
       <c r="C837" t="n">
@@ -21769,16 +21769,16 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-08</t>
+          <t>VB020101-01-02-M-08</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AZUL REY</t>
         </is>
       </c>
       <c r="C838" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D838" t="inlineStr"/>
       <c r="E838" t="inlineStr"/>
@@ -21791,16 +21791,16 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>VB0105-01-02-M-31</t>
+          <t>VB020101-01-03-L-08</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-M-SAFARI</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AZUL REY</t>
         </is>
       </c>
       <c r="C839" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D839" t="inlineStr"/>
       <c r="E839" t="inlineStr"/>
@@ -21813,16 +21813,16 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-05</t>
+          <t>VB020101-01-03-L-05</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C840" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D840" t="inlineStr"/>
       <c r="E840" t="inlineStr"/>
@@ -21835,16 +21835,16 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-05</t>
+          <t>VB020101-01-02-M-05</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C841" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D841" t="inlineStr"/>
       <c r="E841" t="inlineStr"/>
@@ -23291,16 +23291,16 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>VB020103-03-03-L-20</t>
+          <t>VB020105-01-03-L-11</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C896" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D896" t="inlineStr"/>
       <c r="E896" t="inlineStr"/>
@@ -23313,16 +23313,16 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-11</t>
+          <t>VB020103-03-03-L-20</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C897" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D897" t="inlineStr"/>
       <c r="E897" t="inlineStr"/>
@@ -23401,16 +23401,16 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-24</t>
+          <t>VB020303-01-02-M-25</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C901" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="D901" t="inlineStr"/>
       <c r="E901" t="inlineStr"/>
@@ -23423,16 +23423,16 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-25</t>
+          <t>VB020105-01-01-S-05</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C902" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D902" t="inlineStr"/>
       <c r="E902" t="inlineStr"/>
@@ -23445,16 +23445,16 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-13</t>
+          <t>VB020105-01-02-M-05</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C903" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D903" t="inlineStr"/>
       <c r="E903" t="inlineStr"/>
@@ -23467,16 +23467,16 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-25</t>
+          <t>VB020103-03-03-L-32</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C904" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="D904" t="inlineStr"/>
       <c r="E904" t="inlineStr"/>
@@ -23489,16 +23489,16 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-05</t>
+          <t>VB020101-01-02-M-19</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C905" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D905" t="inlineStr"/>
       <c r="E905" t="inlineStr"/>
@@ -23511,16 +23511,16 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-05</t>
+          <t>VB020105-01-01-S-15</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-PURPURA</t>
         </is>
       </c>
       <c r="C906" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D906" t="inlineStr"/>
       <c r="E906" t="inlineStr"/>
@@ -23533,16 +23533,16 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>VB020103-03-03-L-32</t>
+          <t>VB020105-01-02-M-11</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C907" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="D907" t="inlineStr"/>
       <c r="E907" t="inlineStr"/>
@@ -23555,16 +23555,16 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-11</t>
+          <t>VB020105-01-03-L-07</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C908" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D908" t="inlineStr"/>
       <c r="E908" t="inlineStr"/>
@@ -23577,16 +23577,16 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-07</t>
+          <t>VB020303-01-02-M-24</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C909" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="D909" t="inlineStr"/>
       <c r="E909" t="inlineStr"/>
@@ -23599,16 +23599,16 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-19</t>
+          <t>VB020303-01-01-S-25</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C910" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D910" t="inlineStr"/>
       <c r="E910" t="inlineStr"/>
@@ -23621,16 +23621,16 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-15</t>
+          <t>VB020105-01-03-L-08</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AZUL REY</t>
         </is>
       </c>
       <c r="C911" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D911" t="inlineStr"/>
       <c r="E911" t="inlineStr"/>
@@ -23643,16 +23643,16 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-08</t>
+          <t>VB020103-03-02-M-20</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C912" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="D912" t="inlineStr"/>
       <c r="E912" t="inlineStr"/>
@@ -23665,16 +23665,16 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>VB020103-03-02-M-20</t>
+          <t>VB020105-01-01-S-13</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-NARANJA</t>
         </is>
       </c>
       <c r="C913" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D913" t="inlineStr"/>
       <c r="E913" t="inlineStr"/>
@@ -23687,16 +23687,16 @@
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-25</t>
+          <t>VB020105-01-01-S-08</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
         </is>
       </c>
       <c r="C914" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D914" t="inlineStr"/>
       <c r="E914" t="inlineStr"/>
@@ -23709,16 +23709,16 @@
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>VB020103-03-02-M-32</t>
+          <t>VB020303-01-03-L-24</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C915" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D915" t="inlineStr"/>
       <c r="E915" t="inlineStr"/>
@@ -23731,16 +23731,16 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-08</t>
+          <t>VB020103-03-02-M-32</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C916" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="D916" t="inlineStr"/>
       <c r="E916" t="inlineStr"/>
@@ -23753,16 +23753,16 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>VB020103-01-02-M-26</t>
+          <t>VB020303-01-03-L-25</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C917" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D917" t="inlineStr"/>
       <c r="E917" t="inlineStr"/>
@@ -23775,16 +23775,16 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-24</t>
+          <t>VB020103-01-02-M-26</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
         </is>
       </c>
       <c r="C918" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D918" t="inlineStr"/>
       <c r="E918" t="inlineStr"/>
@@ -23797,16 +23797,16 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-13</t>
+          <t>VB020105-01-03-L-13</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
         </is>
       </c>
       <c r="C919" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D919" t="inlineStr"/>
       <c r="E919" t="inlineStr"/>
@@ -23819,16 +23819,16 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-13</t>
+          <t>VB020105-01-02-M-13</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
         </is>
       </c>
       <c r="C920" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D920" t="inlineStr"/>
       <c r="E920" t="inlineStr"/>
@@ -27273,16 +27273,16 @@
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-14</t>
+          <t>VB0306-01-02-M-16</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
+          <t>TOP BÁSICO LUISA-M-ROJO</t>
         </is>
       </c>
       <c r="C1077" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D1077" t="inlineStr"/>
       <c r="E1077" t="inlineStr"/>
@@ -27295,16 +27295,16 @@
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-14</t>
+          <t>VB0306-01-03-L-16</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-PALO DE ROSA</t>
+          <t>TOP BÁSICO LUISA-L-ROJO</t>
         </is>
       </c>
       <c r="C1078" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D1078" t="inlineStr"/>
       <c r="E1078" t="inlineStr"/>
@@ -27317,16 +27317,16 @@
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-16</t>
+          <t>VB0306-01-02-M-14</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-ROJO</t>
+          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C1079" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D1079" t="inlineStr"/>
       <c r="E1079" t="inlineStr"/>
@@ -27339,16 +27339,16 @@
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-14</t>
+          <t>VB0306-01-01-S-14</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-PALO DE ROSA</t>
+          <t>TOP BÁSICO LUISA-S-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C1080" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D1080" t="inlineStr"/>
       <c r="E1080" t="inlineStr"/>
@@ -27361,16 +27361,16 @@
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-16</t>
+          <t>VB0306-01-01-S-16</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-ROJO</t>
+          <t>TOP BÁSICO LUISA-S-ROJO</t>
         </is>
       </c>
       <c r="C1081" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D1081" t="inlineStr"/>
       <c r="E1081" t="inlineStr"/>
@@ -27383,16 +27383,16 @@
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-16</t>
+          <t>VB0306-01-03-L-14</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-ROJO</t>
+          <t>TOP BÁSICO LUISA-L-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C1082" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D1082" t="inlineStr"/>
       <c r="E1082" t="inlineStr"/>
@@ -27405,16 +27405,16 @@
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-05</t>
+          <t>VB020202-01-03-L-04</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AMARILLO</t>
         </is>
       </c>
       <c r="C1083" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D1083" t="inlineStr"/>
       <c r="E1083" t="inlineStr"/>
@@ -27427,16 +27427,16 @@
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-27</t>
+          <t>VB020205-02-01-S-12</t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PITON AZUL</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-MORADO</t>
         </is>
       </c>
       <c r="C1084" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D1084" t="inlineStr"/>
       <c r="E1084" t="inlineStr"/>
@@ -27449,16 +27449,16 @@
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-29</t>
+          <t>VB020205-02-01-S-10</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PITON ROSADO</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-FUCSIA</t>
         </is>
       </c>
       <c r="C1085" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D1085" t="inlineStr"/>
       <c r="E1085" t="inlineStr"/>
@@ -27471,16 +27471,16 @@
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-29</t>
+          <t>VB020205-02-01-S-22</t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PITON ROSADO</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-FLORES</t>
         </is>
       </c>
       <c r="C1086" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="D1086" t="inlineStr"/>
       <c r="E1086" t="inlineStr"/>
@@ -27493,16 +27493,16 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-29</t>
+          <t>VB020205-02-01-S-07</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PITON ROSADO</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1087" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D1087" t="inlineStr"/>
       <c r="E1087" t="inlineStr"/>
@@ -27515,16 +27515,16 @@
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-05</t>
+          <t>VB020205-02-01-S-04</t>
         </is>
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-AMARILLO</t>
         </is>
       </c>
       <c r="C1088" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D1088" t="inlineStr"/>
       <c r="E1088" t="inlineStr"/>
@@ -27537,16 +27537,16 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>VB0105-01-02-M-31</t>
+          <t>VB020205-02-02-M-22</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-M-SAFARI</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-FLORES</t>
         </is>
       </c>
       <c r="C1089" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D1089" t="inlineStr"/>
       <c r="E1089" t="inlineStr"/>
@@ -27559,16 +27559,16 @@
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-05</t>
+          <t>VB020205-02-02-M-07</t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1090" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D1090" t="inlineStr"/>
       <c r="E1090" t="inlineStr"/>
@@ -27581,16 +27581,16 @@
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>VB0105-01-03-L-31</t>
+          <t>VB020205-02-02-M-04</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-L-SAFARI</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-AMARILLO</t>
         </is>
       </c>
       <c r="C1091" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D1091" t="inlineStr"/>
       <c r="E1091" t="inlineStr"/>
@@ -27603,16 +27603,16 @@
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>VB020402-01-01-S-31</t>
+          <t>VB020205-02-03-L-12</t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS BUSO TALLE ALTO-S-SAFARI</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-MORADO</t>
         </is>
       </c>
       <c r="C1092" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D1092" t="inlineStr"/>
       <c r="E1092" t="inlineStr"/>
@@ -27625,16 +27625,16 @@
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>VB020402-01-02-M-31</t>
+          <t>VB020205-02-03-L-10</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS BUSO TALLE ALTO-M-SAFARI</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-FUCSIA</t>
         </is>
       </c>
       <c r="C1093" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D1093" t="inlineStr"/>
       <c r="E1093" t="inlineStr"/>
@@ -27647,16 +27647,16 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>VB0105-01-01-S-31</t>
+          <t>VB020205-02-03-L-22</t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-S-SAFARI</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-FLORES</t>
         </is>
       </c>
       <c r="C1094" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D1094" t="inlineStr"/>
       <c r="E1094" t="inlineStr"/>
@@ -27669,16 +27669,16 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-19</t>
+          <t>VB020205-02-03-L-07</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1095" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D1095" t="inlineStr"/>
       <c r="E1095" t="inlineStr"/>
@@ -27691,16 +27691,16 @@
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-22</t>
+          <t>VB020205-02-03-L-04</t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-FLORES</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-AMARILLO</t>
         </is>
       </c>
       <c r="C1096" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D1096" t="inlineStr"/>
       <c r="E1096" t="inlineStr"/>
@@ -27713,16 +27713,16 @@
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-08</t>
+          <t>VB020205-03-03-L-21</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-ASTRAL</t>
         </is>
       </c>
       <c r="C1097" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D1097" t="inlineStr"/>
       <c r="E1097" t="inlineStr"/>
@@ -27735,16 +27735,16 @@
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-04</t>
+          <t>VB020205-03-02-M-21</t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AMARILLO</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-ASTRAL</t>
         </is>
       </c>
       <c r="C1098" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D1098" t="inlineStr"/>
       <c r="E1098" t="inlineStr"/>
@@ -27757,16 +27757,16 @@
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-19</t>
+          <t>VB020205-03-01-S-21</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-ASTRAL</t>
         </is>
       </c>
       <c r="C1099" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D1099" t="inlineStr"/>
       <c r="E1099" t="inlineStr"/>
@@ -27779,16 +27779,16 @@
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-22</t>
+          <t>VB0103-01-02-M-16</t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-FLORES</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-ROJO</t>
         </is>
       </c>
       <c r="C1100" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D1100" t="inlineStr"/>
       <c r="E1100" t="inlineStr"/>
@@ -27801,16 +27801,16 @@
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-08</t>
+          <t>VB020104-01-01-S-02</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-NEGRO</t>
         </is>
       </c>
       <c r="C1101" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D1101" t="inlineStr"/>
       <c r="E1101" t="inlineStr"/>
@@ -27823,16 +27823,16 @@
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-04</t>
+          <t>VB020104-01-02-M-02</t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AMARILLO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-M-NEGRO</t>
         </is>
       </c>
       <c r="C1102" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D1102" t="inlineStr"/>
       <c r="E1102" t="inlineStr"/>
@@ -27845,16 +27845,16 @@
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-19</t>
+          <t>VB020104-01-03-L-02</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-NEGRO</t>
         </is>
       </c>
       <c r="C1103" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D1103" t="inlineStr"/>
       <c r="E1103" t="inlineStr"/>
@@ -27867,16 +27867,16 @@
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-22</t>
+          <t>VB0103-01-01-S-16</t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-FLORES</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-ROJO</t>
         </is>
       </c>
       <c r="C1104" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D1104" t="inlineStr"/>
       <c r="E1104" t="inlineStr"/>
@@ -27889,16 +27889,16 @@
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-08</t>
+          <t>VB0103-01-03-L-16</t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL REY</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-ROJO</t>
         </is>
       </c>
       <c r="C1105" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D1105" t="inlineStr"/>
       <c r="E1105" t="inlineStr"/>
@@ -27911,16 +27911,16 @@
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-04</t>
+          <t>VB0103-01-01-S-02</t>
         </is>
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AMARILLO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-NEGRO</t>
         </is>
       </c>
       <c r="C1106" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D1106" t="inlineStr"/>
       <c r="E1106" t="inlineStr"/>
@@ -27933,16 +27933,16 @@
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-12</t>
+          <t>VB0103-01-01-S-01</t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-MORADO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-BLANCO</t>
         </is>
       </c>
       <c r="C1107" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D1107" t="inlineStr"/>
       <c r="E1107" t="inlineStr"/>
@@ -27955,16 +27955,16 @@
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-10</t>
+          <t>VB0103-01-03-L-01</t>
         </is>
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-FUCSIA</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-BLANCO</t>
         </is>
       </c>
       <c r="C1108" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D1108" t="inlineStr"/>
       <c r="E1108" t="inlineStr"/>
@@ -27977,16 +27977,16 @@
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-22</t>
+          <t>VB020101-01-02-M-05</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-FLORES</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C1109" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="D1109" t="inlineStr"/>
       <c r="E1109" t="inlineStr"/>
@@ -27999,16 +27999,16 @@
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-07</t>
+          <t>VB020101-01-03-L-05</t>
         </is>
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C1110" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D1110" t="inlineStr"/>
       <c r="E1110" t="inlineStr"/>
@@ -28021,16 +28021,16 @@
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-04</t>
+          <t>VB020101-01-03-L-27</t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-AMARILLO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PITON AZUL</t>
         </is>
       </c>
       <c r="C1111" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D1111" t="inlineStr"/>
       <c r="E1111" t="inlineStr"/>
@@ -28043,16 +28043,16 @@
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-22</t>
+          <t>VB020101-01-01-S-29</t>
         </is>
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-FLORES</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PITON ROSADO</t>
         </is>
       </c>
       <c r="C1112" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D1112" t="inlineStr"/>
       <c r="E1112" t="inlineStr"/>
@@ -28065,16 +28065,16 @@
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-07</t>
+          <t>VB020101-01-02-M-29</t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PITON ROSADO</t>
         </is>
       </c>
       <c r="C1113" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D1113" t="inlineStr"/>
       <c r="E1113" t="inlineStr"/>
@@ -28087,16 +28087,16 @@
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-04</t>
+          <t>VB020101-01-03-L-29</t>
         </is>
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-AMARILLO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PITON ROSADO</t>
         </is>
       </c>
       <c r="C1114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D1114" t="inlineStr"/>
       <c r="E1114" t="inlineStr"/>
@@ -28109,16 +28109,16 @@
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-12</t>
+          <t>VB020101-01-01-S-05</t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-MORADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C1115" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D1115" t="inlineStr"/>
       <c r="E1115" t="inlineStr"/>
@@ -28131,16 +28131,16 @@
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-10</t>
+          <t>VB0105-01-03-L-31</t>
         </is>
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-FUCSIA</t>
+          <t>VB ENTERO TANGA-L-SAFARI</t>
         </is>
       </c>
       <c r="C1116" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D1116" t="inlineStr"/>
       <c r="E1116" t="inlineStr"/>
@@ -28153,16 +28153,16 @@
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-22</t>
+          <t>VB020402-01-01-S-31</t>
         </is>
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-FLORES</t>
+          <t>VB DOS PIEZAS BUSO TALLE ALTO-S-SAFARI</t>
         </is>
       </c>
       <c r="C1117" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D1117" t="inlineStr"/>
       <c r="E1117" t="inlineStr"/>
@@ -28175,16 +28175,16 @@
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-07</t>
+          <t>VB020402-01-02-M-31</t>
         </is>
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS BUSO TALLE ALTO-M-SAFARI</t>
         </is>
       </c>
       <c r="C1118" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D1118" t="inlineStr"/>
       <c r="E1118" t="inlineStr"/>
@@ -28197,16 +28197,16 @@
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-04</t>
+          <t>VB0105-01-02-M-31</t>
         </is>
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-AMARILLO</t>
+          <t>VB ENTERO TANGA-M-SAFARI</t>
         </is>
       </c>
       <c r="C1119" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D1119" t="inlineStr"/>
       <c r="E1119" t="inlineStr"/>
@@ -28219,12 +28219,12 @@
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>VB020205-03-03-L-21</t>
+          <t>VB0105-01-01-S-31</t>
         </is>
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-ASTRAL</t>
+          <t>VB ENTERO TANGA-S-SAFARI</t>
         </is>
       </c>
       <c r="C1120" t="n">
@@ -28241,16 +28241,16 @@
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>VB020205-03-02-M-21</t>
+          <t>VB020202-01-01-S-19</t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-ASTRAL</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1121" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D1121" t="inlineStr"/>
       <c r="E1121" t="inlineStr"/>
@@ -28263,16 +28263,16 @@
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>VB020205-03-01-S-21</t>
+          <t>VB020202-01-01-S-22</t>
         </is>
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-ASTRAL</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-FLORES</t>
         </is>
       </c>
       <c r="C1122" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D1122" t="inlineStr"/>
       <c r="E1122" t="inlineStr"/>
@@ -28285,16 +28285,16 @@
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-02</t>
+          <t>VB020202-01-01-S-08</t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL REY</t>
         </is>
       </c>
       <c r="C1123" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D1123" t="inlineStr"/>
       <c r="E1123" t="inlineStr"/>
@@ -28307,16 +28307,16 @@
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>VB020104-01-02-M-02</t>
+          <t>VB020202-01-01-S-04</t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-M-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AMARILLO</t>
         </is>
       </c>
       <c r="C1124" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D1124" t="inlineStr"/>
       <c r="E1124" t="inlineStr"/>
@@ -28329,16 +28329,16 @@
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-02</t>
+          <t>VB020202-01-02-M-19</t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1125" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D1125" t="inlineStr"/>
       <c r="E1125" t="inlineStr"/>
@@ -28351,16 +28351,16 @@
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-16</t>
+          <t>VB020202-01-02-M-22</t>
         </is>
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-ROJO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-FLORES</t>
         </is>
       </c>
       <c r="C1126" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D1126" t="inlineStr"/>
       <c r="E1126" t="inlineStr"/>
@@ -28373,16 +28373,16 @@
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>VB0103-01-02-M-16</t>
+          <t>VB020202-01-02-M-08</t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-ROJO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AZUL REY</t>
         </is>
       </c>
       <c r="C1127" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D1127" t="inlineStr"/>
       <c r="E1127" t="inlineStr"/>
@@ -28395,16 +28395,16 @@
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-16</t>
+          <t>VB020202-01-02-M-04</t>
         </is>
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-ROJO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AMARILLO</t>
         </is>
       </c>
       <c r="C1128" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D1128" t="inlineStr"/>
       <c r="E1128" t="inlineStr"/>
@@ -28417,16 +28417,16 @@
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-02</t>
+          <t>VB020202-01-03-L-19</t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1129" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D1129" t="inlineStr"/>
       <c r="E1129" t="inlineStr"/>
@@ -28439,16 +28439,16 @@
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-01</t>
+          <t>VB020202-01-03-L-22</t>
         </is>
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-FLORES</t>
         </is>
       </c>
       <c r="C1130" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D1130" t="inlineStr"/>
       <c r="E1130" t="inlineStr"/>
@@ -28461,16 +28461,16 @@
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-01</t>
+          <t>VB020202-01-03-L-08</t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL REY</t>
         </is>
       </c>
       <c r="C1131" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D1131" t="inlineStr"/>
       <c r="E1131" t="inlineStr"/>
@@ -36423,21 +36423,21 @@
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>314208</t>
+          <t>ME1049</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>GEMTONE AMBER G001</t>
+          <t>TAPA PUSH PULL DORADA ROSCA 24</t>
         </is>
       </c>
       <c r="C1438" t="n">
-        <v>73488</v>
+        <v>3386</v>
       </c>
       <c r="D1438" t="inlineStr"/>
       <c r="E1438" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1438" t="inlineStr">
@@ -36449,21 +36449,21 @@
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>ME1049</t>
+          <t>314208</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>TAPA PUSH PULL DORADA ROSCA 24</t>
+          <t>GEMTONE AMBER G001</t>
         </is>
       </c>
       <c r="C1439" t="n">
-        <v>3386</v>
+        <v>73488</v>
       </c>
       <c r="D1439" t="inlineStr"/>
       <c r="E1439" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1439" t="inlineStr">
@@ -36865,21 +36865,21 @@
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>ET0202</t>
+          <t>ME0505</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>ETIQUETA PERFUME CABELLO ARRIESGAD 120ML</t>
+          <t>BALA TRANSPARENTE 120ML</t>
         </is>
       </c>
       <c r="C1455" t="n">
-        <v>140</v>
+        <v>2303</v>
       </c>
       <c r="D1455" t="inlineStr"/>
       <c r="E1455" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1455" t="inlineStr">
@@ -36891,21 +36891,21 @@
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>ME0505</t>
+          <t>ET0202</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 120ML</t>
+          <t>ETIQUETA PERFUME CABELLO ARRIESGAD 120ML</t>
         </is>
       </c>
       <c r="C1456" t="n">
-        <v>2303</v>
+        <v>140</v>
       </c>
       <c r="D1456" t="inlineStr"/>
       <c r="E1456" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1456" t="inlineStr">
@@ -37203,16 +37203,16 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>ME1025</t>
+          <t>ME0503</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>TAPA AIRLESS TRANSPARENTE CON SUBTAPA</t>
+          <t>AIRLESS TRANSPAREN CON ARO PLATA 30ML</t>
         </is>
       </c>
       <c r="C1468" t="n">
-        <v>9930</v>
+        <v>9967</v>
       </c>
       <c r="D1468" t="inlineStr"/>
       <c r="E1468" t="inlineStr">
@@ -37229,16 +37229,16 @@
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>ME0503</t>
+          <t>ME1025</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>AIRLESS TRANSPAREN CON ARO PLATA 30ML</t>
+          <t>TAPA AIRLESS TRANSPARENTE CON SUBTAPA</t>
         </is>
       </c>
       <c r="C1469" t="n">
-        <v>9967</v>
+        <v>9930</v>
       </c>
       <c r="D1469" t="inlineStr"/>
       <c r="E1469" t="inlineStr">
@@ -37775,21 +37775,21 @@
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>173501</t>
+          <t>ME1043</t>
         </is>
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>ULTRAMAR U-200 AZUL</t>
+          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
         </is>
       </c>
       <c r="C1490" t="n">
-        <v>5025</v>
+        <v>2731</v>
       </c>
       <c r="D1490" t="inlineStr"/>
       <c r="E1490" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1490" t="inlineStr">
@@ -37801,16 +37801,16 @@
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>ME1043</t>
+          <t>ME1044</t>
         </is>
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
+          <t>TAPA FLIP TOP PLATEADA ROSCA 18</t>
         </is>
       </c>
       <c r="C1491" t="n">
-        <v>2731</v>
+        <v>39166</v>
       </c>
       <c r="D1491" t="inlineStr"/>
       <c r="E1491" t="inlineStr">
@@ -37827,21 +37827,21 @@
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>ME1044</t>
+          <t>173501</t>
         </is>
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP PLATEADA ROSCA 18</t>
+          <t>ULTRAMAR U-200 AZUL</t>
         </is>
       </c>
       <c r="C1492" t="n">
-        <v>39166</v>
+        <v>5025</v>
       </c>
       <c r="D1492" t="inlineStr"/>
       <c r="E1492" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1492" t="inlineStr">
@@ -38607,16 +38607,16 @@
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>ME1057</t>
+          <t>ME1058</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>WHITE FOAM PUMP 42/410</t>
+          <t>WHITE PUMP ESPUMERO</t>
         </is>
       </c>
       <c r="C1522" t="n">
-        <v>1000</v>
+        <v>7417</v>
       </c>
       <c r="D1522" t="inlineStr"/>
       <c r="E1522" t="inlineStr">
@@ -38633,16 +38633,16 @@
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>ME1058</t>
+          <t>ME1057</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>WHITE PUMP ESPUMERO</t>
+          <t>WHITE FOAM PUMP 42/410</t>
         </is>
       </c>
       <c r="C1523" t="n">
-        <v>7417</v>
+        <v>1000</v>
       </c>
       <c r="D1523" t="inlineStr"/>
       <c r="E1523" t="inlineStr">
@@ -38763,16 +38763,16 @@
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>ME0511</t>
+          <t>ME1067</t>
         </is>
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>ENV PEAD KABA B28 500ML</t>
+          <t>TAPA NARANJA RUBOR EN BARRA SALLY</t>
         </is>
       </c>
       <c r="C1528" t="n">
-        <v>28261</v>
+        <v>19440</v>
       </c>
       <c r="D1528" t="inlineStr"/>
       <c r="E1528" t="inlineStr">
@@ -38789,21 +38789,21 @@
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>ET0253</t>
+          <t>ME0578</t>
         </is>
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>ETIQUETA BRONC DE CHOCOLATE MIEL 45ML</t>
+          <t>ENVASE ROJO RUBOR EN CREMA RUBY</t>
         </is>
       </c>
       <c r="C1529" t="n">
-        <v>22864</v>
+        <v>19980</v>
       </c>
       <c r="D1529" t="inlineStr"/>
       <c r="E1529" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1529" t="inlineStr">
@@ -38815,16 +38815,16 @@
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>ME1067</t>
+          <t>ME0579</t>
         </is>
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>TAPA NARANJA RUBOR EN BARRA SALLY</t>
+          <t>ENVASE NARANJA RUBOR EN CREMA SALLY</t>
         </is>
       </c>
       <c r="C1530" t="n">
-        <v>19440</v>
+        <v>19475</v>
       </c>
       <c r="D1530" t="inlineStr"/>
       <c r="E1530" t="inlineStr">
@@ -38841,16 +38841,16 @@
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>ME0578</t>
+          <t>ME1055</t>
         </is>
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>ENVASE ROJO RUBOR EN CREMA RUBY</t>
+          <t>TAPA SPRAY VERDE ROSCA 18</t>
         </is>
       </c>
       <c r="C1531" t="n">
-        <v>19980</v>
+        <v>11362</v>
       </c>
       <c r="D1531" t="inlineStr"/>
       <c r="E1531" t="inlineStr">
@@ -38867,16 +38867,16 @@
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>ME0579</t>
+          <t>ME0511</t>
         </is>
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>ENVASE NARANJA RUBOR EN CREMA SALLY</t>
+          <t>ENV PEAD KABA B28 500ML</t>
         </is>
       </c>
       <c r="C1532" t="n">
-        <v>19475</v>
+        <v>28261</v>
       </c>
       <c r="D1532" t="inlineStr"/>
       <c r="E1532" t="inlineStr">
@@ -38893,21 +38893,21 @@
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>ME1055</t>
+          <t>ET0253</t>
         </is>
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>TAPA SPRAY VERDE ROSCA 18</t>
+          <t>ETIQUETA BRONC DE CHOCOLATE MIEL 45ML</t>
         </is>
       </c>
       <c r="C1533" t="n">
-        <v>11362</v>
+        <v>22864</v>
       </c>
       <c r="D1533" t="inlineStr"/>
       <c r="E1533" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1533" t="inlineStr">
@@ -38997,16 +38997,16 @@
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>ME0529</t>
+          <t>ME0532</t>
         </is>
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>ENVASE VIDRIO ROSADO TONICO ROSAS 120ML</t>
+          <t>ENVASE VIDRIO VERDE MARCADO 30ML</t>
         </is>
       </c>
       <c r="C1537" t="n">
-        <v>3818</v>
+        <v>3459</v>
       </c>
       <c r="D1537" t="inlineStr"/>
       <c r="E1537" t="inlineStr">
@@ -39023,16 +39023,16 @@
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>ME0532</t>
+          <t>ME0529</t>
         </is>
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>ENVASE VIDRIO VERDE MARCADO 30ML</t>
+          <t>ENVASE VIDRIO ROSADO TONICO ROSAS 120ML</t>
         </is>
       </c>
       <c r="C1538" t="n">
-        <v>3459</v>
+        <v>3818</v>
       </c>
       <c r="D1538" t="inlineStr"/>
       <c r="E1538" t="inlineStr">
@@ -39179,16 +39179,16 @@
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>ME0507</t>
+          <t>ME0504</t>
         </is>
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 30ML</t>
+          <t>BALA NEGRA LARGA 120ML</t>
         </is>
       </c>
       <c r="C1544" t="n">
-        <v>24300</v>
+        <v>9239</v>
       </c>
       <c r="D1544" t="inlineStr"/>
       <c r="E1544" t="inlineStr">
@@ -39205,16 +39205,16 @@
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>ME0504</t>
+          <t>ME1028</t>
         </is>
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>BALA NEGRA LARGA 120ML</t>
+          <t>TAPA CON APLICADOR PUNTA PINCEL</t>
         </is>
       </c>
       <c r="C1545" t="n">
-        <v>9239</v>
+        <v>15877</v>
       </c>
       <c r="D1545" t="inlineStr"/>
       <c r="E1545" t="inlineStr">
@@ -39231,16 +39231,16 @@
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>ME1028</t>
+          <t>ME1059</t>
         </is>
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>TAPA CON APLICADOR PUNTA PINCEL</t>
+          <t>WIPER ( ESCURRIDOR/BARREDOR) NATURAL</t>
         </is>
       </c>
       <c r="C1546" t="n">
-        <v>15877</v>
+        <v>30387</v>
       </c>
       <c r="D1546" t="inlineStr"/>
       <c r="E1546" t="inlineStr">
@@ -39257,16 +39257,16 @@
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>ME1059</t>
+          <t>ME0507</t>
         </is>
       </c>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>WIPER ( ESCURRIDOR/BARREDOR) NATURAL</t>
+          <t>BALA TRANSPARENTE 30ML</t>
         </is>
       </c>
       <c r="C1547" t="n">
-        <v>30387</v>
+        <v>24300</v>
       </c>
       <c r="D1547" t="inlineStr"/>
       <c r="E1547" t="inlineStr">
@@ -39361,16 +39361,16 @@
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>ME1039</t>
+          <t>ME1501</t>
         </is>
       </c>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP 28 MM MORADO SANGRIA</t>
+          <t>TAPON DE VIDRIO ROSCA 28</t>
         </is>
       </c>
       <c r="C1551" t="n">
-        <v>37733</v>
+        <v>10552</v>
       </c>
       <c r="D1551" t="inlineStr"/>
       <c r="E1551" t="inlineStr">
@@ -39387,21 +39387,21 @@
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>ET02124</t>
+          <t>ME1039</t>
         </is>
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>ETIQUETA UNGUENTO GRANDE 120GR</t>
+          <t>TAPA FLIP TOP 28 MM MORADO SANGRIA</t>
         </is>
       </c>
       <c r="C1552" t="n">
-        <v>299</v>
+        <v>37733</v>
       </c>
       <c r="D1552" t="inlineStr"/>
       <c r="E1552" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1552" t="inlineStr">
@@ -39413,21 +39413,21 @@
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>ME1501</t>
+          <t>ET02124</t>
         </is>
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>TAPON DE VIDRIO ROSCA 28</t>
+          <t>ETIQUETA UNGUENTO GRANDE 120GR</t>
         </is>
       </c>
       <c r="C1553" t="n">
-        <v>10552</v>
+        <v>299</v>
       </c>
       <c r="D1553" t="inlineStr"/>
       <c r="E1553" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1553" t="inlineStr">
@@ -39465,16 +39465,16 @@
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>ME0545</t>
+          <t>ME0523</t>
         </is>
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>TUBO COLAP EXFOLIANTE CAPILAR 220GR V1</t>
+          <t>ENVASE PVC COLOR BLANCO POCIMA 6ML</t>
         </is>
       </c>
       <c r="C1555" t="n">
-        <v>1909</v>
+        <v>33606</v>
       </c>
       <c r="D1555" t="inlineStr"/>
       <c r="E1555" t="inlineStr">
@@ -39491,16 +39491,16 @@
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>ME0523</t>
+          <t>ME0542</t>
         </is>
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>ENVASE PVC COLOR BLANCO POCIMA 6ML</t>
+          <t>TUBO COLAP ANTOBRONCEADORA 120ML V1</t>
         </is>
       </c>
       <c r="C1556" t="n">
-        <v>33606</v>
+        <v>1178</v>
       </c>
       <c r="D1556" t="inlineStr"/>
       <c r="E1556" t="inlineStr">
@@ -39517,16 +39517,16 @@
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>ME0542</t>
+          <t>ME0545</t>
         </is>
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>TUBO COLAP ANTOBRONCEADORA 120ML V1</t>
+          <t>TUBO COLAP EXFOLIANTE CAPILAR 220GR V1</t>
         </is>
       </c>
       <c r="C1557" t="n">
-        <v>1178</v>
+        <v>1909</v>
       </c>
       <c r="D1557" t="inlineStr"/>
       <c r="E1557" t="inlineStr">
@@ -39699,16 +39699,16 @@
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>ME0555</t>
+          <t>ME0518</t>
         </is>
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>TUBO COLAPSIBLE COCO LOCO 10ML</t>
+          <t>ENVASE CON TAPA FUCSIA KABA MAKEUP 10ML</t>
         </is>
       </c>
       <c r="C1564" t="n">
-        <v>6000</v>
+        <v>7313</v>
       </c>
       <c r="D1564" t="inlineStr"/>
       <c r="E1564" t="inlineStr">
@@ -39725,16 +39725,16 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>ME0554</t>
+          <t>ME0555</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>TUBO COLAPSIBE DAIQUIRÍ 10ML</t>
+          <t>TUBO COLAPSIBLE COCO LOCO 10ML</t>
         </is>
       </c>
       <c r="C1565" t="n">
-        <v>9894</v>
+        <v>6000</v>
       </c>
       <c r="D1565" t="inlineStr"/>
       <c r="E1565" t="inlineStr">
@@ -39751,16 +39751,16 @@
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>ME0558</t>
+          <t>ME0554</t>
         </is>
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>TUBO COLAPSIBLE MARTINI 10ML</t>
+          <t>TUBO COLAPSIBE DAIQUIRÍ 10ML</t>
         </is>
       </c>
       <c r="C1566" t="n">
-        <v>6188</v>
+        <v>9894</v>
       </c>
       <c r="D1566" t="inlineStr"/>
       <c r="E1566" t="inlineStr">
@@ -39777,16 +39777,16 @@
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>ME0556</t>
+          <t>ME0558</t>
         </is>
       </c>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>TUBO COLAPSIBLE MANHATTAN 10ML</t>
+          <t>TUBO COLAPSIBLE MARTINI 10ML</t>
         </is>
       </c>
       <c r="C1567" t="n">
-        <v>6236</v>
+        <v>6188</v>
       </c>
       <c r="D1567" t="inlineStr"/>
       <c r="E1567" t="inlineStr">
@@ -39803,16 +39803,16 @@
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>ME0560</t>
+          <t>ME0556</t>
         </is>
       </c>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>TUBO COLAPSIBLE SUNRISE 10ML</t>
+          <t>TUBO COLAPSIBLE MANHATTAN 10ML</t>
         </is>
       </c>
       <c r="C1568" t="n">
-        <v>6429</v>
+        <v>6236</v>
       </c>
       <c r="D1568" t="inlineStr"/>
       <c r="E1568" t="inlineStr">
@@ -39829,16 +39829,16 @@
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>ME0557</t>
+          <t>ME0560</t>
         </is>
       </c>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>TUBO COLAPSIBLE MARGARITA 10ML</t>
+          <t>TUBO COLAPSIBLE SUNRISE 10ML</t>
         </is>
       </c>
       <c r="C1569" t="n">
-        <v>6155</v>
+        <v>6429</v>
       </c>
       <c r="D1569" t="inlineStr"/>
       <c r="E1569" t="inlineStr">
@@ -39855,16 +39855,16 @@
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>ME0518</t>
+          <t>ME0557</t>
         </is>
       </c>
       <c r="B1570" t="inlineStr">
         <is>
-          <t>ENVASE CON TAPA FUCSIA KABA MAKEUP 10ML</t>
+          <t>TUBO COLAPSIBLE MARGARITA 10ML</t>
         </is>
       </c>
       <c r="C1570" t="n">
-        <v>7313</v>
+        <v>6155</v>
       </c>
       <c r="D1570" t="inlineStr"/>
       <c r="E1570" t="inlineStr">
@@ -39959,16 +39959,16 @@
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>ET02106</t>
+          <t>ETC0112</t>
         </is>
       </c>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>ETIQUETA SHAMP CANNABIS ARGAN 500ML  V1</t>
+          <t>CAJA GLOSS GOLDEN HOUR</t>
         </is>
       </c>
       <c r="C1574" t="n">
-        <v>7666</v>
+        <v>16962</v>
       </c>
       <c r="D1574" t="inlineStr"/>
       <c r="E1574" t="inlineStr">
@@ -39985,16 +39985,16 @@
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>ETC0112</t>
+          <t>ET02106</t>
         </is>
       </c>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>CAJA GLOSS GOLDEN HOUR</t>
+          <t>ETIQUETA SHAMP CANNABIS ARGAN 500ML  V1</t>
         </is>
       </c>
       <c r="C1575" t="n">
-        <v>16962</v>
+        <v>7666</v>
       </c>
       <c r="D1575" t="inlineStr"/>
       <c r="E1575" t="inlineStr">
@@ -40297,16 +40297,16 @@
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>ET0247</t>
+          <t>ET02128</t>
         </is>
       </c>
       <c r="B1587" t="inlineStr">
         <is>
-          <t>ETIQUETA ACONDICIONADOR CERAMIDAS 500ML</t>
+          <t>ETIQUETA DESMAQUILLANTE BIFASICO 30ML</t>
         </is>
       </c>
       <c r="C1587" t="n">
-        <v>78798</v>
+        <v>60815</v>
       </c>
       <c r="D1587" t="inlineStr"/>
       <c r="E1587" t="inlineStr">
@@ -40323,16 +40323,16 @@
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>ET02128</t>
+          <t>ET02119</t>
         </is>
       </c>
       <c r="B1588" t="inlineStr">
         <is>
-          <t>ETIQUETA DESMAQUILLANTE BIFASICO 30ML</t>
+          <t>ETIQUETA TONICO FACIAL DESP E ILUM 30ML</t>
         </is>
       </c>
       <c r="C1588" t="n">
-        <v>60815</v>
+        <v>32838</v>
       </c>
       <c r="D1588" t="inlineStr"/>
       <c r="E1588" t="inlineStr">
@@ -40349,16 +40349,16 @@
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>ET02119</t>
+          <t>ET0247</t>
         </is>
       </c>
       <c r="B1589" t="inlineStr">
         <is>
-          <t>ETIQUETA TONICO FACIAL DESP E ILUM 30ML</t>
+          <t>ETIQUETA ACONDICIONADOR CERAMIDAS 500ML</t>
         </is>
       </c>
       <c r="C1589" t="n">
-        <v>32838</v>
+        <v>78798</v>
       </c>
       <c r="D1589" t="inlineStr"/>
       <c r="E1589" t="inlineStr">
@@ -40401,16 +40401,16 @@
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>ET0247ESP</t>
+          <t>ET0205</t>
         </is>
       </c>
       <c r="B1591" t="inlineStr">
         <is>
-          <t>ETIQUETA ACOND DE CERAMIDAS ESPAÑA</t>
+          <t>ETIQUETA TONICO CAPILAR KABA 30ML</t>
         </is>
       </c>
       <c r="C1591" t="n">
-        <v>2524</v>
+        <v>14461</v>
       </c>
       <c r="D1591" t="inlineStr"/>
       <c r="E1591" t="inlineStr">
@@ -40427,16 +40427,16 @@
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>ET0205</t>
+          <t>ET0247ESP</t>
         </is>
       </c>
       <c r="B1592" t="inlineStr">
         <is>
-          <t>ETIQUETA TONICO CAPILAR KABA 30ML</t>
+          <t>ETIQUETA ACOND DE CERAMIDAS ESPAÑA</t>
         </is>
       </c>
       <c r="C1592" t="n">
-        <v>14461</v>
+        <v>2524</v>
       </c>
       <c r="D1592" t="inlineStr"/>
       <c r="E1592" t="inlineStr">
@@ -40453,16 +40453,16 @@
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>ETC0129</t>
+          <t>ETC0133</t>
         </is>
       </c>
       <c r="B1593" t="inlineStr">
         <is>
-          <t>CAJA RUBOR LÍQUIDO DAIQUIRI</t>
+          <t>CAJA RUBOR LÍQUIDO SEX ON THE BEACH</t>
         </is>
       </c>
       <c r="C1593" t="n">
-        <v>7012</v>
+        <v>6305</v>
       </c>
       <c r="D1593" t="inlineStr"/>
       <c r="E1593" t="inlineStr">
@@ -40479,16 +40479,16 @@
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>ETC0128</t>
+          <t>ETC0129</t>
         </is>
       </c>
       <c r="B1594" t="inlineStr">
         <is>
-          <t>CAJA RUBOR LÍQUIDO COCO LOCO</t>
+          <t>CAJA RUBOR LÍQUIDO DAIQUIRI</t>
         </is>
       </c>
       <c r="C1594" t="n">
-        <v>7796</v>
+        <v>7012</v>
       </c>
       <c r="D1594" t="inlineStr"/>
       <c r="E1594" t="inlineStr">
@@ -40505,16 +40505,16 @@
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>ETC0132</t>
+          <t>ETC0128</t>
         </is>
       </c>
       <c r="B1595" t="inlineStr">
         <is>
-          <t>CAJA RUBOR LÍQUIDO MARTINI</t>
+          <t>CAJA RUBOR LÍQUIDO COCO LOCO</t>
         </is>
       </c>
       <c r="C1595" t="n">
-        <v>8992</v>
+        <v>7796</v>
       </c>
       <c r="D1595" t="inlineStr"/>
       <c r="E1595" t="inlineStr">
@@ -40531,16 +40531,16 @@
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>ETC0130</t>
+          <t>ETC0132</t>
         </is>
       </c>
       <c r="B1596" t="inlineStr">
         <is>
-          <t>CAJA RUBOR LÍQUIDO MANHATTAN</t>
+          <t>CAJA RUBOR LÍQUIDO MARTINI</t>
         </is>
       </c>
       <c r="C1596" t="n">
-        <v>5950</v>
+        <v>8992</v>
       </c>
       <c r="D1596" t="inlineStr"/>
       <c r="E1596" t="inlineStr">
@@ -40557,16 +40557,16 @@
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>ETC0134</t>
+          <t>ETC0130</t>
         </is>
       </c>
       <c r="B1597" t="inlineStr">
         <is>
-          <t>CAJA RUBOR LÍQUIDO SUNRISE</t>
+          <t>CAJA RUBOR LÍQUIDO MANHATTAN</t>
         </is>
       </c>
       <c r="C1597" t="n">
-        <v>8007</v>
+        <v>5950</v>
       </c>
       <c r="D1597" t="inlineStr"/>
       <c r="E1597" t="inlineStr">
@@ -40583,16 +40583,16 @@
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>ETC0131</t>
+          <t>ETC0134</t>
         </is>
       </c>
       <c r="B1598" t="inlineStr">
         <is>
-          <t>CAJA RUBOR LÍQUIDO MARGARITA</t>
+          <t>CAJA RUBOR LÍQUIDO SUNRISE</t>
         </is>
       </c>
       <c r="C1598" t="n">
-        <v>9064</v>
+        <v>8007</v>
       </c>
       <c r="D1598" t="inlineStr"/>
       <c r="E1598" t="inlineStr">
@@ -40609,16 +40609,16 @@
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>ETC0133</t>
+          <t>ETC0131</t>
         </is>
       </c>
       <c r="B1599" t="inlineStr">
         <is>
-          <t>CAJA RUBOR LÍQUIDO SEX ON THE BEACH</t>
+          <t>CAJA RUBOR LÍQUIDO MARGARITA</t>
         </is>
       </c>
       <c r="C1599" t="n">
-        <v>6305</v>
+        <v>9064</v>
       </c>
       <c r="D1599" t="inlineStr"/>
       <c r="E1599" t="inlineStr">
@@ -40817,21 +40817,21 @@
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>ET0204</t>
+          <t>ME0543</t>
         </is>
       </c>
       <c r="B1607" t="inlineStr">
         <is>
-          <t>ETIQUETA PERFUME CABELLO SOÑADORA 120ML</t>
+          <t>TUBO COLAP CONTORNO DE OJOS 15ML V1</t>
         </is>
       </c>
       <c r="C1607" t="n">
-        <v>184</v>
+        <v>22670</v>
       </c>
       <c r="D1607" t="inlineStr"/>
       <c r="E1607" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1607" t="inlineStr">
@@ -40843,21 +40843,21 @@
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>ME0543</t>
+          <t>ET0204</t>
         </is>
       </c>
       <c r="B1608" t="inlineStr">
         <is>
-          <t>TUBO COLAP CONTORNO DE OJOS 15ML V1</t>
+          <t>ETIQUETA PERFUME CABELLO SOÑADORA 120ML</t>
         </is>
       </c>
       <c r="C1608" t="n">
-        <v>22670</v>
+        <v>184</v>
       </c>
       <c r="D1608" t="inlineStr"/>
       <c r="E1608" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1608" t="inlineStr">
@@ -41259,16 +41259,16 @@
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>ME1012</t>
+          <t>ME1068</t>
         </is>
       </c>
       <c r="B1624" t="inlineStr">
         <is>
-          <t>BOMBA ENCASQUE DORADA/BRONCEADORES</t>
+          <t>TAPA SPRAY BLANCA R 18/410 (DEPILADOR N)</t>
         </is>
       </c>
       <c r="C1624" t="n">
-        <v>17890</v>
+        <v>257740</v>
       </c>
       <c r="D1624" t="inlineStr"/>
       <c r="E1624" t="inlineStr">
@@ -41285,21 +41285,21 @@
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>ET02138</t>
+          <t>ME1012</t>
         </is>
       </c>
       <c r="B1625" t="inlineStr">
         <is>
-          <t>ETIQUETA KERATINA ALISADOR KABA 500 ML</t>
+          <t>BOMBA ENCASQUE DORADA/BRONCEADORES</t>
         </is>
       </c>
       <c r="C1625" t="n">
-        <v>2868</v>
+        <v>17890</v>
       </c>
       <c r="D1625" t="inlineStr"/>
       <c r="E1625" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1625" t="inlineStr">
@@ -41311,16 +41311,16 @@
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>ET02139</t>
+          <t>ET02138</t>
         </is>
       </c>
       <c r="B1626" t="inlineStr">
         <is>
-          <t>ETIQUETA KERATINA ALISADOR KABA 250 ML</t>
+          <t>ETIQUETA KERATINA ALISADOR KABA 500 ML</t>
         </is>
       </c>
       <c r="C1626" t="n">
-        <v>1368</v>
+        <v>2868</v>
       </c>
       <c r="D1626" t="inlineStr"/>
       <c r="E1626" t="inlineStr">
@@ -41337,21 +41337,21 @@
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>ME1068</t>
+          <t>ET02139</t>
         </is>
       </c>
       <c r="B1627" t="inlineStr">
         <is>
-          <t>TAPA SPRAY BLANCA R 18/410 (DEPILADOR N)</t>
+          <t>ETIQUETA KERATINA ALISADOR KABA 250 ML</t>
         </is>
       </c>
       <c r="C1627" t="n">
-        <v>257740</v>
+        <v>1368</v>
       </c>
       <c r="D1627" t="inlineStr"/>
       <c r="E1627" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1627" t="inlineStr">
@@ -41467,16 +41467,16 @@
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>ET0270</t>
+          <t>ET0252</t>
         </is>
       </c>
       <c r="B1632" t="inlineStr">
         <is>
-          <t>ETIQUETA ESPM AUTOBRONCEADORA TONO MEDIO</t>
+          <t>ETIQUETA BRONC DE CHOCOLATE MIEL 200ML</t>
         </is>
       </c>
       <c r="C1632" t="n">
-        <v>9197</v>
+        <v>2169</v>
       </c>
       <c r="D1632" t="inlineStr"/>
       <c r="E1632" t="inlineStr">
@@ -41493,16 +41493,16 @@
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>ET0252</t>
+          <t>ET0270</t>
         </is>
       </c>
       <c r="B1633" t="inlineStr">
         <is>
-          <t>ETIQUETA BRONC DE CHOCOLATE MIEL 200ML</t>
+          <t>ETIQUETA ESPM AUTOBRONCEADORA TONO MEDIO</t>
         </is>
       </c>
       <c r="C1633" t="n">
-        <v>2169</v>
+        <v>9197</v>
       </c>
       <c r="D1633" t="inlineStr"/>
       <c r="E1633" t="inlineStr">
@@ -41827,21 +41827,21 @@
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>314202</t>
+          <t>ME0527</t>
         </is>
       </c>
       <c r="B1646" t="inlineStr">
         <is>
-          <t>CLOISONNE ROUGE FLAMBE 440X</t>
+          <t>ENVASE VIDRIO ROSADO MARCADO 30ML</t>
         </is>
       </c>
       <c r="C1646" t="n">
-        <v>6266</v>
+        <v>46</v>
       </c>
       <c r="D1646" t="inlineStr"/>
       <c r="E1646" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1646" t="inlineStr">
@@ -41853,21 +41853,21 @@
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>ME0527</t>
+          <t>314202</t>
         </is>
       </c>
       <c r="B1647" t="inlineStr">
         <is>
-          <t>ENVASE VIDRIO ROSADO MARCADO 30ML</t>
+          <t>CLOISONNE ROUGE FLAMBE 440X</t>
         </is>
       </c>
       <c r="C1647" t="n">
-        <v>46</v>
+        <v>6266</v>
       </c>
       <c r="D1647" t="inlineStr"/>
       <c r="E1647" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1647" t="inlineStr">
@@ -42269,21 +42269,21 @@
     <row r="1663">
       <c r="A1663" t="inlineStr">
         <is>
-          <t>ETC0160</t>
+          <t>ME0553</t>
         </is>
       </c>
       <c r="B1663" t="inlineStr">
         <is>
-          <t>CAJA RUBOR EN CREMA RUBY</t>
+          <t>TUBO COLAP TTO REVITALIZANTE 230ML V1</t>
         </is>
       </c>
       <c r="C1663" t="n">
-        <v>10536</v>
+        <v>478</v>
       </c>
       <c r="D1663" t="inlineStr"/>
       <c r="E1663" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1663" t="inlineStr">
@@ -42295,16 +42295,16 @@
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>ETC0161</t>
+          <t>ETC0160</t>
         </is>
       </c>
       <c r="B1664" t="inlineStr">
         <is>
-          <t>CAJA RUBOR EN CREMA SALLY</t>
+          <t>CAJA RUBOR EN CREMA RUBY</t>
         </is>
       </c>
       <c r="C1664" t="n">
-        <v>10328</v>
+        <v>10536</v>
       </c>
       <c r="D1664" t="inlineStr"/>
       <c r="E1664" t="inlineStr">
@@ -42321,21 +42321,21 @@
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>ME0553</t>
+          <t>ETC0161</t>
         </is>
       </c>
       <c r="B1665" t="inlineStr">
         <is>
-          <t>TUBO COLAP TTO REVITALIZANTE 230ML V1</t>
+          <t>CAJA RUBOR EN CREMA SALLY</t>
         </is>
       </c>
       <c r="C1665" t="n">
-        <v>478</v>
+        <v>10328</v>
       </c>
       <c r="D1665" t="inlineStr"/>
       <c r="E1665" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1665" t="inlineStr">
@@ -42347,16 +42347,16 @@
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>ME1066</t>
+          <t>ME1065</t>
         </is>
       </c>
       <c r="B1666" t="inlineStr">
         <is>
-          <t>TAPA ROJA RUBOR EN BARRA RUBY</t>
+          <t>TAPA ROSADA RUBOR EN BARRA GINGER</t>
         </is>
       </c>
       <c r="C1666" t="n">
-        <v>20520</v>
+        <v>20080</v>
       </c>
       <c r="D1666" t="inlineStr"/>
       <c r="E1666" t="inlineStr">
@@ -42373,16 +42373,16 @@
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>ME1065</t>
+          <t>ME1066</t>
         </is>
       </c>
       <c r="B1667" t="inlineStr">
         <is>
-          <t>TAPA ROSADA RUBOR EN BARRA GINGER</t>
+          <t>TAPA ROJA RUBOR EN BARRA RUBY</t>
         </is>
       </c>
       <c r="C1667" t="n">
-        <v>20080</v>
+        <v>20520</v>
       </c>
       <c r="D1667" t="inlineStr"/>
       <c r="E1667" t="inlineStr">
@@ -42789,21 +42789,21 @@
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>ETC0173</t>
+          <t>ME0506</t>
         </is>
       </c>
       <c r="B1683" t="inlineStr">
         <is>
-          <t>CAJA TONICO CAPILAR KABA ROSADA 120ML</t>
+          <t>BALA TRANSPARENTE 260/250 ML</t>
         </is>
       </c>
       <c r="C1683" t="n">
-        <v>193</v>
+        <v>4464</v>
       </c>
       <c r="D1683" t="inlineStr"/>
       <c r="E1683" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1683" t="inlineStr">
@@ -42815,21 +42815,21 @@
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>ME0506</t>
+          <t>ETC0173</t>
         </is>
       </c>
       <c r="B1684" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 260/250 ML</t>
+          <t>CAJA TONICO CAPILAR KABA ROSADA 120ML</t>
         </is>
       </c>
       <c r="C1684" t="n">
-        <v>4464</v>
+        <v>193</v>
       </c>
       <c r="D1684" t="inlineStr"/>
       <c r="E1684" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1684" t="inlineStr">
@@ -42841,16 +42841,16 @@
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>ET0236</t>
+          <t>ET0217</t>
         </is>
       </c>
       <c r="B1685" t="inlineStr">
         <is>
-          <t>ETIQUETA TONICO CAPILAR KABA 120ML</t>
+          <t>STICKER RUBOR EN CREMA 01 RUBY</t>
         </is>
       </c>
       <c r="C1685" t="n">
-        <v>107</v>
+        <v>4500</v>
       </c>
       <c r="D1685" t="inlineStr"/>
       <c r="E1685" t="inlineStr">
@@ -42867,12 +42867,12 @@
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>ET0217</t>
+          <t>ET0218</t>
         </is>
       </c>
       <c r="B1686" t="inlineStr">
         <is>
-          <t>STICKER RUBOR EN CREMA 01 RUBY</t>
+          <t>STICKER RUBOR EN CREMA 02 SALLY</t>
         </is>
       </c>
       <c r="C1686" t="n">
@@ -42893,12 +42893,12 @@
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>ET0218</t>
+          <t>ET0219</t>
         </is>
       </c>
       <c r="B1687" t="inlineStr">
         <is>
-          <t>STICKER RUBOR EN CREMA 02 SALLY</t>
+          <t>STICKER RUBOR EN CREMA 03 GINGER</t>
         </is>
       </c>
       <c r="C1687" t="n">
@@ -42919,16 +42919,16 @@
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>ET0219</t>
+          <t>ET0236</t>
         </is>
       </c>
       <c r="B1688" t="inlineStr">
         <is>
-          <t>STICKER RUBOR EN CREMA 03 GINGER</t>
+          <t>ETIQUETA TONICO CAPILAR KABA 120ML</t>
         </is>
       </c>
       <c r="C1688" t="n">
-        <v>4500</v>
+        <v>107</v>
       </c>
       <c r="D1688" t="inlineStr"/>
       <c r="E1688" t="inlineStr">
@@ -42971,16 +42971,16 @@
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>ME0533VG</t>
+          <t>ME1001VG</t>
         </is>
       </c>
       <c r="B1690" t="inlineStr">
         <is>
-          <t>ENVASE Y TAPA APLICADOR VIVIANA GRONDONA</t>
+          <t>TAPA BRONCEADOR R/24 VIVIANA GRONDONA</t>
         </is>
       </c>
       <c r="C1690" t="n">
-        <v>11568</v>
+        <v>12219</v>
       </c>
       <c r="D1690" t="inlineStr"/>
       <c r="E1690" t="inlineStr">
@@ -42997,16 +42997,16 @@
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>ME1001VG</t>
+          <t>ME0533VG</t>
         </is>
       </c>
       <c r="B1691" t="inlineStr">
         <is>
-          <t>TAPA BRONCEADOR R/24 VIVIANA GRONDONA</t>
+          <t>ENVASE Y TAPA APLICADOR VIVIANA GRONDONA</t>
         </is>
       </c>
       <c r="C1691" t="n">
-        <v>12219</v>
+        <v>11568</v>
       </c>
       <c r="D1691" t="inlineStr"/>
       <c r="E1691" t="inlineStr">
@@ -43075,16 +43075,16 @@
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>ME0516</t>
+          <t>ME1047</t>
         </is>
       </c>
       <c r="B1694" t="inlineStr">
         <is>
-          <t>ENVASE PET CILINDRICO 30ML</t>
+          <t>TAPA PLASTICA PUSH PULL 24/410 ROS 517C</t>
         </is>
       </c>
       <c r="C1694" t="n">
-        <v>386</v>
+        <v>811</v>
       </c>
       <c r="D1694" t="inlineStr"/>
       <c r="E1694" t="inlineStr">
@@ -43101,16 +43101,16 @@
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>ME1047</t>
+          <t>ME0516</t>
         </is>
       </c>
       <c r="B1695" t="inlineStr">
         <is>
-          <t>TAPA PLASTICA PUSH PULL 24/410 ROS 517C</t>
+          <t>ENVASE PET CILINDRICO 30ML</t>
         </is>
       </c>
       <c r="C1695" t="n">
-        <v>811</v>
+        <v>386</v>
       </c>
       <c r="D1695" t="inlineStr"/>
       <c r="E1695" t="inlineStr">
@@ -43465,16 +43465,16 @@
     <row r="1709">
       <c r="A1709" t="inlineStr">
         <is>
-          <t>ME0508</t>
+          <t>ME0533CA</t>
         </is>
       </c>
       <c r="B1709" t="inlineStr">
         <is>
-          <t>BALA TRANSPARENTE 60ML</t>
+          <t>ENVASE Y TAPA APLICADOR FUCSIA CARA</t>
         </is>
       </c>
       <c r="C1709" t="n">
-        <v>2000</v>
+        <v>3940</v>
       </c>
       <c r="D1709" t="inlineStr"/>
       <c r="E1709" t="inlineStr">
@@ -43491,16 +43491,16 @@
     <row r="1710">
       <c r="A1710" t="inlineStr">
         <is>
-          <t>ME0533CA</t>
+          <t>ME0508</t>
         </is>
       </c>
       <c r="B1710" t="inlineStr">
         <is>
-          <t>ENVASE Y TAPA APLICADOR FUCSIA CARA</t>
+          <t>BALA TRANSPARENTE 60ML</t>
         </is>
       </c>
       <c r="C1710" t="n">
-        <v>3940</v>
+        <v>2000</v>
       </c>
       <c r="D1710" t="inlineStr"/>
       <c r="E1710" t="inlineStr">
@@ -43543,16 +43543,16 @@
     <row r="1712">
       <c r="A1712" t="inlineStr">
         <is>
-          <t>ET02130USA</t>
+          <t>ET02105USA</t>
         </is>
       </c>
       <c r="B1712" t="inlineStr">
         <is>
-          <t>ETIQUETA EXFOLIATING BODY BUTTER OMG</t>
+          <t>ETIQUETA SERUM WITH VITAMIN C KABA</t>
         </is>
       </c>
       <c r="C1712" t="n">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="D1712" t="inlineStr"/>
       <c r="E1712" t="inlineStr">
@@ -43569,16 +43569,16 @@
     <row r="1713">
       <c r="A1713" t="inlineStr">
         <is>
-          <t>ET02131USA</t>
+          <t>ET02113</t>
         </is>
       </c>
       <c r="B1713" t="inlineStr">
         <is>
-          <t>ETIQUETA MOISTURIZING BODY BUTTER OMG</t>
+          <t>ETIQUETA SHAMPOO ROMERO 450ML</t>
         </is>
       </c>
       <c r="C1713" t="n">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="D1713" t="inlineStr"/>
       <c r="E1713" t="inlineStr">
@@ -43595,16 +43595,16 @@
     <row r="1714">
       <c r="A1714" t="inlineStr">
         <is>
-          <t>ET0269USA</t>
+          <t>ET02130USA</t>
         </is>
       </c>
       <c r="B1714" t="inlineStr">
         <is>
-          <t>ETIQUETA FAST HAIR REMOVAL OMG</t>
+          <t>ETIQUETA EXFOLIATING BODY BUTTER OMG</t>
         </is>
       </c>
       <c r="C1714" t="n">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="D1714" t="inlineStr"/>
       <c r="E1714" t="inlineStr">
@@ -43621,12 +43621,12 @@
     <row r="1715">
       <c r="A1715" t="inlineStr">
         <is>
-          <t>ET02105USA</t>
+          <t>ET02131USA</t>
         </is>
       </c>
       <c r="B1715" t="inlineStr">
         <is>
-          <t>ETIQUETA SERUM WITH VITAMIN C KABA</t>
+          <t>ETIQUETA MOISTURIZING BODY BUTTER OMG</t>
         </is>
       </c>
       <c r="C1715" t="n">
@@ -43647,16 +43647,16 @@
     <row r="1716">
       <c r="A1716" t="inlineStr">
         <is>
-          <t>ET02113</t>
+          <t>ET0269USA</t>
         </is>
       </c>
       <c r="B1716" t="inlineStr">
         <is>
-          <t>ETIQUETA SHAMPOO ROMERO 450ML</t>
+          <t>ETIQUETA FAST HAIR REMOVAL OMG</t>
         </is>
       </c>
       <c r="C1716" t="n">
-        <v>3900</v>
+        <v>5500</v>
       </c>
       <c r="D1716" t="inlineStr"/>
       <c r="E1716" t="inlineStr">
@@ -43699,21 +43699,21 @@
     <row r="1718">
       <c r="A1718" t="inlineStr">
         <is>
-          <t>ET0202VAIU</t>
+          <t>ME1002VAIU</t>
         </is>
       </c>
       <c r="B1718" t="inlineStr">
         <is>
-          <t>ETIQUETA SERUM VITAMINA C X 30 ML VAIU S</t>
+          <t>TAPA TRATAMIENTO 24/410 CASQUETE DORADO/</t>
         </is>
       </c>
       <c r="C1718" t="n">
-        <v>445</v>
+        <v>72</v>
       </c>
       <c r="D1718" t="inlineStr"/>
       <c r="E1718" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1718" t="inlineStr">
@@ -43725,16 +43725,16 @@
     <row r="1719">
       <c r="A1719" t="inlineStr">
         <is>
-          <t>ME1002VAIU</t>
+          <t>ME0502VAIU</t>
         </is>
       </c>
       <c r="B1719" t="inlineStr">
         <is>
-          <t>TAPA TRATAMIENTO 24/410 CASQUETE DORADO/</t>
+          <t>ENV 20/410 30ML VID RED BLANCO MATE/VAIU</t>
         </is>
       </c>
       <c r="C1719" t="n">
-        <v>72</v>
+        <v>372</v>
       </c>
       <c r="D1719" t="inlineStr"/>
       <c r="E1719" t="inlineStr">
@@ -43751,16 +43751,16 @@
     <row r="1720">
       <c r="A1720" t="inlineStr">
         <is>
-          <t>ME0502VAIU</t>
+          <t>ME0504VAIU</t>
         </is>
       </c>
       <c r="B1720" t="inlineStr">
         <is>
-          <t>ENV 20/410 30ML VID RED BLANCO MATE/VAIU</t>
+          <t>ENV 20/410 30ML VID RED AMARILLO MATE/VA</t>
         </is>
       </c>
       <c r="C1720" t="n">
-        <v>372</v>
+        <v>59</v>
       </c>
       <c r="D1720" t="inlineStr"/>
       <c r="E1720" t="inlineStr">
@@ -43777,21 +43777,21 @@
     <row r="1721">
       <c r="A1721" t="inlineStr">
         <is>
-          <t>ME0504VAIU</t>
+          <t>ET0202VAIU</t>
         </is>
       </c>
       <c r="B1721" t="inlineStr">
         <is>
-          <t>ENV 20/410 30ML VID RED AMARILLO MATE/VA</t>
+          <t>ETIQUETA SERUM VITAMINA C X 30 ML VAIU S</t>
         </is>
       </c>
       <c r="C1721" t="n">
-        <v>59</v>
+        <v>445</v>
       </c>
       <c r="D1721" t="inlineStr"/>
       <c r="E1721" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1721" t="inlineStr">
@@ -43829,16 +43829,16 @@
     <row r="1723">
       <c r="A1723" t="inlineStr">
         <is>
-          <t>ET0232</t>
+          <t>ET02113USA</t>
         </is>
       </c>
       <c r="B1723" t="inlineStr">
         <is>
-          <t>ETIQUETA SHAMPOO DE CEBOLLA 1 LITRO</t>
+          <t>ETIQUETA ROSEMARY SHAMPOO LA RECETA</t>
         </is>
       </c>
       <c r="C1723" t="n">
-        <v>18075</v>
+        <v>5500</v>
       </c>
       <c r="D1723" t="inlineStr"/>
       <c r="E1723" t="inlineStr">
@@ -43855,12 +43855,12 @@
     <row r="1724">
       <c r="A1724" t="inlineStr">
         <is>
-          <t>ET02113USA</t>
+          <t>ET02106USA</t>
         </is>
       </c>
       <c r="B1724" t="inlineStr">
         <is>
-          <t>ETIQUETA ROSEMARY SHAMPOO LA RECETA</t>
+          <t>ETIQUETA SHAMPOO ARGAN LA RECETA USA</t>
         </is>
       </c>
       <c r="C1724" t="n">
@@ -43881,16 +43881,16 @@
     <row r="1725">
       <c r="A1725" t="inlineStr">
         <is>
-          <t>ET02106USA</t>
+          <t>ET0287USA</t>
         </is>
       </c>
       <c r="B1725" t="inlineStr">
         <is>
-          <t>ETIQUETA SHAMPOO ARGAN LA RECETA USA</t>
+          <t>ETIQUETA CORPORAL BUTTER DLUCHI</t>
         </is>
       </c>
       <c r="C1725" t="n">
-        <v>5500</v>
+        <v>5200</v>
       </c>
       <c r="D1725" t="inlineStr"/>
       <c r="E1725" t="inlineStr">
@@ -43907,16 +43907,16 @@
     <row r="1726">
       <c r="A1726" t="inlineStr">
         <is>
-          <t>ET0287USA</t>
+          <t>ET0232</t>
         </is>
       </c>
       <c r="B1726" t="inlineStr">
         <is>
-          <t>ETIQUETA CORPORAL BUTTER DLUCHI</t>
+          <t>ETIQUETA SHAMPOO DE CEBOLLA 1 LITRO</t>
         </is>
       </c>
       <c r="C1726" t="n">
-        <v>5200</v>
+        <v>18075</v>
       </c>
       <c r="D1726" t="inlineStr"/>
       <c r="E1726" t="inlineStr">
@@ -43933,21 +43933,21 @@
     <row r="1727">
       <c r="A1727" t="inlineStr">
         <is>
-          <t>TE8014</t>
+          <t>ME1504</t>
         </is>
       </c>
       <c r="B1727" t="inlineStr">
         <is>
-          <t>TERMA (16.7X9)</t>
+          <t>TAPON DE VIDRIO ROSCA 24</t>
         </is>
       </c>
       <c r="C1727" t="n">
-        <v>1000</v>
+        <v>50000</v>
       </c>
       <c r="D1727" t="inlineStr"/>
       <c r="E1727" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1727" t="inlineStr">
@@ -43959,16 +43959,16 @@
     <row r="1728">
       <c r="A1728" t="inlineStr">
         <is>
-          <t>TE8015</t>
+          <t>TE8014</t>
         </is>
       </c>
       <c r="B1728" t="inlineStr">
         <is>
-          <t>TERMA (8.5X21)</t>
+          <t>TERMA (16.7X9)</t>
         </is>
       </c>
       <c r="C1728" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="D1728" t="inlineStr"/>
       <c r="E1728" t="inlineStr">
@@ -43985,16 +43985,16 @@
     <row r="1729">
       <c r="A1729" t="inlineStr">
         <is>
-          <t>TE8016</t>
+          <t>TE8015</t>
         </is>
       </c>
       <c r="B1729" t="inlineStr">
         <is>
-          <t>TERMA (5.5X13)</t>
+          <t>TERMA (8.5X21)</t>
         </is>
       </c>
       <c r="C1729" t="n">
-        <v>32000</v>
+        <v>5000</v>
       </c>
       <c r="D1729" t="inlineStr"/>
       <c r="E1729" t="inlineStr">
@@ -44011,16 +44011,16 @@
     <row r="1730">
       <c r="A1730" t="inlineStr">
         <is>
-          <t>TE8017</t>
+          <t>TE8016</t>
         </is>
       </c>
       <c r="B1730" t="inlineStr">
         <is>
-          <t>TERMA (5.7X13.5)</t>
+          <t>TERMA (5.5X13)</t>
         </is>
       </c>
       <c r="C1730" t="n">
-        <v>46000</v>
+        <v>32000</v>
       </c>
       <c r="D1730" t="inlineStr"/>
       <c r="E1730" t="inlineStr">
@@ -44037,21 +44037,21 @@
     <row r="1731">
       <c r="A1731" t="inlineStr">
         <is>
-          <t>ME1504</t>
+          <t>TE8017</t>
         </is>
       </c>
       <c r="B1731" t="inlineStr">
         <is>
-          <t>TAPON DE VIDRIO ROSCA 24</t>
+          <t>TERMA (5.7X13.5)</t>
         </is>
       </c>
       <c r="C1731" t="n">
-        <v>50000</v>
+        <v>46000</v>
       </c>
       <c r="D1731" t="inlineStr"/>
       <c r="E1731" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1731" t="inlineStr">
@@ -44089,16 +44089,16 @@
     <row r="1733">
       <c r="A1733" t="inlineStr">
         <is>
-          <t>TE8026</t>
+          <t>TE8022</t>
         </is>
       </c>
       <c r="B1733" t="inlineStr">
         <is>
-          <t>TERMA (20.3X100)</t>
+          <t>TERMA (16.5X9)</t>
         </is>
       </c>
       <c r="C1733" t="n">
-        <v>45000</v>
+        <v>23000</v>
       </c>
       <c r="D1733" t="inlineStr"/>
       <c r="E1733" t="inlineStr">
@@ -44115,16 +44115,16 @@
     <row r="1734">
       <c r="A1734" t="inlineStr">
         <is>
-          <t>TE8022</t>
+          <t>TE8023</t>
         </is>
       </c>
       <c r="B1734" t="inlineStr">
         <is>
-          <t>TERMA (16.5X9)</t>
+          <t>TERMA (45X118)</t>
         </is>
       </c>
       <c r="C1734" t="n">
-        <v>23000</v>
+        <v>7500</v>
       </c>
       <c r="D1734" t="inlineStr"/>
       <c r="E1734" t="inlineStr">
@@ -44141,16 +44141,16 @@
     <row r="1735">
       <c r="A1735" t="inlineStr">
         <is>
-          <t>TE8023</t>
+          <t>TE8024</t>
         </is>
       </c>
       <c r="B1735" t="inlineStr">
         <is>
-          <t>TERMA (45X118)</t>
+          <t>TERMA (45X115)</t>
         </is>
       </c>
       <c r="C1735" t="n">
-        <v>7500</v>
+        <v>1000</v>
       </c>
       <c r="D1735" t="inlineStr"/>
       <c r="E1735" t="inlineStr">
@@ -44167,16 +44167,16 @@
     <row r="1736">
       <c r="A1736" t="inlineStr">
         <is>
-          <t>TE8024</t>
+          <t>TE8025</t>
         </is>
       </c>
       <c r="B1736" t="inlineStr">
         <is>
-          <t>TERMA (45X115)</t>
+          <t>TERMA (8.2X21)</t>
         </is>
       </c>
       <c r="C1736" t="n">
-        <v>1000</v>
+        <v>64000</v>
       </c>
       <c r="D1736" t="inlineStr"/>
       <c r="E1736" t="inlineStr">
@@ -44193,16 +44193,16 @@
     <row r="1737">
       <c r="A1737" t="inlineStr">
         <is>
-          <t>TE8025</t>
+          <t>TE8026</t>
         </is>
       </c>
       <c r="B1737" t="inlineStr">
         <is>
-          <t>TERMA (8.2X21)</t>
+          <t>TERMA (20.3X100)</t>
         </is>
       </c>
       <c r="C1737" t="n">
-        <v>64000</v>
+        <v>45000</v>
       </c>
       <c r="D1737" t="inlineStr"/>
       <c r="E1737" t="inlineStr">
@@ -52117,21 +52117,21 @@
     <row r="2034">
       <c r="A2034" t="inlineStr">
         <is>
-          <t>173501</t>
+          <t>ME1043</t>
         </is>
       </c>
       <c r="B2034" t="inlineStr">
         <is>
-          <t>ULTRAMAR U-200 AZUL</t>
+          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
         </is>
       </c>
       <c r="C2034" t="n">
-        <v>309</v>
+        <v>3588</v>
       </c>
       <c r="D2034" t="inlineStr"/>
       <c r="E2034" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F2034" t="inlineStr">
@@ -52143,21 +52143,21 @@
     <row r="2035">
       <c r="A2035" t="inlineStr">
         <is>
-          <t>ME1043</t>
+          <t>173501</t>
         </is>
       </c>
       <c r="B2035" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
+          <t>ULTRAMAR U-200 AZUL</t>
         </is>
       </c>
       <c r="C2035" t="n">
-        <v>3588</v>
+        <v>309</v>
       </c>
       <c r="D2035" t="inlineStr"/>
       <c r="E2035" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F2035" t="inlineStr">
@@ -52975,16 +52975,16 @@
     <row r="2067">
       <c r="A2067" t="inlineStr">
         <is>
-          <t>ME0572</t>
+          <t>ME0544</t>
         </is>
       </c>
       <c r="B2067" t="inlineStr">
         <is>
-          <t>COLAPSIBLE AZUL CREMA CORPORAL ACLARANTE</t>
+          <t>TUBO COLAP DERMOACLARANTE 60ML V1</t>
         </is>
       </c>
       <c r="C2067" t="n">
-        <v>5068</v>
+        <v>815</v>
       </c>
       <c r="D2067" t="inlineStr"/>
       <c r="E2067" t="inlineStr">
@@ -53001,16 +53001,16 @@
     <row r="2068">
       <c r="A2068" t="inlineStr">
         <is>
-          <t>ME0544</t>
+          <t>ME0572</t>
         </is>
       </c>
       <c r="B2068" t="inlineStr">
         <is>
-          <t>TUBO COLAP DERMOACLARANTE 60ML V1</t>
+          <t>COLAPSIBLE AZUL CREMA CORPORAL ACLARANTE</t>
         </is>
       </c>
       <c r="C2068" t="n">
-        <v>815</v>
+        <v>5068</v>
       </c>
       <c r="D2068" t="inlineStr"/>
       <c r="E2068" t="inlineStr">
@@ -54067,16 +54067,16 @@
     <row r="2109">
       <c r="A2109" t="inlineStr">
         <is>
-          <t>ETC0103STOP</t>
+          <t>TE8025</t>
         </is>
       </c>
       <c r="B2109" t="inlineStr">
         <is>
-          <t>CAJA ENTRE AMIGAS SABEMOS STOP JEANS</t>
+          <t>TERMA (8.2X21)</t>
         </is>
       </c>
       <c r="C2109" t="n">
-        <v>120</v>
+        <v>2000</v>
       </c>
       <c r="D2109" t="inlineStr"/>
       <c r="E2109" t="inlineStr">
@@ -54093,16 +54093,16 @@
     <row r="2110">
       <c r="A2110" t="inlineStr">
         <is>
-          <t>TE8025</t>
+          <t>ETC0103STOP</t>
         </is>
       </c>
       <c r="B2110" t="inlineStr">
         <is>
-          <t>TERMA (8.2X21)</t>
+          <t>CAJA ENTRE AMIGAS SABEMOS STOP JEANS</t>
         </is>
       </c>
       <c r="C2110" t="n">
-        <v>2000</v>
+        <v>120</v>
       </c>
       <c r="D2110" t="inlineStr"/>
       <c r="E2110" t="inlineStr">

--- a/inventario_operaciones.xlsx
+++ b/inventario_operaciones.xlsx
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1745</v>
+        <v>1739</v>
       </c>
       <c r="D13" t="n">
         <v>5287.328244274809</v>
@@ -787,19 +787,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D031009</t>
+          <t>K010402</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ESPUMA AUTOBRONCEADORA TON OSCURO DLUCHI</t>
+          <t>PERFUME PARA EL CABELLO CONFIDENTE KABA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>309</v>
+        <v>189</v>
       </c>
       <c r="D14" t="n">
-        <v>666.412213740458</v>
+        <v>1163.473282442748</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -815,19 +815,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K010402</t>
+          <t>D030601</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO CONFIDENTE KABA</t>
+          <t>FRESHING POP AFTER SUN DLUCHI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>189</v>
+        <v>223</v>
       </c>
       <c r="D15" t="n">
-        <v>1163.473282442748</v>
+        <v>267.9389312977099</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -843,19 +843,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D030601</t>
+          <t>K010403</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FRESHING POP AFTER SUN DLUCHI</t>
+          <t>PERFUME PARA EL CABELLO SOÑADORA KABA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="D16" t="n">
-        <v>267.9389312977099</v>
+        <v>1100.954198473282</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -871,19 +871,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K010403</t>
+          <t>D031009</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO SOÑADORA KABA</t>
+          <t>ESPUMA AUTOBRONCEADORA TON OSCURO DLUCHI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>204</v>
+        <v>309</v>
       </c>
       <c r="D17" t="n">
-        <v>1100.954198473282</v>
+        <v>666.412213740458</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1011,19 +1011,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KM041101</t>
+          <t>K010102</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS ALMENDRA</t>
+          <t>SHAMPO KIDS KABA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>686</v>
+        <v>94</v>
       </c>
       <c r="D22" t="n">
-        <v>2872.786259541985</v>
+        <v>2141.106870229008</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1039,19 +1039,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K010102</t>
+          <t>R010302</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SHAMPO KIDS KABA</t>
+          <t>TONICO CAPILAR LA RECETA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>94</v>
+        <v>288</v>
       </c>
       <c r="D23" t="n">
-        <v>2141.106870229008</v>
+        <v>3218.702290076336</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R010302</t>
+          <t>KM041101</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TONICO CAPILAR LA RECETA</t>
+          <t>CORRECTOR DE OJERAS ALMENDRA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>288</v>
+        <v>686</v>
       </c>
       <c r="D24" t="n">
-        <v>3218.702290076336</v>
+        <v>2872.786259541985</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-857</v>
+        <v>-865</v>
       </c>
       <c r="D25" t="n">
         <v>33819.04580152671</v>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-322</v>
+        <v>-331</v>
       </c>
       <c r="D31" t="n">
         <v>23981.2213740458</v>
@@ -1459,19 +1459,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KM041104</t>
+          <t>K020506</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS CARAMELO</t>
+          <t>MASCARILLA FACIAL DE CHOCOLATE KABA</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>818</v>
+        <v>198</v>
       </c>
       <c r="D38" t="n">
-        <v>217.4427480916031</v>
+        <v>138.7786259541985</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1487,19 +1487,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>K020506</t>
+          <t>KM041304</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MASCARILLA FACIAL DE CHOCOLATE KABA</t>
+          <t>DROPS PINK GOLD</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>198</v>
+        <v>782</v>
       </c>
       <c r="D39" t="n">
-        <v>138.7786259541985</v>
+        <v>178.6259541984733</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1515,19 +1515,19 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KM041304</t>
+          <t>KM041104</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DROPS PINK GOLD</t>
+          <t>CORRECTOR DE OJERAS CARAMELO</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>782</v>
+        <v>818</v>
       </c>
       <c r="D40" t="n">
-        <v>178.6259541984733</v>
+        <v>217.4427480916031</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1543,19 +1543,19 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KM041301</t>
+          <t>KM041302</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE GOLD</t>
+          <t>DROPS CHAMPAGNE SILVER</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>507</v>
+        <v>762</v>
       </c>
       <c r="D41" t="n">
-        <v>760.8778625954199</v>
+        <v>192.7099236641222</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1571,19 +1571,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KM041302</t>
+          <t>KM041301</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE SILVER</t>
+          <t>DROPS CHAMPAGNE GOLD</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>762</v>
+        <v>507</v>
       </c>
       <c r="D42" t="n">
-        <v>192.7099236641222</v>
+        <v>760.8778625954199</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1655,19 +1655,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KM041308</t>
+          <t>KM041106</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ILUMINADOR LIQUIDO PRETTY GIRL</t>
+          <t>CORRECTOR DE OJERAS MIEL</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>168</v>
+        <v>904</v>
       </c>
       <c r="D45" t="n">
-        <v>148.3969465648855</v>
+        <v>1522.786259541985</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1683,19 +1683,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KM041106</t>
+          <t>KM041308</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS MIEL</t>
+          <t>ILUMINADOR LIQUIDO PRETTY GIRL</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>904</v>
+        <v>168</v>
       </c>
       <c r="D46" t="n">
-        <v>1522.786259541985</v>
+        <v>148.3969465648855</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="D47" t="n">
         <v>1436.221374045801</v>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D51" t="n">
         <v>1270.30534351145</v>
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="D67" t="n">
         <v>2000.610687022901</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D73" t="n">
         <v>177.5954198473282</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D82" t="n">
         <v>9.732824427480915</v>
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D85" t="n">
         <v>87.25190839694656</v>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D92" t="n">
         <v>162.1374045801527</v>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="D97" t="n">
         <v>11863.1679389313</v>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D102" t="n">
         <v>95.95419847328245</v>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="D104" t="n">
         <v>15285.91603053435</v>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D106" t="n">
         <v>260.9541984732824</v>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D114" t="n">
         <v>722.9770992366413</v>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
@@ -3673,19 +3673,19 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>KITK0206</t>
+          <t>KITK0301</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>KIT RUTINA AM KABA</t>
+          <t>KIT ADIOS MANCHAS KABA</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D118" t="n">
-        <v>34.69465648854962</v>
+        <v>98.58778625954199</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3701,19 +3701,19 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KITK0301</t>
+          <t>KITK0206</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>KIT ADIOS MANCHAS KABA</t>
+          <t>KIT RUTINA AM KABA</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D119" t="n">
-        <v>98.58778625954199</v>
+        <v>34.69465648854962</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D121" t="n">
         <v>230.7251908396946</v>
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D126" t="n">
         <v>82.32824427480917</v>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D127" t="n">
         <v>118.5114503816794</v>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D128" t="n">
         <v>520.8778625954199</v>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D129" t="n">
         <v>4484.885496183206</v>
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D135" t="n">
         <v>324.2748091603053</v>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D138" t="n">
         <v>1399.809160305344</v>
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D139" t="n">
         <v>1701.068702290076</v>
@@ -4399,19 +4399,19 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>KITD0304</t>
+          <t>K020502</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>KIT BRONCEOPERF VAR ZANA CANELA DLUCHI</t>
+          <t>ESPUMA LIMPIADORA FACIAL KABA</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>33</v>
+        <v>263</v>
       </c>
       <c r="D144" t="n">
-        <v>116.9083969465649</v>
+        <v>1723.396946564885</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4427,19 +4427,19 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>K020502</t>
+          <t>KITD0304</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ESPUMA LIMPIADORA FACIAL KABA</t>
+          <t>KIT BRONCEOPERF VAR ZANA CANELA DLUCHI</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>263</v>
+        <v>30</v>
       </c>
       <c r="D145" t="n">
-        <v>1723.396946564885</v>
+        <v>116.9083969465649</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4719,16 +4719,16 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>D051501</t>
+          <t>K051501</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE DLUCHI</t>
+          <t>COSMETIQUERA GRANDE KABA</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
@@ -4745,16 +4745,16 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>K051501</t>
+          <t>D051501</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE KABA</t>
+          <t>COSMETIQUERA GRANDE DLUCHI</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
@@ -5333,19 +5333,19 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>D031009</t>
+          <t>D030601</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ESPUMA AUTOBRONCEADORA TON OSCURO DLUCHI</t>
+          <t>FRESHING POP AFTER SUN DLUCHI</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D179" t="n">
-        <v>666.412213740458</v>
+        <v>267.9389312977099</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -5361,19 +5361,19 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>D030601</t>
+          <t>D031009</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>FRESHING POP AFTER SUN DLUCHI</t>
+          <t>ESPUMA AUTOBRONCEADORA TON OSCURO DLUCHI</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D180" t="n">
-        <v>267.9389312977099</v>
+        <v>666.412213740458</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -7063,19 +7063,19 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>D031009</t>
+          <t>K010402</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>ESPUMA AUTOBRONCEADORA TON OSCURO DLUCHI</t>
+          <t>PERFUME PARA EL CABELLO CONFIDENTE KABA</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>1001</v>
+        <v>1512</v>
       </c>
       <c r="D243" t="n">
-        <v>666.412213740458</v>
+        <v>1163.473282442748</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -7091,19 +7091,19 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>K010402</t>
+          <t>D030601</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO CONFIDENTE KABA</t>
+          <t>FRESHING POP AFTER SUN DLUCHI</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>1512</v>
+        <v>18072</v>
       </c>
       <c r="D244" t="n">
-        <v>1163.473282442748</v>
+        <v>267.9389312977099</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -7119,19 +7119,19 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>D030601</t>
+          <t>K010403</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>FRESHING POP AFTER SUN DLUCHI</t>
+          <t>PERFUME PARA EL CABELLO SOÑADORA KABA</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>18072</v>
+        <v>4205</v>
       </c>
       <c r="D245" t="n">
-        <v>267.9389312977099</v>
+        <v>1100.954198473282</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -7147,19 +7147,19 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>K010403</t>
+          <t>D031009</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO SOÑADORA KABA</t>
+          <t>ESPUMA AUTOBRONCEADORA TON OSCURO DLUCHI</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>4205</v>
+        <v>1001</v>
       </c>
       <c r="D246" t="n">
-        <v>1100.954198473282</v>
+        <v>666.412213740458</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -9325,19 +9325,19 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>KM041302</t>
+          <t>KM041301</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE SILVER</t>
+          <t>DROPS CHAMPAGNE GOLD</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>6380</v>
+        <v>4443</v>
       </c>
       <c r="D328" t="n">
-        <v>192.7099236641222</v>
+        <v>760.8778625954199</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -9353,19 +9353,19 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>KM041301</t>
+          <t>KM041302</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE GOLD</t>
+          <t>DROPS CHAMPAGNE SILVER</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>4443</v>
+        <v>6380</v>
       </c>
       <c r="D329" t="n">
-        <v>760.8778625954199</v>
+        <v>192.7099236641222</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -9967,16 +9967,16 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>K010312</t>
+          <t>K030902</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>MINI TRATO CAPILAR REPOLARIZADOR 30ML</t>
+          <t>MINI GEL LIPOREDUCTOR 30ML</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>1996</v>
+        <v>1323</v>
       </c>
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
@@ -9993,16 +9993,16 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>K030902</t>
+          <t>K010312</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>MINI GEL LIPOREDUCTOR 30ML</t>
+          <t>MINI TRATO CAPILAR REPOLARIZADOR 30ML</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>1323</v>
+        <v>1996</v>
       </c>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
@@ -11823,16 +11823,16 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>KITC010201</t>
+          <t>C030606</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>KIT VIVIANA GRONDONA</t>
+          <t>GLOW GIRLS SOPHIE ECHEVERRRI</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>5496</v>
+        <v>7990</v>
       </c>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr">
@@ -11849,16 +11849,16 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>C030606</t>
+          <t>KITC010201</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>GLOW GIRLS SOPHIE ECHEVERRRI</t>
+          <t>KIT VIVIANA GRONDONA</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>7990</v>
+        <v>5496</v>
       </c>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr">
@@ -12809,19 +12809,19 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>KITD0304</t>
+          <t>K020502</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>KIT BRONCEOPERF VAR ZANA CANELA DLUCHI</t>
+          <t>ESPUMA LIMPIADORA FACIAL KABA</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>15</v>
+        <v>848</v>
       </c>
       <c r="D457" t="n">
-        <v>116.9083969465649</v>
+        <v>1723.396946564885</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
@@ -12837,19 +12837,19 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>K020502</t>
+          <t>KITK0202</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>ESPUMA LIMPIADORA FACIAL KABA</t>
+          <t>KIT FACIAL ANTIOXIDANTE KABA</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>848</v>
+        <v>12</v>
       </c>
       <c r="D458" t="n">
-        <v>1723.396946564885</v>
+        <v>12.36641221374046</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
@@ -12865,19 +12865,19 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>KITK0202</t>
+          <t>KITD0304</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>KIT FACIAL ANTIOXIDANTE KABA</t>
+          <t>KIT BRONCEOPERF VAR ZANA CANELA DLUCHI</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D459" t="n">
-        <v>12.36641221374046</v>
+        <v>116.9083969465649</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
@@ -13167,16 +13167,16 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>KITN0102</t>
+          <t>KITD0910</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>KIT SELF LOVE RITUAL</t>
+          <t>KIT PIEL CANELA MEDIO</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D470" t="inlineStr"/>
       <c r="E470" t="inlineStr">
@@ -13193,16 +13193,16 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>KITD0910</t>
+          <t>KITN0102</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>KIT PIEL CANELA MEDIO</t>
+          <t>KIT SELF LOVE RITUAL</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="D471" t="inlineStr"/>
       <c r="E471" t="inlineStr">
@@ -15525,16 +15525,16 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>IL051702</t>
+          <t>D051703</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>LLAVERO CASETTE</t>
+          <t>BOLSO PLAYERO</t>
         </is>
       </c>
       <c r="C561" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr">
@@ -15551,16 +15551,16 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>D051703</t>
+          <t>IL051701</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>BOLSO PLAYERO</t>
+          <t>WALMAN</t>
         </is>
       </c>
       <c r="C562" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D562" t="inlineStr"/>
       <c r="E562" t="inlineStr">
@@ -15577,16 +15577,16 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>IL051701</t>
+          <t>K051702</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>WALMAN</t>
+          <t>PELICULA INSTANTANEA</t>
         </is>
       </c>
       <c r="C563" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D563" t="inlineStr"/>
       <c r="E563" t="inlineStr">
@@ -15603,12 +15603,12 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>K051702</t>
+          <t>K051701</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>PELICULA INSTANTANEA</t>
+          <t>CAMARA INSTANTANEA</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -15629,16 +15629,16 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>K051701</t>
+          <t>IL051702</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>CAMARA INSTANTANEA</t>
+          <t>LLAVERO CASETTE</t>
         </is>
       </c>
       <c r="C565" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D565" t="inlineStr"/>
       <c r="E565" t="inlineStr">
@@ -16637,25 +16637,19 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>D051601</t>
+          <t>VB0104-01-02-M-02</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>CEPILLO APLICADOR AUTOBRONCEADOR DLUCHI</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-NEGRO</t>
         </is>
       </c>
       <c r="C605" t="n">
-        <v>936</v>
-      </c>
-      <c r="D605" t="n">
-        <v>1017.137404580153</v>
-      </c>
-      <c r="E605" t="inlineStr">
-        <is>
-          <t>PRODUCTO MANUFACTURADO</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D605" t="inlineStr"/>
+      <c r="E605" t="inlineStr"/>
       <c r="F605" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -16665,16 +16659,16 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>VB0104-01-02-M-02</t>
+          <t>VB0104-01-03-L-02</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-NEGRO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-NEGRO</t>
         </is>
       </c>
       <c r="C606" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr"/>
@@ -16687,16 +16681,16 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>VB0104-01-03-L-02</t>
+          <t>VB020101-01-01-S-06</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C607" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D607" t="inlineStr"/>
       <c r="E607" t="inlineStr"/>
@@ -16709,16 +16703,16 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-06</t>
+          <t>VB020105-01-03-L-11</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AZUL CELESTE</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C608" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr"/>
@@ -16731,16 +16725,16 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-11</t>
+          <t>VB0104-01-01-S-02</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-FUCSIA NEON</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-NEGRO</t>
         </is>
       </c>
       <c r="C609" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr"/>
@@ -16753,16 +16747,16 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>VB0104-01-01-S-02</t>
+          <t>VB020103-03-03-L-20</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C610" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr"/>
@@ -16775,16 +16769,16 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>VB020103-03-03-L-20</t>
+          <t>VB020303-01-02-M-24</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-L-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C611" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr"/>
@@ -16797,12 +16791,12 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-24</t>
+          <t>VB020101-01-02-M-25</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C612" t="n">
@@ -16819,16 +16813,16 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-25</t>
+          <t>VB020105-01-01-S-13</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-NARANJA</t>
         </is>
       </c>
       <c r="C613" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
@@ -16841,16 +16835,16 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-13</t>
+          <t>VB020303-01-02-M-25</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-NARANJA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C614" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
@@ -16863,16 +16857,16 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-25</t>
+          <t>VB020303-01-01-S-24</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C615" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr"/>
@@ -16885,12 +16879,12 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-24</t>
+          <t>VB020105-01-01-S-05</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C616" t="n">
@@ -16907,12 +16901,12 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-05</t>
+          <t>VB020105-01-02-M-05</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C617" t="n">
@@ -16929,12 +16923,12 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-05</t>
+          <t>VB020101-01-01-S-25</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C618" t="n">
@@ -16951,12 +16945,12 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-25</t>
+          <t>VB020101-01-03-L-25</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C619" t="n">
@@ -16973,16 +16967,16 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-25</t>
+          <t>VB020303-01-01-S-25</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C620" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D620" t="inlineStr"/>
       <c r="E620" t="inlineStr"/>
@@ -16995,16 +16989,16 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-25</t>
+          <t>VB020105-01-02-M-11</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C621" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D621" t="inlineStr"/>
       <c r="E621" t="inlineStr"/>
@@ -17017,16 +17011,16 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-11</t>
+          <t>VB020101-01-02-M-06</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C622" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D622" t="inlineStr"/>
       <c r="E622" t="inlineStr"/>
@@ -17039,16 +17033,16 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-06</t>
+          <t>VB020101-01-03-L-06</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AZUL CELESTE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C623" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D623" t="inlineStr"/>
       <c r="E623" t="inlineStr"/>
@@ -17061,12 +17055,12 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-06</t>
+          <t>VB020105-01-03-L-13</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AZUL CELESTE</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
         </is>
       </c>
       <c r="C624" t="n">
@@ -17083,19 +17077,23 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-13</t>
+          <t>DISACK010101</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-NARANJA</t>
+          <t>DISPLEY SACHET DE SHAMPO DE CEBOLLA KABA</t>
         </is>
       </c>
       <c r="C625" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D625" t="inlineStr"/>
-      <c r="E625" t="inlineStr"/>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>PRODUCTO MANUFACTURADO</t>
+        </is>
+      </c>
       <c r="F625" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -17105,23 +17103,19 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>DISACK010101</t>
+          <t>VB020103-01-02-M-26</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>DISPLEY SACHET DE SHAMPO DE CEBOLLA KABA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
         </is>
       </c>
       <c r="C626" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D626" t="inlineStr"/>
-      <c r="E626" t="inlineStr">
-        <is>
-          <t>PRODUCTO MANUFACTURADO</t>
-        </is>
-      </c>
+      <c r="E626" t="inlineStr"/>
       <c r="F626" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -17131,12 +17125,12 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>VB020103-01-02-M-26</t>
+          <t>VB020105-01-02-M-13</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-M-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
         </is>
       </c>
       <c r="C627" t="n">
@@ -17153,16 +17147,16 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-13</t>
+          <t>VB020101-01-01-S-14</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C628" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D628" t="inlineStr"/>
       <c r="E628" t="inlineStr"/>
@@ -17175,12 +17169,12 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-14</t>
+          <t>VB020103-03-02-M-20</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C629" t="n">
@@ -17197,12 +17191,12 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>VB020103-03-02-M-20</t>
+          <t>VB020303-01-03-L-25</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C630" t="n">
@@ -17219,16 +17213,16 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-25</t>
+          <t>VB020105-01-01-S-08</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
         </is>
       </c>
       <c r="C631" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D631" t="inlineStr"/>
       <c r="E631" t="inlineStr"/>
@@ -17241,16 +17235,16 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-08</t>
+          <t>VB020303-01-03-L-24</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C632" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D632" t="inlineStr"/>
       <c r="E632" t="inlineStr"/>
@@ -17263,16 +17257,16 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-24</t>
+          <t>VB020105-01-03-L-05</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C633" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D633" t="inlineStr"/>
       <c r="E633" t="inlineStr"/>
@@ -17285,16 +17279,16 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-05</t>
+          <t>VB020303-01-01-S-30</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-PLUMAS</t>
         </is>
       </c>
       <c r="C634" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D634" t="inlineStr"/>
       <c r="E634" t="inlineStr"/>
@@ -17307,16 +17301,16 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-30</t>
+          <t>VB020103-03-01-S-20</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C635" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr"/>
@@ -17329,16 +17323,16 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>VB020103-03-01-S-20</t>
+          <t>VB020303-01-02-M-30</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-PLUMAS</t>
         </is>
       </c>
       <c r="C636" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D636" t="inlineStr"/>
       <c r="E636" t="inlineStr"/>
@@ -17351,12 +17345,12 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-30</t>
+          <t>VB020101-01-01-S-30</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PLUMAS</t>
         </is>
       </c>
       <c r="C637" t="n">
@@ -17373,16 +17367,16 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-30</t>
+          <t>VB020101-01-03-L-19</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C638" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D638" t="inlineStr"/>
       <c r="E638" t="inlineStr"/>
@@ -17395,12 +17389,12 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-19</t>
+          <t>VB020101-01-02-M-14</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C639" t="n">
@@ -17417,16 +17411,16 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-14</t>
+          <t>VB020101-01-03-L-14</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D640" t="inlineStr"/>
       <c r="E640" t="inlineStr"/>
@@ -17439,16 +17433,16 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-14</t>
+          <t>VB020103-01-01-S-26</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-S-MISTICO</t>
         </is>
       </c>
       <c r="C641" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr"/>
@@ -17461,16 +17455,16 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>VB020103-01-01-S-26</t>
+          <t>VB020101-01-03-L-30</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-S-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PLUMAS</t>
         </is>
       </c>
       <c r="C642" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D642" t="inlineStr"/>
       <c r="E642" t="inlineStr"/>
@@ -17483,16 +17477,16 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-30</t>
+          <t>VB020101-01-01-S-19</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C643" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D643" t="inlineStr"/>
       <c r="E643" t="inlineStr"/>
@@ -17505,12 +17499,12 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-19</t>
+          <t>VB020303-01-03-L-30</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
         </is>
       </c>
       <c r="C644" t="n">
@@ -17527,12 +17521,12 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-30</t>
+          <t>VB020105-01-03-L-15</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-PURPURA</t>
         </is>
       </c>
       <c r="C645" t="n">
@@ -17549,16 +17543,16 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-15</t>
+          <t>VB020105-01-02-M-08</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
         </is>
       </c>
       <c r="C646" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D646" t="inlineStr"/>
       <c r="E646" t="inlineStr"/>
@@ -17571,16 +17565,16 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-08</t>
+          <t>VB020103-01-03-L-26</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-L-MISTICO</t>
         </is>
       </c>
       <c r="C647" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D647" t="inlineStr"/>
       <c r="E647" t="inlineStr"/>
@@ -17593,12 +17587,12 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>VB020103-01-03-L-26</t>
+          <t>VB020105-01-01-S-11</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-L-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C648" t="n">
@@ -17615,19 +17609,23 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-11</t>
+          <t>K051501</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-FUCSIA NEON</t>
+          <t>COSMETIQUERA GRANDE KABA</t>
         </is>
       </c>
       <c r="C649" t="n">
-        <v>2</v>
+        <v>3533</v>
       </c>
       <c r="D649" t="inlineStr"/>
-      <c r="E649" t="inlineStr"/>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>COMPRA GRAVADA SIN LOTES</t>
+        </is>
+      </c>
       <c r="F649" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -17637,21 +17635,23 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>K051501</t>
+          <t>D051601</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE KABA</t>
+          <t>CEPILLO APLICADOR AUTOBRONCEADOR DLUCHI</t>
         </is>
       </c>
       <c r="C650" t="n">
-        <v>3533</v>
-      </c>
-      <c r="D650" t="inlineStr"/>
+        <v>936</v>
+      </c>
+      <c r="D650" t="n">
+        <v>1017.137404580153</v>
+      </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>COMPRA GRAVADA SIN LOTES</t>
+          <t>PRODUCTO MANUFACTURADO</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
@@ -17663,19 +17663,23 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-15</t>
+          <t>D051705</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-PURPURA</t>
+          <t>TERMO DLUCHI 450ML</t>
         </is>
       </c>
       <c r="C651" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D651" t="inlineStr"/>
-      <c r="E651" t="inlineStr"/>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>PRODUCTO MANUFACTURADO</t>
+        </is>
+      </c>
       <c r="F651" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -17685,12 +17689,12 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-26</t>
+          <t>VB020204-01-01-S-15</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-MISTICO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-PURPURA</t>
         </is>
       </c>
       <c r="C652" t="n">
@@ -17707,23 +17711,19 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>D051705</t>
+          <t>VB020303-01-03-L-26</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>TERMO DLUCHI 450ML</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-MISTICO</t>
         </is>
       </c>
       <c r="C653" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="D653" t="inlineStr"/>
-      <c r="E653" t="inlineStr">
-        <is>
-          <t>PRODUCTO MANUFACTURADO</t>
-        </is>
-      </c>
+      <c r="E653" t="inlineStr"/>
       <c r="F653" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -17733,16 +17733,16 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-02</t>
+          <t>VB020303-01-02-M-26</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-NEGRO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-MISTICO</t>
         </is>
       </c>
       <c r="C654" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D654" t="inlineStr"/>
       <c r="E654" t="inlineStr"/>
@@ -17755,16 +17755,16 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>VB020203-01-02-M-01</t>
+          <t>VB020101-01-01-S-03</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C655" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D655" t="inlineStr"/>
       <c r="E655" t="inlineStr"/>
@@ -17777,16 +17777,16 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>VB020203-01-03-L-02</t>
+          <t>VB020204-01-02-M-08</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
         </is>
       </c>
       <c r="C656" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D656" t="inlineStr"/>
       <c r="E656" t="inlineStr"/>
@@ -17799,16 +17799,16 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-05</t>
+          <t>VB020202-01-02-M-23</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C657" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D657" t="inlineStr"/>
       <c r="E657" t="inlineStr"/>
@@ -17821,16 +17821,16 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-26</t>
+          <t>VB0105-01-03-L-23</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-MISTICO</t>
+          <t>VB ENTERO TANGA-L-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C658" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D658" t="inlineStr"/>
       <c r="E658" t="inlineStr"/>
@@ -17843,16 +17843,16 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-03</t>
+          <t>VB020203-01-03-L-01</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-BLANCO</t>
         </is>
       </c>
       <c r="C659" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D659" t="inlineStr"/>
       <c r="E659" t="inlineStr"/>
@@ -17865,16 +17865,16 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-08</t>
+          <t>VB0302-01-02-M-02</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
+          <t>PANTALON ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C660" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D660" t="inlineStr"/>
       <c r="E660" t="inlineStr"/>
@@ -17887,16 +17887,16 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-23</t>
+          <t>VB020203-01-02-M-01</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-BLANCO</t>
         </is>
       </c>
       <c r="C661" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D661" t="inlineStr"/>
       <c r="E661" t="inlineStr"/>
@@ -17909,16 +17909,16 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>VB0105-01-03-L-23</t>
+          <t>VB020203-01-03-L-02</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-L-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-NEGRO</t>
         </is>
       </c>
       <c r="C662" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D662" t="inlineStr"/>
       <c r="E662" t="inlineStr"/>
@@ -17931,16 +17931,16 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>VB020203-01-03-L-01</t>
+          <t>VB020204-01-02-M-05</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C663" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr"/>
@@ -17953,16 +17953,16 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-15</t>
+          <t>VB020202-01-03-L-02</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PURPURA</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C664" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D664" t="inlineStr"/>
       <c r="E664" t="inlineStr"/>
@@ -17975,16 +17975,16 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-13</t>
+          <t>VB020202-01-02-M-02</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C665" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D665" t="inlineStr"/>
       <c r="E665" t="inlineStr"/>
@@ -17997,12 +17997,12 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-15</t>
+          <t>VB020203-01-02-M-17</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-ROSADO</t>
         </is>
       </c>
       <c r="C666" t="n">
@@ -18019,12 +18019,12 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-32</t>
+          <t>VB020202-01-01-S-02</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
         </is>
       </c>
       <c r="C667" t="n">
@@ -18041,16 +18041,16 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-23</t>
+          <t>VB020101-01-02-M-15</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PURPURA</t>
         </is>
       </c>
       <c r="C668" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D668" t="inlineStr"/>
       <c r="E668" t="inlineStr"/>
@@ -18063,16 +18063,16 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-23</t>
+          <t>VB020204-01-01-S-13</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
         </is>
       </c>
       <c r="C669" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D669" t="inlineStr"/>
       <c r="E669" t="inlineStr"/>
@@ -18085,12 +18085,12 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>VB0103-01-02-M-32</t>
+          <t>VB0302-01-02-M-01</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
+          <t>PANTALON ALTO-M-BLANCO</t>
         </is>
       </c>
       <c r="C670" t="n">
@@ -18107,16 +18107,16 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-01</t>
+          <t>VB0302-01-01-S-02</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-BLANCO</t>
+          <t>PANTALON ALTO-S-NEGRO</t>
         </is>
       </c>
       <c r="C671" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D671" t="inlineStr"/>
       <c r="E671" t="inlineStr"/>
@@ -18129,16 +18129,16 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-02</t>
+          <t>VB020204-01-03-L-08</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
         </is>
       </c>
       <c r="C672" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D672" t="inlineStr"/>
       <c r="E672" t="inlineStr"/>
@@ -18151,16 +18151,16 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-08</t>
+          <t>VB0103-01-01-S-32</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C673" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D673" t="inlineStr"/>
       <c r="E673" t="inlineStr"/>
@@ -18173,16 +18173,16 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-32</t>
+          <t>VB020204-01-03-L-07</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C674" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D674" t="inlineStr"/>
       <c r="E674" t="inlineStr"/>
@@ -18195,16 +18195,16 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-07</t>
+          <t>VB020105-01-02-M-16</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-ROJO</t>
         </is>
       </c>
       <c r="C675" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D675" t="inlineStr"/>
       <c r="E675" t="inlineStr"/>
@@ -18217,16 +18217,16 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-01</t>
+          <t>VB020105-01-01-S-16</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
         </is>
       </c>
       <c r="C676" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D676" t="inlineStr"/>
       <c r="E676" t="inlineStr"/>
@@ -18239,16 +18239,16 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-08</t>
+          <t>VB020204-01-03-L-15</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
         </is>
       </c>
       <c r="C677" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D677" t="inlineStr"/>
       <c r="E677" t="inlineStr"/>
@@ -18261,16 +18261,16 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-02</t>
+          <t>VB0103-01-03-L-32</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-NEGRO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C678" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D678" t="inlineStr"/>
       <c r="E678" t="inlineStr"/>
@@ -18283,12 +18283,12 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-11</t>
+          <t>VB020202-01-03-L-23</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C679" t="n">
@@ -18305,16 +18305,16 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-16</t>
+          <t>VB020202-01-01-S-23</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-ROJO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C680" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D680" t="inlineStr"/>
       <c r="E680" t="inlineStr"/>
@@ -18327,16 +18327,16 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-16</t>
+          <t>VB0103-01-02-M-32</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C681" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
@@ -18349,16 +18349,16 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-01</t>
+          <t>VB0302-01-03-L-01</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
+          <t>PANTALON ALTO-L-BLANCO</t>
         </is>
       </c>
       <c r="C682" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr"/>
@@ -18371,16 +18371,16 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-02</t>
+          <t>VB020203-01-01-S-01</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
         </is>
       </c>
       <c r="C683" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
@@ -18393,16 +18393,16 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-02</t>
+          <t>VB020203-01-01-S-17</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-ROSADO</t>
         </is>
       </c>
       <c r="C684" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D684" t="inlineStr"/>
       <c r="E684" t="inlineStr"/>
@@ -18415,16 +18415,16 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>VB020203-01-02-M-17</t>
+          <t>VB020105-01-03-L-01</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
         </is>
       </c>
       <c r="C685" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
@@ -18437,16 +18437,16 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-02</t>
+          <t>VB020105-01-01-S-01</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
         </is>
       </c>
       <c r="C686" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D686" t="inlineStr"/>
       <c r="E686" t="inlineStr"/>
@@ -18459,16 +18459,16 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-01</t>
+          <t>VB020101-01-03-L-03</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C687" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D687" t="inlineStr"/>
       <c r="E687" t="inlineStr"/>
@@ -18481,16 +18481,16 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-17</t>
+          <t>VB0105-01-01-S-23</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-ROSADO</t>
+          <t>VB ENTERO TANGA-S-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C688" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D688" t="inlineStr"/>
       <c r="E688" t="inlineStr"/>
@@ -18503,12 +18503,12 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-01</t>
+          <t>VB020204-01-01-S-08</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
         </is>
       </c>
       <c r="C689" t="n">
@@ -18525,16 +18525,16 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-03</t>
+          <t>VB0302-01-03-L-02</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AGUAMARINA</t>
+          <t>PANTALON ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C690" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D690" t="inlineStr"/>
       <c r="E690" t="inlineStr"/>
@@ -18547,16 +18547,16 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>VB0105-01-01-S-23</t>
+          <t>VB020204-01-01-S-11</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-S-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C691" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D691" t="inlineStr"/>
       <c r="E691" t="inlineStr"/>
@@ -18591,16 +18591,16 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-05</t>
+          <t>VB020103-02-03-L-03</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C693" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D693" t="inlineStr"/>
       <c r="E693" t="inlineStr"/>
@@ -18613,16 +18613,16 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-26</t>
+          <t>VB0302-01-01-S-01</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
+          <t>PANTALON ALTO-S-BLANCO</t>
         </is>
       </c>
       <c r="C694" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D694" t="inlineStr"/>
       <c r="E694" t="inlineStr"/>
@@ -18635,16 +18635,16 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-01</t>
+          <t>VB0105-01-02-M-23</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-BLANCO</t>
+          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C695" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D695" t="inlineStr"/>
       <c r="E695" t="inlineStr"/>
@@ -18657,16 +18657,16 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>VB0105-01-02-M-23</t>
+          <t>VB020204-01-03-L-11</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C696" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D696" t="inlineStr"/>
       <c r="E696" t="inlineStr"/>
@@ -18679,12 +18679,12 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-11</t>
+          <t>VB020204-01-01-S-05</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C697" t="n">
@@ -18701,12 +18701,12 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-03</t>
+          <t>VB020303-01-01-S-26</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
         </is>
       </c>
       <c r="C698" t="n">
@@ -18811,16 +18811,16 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-09</t>
+          <t>VB0104-01-01-S-09</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-BEIGE</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-BEIGE</t>
         </is>
       </c>
       <c r="C703" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr"/>
@@ -18833,16 +18833,16 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-09</t>
+          <t>VB0104-01-02-M-09</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-BEIGE</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-BEIGE</t>
         </is>
       </c>
       <c r="C704" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D704" t="inlineStr"/>
       <c r="E704" t="inlineStr"/>
@@ -18855,16 +18855,16 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-19</t>
+          <t>VB0104-01-03-L-09</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-BEIGE</t>
         </is>
       </c>
       <c r="C705" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr"/>
@@ -18877,16 +18877,16 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-37</t>
+          <t>VB020103-05-01-S-36</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-AZUL BEBE-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C706" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D706" t="inlineStr"/>
       <c r="E706" t="inlineStr"/>
@@ -18899,12 +18899,12 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>VB0304-01-02-M-02</t>
+          <t>VB020103-05-03-L-36</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C707" t="n">
@@ -18921,12 +18921,12 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>VB0304-01-03-L-02</t>
+          <t>VB020103-05-01-S-37</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C708" t="n">
@@ -18943,16 +18943,16 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>VB0104-01-01-S-09</t>
+          <t>VB020103-05-03-L-37</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C709" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D709" t="inlineStr"/>
       <c r="E709" t="inlineStr"/>
@@ -18965,16 +18965,16 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>VB0104-01-02-M-09</t>
+          <t>VB0304-01-02-M-02</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-BEIGE</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-M-NEGRO</t>
         </is>
       </c>
       <c r="C710" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D710" t="inlineStr"/>
       <c r="E710" t="inlineStr"/>
@@ -18987,16 +18987,16 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>VB0104-01-03-L-09</t>
+          <t>VB0304-01-03-L-02</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-BEIGE</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-L-NEGRO</t>
         </is>
       </c>
       <c r="C711" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D711" t="inlineStr"/>
       <c r="E711" t="inlineStr"/>
@@ -19053,16 +19053,16 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>VB0305-01-04-U-02</t>
+          <t>VB020103-05-01-S-35</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-NEGRO-BLANCO HUESO</t>
         </is>
       </c>
       <c r="C714" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D714" t="inlineStr"/>
       <c r="E714" t="inlineStr"/>
@@ -19075,12 +19075,12 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-34</t>
+          <t>VB020103-05-02-M-36</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-FAUNA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C715" t="n">
@@ -19097,16 +19097,16 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-35</t>
+          <t>VB0305-01-04-U-09</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-NEGRO-BLANCO HUESO</t>
+          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-BEIGE</t>
         </is>
       </c>
       <c r="C716" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr"/>
@@ -19119,16 +19119,16 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>VB020103-05-02-M-36</t>
+          <t>VB0305-01-04-U-02</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-VIOLETA-CORAL</t>
+          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-NEGRO</t>
         </is>
       </c>
       <c r="C717" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D717" t="inlineStr"/>
       <c r="E717" t="inlineStr"/>
@@ -19141,16 +19141,16 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-36</t>
+          <t>VB020303-01-01-S-34</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-FAUNA</t>
         </is>
       </c>
       <c r="C718" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D718" t="inlineStr"/>
       <c r="E718" t="inlineStr"/>
@@ -19163,16 +19163,16 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-36</t>
+          <t>VB020101-01-04-U-01</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-BLANCO</t>
         </is>
       </c>
       <c r="C719" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D719" t="inlineStr"/>
       <c r="E719" t="inlineStr"/>
@@ -19185,16 +19185,16 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-37</t>
+          <t>VB020101-01-04-U-14</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-AZUL BEBE-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C720" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D720" t="inlineStr"/>
       <c r="E720" t="inlineStr"/>
@@ -19207,16 +19207,16 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>VB0305-01-04-U-09</t>
+          <t>VB020104-01-01-S-17</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-ROSADO</t>
         </is>
       </c>
       <c r="C721" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D721" t="inlineStr"/>
       <c r="E721" t="inlineStr"/>
@@ -19229,16 +19229,16 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-06</t>
+          <t>VB020104-01-03-L-03</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-AZUL CELESTE</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C722" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D722" t="inlineStr"/>
       <c r="E722" t="inlineStr"/>
@@ -19251,16 +19251,16 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-03</t>
+          <t>VB020101-01-04-U-17</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-ROSADO</t>
         </is>
       </c>
       <c r="C723" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="inlineStr"/>
@@ -19273,16 +19273,16 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-03</t>
+          <t>VB020101-01-04-U-06</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C724" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D724" t="inlineStr"/>
       <c r="E724" t="inlineStr"/>
@@ -19295,16 +19295,16 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>VB0301-01-04-U-02</t>
+          <t>VB020104-01-01-S-03</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>FALDA GAIA MACRAME-U-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C725" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D725" t="inlineStr"/>
       <c r="E725" t="inlineStr"/>
@@ -19317,16 +19317,16 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>VB020205-03-02-M-28</t>
+          <t>VB020101-01-04-U-03</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-AGUAMARINA</t>
         </is>
       </c>
       <c r="C726" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr"/>
@@ -19339,16 +19339,16 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-19</t>
+          <t>VB0301-01-04-U-02</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-ANIMAL PRINT CAFÉ</t>
+          <t>FALDA GAIA MACRAME-U-NEGRO</t>
         </is>
       </c>
       <c r="C727" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr"/>
@@ -19361,16 +19361,16 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-28</t>
+          <t>VB020205-03-02-M-28</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-PITON BEIGE</t>
         </is>
       </c>
       <c r="C728" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr"/>
@@ -19383,16 +19383,16 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-28</t>
+          <t>VB020303-01-03-L-19</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-PITON BEIGE</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C729" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D729" t="inlineStr"/>
       <c r="E729" t="inlineStr"/>
@@ -19405,16 +19405,16 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-19</t>
+          <t>VB020205-03-01-S-28</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-PITON BEIGE</t>
         </is>
       </c>
       <c r="C730" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D730" t="inlineStr"/>
       <c r="E730" t="inlineStr"/>
@@ -19427,12 +19427,12 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-28</t>
+          <t>VB020103-04-02-M-09</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-BEIGE</t>
         </is>
       </c>
       <c r="C731" t="n">
@@ -19449,12 +19449,12 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-19</t>
+          <t>VB020103-04-03-L-09</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-BEIGE</t>
         </is>
       </c>
       <c r="C732" t="n">
@@ -19471,16 +19471,16 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>VB020205-03-03-L-28</t>
+          <t>VB020103-04-01-S-19</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C733" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D733" t="inlineStr"/>
       <c r="E733" t="inlineStr"/>
@@ -19493,12 +19493,12 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-19</t>
+          <t>VB020103-04-02-M-19</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C734" t="n">
@@ -19515,12 +19515,12 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>VB020205-03-01-S-28</t>
+          <t>VB020103-04-01-S-28</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-PITON BEIGE</t>
         </is>
       </c>
       <c r="C735" t="n">
@@ -19537,12 +19537,12 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-02</t>
+          <t>VB020103-04-02-M-28</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-PITON BEIGE</t>
         </is>
       </c>
       <c r="C736" t="n">
@@ -19559,16 +19559,16 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-01</t>
+          <t>VB020303-01-01-S-19</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-BLANCO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C737" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D737" t="inlineStr"/>
       <c r="E737" t="inlineStr"/>
@@ -19581,16 +19581,16 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-03</t>
+          <t>VB020103-04-03-L-28</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-PITON BEIGE</t>
         </is>
       </c>
       <c r="C738" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D738" t="inlineStr"/>
       <c r="E738" t="inlineStr"/>
@@ -19603,16 +19603,16 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-03</t>
+          <t>VB020303-01-02-M-19</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C739" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D739" t="inlineStr"/>
       <c r="E739" t="inlineStr"/>
@@ -19625,16 +19625,16 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-02</t>
+          <t>VB020205-03-03-L-28</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-PITON BEIGE</t>
         </is>
       </c>
       <c r="C740" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D740" t="inlineStr"/>
       <c r="E740" t="inlineStr"/>
@@ -19647,12 +19647,12 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-01</t>
+          <t>VB0306-01-01-S-02</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-BLANCO</t>
+          <t>TOP BÁSICO LUISA-S-NEGRO</t>
         </is>
       </c>
       <c r="C741" t="n">
@@ -19669,12 +19669,12 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-03</t>
+          <t>VB0306-01-03-L-01</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-AGUAMARINA</t>
+          <t>TOP BÁSICO LUISA-L-BLANCO</t>
         </is>
       </c>
       <c r="C742" t="n">
@@ -19691,12 +19691,12 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-01</t>
+          <t>VB0306-01-02-M-03</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-BLANCO</t>
+          <t>TOP BÁSICO LUISA-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C743" t="n">
@@ -19713,16 +19713,16 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-11</t>
+          <t>VB0306-01-01-S-03</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-FUCSIA NEON</t>
+          <t>TOP BÁSICO LUISA-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C744" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D744" t="inlineStr"/>
       <c r="E744" t="inlineStr"/>
@@ -19735,16 +19735,16 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-13</t>
+          <t>VB0306-01-03-L-02</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
+          <t>TOP BÁSICO LUISA-L-NEGRO</t>
         </is>
       </c>
       <c r="C745" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D745" t="inlineStr"/>
       <c r="E745" t="inlineStr"/>
@@ -19757,16 +19757,16 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-15</t>
+          <t>VB0306-01-02-M-02</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PURPURA</t>
+          <t>TOP BÁSICO LUISA-M-NEGRO</t>
         </is>
       </c>
       <c r="C746" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D746" t="inlineStr"/>
       <c r="E746" t="inlineStr"/>
@@ -19779,16 +19779,16 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-07</t>
+          <t>VB0306-01-02-M-01</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL CIAN</t>
+          <t>TOP BÁSICO LUISA-M-BLANCO</t>
         </is>
       </c>
       <c r="C747" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D747" t="inlineStr"/>
       <c r="E747" t="inlineStr"/>
@@ -19801,16 +19801,16 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-15</t>
+          <t>VB0306-01-03-L-03</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-PURPURA</t>
+          <t>TOP BÁSICO LUISA-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C748" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D748" t="inlineStr"/>
       <c r="E748" t="inlineStr"/>
@@ -19823,16 +19823,16 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>VB020101-03-01-S-02</t>
+          <t>VB0306-01-01-S-01</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-S-NEGRO</t>
+          <t>TOP BÁSICO LUISA-S-BLANCO</t>
         </is>
       </c>
       <c r="C749" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D749" t="inlineStr"/>
       <c r="E749" t="inlineStr"/>
@@ -19845,16 +19845,16 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>VB020101-03-03-L-01</t>
+          <t>VB020204-01-02-M-11</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-L-BLANCO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C750" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D750" t="inlineStr"/>
       <c r="E750" t="inlineStr"/>
@@ -19867,16 +19867,16 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>VB020101-03-01-S-01</t>
+          <t>VB020204-01-02-M-13</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-S-BLANCO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
         </is>
       </c>
       <c r="C751" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D751" t="inlineStr"/>
       <c r="E751" t="inlineStr"/>
@@ -19889,12 +19889,12 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-33</t>
+          <t>VB020101-01-03-L-15</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-TIE DYE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PURPURA</t>
         </is>
       </c>
       <c r="C752" t="n">
@@ -19911,16 +19911,16 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-02</t>
+          <t>VB020204-01-01-S-07</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL CIAN</t>
         </is>
       </c>
       <c r="C753" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D753" t="inlineStr"/>
       <c r="E753" t="inlineStr"/>
@@ -19933,16 +19933,16 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-02</t>
+          <t>VB020204-01-02-M-15</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-PURPURA</t>
         </is>
       </c>
       <c r="C754" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D754" t="inlineStr"/>
       <c r="E754" t="inlineStr"/>
@@ -19955,16 +19955,16 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>VB0105-02-03-L-17</t>
+          <t>VB020101-03-01-S-02</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-S-NEGRO</t>
         </is>
       </c>
       <c r="C755" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D755" t="inlineStr"/>
       <c r="E755" t="inlineStr"/>
@@ -19977,12 +19977,12 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-17</t>
+          <t>VB020101-03-03-L-01</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-L-BLANCO</t>
         </is>
       </c>
       <c r="C756" t="n">
@@ -19999,12 +19999,12 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-17</t>
+          <t>VB020101-03-01-S-01</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ENCAJE-S-BLANCO</t>
         </is>
       </c>
       <c r="C757" t="n">
@@ -20021,12 +20021,12 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>VB0105-02-03-L-18</t>
+          <t>VB0105-02-01-S-33</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-VERDE MENTA</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-TIE DYE</t>
         </is>
       </c>
       <c r="C758" t="n">
@@ -20043,16 +20043,16 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>VB0105-02-01-S-18</t>
+          <t>VB0105-02-02-M-02</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-VERDE MENTA</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-NEGRO</t>
         </is>
       </c>
       <c r="C759" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D759" t="inlineStr"/>
       <c r="E759" t="inlineStr"/>
@@ -20065,12 +20065,12 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>VB0105-02-02-M-18</t>
+          <t>VB0105-02-01-S-02</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-VERDE MENTA</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-NEGRO</t>
         </is>
       </c>
       <c r="C760" t="n">
@@ -20087,16 +20087,16 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-09</t>
+          <t>VB0105-02-03-L-17</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-BEIGE</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-ROSADO</t>
         </is>
       </c>
       <c r="C761" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D761" t="inlineStr"/>
       <c r="E761" t="inlineStr"/>
@@ -20109,16 +20109,16 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-09</t>
+          <t>VB0105-02-02-M-17</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-BEIGE</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-ROSADO</t>
         </is>
       </c>
       <c r="C762" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D762" t="inlineStr"/>
       <c r="E762" t="inlineStr"/>
@@ -20131,16 +20131,16 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>VB0303-01-02-M-01</t>
+          <t>VB0105-02-01-S-17</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>SHORT ALTO-M-BLANCO</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-ROSADO</t>
         </is>
       </c>
       <c r="C763" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D763" t="inlineStr"/>
       <c r="E763" t="inlineStr"/>
@@ -20153,16 +20153,16 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>VB0303-01-01-S-02</t>
+          <t>VB0105-02-03-L-18</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>SHORT ALTO-S-NEGRO</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-L-VERDE MENTA</t>
         </is>
       </c>
       <c r="C764" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D764" t="inlineStr"/>
       <c r="E764" t="inlineStr"/>
@@ -20175,12 +20175,12 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>VB0303-01-03-L-09</t>
+          <t>VB0105-02-01-S-18</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>SHORT ALTO-L-BEIGE</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-S-VERDE MENTA</t>
         </is>
       </c>
       <c r="C765" t="n">
@@ -20197,16 +20197,16 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>VB0303-01-02-M-09</t>
+          <t>VB0105-02-02-M-18</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>SHORT ALTO-M-BEIGE</t>
+          <t>VB ENTERO TANGA ESCOTE DELANTERO-M-VERDE MENTA</t>
         </is>
       </c>
       <c r="C766" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D766" t="inlineStr"/>
       <c r="E766" t="inlineStr"/>
@@ -20219,16 +20219,16 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>VB0303-01-01-S-09</t>
+          <t>VB0302-01-02-M-09</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>SHORT ALTO-S-BEIGE</t>
+          <t>PANTALON ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C767" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D767" t="inlineStr"/>
       <c r="E767" t="inlineStr"/>
@@ -20241,12 +20241,12 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-09</t>
+          <t>VB0302-01-01-S-09</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-BEIGE</t>
+          <t>PANTALON ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C768" t="n">
@@ -20263,16 +20263,16 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-02</t>
+          <t>VB0303-01-02-M-01</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-NEGRO</t>
+          <t>SHORT ALTO-M-BLANCO</t>
         </is>
       </c>
       <c r="C769" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D769" t="inlineStr"/>
       <c r="E769" t="inlineStr"/>
@@ -20285,16 +20285,16 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>VB020101-02-03-L-18</t>
+          <t>VB0303-01-01-S-02</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-VERDE MENTA</t>
+          <t>SHORT ALTO-S-NEGRO</t>
         </is>
       </c>
       <c r="C770" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D770" t="inlineStr"/>
       <c r="E770" t="inlineStr"/>
@@ -20307,16 +20307,16 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>VB020101-02-01-S-18</t>
+          <t>VB0303-01-03-L-09</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-S-VERDE MENTA</t>
+          <t>SHORT ALTO-L-BEIGE</t>
         </is>
       </c>
       <c r="C771" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D771" t="inlineStr"/>
       <c r="E771" t="inlineStr"/>
@@ -20329,16 +20329,16 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-06</t>
+          <t>VB0303-01-02-M-09</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AZUL CELESTE</t>
+          <t>SHORT ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C772" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D772" t="inlineStr"/>
       <c r="E772" t="inlineStr"/>
@@ -20351,16 +20351,16 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>VB020104-01-02-M-06</t>
+          <t>VB0303-01-01-S-09</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-M-AZUL CELESTE</t>
+          <t>SHORT ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C773" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D773" t="inlineStr"/>
       <c r="E773" t="inlineStr"/>
@@ -20373,12 +20373,12 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>VB020101-02-03-L-01</t>
+          <t>VB0302-01-03-L-09</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-BLANCO</t>
+          <t>PANTALON ALTO-L-BEIGE</t>
         </is>
       </c>
       <c r="C774" t="n">
@@ -20395,12 +20395,12 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>VB020101-02-01-S-01</t>
+          <t>VB020203-01-01-S-02</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-S-BLANCO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-NEGRO</t>
         </is>
       </c>
       <c r="C775" t="n">
@@ -20417,16 +20417,16 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>VB020101-02-03-L-17</t>
+          <t>VB020101-02-03-L-18</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-VERDE MENTA</t>
         </is>
       </c>
       <c r="C776" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D776" t="inlineStr"/>
       <c r="E776" t="inlineStr"/>
@@ -20439,16 +20439,16 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>VB020101-02-02-M-17</t>
+          <t>VB020101-02-01-S-18</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-M-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-S-VERDE MENTA</t>
         </is>
       </c>
       <c r="C777" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D777" t="inlineStr"/>
       <c r="E777" t="inlineStr"/>
@@ -20461,16 +20461,16 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>VB0301-01-04-U-09</t>
+          <t>VB020104-01-03-L-06</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>FALDA GAIA MACRAME-U-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C778" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D778" t="inlineStr"/>
       <c r="E778" t="inlineStr"/>
@@ -20483,16 +20483,16 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-06</t>
+          <t>VB020104-01-02-M-06</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AZUL CELESTE</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-M-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C779" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D779" t="inlineStr"/>
       <c r="E779" t="inlineStr"/>
@@ -20505,12 +20505,12 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-17</t>
+          <t>VB020101-02-03-L-01</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-BLANCO</t>
         </is>
       </c>
       <c r="C780" t="n">
@@ -20527,16 +20527,16 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-01</t>
+          <t>VB020101-02-01-S-01</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-S-BLANCO</t>
         </is>
       </c>
       <c r="C781" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D781" t="inlineStr"/>
       <c r="E781" t="inlineStr"/>
@@ -20549,16 +20549,16 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-14</t>
+          <t>VB020101-02-03-L-17</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-L-ROSADO</t>
         </is>
       </c>
       <c r="C782" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D782" t="inlineStr"/>
       <c r="E782" t="inlineStr"/>
@@ -20571,16 +20571,16 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-17</t>
+          <t>VB020101-02-02-M-17</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR ARO-M-ROSADO</t>
         </is>
       </c>
       <c r="C783" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D783" t="inlineStr"/>
       <c r="E783" t="inlineStr"/>
@@ -20593,12 +20593,12 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-03</t>
+          <t>VB0301-01-04-U-09</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AGUAMARINA</t>
+          <t>FALDA GAIA MACRAME-U-BEIGE</t>
         </is>
       </c>
       <c r="C784" t="n">
@@ -20615,16 +20615,16 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>VB020101-01-04-U-17</t>
+          <t>VB020104-01-01-S-06</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-U-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AZUL CELESTE</t>
         </is>
       </c>
       <c r="C785" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D785" t="inlineStr"/>
       <c r="E785" t="inlineStr"/>
@@ -20637,16 +20637,16 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-02</t>
+          <t>VB020104-01-03-L-17</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-ROSADO</t>
         </is>
       </c>
       <c r="C786" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D786" t="inlineStr"/>
       <c r="E786" t="inlineStr"/>
@@ -20659,19 +20659,23 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-14</t>
+          <t>KITN0103</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-PALO DE ROSA</t>
+          <t>KIT FULL CARE</t>
         </is>
       </c>
       <c r="C787" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D787" t="inlineStr"/>
-      <c r="E787" t="inlineStr"/>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>PRODUCTO MANUFACTURADO</t>
+        </is>
+      </c>
       <c r="F787" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -20681,12 +20685,12 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-14</t>
+          <t>VB0306-01-03-L-16</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
+          <t>TOP BÁSICO LUISA-L-ROJO</t>
         </is>
       </c>
       <c r="C788" t="n">
@@ -20703,12 +20707,12 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-16</t>
+          <t>VB0306-01-01-S-14</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-ROJO</t>
+          <t>TOP BÁSICO LUISA-S-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -20725,12 +20729,12 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-16</t>
+          <t>VB0306-01-02-M-14</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-ROJO</t>
+          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C790" t="n">
@@ -20747,12 +20751,12 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-14</t>
+          <t>VB0306-01-02-M-16</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-PALO DE ROSA</t>
+          <t>TOP BÁSICO LUISA-M-ROJO</t>
         </is>
       </c>
       <c r="C791" t="n">
@@ -20769,12 +20773,12 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-16</t>
+          <t>VB0306-01-03-L-14</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-ROJO</t>
+          <t>TOP BÁSICO LUISA-L-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C792" t="n">
@@ -20791,23 +20795,19 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>KITN0103</t>
+          <t>VB0306-01-01-S-16</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>KIT FULL CARE</t>
+          <t>TOP BÁSICO LUISA-S-ROJO</t>
         </is>
       </c>
       <c r="C793" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D793" t="inlineStr"/>
-      <c r="E793" t="inlineStr">
-        <is>
-          <t>PRODUCTO MANUFACTURADO</t>
-        </is>
-      </c>
+      <c r="E793" t="inlineStr"/>
       <c r="F793" t="inlineStr">
         <is>
           <t>Almacenamiento PT</t>
@@ -21103,16 +21103,16 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-16</t>
+          <t>VB020101-01-02-M-16</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ROJO</t>
         </is>
       </c>
       <c r="C807" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D807" t="inlineStr"/>
       <c r="E807" t="inlineStr"/>
@@ -21125,16 +21125,16 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-17</t>
+          <t>VB020101-01-01-S-16</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-ROJO</t>
         </is>
       </c>
       <c r="C808" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D808" t="inlineStr"/>
       <c r="E808" t="inlineStr"/>
@@ -21147,16 +21147,16 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-17</t>
+          <t>VB020101-01-03-L-17</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-ROSADO</t>
         </is>
       </c>
       <c r="C809" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D809" t="inlineStr"/>
       <c r="E809" t="inlineStr"/>
@@ -21169,16 +21169,16 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-02</t>
+          <t>VB020101-01-02-M-17</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ROSADO</t>
         </is>
       </c>
       <c r="C810" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D810" t="inlineStr"/>
       <c r="E810" t="inlineStr"/>
@@ -21191,16 +21191,16 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-16</t>
+          <t>VB020104-01-01-S-02</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-NEGRO</t>
         </is>
       </c>
       <c r="C811" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D811" t="inlineStr"/>
       <c r="E811" t="inlineStr"/>
@@ -24231,16 +24231,16 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>VB020203-01-03-L-01</t>
+          <t>VB020202-01-01-S-02</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
         </is>
       </c>
       <c r="C938" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D938" t="inlineStr"/>
       <c r="E938" t="inlineStr"/>
@@ -24253,16 +24253,16 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>VB0105-01-03-L-23</t>
+          <t>VB020202-01-03-L-09</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-L-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-BEIGE</t>
         </is>
       </c>
       <c r="C939" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D939" t="inlineStr"/>
       <c r="E939" t="inlineStr"/>
@@ -24275,16 +24275,16 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-23</t>
+          <t>VB020202-01-02-M-09</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C940" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D940" t="inlineStr"/>
       <c r="E940" t="inlineStr"/>
@@ -24297,16 +24297,16 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-08</t>
+          <t>VB020202-01-02-M-02</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C941" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D941" t="inlineStr"/>
       <c r="E941" t="inlineStr"/>
@@ -24319,16 +24319,16 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-26</t>
+          <t>VB020202-01-03-L-02</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-MISTICO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C942" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="D942" t="inlineStr"/>
       <c r="E942" t="inlineStr"/>
@@ -24517,16 +24517,16 @@
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-01</t>
+          <t>VB020203-01-03-L-01</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-BLANCO</t>
         </is>
       </c>
       <c r="C951" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D951" t="inlineStr"/>
       <c r="E951" t="inlineStr"/>
@@ -24539,16 +24539,16 @@
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-01</t>
+          <t>VB0105-01-03-L-23</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-BLANCO</t>
+          <t>VB ENTERO TANGA-L-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C952" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D952" t="inlineStr"/>
       <c r="E952" t="inlineStr"/>
@@ -24561,12 +24561,12 @@
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-09</t>
+          <t>VB020202-01-02-M-23</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-BEIGE</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C953" t="n">
@@ -24583,16 +24583,16 @@
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-01</t>
+          <t>VB020204-01-02-M-08</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
         </is>
       </c>
       <c r="C954" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D954" t="inlineStr"/>
       <c r="E954" t="inlineStr"/>
@@ -24605,16 +24605,16 @@
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-02</t>
+          <t>VB020303-01-02-M-26</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-MISTICO</t>
         </is>
       </c>
       <c r="C955" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D955" t="inlineStr"/>
       <c r="E955" t="inlineStr"/>
@@ -24627,16 +24627,16 @@
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-09</t>
+          <t>VB020303-01-03-L-26</t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-BEIGE</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-MISTICO</t>
         </is>
       </c>
       <c r="C956" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D956" t="inlineStr"/>
       <c r="E956" t="inlineStr"/>
@@ -24649,16 +24649,16 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-09</t>
+          <t>VB020204-01-01-S-15</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-BEIGE</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-PURPURA</t>
         </is>
       </c>
       <c r="C957" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D957" t="inlineStr"/>
       <c r="E957" t="inlineStr"/>
@@ -24671,16 +24671,16 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-02</t>
+          <t>VB020105-01-01-S-01</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
         </is>
       </c>
       <c r="C958" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D958" t="inlineStr"/>
       <c r="E958" t="inlineStr"/>
@@ -24693,16 +24693,16 @@
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-02</t>
+          <t>VB020105-01-03-L-01</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
         </is>
       </c>
       <c r="C959" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D959" t="inlineStr"/>
       <c r="E959" t="inlineStr"/>
@@ -24715,16 +24715,16 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-01</t>
+          <t>VB020105-01-02-M-01</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-BLANCO</t>
         </is>
       </c>
       <c r="C960" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D960" t="inlineStr"/>
       <c r="E960" t="inlineStr"/>
@@ -24737,16 +24737,16 @@
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-16</t>
+          <t>VB020202-01-01-S-09</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-ROJO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C961" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D961" t="inlineStr"/>
       <c r="E961" t="inlineStr"/>
@@ -24759,16 +24759,16 @@
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-16</t>
+          <t>VB020203-01-01-S-01</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
         </is>
       </c>
       <c r="C962" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D962" t="inlineStr"/>
       <c r="E962" t="inlineStr"/>
@@ -24781,16 +24781,16 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-16</t>
+          <t>VB020105-01-03-L-16</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-ROJO</t>
         </is>
       </c>
       <c r="C963" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D963" t="inlineStr"/>
       <c r="E963" t="inlineStr"/>
@@ -24803,16 +24803,16 @@
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-11</t>
+          <t>VB0302-01-03-L-01</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
+          <t>PANTALON ALTO-L-BLANCO</t>
         </is>
       </c>
       <c r="C964" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D964" t="inlineStr"/>
       <c r="E964" t="inlineStr"/>
@@ -24825,16 +24825,16 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-02</t>
+          <t>VB020103-02-03-L-02</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-NEGRO</t>
         </is>
       </c>
       <c r="C965" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D965" t="inlineStr"/>
       <c r="E965" t="inlineStr"/>
@@ -24847,16 +24847,16 @@
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-08</t>
+          <t>VB020204-01-02-M-07</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AZUL CIAN</t>
         </is>
       </c>
       <c r="C966" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D966" t="inlineStr"/>
       <c r="E966" t="inlineStr"/>
@@ -24869,16 +24869,16 @@
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-01</t>
+          <t>VB0103-01-02-M-32</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-BLANCO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C967" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D967" t="inlineStr"/>
       <c r="E967" t="inlineStr"/>
@@ -24891,16 +24891,16 @@
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-02</t>
+          <t>VB020202-01-01-S-23</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C968" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D968" t="inlineStr"/>
       <c r="E968" t="inlineStr"/>
@@ -24913,16 +24913,16 @@
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-07</t>
+          <t>VB020202-01-03-L-23</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C969" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D969" t="inlineStr"/>
       <c r="E969" t="inlineStr"/>
@@ -24935,16 +24935,16 @@
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-07</t>
+          <t>VB0103-01-03-L-32</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C970" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D970" t="inlineStr"/>
       <c r="E970" t="inlineStr"/>
@@ -24957,16 +24957,16 @@
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-01</t>
+          <t>VB020204-01-03-L-15</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
         </is>
       </c>
       <c r="C971" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D971" t="inlineStr"/>
       <c r="E971" t="inlineStr"/>
@@ -24979,16 +24979,16 @@
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-32</t>
+          <t>VB020105-01-01-S-16</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
         </is>
       </c>
       <c r="C972" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D972" t="inlineStr"/>
       <c r="E972" t="inlineStr"/>
@@ -25001,16 +25001,16 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-08</t>
+          <t>VB020105-01-02-M-16</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-ROJO</t>
         </is>
       </c>
       <c r="C973" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D973" t="inlineStr"/>
       <c r="E973" t="inlineStr"/>
@@ -25023,16 +25023,16 @@
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-01</t>
+          <t>VB020204-01-03-L-07</t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-BLANCO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C974" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D974" t="inlineStr"/>
       <c r="E974" t="inlineStr"/>
@@ -25045,16 +25045,16 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>VB0103-01-02-M-32</t>
+          <t>VB020103-02-03-L-01</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-BLANCO</t>
         </is>
       </c>
       <c r="C975" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D975" t="inlineStr"/>
       <c r="E975" t="inlineStr"/>
@@ -25067,16 +25067,16 @@
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-23</t>
+          <t>VB0103-01-01-S-32</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C976" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D976" t="inlineStr"/>
       <c r="E976" t="inlineStr"/>
@@ -25089,16 +25089,16 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-23</t>
+          <t>VB020204-01-03-L-08</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
         </is>
       </c>
       <c r="C977" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D977" t="inlineStr"/>
       <c r="E977" t="inlineStr"/>
@@ -25111,16 +25111,16 @@
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-32</t>
+          <t>VB0302-01-02-M-01</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
+          <t>PANTALON ALTO-M-BLANCO</t>
         </is>
       </c>
       <c r="C978" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D978" t="inlineStr"/>
       <c r="E978" t="inlineStr"/>
@@ -25133,16 +25133,16 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-15</t>
+          <t>VB020204-01-01-S-13</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
         </is>
       </c>
       <c r="C979" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D979" t="inlineStr"/>
       <c r="E979" t="inlineStr"/>
@@ -25155,16 +25155,16 @@
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-13</t>
+          <t>VB020103-02-01-S-03</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C980" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D980" t="inlineStr"/>
       <c r="E980" t="inlineStr"/>
@@ -25177,16 +25177,16 @@
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-26</t>
+          <t>VB020103-02-01-S-02</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-NEGRO</t>
         </is>
       </c>
       <c r="C981" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D981" t="inlineStr"/>
       <c r="E981" t="inlineStr"/>
@@ -25199,16 +25199,16 @@
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-15</t>
+          <t>VB020103-02-02-M-03</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C982" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D982" t="inlineStr"/>
       <c r="E982" t="inlineStr"/>
@@ -25221,16 +25221,16 @@
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-03</t>
+          <t>VB020303-01-01-S-26</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
         </is>
       </c>
       <c r="C983" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D983" t="inlineStr"/>
       <c r="E983" t="inlineStr"/>
@@ -25243,16 +25243,16 @@
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-02</t>
+          <t>VB020204-01-01-S-05</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C984" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D984" t="inlineStr"/>
       <c r="E984" t="inlineStr"/>
@@ -25265,16 +25265,16 @@
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>VB020103-02-02-M-03</t>
+          <t>VB020103-02-02-M-17</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-ROSADO</t>
         </is>
       </c>
       <c r="C985" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D985" t="inlineStr"/>
       <c r="E985" t="inlineStr"/>
@@ -25287,16 +25287,16 @@
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-03</t>
+          <t>VB020204-01-03-L-11</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C986" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D986" t="inlineStr"/>
       <c r="E986" t="inlineStr"/>
@@ -25309,16 +25309,16 @@
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-11</t>
+          <t>VB0105-01-02-M-23</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
+          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C987" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D987" t="inlineStr"/>
       <c r="E987" t="inlineStr"/>
@@ -25331,16 +25331,16 @@
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>VB0105-01-02-M-23</t>
+          <t>VB0302-01-01-S-01</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
+          <t>PANTALON ALTO-S-BLANCO</t>
         </is>
       </c>
       <c r="C988" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D988" t="inlineStr"/>
       <c r="E988" t="inlineStr"/>
@@ -25353,16 +25353,16 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-01</t>
+          <t>VB020103-02-01-S-17</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-ROSADO</t>
         </is>
       </c>
       <c r="C989" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D989" t="inlineStr"/>
       <c r="E989" t="inlineStr"/>
@@ -25375,16 +25375,16 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-17</t>
+          <t>VB020103-02-03-L-03</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C990" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D990" t="inlineStr"/>
       <c r="E990" t="inlineStr"/>
@@ -25397,16 +25397,16 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-26</t>
+          <t>VB020103-02-03-L-17</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-ROSADO</t>
         </is>
       </c>
       <c r="C991" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D991" t="inlineStr"/>
       <c r="E991" t="inlineStr"/>
@@ -25419,16 +25419,16 @@
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-05</t>
+          <t>VB020204-01-01-S-11</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C992" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D992" t="inlineStr"/>
       <c r="E992" t="inlineStr"/>
@@ -25441,16 +25441,16 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>VB020103-02-02-M-17</t>
+          <t>VB0302-01-03-L-02</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-ROSADO</t>
+          <t>PANTALON ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C993" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D993" t="inlineStr"/>
       <c r="E993" t="inlineStr"/>
@@ -25463,16 +25463,16 @@
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-17</t>
+          <t>VB020204-01-01-S-08</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-ROSADO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
         </is>
       </c>
       <c r="C994" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D994" t="inlineStr"/>
       <c r="E994" t="inlineStr"/>
@@ -25617,16 +25617,16 @@
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-19</t>
+          <t>VB020103-04-01-S-19</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1001" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D1001" t="inlineStr"/>
       <c r="E1001" t="inlineStr"/>
@@ -25639,16 +25639,16 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-28</t>
+          <t>VB020103-04-03-L-09</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-BEIGE</t>
         </is>
       </c>
       <c r="C1002" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D1002" t="inlineStr"/>
       <c r="E1002" t="inlineStr"/>
@@ -25661,16 +25661,16 @@
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-19</t>
+          <t>VB020103-04-02-M-09</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-BEIGE</t>
         </is>
       </c>
       <c r="C1003" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D1003" t="inlineStr"/>
       <c r="E1003" t="inlineStr"/>
@@ -25683,16 +25683,16 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>VB020205-03-01-S-28</t>
+          <t>VB020205-03-03-L-28</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-PITON BEIGE</t>
         </is>
       </c>
       <c r="C1004" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D1004" t="inlineStr"/>
       <c r="E1004" t="inlineStr"/>
@@ -25705,16 +25705,16 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-19</t>
+          <t>VB020303-01-02-M-19</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1005" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D1005" t="inlineStr"/>
       <c r="E1005" t="inlineStr"/>
@@ -25727,16 +25727,16 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>VB020205-03-03-L-28</t>
+          <t>VB020103-04-03-L-28</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-PITON BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-PITON BEIGE</t>
         </is>
       </c>
       <c r="C1006" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1006" t="inlineStr"/>
       <c r="E1006" t="inlineStr"/>
@@ -25749,16 +25749,16 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>VB020205-03-02-M-28</t>
+          <t>VB020303-01-01-S-19</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-PITON BEIGE</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1007" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D1007" t="inlineStr"/>
       <c r="E1007" t="inlineStr"/>
@@ -25771,16 +25771,16 @@
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-01</t>
+          <t>VB020205-03-01-S-28</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-PITON BEIGE</t>
         </is>
       </c>
       <c r="C1008" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D1008" t="inlineStr"/>
       <c r="E1008" t="inlineStr"/>
@@ -25793,12 +25793,12 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-03</t>
+          <t>VB020303-01-03-L-19</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-AGUAMARINA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1009" t="n">
@@ -25815,16 +25815,16 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-01</t>
+          <t>VB020205-03-02-M-28</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-PITON BEIGE</t>
         </is>
       </c>
       <c r="C1010" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D1010" t="inlineStr"/>
       <c r="E1010" t="inlineStr"/>
@@ -25837,16 +25837,16 @@
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-02</t>
+          <t>VB0306-01-01-S-03</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-NEGRO</t>
+          <t>TOP BÁSICO LUISA-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1011" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D1011" t="inlineStr"/>
       <c r="E1011" t="inlineStr"/>
@@ -25859,16 +25859,16 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-03</t>
+          <t>VB0306-01-02-M-03</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-AGUAMARINA</t>
+          <t>TOP BÁSICO LUISA-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1012" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D1012" t="inlineStr"/>
       <c r="E1012" t="inlineStr"/>
@@ -25881,16 +25881,16 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-03</t>
+          <t>VB0306-01-03-L-01</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-AGUAMARINA</t>
+          <t>TOP BÁSICO LUISA-L-BLANCO</t>
         </is>
       </c>
       <c r="C1013" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D1013" t="inlineStr"/>
       <c r="E1013" t="inlineStr"/>
@@ -25903,16 +25903,16 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-01</t>
+          <t>VB0306-01-01-S-02</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-BLANCO</t>
+          <t>TOP BÁSICO LUISA-S-NEGRO</t>
         </is>
       </c>
       <c r="C1014" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D1014" t="inlineStr"/>
       <c r="E1014" t="inlineStr"/>
@@ -25925,16 +25925,16 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-02</t>
+          <t>VB0306-01-01-S-01</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-NEGRO</t>
+          <t>TOP BÁSICO LUISA-S-BLANCO</t>
         </is>
       </c>
       <c r="C1015" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D1015" t="inlineStr"/>
       <c r="E1015" t="inlineStr"/>
@@ -25947,16 +25947,16 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-09</t>
+          <t>VB0306-01-03-L-03</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-BEIGE</t>
+          <t>TOP BÁSICO LUISA-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1016" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D1016" t="inlineStr"/>
       <c r="E1016" t="inlineStr"/>
@@ -25969,16 +25969,16 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>VB020103-04-01-S-19</t>
+          <t>VB0306-01-02-M-01</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-ANIMAL PRINT CAFÉ</t>
+          <t>TOP BÁSICO LUISA-M-BLANCO</t>
         </is>
       </c>
       <c r="C1017" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="D1017" t="inlineStr"/>
       <c r="E1017" t="inlineStr"/>
@@ -25991,16 +25991,16 @@
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>VB020103-04-03-L-09</t>
+          <t>VB0306-01-02-M-02</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-L-BEIGE</t>
+          <t>TOP BÁSICO LUISA-M-NEGRO</t>
         </is>
       </c>
       <c r="C1018" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D1018" t="inlineStr"/>
       <c r="E1018" t="inlineStr"/>
@@ -26013,16 +26013,16 @@
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>VB020103-04-02-M-09</t>
+          <t>VB0306-01-03-L-02</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-M-BEIGE</t>
+          <t>TOP BÁSICO LUISA-L-NEGRO</t>
         </is>
       </c>
       <c r="C1019" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D1019" t="inlineStr"/>
       <c r="E1019" t="inlineStr"/>
@@ -26035,16 +26035,16 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>VB0104-01-03-L-09</t>
+          <t>VB020103-04-01-S-09</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI VENUS-S-BEIGE</t>
         </is>
       </c>
       <c r="C1020" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="D1020" t="inlineStr"/>
       <c r="E1020" t="inlineStr"/>
@@ -26057,16 +26057,16 @@
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>VB0104-01-02-M-09</t>
+          <t>VB0104-01-03-L-09</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-BEIGE</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-L-BEIGE</t>
         </is>
       </c>
       <c r="C1021" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="D1021" t="inlineStr"/>
       <c r="E1021" t="inlineStr"/>
@@ -26079,16 +26079,16 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>VB0104-01-01-S-09</t>
+          <t>VB0104-01-02-M-09</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-BEIGE</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-M-BEIGE</t>
         </is>
       </c>
       <c r="C1022" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D1022" t="inlineStr"/>
       <c r="E1022" t="inlineStr"/>
@@ -26101,16 +26101,16 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-35</t>
+          <t>VB0104-01-01-S-09</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-NEGRO-BLANCO HUESO</t>
+          <t>VB ENTERO PANTY PICAPIEDRA AFRODITA-S-BEIGE</t>
         </is>
       </c>
       <c r="C1023" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D1023" t="inlineStr"/>
       <c r="E1023" t="inlineStr"/>
@@ -26123,16 +26123,16 @@
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>VB0304-01-03-L-02</t>
+          <t>VB020103-05-03-L-35</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-NEGRO-BLANCO HUESO</t>
         </is>
       </c>
       <c r="C1024" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D1024" t="inlineStr"/>
       <c r="E1024" t="inlineStr"/>
@@ -26145,12 +26145,12 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>VB0304-01-02-M-02</t>
+          <t>VB0304-01-03-L-02</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-M-NEGRO</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-L-NEGRO</t>
         </is>
       </c>
       <c r="C1025" t="n">
@@ -26167,16 +26167,16 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-37</t>
+          <t>VB0304-01-02-M-02</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-AZUL BEBE-AGUAMARINA</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-M-NEGRO</t>
         </is>
       </c>
       <c r="C1026" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D1026" t="inlineStr"/>
       <c r="E1026" t="inlineStr"/>
@@ -26189,16 +26189,16 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>VB0307-01-04-U-13</t>
+          <t>VB020103-05-03-L-37</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>PAÑOLETA-U-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1027" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D1027" t="inlineStr"/>
       <c r="E1027" t="inlineStr"/>
@@ -26211,16 +26211,16 @@
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-37</t>
+          <t>VB0307-01-04-U-13</t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-AZUL BEBE-AGUAMARINA</t>
+          <t>PAÑOLETA-U-NARANJA</t>
         </is>
       </c>
       <c r="C1028" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D1028" t="inlineStr"/>
       <c r="E1028" t="inlineStr"/>
@@ -26233,16 +26233,16 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>VB020103-05-02-M-37</t>
+          <t>VB020103-05-01-S-37</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-AZUL BEBE-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1029" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D1029" t="inlineStr"/>
       <c r="E1029" t="inlineStr"/>
@@ -26255,16 +26255,16 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>VB020103-05-03-L-36</t>
+          <t>VB020103-05-02-M-37</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-AZUL BEBE-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1030" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D1030" t="inlineStr"/>
       <c r="E1030" t="inlineStr"/>
@@ -26277,16 +26277,16 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-36</t>
+          <t>VB020103-05-03-L-36</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-L-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C1031" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D1031" t="inlineStr"/>
       <c r="E1031" t="inlineStr"/>
@@ -26299,16 +26299,16 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>VB020103-05-02-M-36</t>
+          <t>VB020103-05-01-S-36</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-VIOLETA-CORAL</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C1032" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1032" t="inlineStr"/>
       <c r="E1032" t="inlineStr"/>
@@ -26321,16 +26321,16 @@
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>VB0304-01-03-L-09</t>
+          <t>VB020303-01-01-S-34</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-L-BEIGE</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-FAUNA</t>
         </is>
       </c>
       <c r="C1033" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D1033" t="inlineStr"/>
       <c r="E1033" t="inlineStr"/>
@@ -26343,16 +26343,16 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>VB020103-05-01-S-35</t>
+          <t>VB0304-01-02-M-09</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-NEGRO-BLANCO HUESO</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-M-BEIGE</t>
         </is>
       </c>
       <c r="C1034" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D1034" t="inlineStr"/>
       <c r="E1034" t="inlineStr"/>
@@ -26365,12 +26365,12 @@
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>VB020103-05-02-M-35</t>
+          <t>VB0305-01-04-U-02</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-NEGRO-BLANCO HUESO</t>
+          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-NEGRO</t>
         </is>
       </c>
       <c r="C1035" t="n">
@@ -26387,16 +26387,16 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-34</t>
+          <t>VB0304-01-01-S-09</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-FAUNA</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-S-BEIGE</t>
         </is>
       </c>
       <c r="C1036" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D1036" t="inlineStr"/>
       <c r="E1036" t="inlineStr"/>
@@ -26409,16 +26409,16 @@
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>VB0304-01-02-M-09</t>
+          <t>VB0305-01-04-U-09</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-M-BEIGE</t>
+          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-BEIGE</t>
         </is>
       </c>
       <c r="C1037" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D1037" t="inlineStr"/>
       <c r="E1037" t="inlineStr"/>
@@ -26431,16 +26431,16 @@
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>VB0305-01-04-U-02</t>
+          <t>VB020103-05-02-M-36</t>
         </is>
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-VIOLETA-CORAL</t>
         </is>
       </c>
       <c r="C1038" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D1038" t="inlineStr"/>
       <c r="E1038" t="inlineStr"/>
@@ -26453,16 +26453,16 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>VB0304-01-01-S-09</t>
+          <t>VB0304-01-03-L-09</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>SET BRIANA (PANTALON - CROP TOP ML-S-BEIGE</t>
+          <t>SET BRIANA (PANTALON - CROP TOP ML-L-BEIGE</t>
         </is>
       </c>
       <c r="C1039" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D1039" t="inlineStr"/>
       <c r="E1039" t="inlineStr"/>
@@ -26475,16 +26475,16 @@
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-34</t>
+          <t>VB020103-05-01-S-35</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-FAUNA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-S-NEGRO-BLANCO HUESO</t>
         </is>
       </c>
       <c r="C1040" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D1040" t="inlineStr"/>
       <c r="E1040" t="inlineStr"/>
@@ -26497,16 +26497,16 @@
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-34</t>
+          <t>VB020103-05-02-M-35</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-FAUNA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI IRIS-M-NEGRO-BLANCO HUESO</t>
         </is>
       </c>
       <c r="C1041" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D1041" t="inlineStr"/>
       <c r="E1041" t="inlineStr"/>
@@ -26519,16 +26519,16 @@
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>VB0301-01-04-U-02</t>
+          <t>VB020303-01-03-L-34</t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>FALDA GAIA MACRAME-U-NEGRO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-FAUNA</t>
         </is>
       </c>
       <c r="C1042" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D1042" t="inlineStr"/>
       <c r="E1042" t="inlineStr"/>
@@ -26541,16 +26541,16 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-03</t>
+          <t>VB020303-01-02-M-34</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-FAUNA</t>
         </is>
       </c>
       <c r="C1043" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D1043" t="inlineStr"/>
       <c r="E1043" t="inlineStr"/>
@@ -26563,16 +26563,16 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>VB020104-01-02-M-03</t>
+          <t>VB0301-01-04-U-02</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-M-AGUAMARINA</t>
+          <t>FALDA GAIA MACRAME-U-NEGRO</t>
         </is>
       </c>
       <c r="C1044" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D1044" t="inlineStr"/>
       <c r="E1044" t="inlineStr"/>
@@ -26585,16 +26585,16 @@
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>VB0305-01-04-U-09</t>
+          <t>VB020104-01-01-S-03</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>SALIDA DE BAÑO ARTEMISA MACRAME-U-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1045" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D1045" t="inlineStr"/>
       <c r="E1045" t="inlineStr"/>
@@ -26607,16 +26607,16 @@
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-07</t>
+          <t>VB020104-01-02-M-03</t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1046" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D1046" t="inlineStr"/>
       <c r="E1046" t="inlineStr"/>
@@ -26629,16 +26629,16 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-13</t>
+          <t>VB020104-01-03-L-03</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1047" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D1047" t="inlineStr"/>
       <c r="E1047" t="inlineStr"/>
@@ -26651,16 +26651,16 @@
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-11</t>
+          <t>VB020104-01-01-S-17</t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-ROSADO</t>
         </is>
       </c>
       <c r="C1048" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D1048" t="inlineStr"/>
       <c r="E1048" t="inlineStr"/>
@@ -26673,16 +26673,16 @@
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-15</t>
+          <t>VB020104-01-02-M-17</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-M-ROSADO</t>
         </is>
       </c>
       <c r="C1049" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D1049" t="inlineStr"/>
       <c r="E1049" t="inlineStr"/>
@@ -26695,16 +26695,16 @@
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-03</t>
+          <t>VB020204-01-02-M-11</t>
         </is>
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C1050" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D1050" t="inlineStr"/>
       <c r="E1050" t="inlineStr"/>
@@ -26717,16 +26717,16 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-17</t>
+          <t>VB020204-01-01-S-07</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-ROSADO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1051" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D1051" t="inlineStr"/>
       <c r="E1051" t="inlineStr"/>
@@ -26739,16 +26739,16 @@
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>VB020104-01-02-M-17</t>
+          <t>VB020204-01-02-M-13</t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-M-ROSADO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
         </is>
       </c>
       <c r="C1052" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D1052" t="inlineStr"/>
       <c r="E1052" t="inlineStr"/>
@@ -27355,16 +27355,16 @@
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-02</t>
+          <t>VB020204-01-02-M-15</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-PURPURA</t>
         </is>
       </c>
       <c r="C1080" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D1080" t="inlineStr"/>
       <c r="E1080" t="inlineStr"/>
@@ -27399,16 +27399,16 @@
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-16</t>
+          <t>VB0306-01-01-S-16</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-ROJO</t>
+          <t>TOP BÁSICO LUISA-S-ROJO</t>
         </is>
       </c>
       <c r="C1082" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D1082" t="inlineStr"/>
       <c r="E1082" t="inlineStr"/>
@@ -27421,16 +27421,16 @@
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-14</t>
+          <t>VB0306-01-03-L-14</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
+          <t>TOP BÁSICO LUISA-L-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C1083" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D1083" t="inlineStr"/>
       <c r="E1083" t="inlineStr"/>
@@ -27443,16 +27443,16 @@
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-14</t>
+          <t>VB0306-01-02-M-16</t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-PALO DE ROSA</t>
+          <t>TOP BÁSICO LUISA-M-ROJO</t>
         </is>
       </c>
       <c r="C1084" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D1084" t="inlineStr"/>
       <c r="E1084" t="inlineStr"/>
@@ -27465,16 +27465,16 @@
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-16</t>
+          <t>VB0306-01-02-M-14</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-ROJO</t>
+          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C1085" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D1085" t="inlineStr"/>
       <c r="E1085" t="inlineStr"/>
@@ -27487,16 +27487,16 @@
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-14</t>
+          <t>VB0306-01-01-S-14</t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-PALO DE ROSA</t>
+          <t>TOP BÁSICO LUISA-S-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C1086" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D1086" t="inlineStr"/>
       <c r="E1086" t="inlineStr"/>
@@ -27509,16 +27509,16 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-05</t>
+          <t>VB020205-02-01-S-04</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-AMARILLO</t>
         </is>
       </c>
       <c r="C1087" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D1087" t="inlineStr"/>
       <c r="E1087" t="inlineStr"/>
@@ -27531,16 +27531,16 @@
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-05</t>
+          <t>VB020205-02-02-M-22</t>
         </is>
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-FLORES</t>
         </is>
       </c>
       <c r="C1088" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D1088" t="inlineStr"/>
       <c r="E1088" t="inlineStr"/>
@@ -27553,16 +27553,16 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-27</t>
+          <t>VB020205-02-02-M-07</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PITON AZUL</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1089" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D1089" t="inlineStr"/>
       <c r="E1089" t="inlineStr"/>
@@ -27575,16 +27575,16 @@
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-29</t>
+          <t>VB020205-02-02-M-04</t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PITON ROSADO</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-AMARILLO</t>
         </is>
       </c>
       <c r="C1090" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D1090" t="inlineStr"/>
       <c r="E1090" t="inlineStr"/>
@@ -27597,16 +27597,16 @@
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-29</t>
+          <t>VB020205-02-03-L-12</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PITON ROSADO</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-MORADO</t>
         </is>
       </c>
       <c r="C1091" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D1091" t="inlineStr"/>
       <c r="E1091" t="inlineStr"/>
@@ -27619,16 +27619,16 @@
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-29</t>
+          <t>VB020205-02-03-L-10</t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PITON ROSADO</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-FUCSIA</t>
         </is>
       </c>
       <c r="C1092" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D1092" t="inlineStr"/>
       <c r="E1092" t="inlineStr"/>
@@ -27641,16 +27641,16 @@
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-05</t>
+          <t>VB020205-02-03-L-22</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-FLORES</t>
         </is>
       </c>
       <c r="C1093" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D1093" t="inlineStr"/>
       <c r="E1093" t="inlineStr"/>
@@ -27663,16 +27663,16 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>VB0105-01-03-L-31</t>
+          <t>VB020205-02-03-L-07</t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-L-SAFARI</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1094" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D1094" t="inlineStr"/>
       <c r="E1094" t="inlineStr"/>
@@ -27685,16 +27685,16 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>VB020402-01-01-S-31</t>
+          <t>VB020205-02-03-L-04</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS BUSO TALLE ALTO-S-SAFARI</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-AMARILLO</t>
         </is>
       </c>
       <c r="C1095" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D1095" t="inlineStr"/>
       <c r="E1095" t="inlineStr"/>
@@ -27707,16 +27707,16 @@
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>VB020402-01-02-M-31</t>
+          <t>VB020205-03-03-L-21</t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS BUSO TALLE ALTO-M-SAFARI</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-ASTRAL</t>
         </is>
       </c>
       <c r="C1096" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D1096" t="inlineStr"/>
       <c r="E1096" t="inlineStr"/>
@@ -27729,16 +27729,16 @@
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>VB0105-01-02-M-31</t>
+          <t>VB020205-03-02-M-21</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-M-SAFARI</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-ASTRAL</t>
         </is>
       </c>
       <c r="C1097" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D1097" t="inlineStr"/>
       <c r="E1097" t="inlineStr"/>
@@ -27751,16 +27751,16 @@
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>VB0105-01-01-S-31</t>
+          <t>VB020205-03-01-S-21</t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-S-SAFARI</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-ASTRAL</t>
         </is>
       </c>
       <c r="C1098" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1098" t="inlineStr"/>
       <c r="E1098" t="inlineStr"/>
@@ -27773,16 +27773,16 @@
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-19</t>
+          <t>VB020104-01-01-S-02</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-NEGRO</t>
         </is>
       </c>
       <c r="C1099" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D1099" t="inlineStr"/>
       <c r="E1099" t="inlineStr"/>
@@ -27795,16 +27795,16 @@
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-22</t>
+          <t>VB020104-01-02-M-02</t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-FLORES</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-M-NEGRO</t>
         </is>
       </c>
       <c r="C1100" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D1100" t="inlineStr"/>
       <c r="E1100" t="inlineStr"/>
@@ -27817,16 +27817,16 @@
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-08</t>
+          <t>VB020104-01-03-L-02</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-NEGRO</t>
         </is>
       </c>
       <c r="C1101" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D1101" t="inlineStr"/>
       <c r="E1101" t="inlineStr"/>
@@ -27839,16 +27839,16 @@
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-04</t>
+          <t>VB0103-01-01-S-16</t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AMARILLO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-ROJO</t>
         </is>
       </c>
       <c r="C1102" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D1102" t="inlineStr"/>
       <c r="E1102" t="inlineStr"/>
@@ -27861,16 +27861,16 @@
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-19</t>
+          <t>VB0103-01-02-M-16</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-ROJO</t>
         </is>
       </c>
       <c r="C1103" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D1103" t="inlineStr"/>
       <c r="E1103" t="inlineStr"/>
@@ -27883,16 +27883,16 @@
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-22</t>
+          <t>VB0103-01-03-L-16</t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-FLORES</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-ROJO</t>
         </is>
       </c>
       <c r="C1104" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D1104" t="inlineStr"/>
       <c r="E1104" t="inlineStr"/>
@@ -27905,16 +27905,16 @@
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-08</t>
+          <t>VB0103-01-01-S-02</t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AZUL REY</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-NEGRO</t>
         </is>
       </c>
       <c r="C1105" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D1105" t="inlineStr"/>
       <c r="E1105" t="inlineStr"/>
@@ -27927,16 +27927,16 @@
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-04</t>
+          <t>VB0103-01-01-S-01</t>
         </is>
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AMARILLO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-BLANCO</t>
         </is>
       </c>
       <c r="C1106" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D1106" t="inlineStr"/>
       <c r="E1106" t="inlineStr"/>
@@ -27949,16 +27949,16 @@
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-19</t>
+          <t>VB0103-01-03-L-01</t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-ANIMAL PRINT CAFÉ</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-BLANCO</t>
         </is>
       </c>
       <c r="C1107" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D1107" t="inlineStr"/>
       <c r="E1107" t="inlineStr"/>
@@ -27971,16 +27971,16 @@
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-22</t>
+          <t>VB0105-01-01-S-31</t>
         </is>
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-FLORES</t>
+          <t>VB ENTERO TANGA-S-SAFARI</t>
         </is>
       </c>
       <c r="C1108" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D1108" t="inlineStr"/>
       <c r="E1108" t="inlineStr"/>
@@ -27993,16 +27993,16 @@
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-08</t>
+          <t>VB020202-01-01-S-19</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1109" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D1109" t="inlineStr"/>
       <c r="E1109" t="inlineStr"/>
@@ -28015,16 +28015,16 @@
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-04</t>
+          <t>VB020202-01-01-S-22</t>
         </is>
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AMARILLO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-FLORES</t>
         </is>
       </c>
       <c r="C1110" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D1110" t="inlineStr"/>
       <c r="E1110" t="inlineStr"/>
@@ -28037,16 +28037,16 @@
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-12</t>
+          <t>VB020202-01-01-S-08</t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-MORADO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL REY</t>
         </is>
       </c>
       <c r="C1111" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D1111" t="inlineStr"/>
       <c r="E1111" t="inlineStr"/>
@@ -28059,16 +28059,16 @@
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-10</t>
+          <t>VB020202-01-01-S-04</t>
         </is>
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-FUCSIA</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AMARILLO</t>
         </is>
       </c>
       <c r="C1112" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D1112" t="inlineStr"/>
       <c r="E1112" t="inlineStr"/>
@@ -28081,16 +28081,16 @@
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-22</t>
+          <t>VB020202-01-02-M-19</t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-FLORES</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1113" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="D1113" t="inlineStr"/>
       <c r="E1113" t="inlineStr"/>
@@ -28103,16 +28103,16 @@
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-07</t>
+          <t>VB020202-01-02-M-22</t>
         </is>
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-FLORES</t>
         </is>
       </c>
       <c r="C1114" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D1114" t="inlineStr"/>
       <c r="E1114" t="inlineStr"/>
@@ -28125,16 +28125,16 @@
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-04</t>
+          <t>VB020202-01-02-M-08</t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-AMARILLO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AZUL REY</t>
         </is>
       </c>
       <c r="C1115" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D1115" t="inlineStr"/>
       <c r="E1115" t="inlineStr"/>
@@ -28147,16 +28147,16 @@
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-22</t>
+          <t>VB020202-01-02-M-04</t>
         </is>
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-FLORES</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AMARILLO</t>
         </is>
       </c>
       <c r="C1116" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D1116" t="inlineStr"/>
       <c r="E1116" t="inlineStr"/>
@@ -28169,16 +28169,16 @@
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-07</t>
+          <t>VB020202-01-03-L-19</t>
         </is>
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1117" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D1117" t="inlineStr"/>
       <c r="E1117" t="inlineStr"/>
@@ -28191,16 +28191,16 @@
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-04</t>
+          <t>VB020202-01-03-L-22</t>
         </is>
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-AMARILLO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-FLORES</t>
         </is>
       </c>
       <c r="C1118" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D1118" t="inlineStr"/>
       <c r="E1118" t="inlineStr"/>
@@ -28213,16 +28213,16 @@
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-12</t>
+          <t>VB020202-01-03-L-08</t>
         </is>
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-MORADO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL REY</t>
         </is>
       </c>
       <c r="C1119" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D1119" t="inlineStr"/>
       <c r="E1119" t="inlineStr"/>
@@ -28235,16 +28235,16 @@
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-10</t>
+          <t>VB020202-01-03-L-04</t>
         </is>
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-FUCSIA</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AMARILLO</t>
         </is>
       </c>
       <c r="C1120" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D1120" t="inlineStr"/>
       <c r="E1120" t="inlineStr"/>
@@ -28257,16 +28257,16 @@
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-22</t>
+          <t>VB020205-02-01-S-12</t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-FLORES</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-MORADO</t>
         </is>
       </c>
       <c r="C1121" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D1121" t="inlineStr"/>
       <c r="E1121" t="inlineStr"/>
@@ -28279,16 +28279,16 @@
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-07</t>
+          <t>VB020205-02-01-S-10</t>
         </is>
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-FUCSIA</t>
         </is>
       </c>
       <c r="C1122" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1122" t="inlineStr"/>
       <c r="E1122" t="inlineStr"/>
@@ -28301,16 +28301,16 @@
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-04</t>
+          <t>VB020205-02-01-S-22</t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-AMARILLO</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-FLORES</t>
         </is>
       </c>
       <c r="C1123" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D1123" t="inlineStr"/>
       <c r="E1123" t="inlineStr"/>
@@ -28323,16 +28323,16 @@
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>VB020205-03-03-L-21</t>
+          <t>VB020205-02-01-S-07</t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-ASTRAL</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1124" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D1124" t="inlineStr"/>
       <c r="E1124" t="inlineStr"/>
@@ -28345,16 +28345,16 @@
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>VB020205-03-02-M-21</t>
+          <t>VB020101-01-02-M-05</t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-ASTRAL</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C1125" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D1125" t="inlineStr"/>
       <c r="E1125" t="inlineStr"/>
@@ -28367,16 +28367,16 @@
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>VB020205-03-01-S-21</t>
+          <t>VB0105-01-02-M-31</t>
         </is>
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-ASTRAL</t>
+          <t>VB ENTERO TANGA-M-SAFARI</t>
         </is>
       </c>
       <c r="C1126" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D1126" t="inlineStr"/>
       <c r="E1126" t="inlineStr"/>
@@ -28389,16 +28389,16 @@
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>VB0103-01-02-M-16</t>
+          <t>VB020101-01-03-L-05</t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C1127" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D1127" t="inlineStr"/>
       <c r="E1127" t="inlineStr"/>
@@ -28411,16 +28411,16 @@
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-02</t>
+          <t>VB020101-01-03-L-27</t>
         </is>
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PITON AZUL</t>
         </is>
       </c>
       <c r="C1128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1128" t="inlineStr"/>
       <c r="E1128" t="inlineStr"/>
@@ -28433,16 +28433,16 @@
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>VB020104-01-02-M-02</t>
+          <t>VB020101-01-01-S-29</t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PITON ROSADO</t>
         </is>
       </c>
       <c r="C1129" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D1129" t="inlineStr"/>
       <c r="E1129" t="inlineStr"/>
@@ -28455,16 +28455,16 @@
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-02</t>
+          <t>VB020101-01-02-M-29</t>
         </is>
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PITON ROSADO</t>
         </is>
       </c>
       <c r="C1130" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1130" t="inlineStr"/>
       <c r="E1130" t="inlineStr"/>
@@ -28477,16 +28477,16 @@
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-16</t>
+          <t>VB020101-01-03-L-29</t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PITON ROSADO</t>
         </is>
       </c>
       <c r="C1131" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D1131" t="inlineStr"/>
       <c r="E1131" t="inlineStr"/>
@@ -28499,16 +28499,16 @@
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-16</t>
+          <t>VB020101-01-01-S-05</t>
         </is>
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C1132" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D1132" t="inlineStr"/>
       <c r="E1132" t="inlineStr"/>
@@ -28521,16 +28521,16 @@
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-02</t>
+          <t>VB0105-01-03-L-31</t>
         </is>
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-NEGRO</t>
+          <t>VB ENTERO TANGA-L-SAFARI</t>
         </is>
       </c>
       <c r="C1133" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D1133" t="inlineStr"/>
       <c r="E1133" t="inlineStr"/>
@@ -28543,16 +28543,16 @@
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-01</t>
+          <t>VB020402-01-01-S-31</t>
         </is>
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-BLANCO</t>
+          <t>VB DOS PIEZAS BUSO TALLE ALTO-S-SAFARI</t>
         </is>
       </c>
       <c r="C1134" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D1134" t="inlineStr"/>
       <c r="E1134" t="inlineStr"/>
@@ -28565,16 +28565,16 @@
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-01</t>
+          <t>VB020402-01-02-M-31</t>
         </is>
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-BLANCO</t>
+          <t>VB DOS PIEZAS BUSO TALLE ALTO-M-SAFARI</t>
         </is>
       </c>
       <c r="C1135" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D1135" t="inlineStr"/>
       <c r="E1135" t="inlineStr"/>
@@ -45043,19 +45043,19 @@
     <row r="1769">
       <c r="A1769" t="inlineStr">
         <is>
-          <t>D031009</t>
+          <t>D030601</t>
         </is>
       </c>
       <c r="B1769" t="inlineStr">
         <is>
-          <t>ESPUMA AUTOBRONCEADORA TON OSCURO DLUCHI</t>
+          <t>FRESHING POP AFTER SUN DLUCHI</t>
         </is>
       </c>
       <c r="C1769" t="n">
-        <v>1</v>
+        <v>166</v>
       </c>
       <c r="D1769" t="n">
-        <v>666.412213740458</v>
+        <v>267.9389312977099</v>
       </c>
       <c r="E1769" t="inlineStr">
         <is>
@@ -45071,19 +45071,19 @@
     <row r="1770">
       <c r="A1770" t="inlineStr">
         <is>
-          <t>D030601</t>
+          <t>K010402</t>
         </is>
       </c>
       <c r="B1770" t="inlineStr">
         <is>
-          <t>FRESHING POP AFTER SUN DLUCHI</t>
+          <t>PERFUME PARA EL CABELLO CONFIDENTE KABA</t>
         </is>
       </c>
       <c r="C1770" t="n">
-        <v>166</v>
+        <v>1</v>
       </c>
       <c r="D1770" t="n">
-        <v>267.9389312977099</v>
+        <v>1163.473282442748</v>
       </c>
       <c r="E1770" t="inlineStr">
         <is>
@@ -45099,19 +45099,19 @@
     <row r="1771">
       <c r="A1771" t="inlineStr">
         <is>
-          <t>K010402</t>
+          <t>K010403</t>
         </is>
       </c>
       <c r="B1771" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO CONFIDENTE KABA</t>
+          <t>PERFUME PARA EL CABELLO SOÑADORA KABA</t>
         </is>
       </c>
       <c r="C1771" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D1771" t="n">
-        <v>1163.473282442748</v>
+        <v>1100.954198473282</v>
       </c>
       <c r="E1771" t="inlineStr">
         <is>
@@ -45127,19 +45127,19 @@
     <row r="1772">
       <c r="A1772" t="inlineStr">
         <is>
-          <t>K010403</t>
+          <t>D031009</t>
         </is>
       </c>
       <c r="B1772" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO SOÑADORA KABA</t>
+          <t>ESPUMA AUTOBRONCEADORA TON OSCURO DLUCHI</t>
         </is>
       </c>
       <c r="C1772" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D1772" t="n">
-        <v>1100.954198473282</v>
+        <v>666.412213740458</v>
       </c>
       <c r="E1772" t="inlineStr">
         <is>
@@ -45183,19 +45183,19 @@
     <row r="1774">
       <c r="A1774" t="inlineStr">
         <is>
-          <t>K010401</t>
+          <t>R010302</t>
         </is>
       </c>
       <c r="B1774" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO PODEROSA KABA</t>
+          <t>TONICO CAPILAR LA RECETA</t>
         </is>
       </c>
       <c r="C1774" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D1774" t="n">
-        <v>1399.809160305344</v>
+        <v>3218.702290076336</v>
       </c>
       <c r="E1774" t="inlineStr">
         <is>
@@ -45211,19 +45211,19 @@
     <row r="1775">
       <c r="A1775" t="inlineStr">
         <is>
-          <t>R010302</t>
+          <t>K010401</t>
         </is>
       </c>
       <c r="B1775" t="inlineStr">
         <is>
-          <t>TONICO CAPILAR LA RECETA</t>
+          <t>PERFUME PARA EL CABELLO PODEROSA KABA</t>
         </is>
       </c>
       <c r="C1775" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D1775" t="n">
-        <v>3218.702290076336</v>
+        <v>1399.809160305344</v>
       </c>
       <c r="E1775" t="inlineStr">
         <is>
@@ -45659,19 +45659,19 @@
     <row r="1791">
       <c r="A1791" t="inlineStr">
         <is>
-          <t>KM041104</t>
+          <t>K020506</t>
         </is>
       </c>
       <c r="B1791" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS CARAMELO</t>
+          <t>MASCARILLA FACIAL DE CHOCOLATE KABA</t>
         </is>
       </c>
       <c r="C1791" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1791" t="n">
-        <v>217.4427480916031</v>
+        <v>138.7786259541985</v>
       </c>
       <c r="E1791" t="inlineStr">
         <is>
@@ -45687,19 +45687,19 @@
     <row r="1792">
       <c r="A1792" t="inlineStr">
         <is>
-          <t>K020506</t>
+          <t>KM041304</t>
         </is>
       </c>
       <c r="B1792" t="inlineStr">
         <is>
-          <t>MASCARILLA FACIAL DE CHOCOLATE KABA</t>
+          <t>DROPS PINK GOLD</t>
         </is>
       </c>
       <c r="C1792" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D1792" t="n">
-        <v>138.7786259541985</v>
+        <v>178.6259541984733</v>
       </c>
       <c r="E1792" t="inlineStr">
         <is>
@@ -45715,19 +45715,19 @@
     <row r="1793">
       <c r="A1793" t="inlineStr">
         <is>
-          <t>KM041304</t>
+          <t>KM041104</t>
         </is>
       </c>
       <c r="B1793" t="inlineStr">
         <is>
-          <t>DROPS PINK GOLD</t>
+          <t>CORRECTOR DE OJERAS CARAMELO</t>
         </is>
       </c>
       <c r="C1793" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D1793" t="n">
-        <v>178.6259541984733</v>
+        <v>217.4427480916031</v>
       </c>
       <c r="E1793" t="inlineStr">
         <is>
@@ -45771,19 +45771,19 @@
     <row r="1795">
       <c r="A1795" t="inlineStr">
         <is>
-          <t>O030501</t>
+          <t>O030801</t>
         </is>
       </c>
       <c r="B1795" t="inlineStr">
         <is>
-          <t>MANTEQUILLA EXFOLIANTE OMG</t>
+          <t>DEPILADOR INSTANTANEO OMG</t>
         </is>
       </c>
       <c r="C1795" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1795" t="n">
-        <v>4206.641221374046</v>
+        <v>38473.96946564886</v>
       </c>
       <c r="E1795" t="inlineStr">
         <is>
@@ -45799,19 +45799,19 @@
     <row r="1796">
       <c r="A1796" t="inlineStr">
         <is>
-          <t>O030801</t>
+          <t>O030501</t>
         </is>
       </c>
       <c r="B1796" t="inlineStr">
         <is>
-          <t>DEPILADOR INSTANTANEO OMG</t>
+          <t>MANTEQUILLA EXFOLIANTE OMG</t>
         </is>
       </c>
       <c r="C1796" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1796" t="n">
-        <v>38473.96946564886</v>
+        <v>4206.641221374046</v>
       </c>
       <c r="E1796" t="inlineStr">
         <is>
